--- a/Conjoncture - comptes trimestriels/data/smpt.xlsx
+++ b/Conjoncture - comptes trimestriels/data/smpt.xlsx
@@ -383,10 +383,10 @@
         <v>17899</v>
       </c>
       <c r="B2">
-        <v>0.8486128517771353</v>
+        <v>0.8488207280433295</v>
       </c>
       <c r="C2">
-        <v>5.18882818549106</v>
+        <v>5.189921053298163</v>
       </c>
     </row>
     <row r="3">
@@ -394,10 +394,10 @@
         <v>17989</v>
       </c>
       <c r="B3">
-        <v>0.8724214197331274</v>
+        <v>0.8726351281478683</v>
       </c>
       <c r="C3">
-        <v>5.225204698056086</v>
+        <v>5.226305227461935</v>
       </c>
     </row>
     <row r="4">
@@ -405,10 +405,10 @@
         <v>18080</v>
       </c>
       <c r="B4">
-        <v>0.8781745007940236</v>
+        <v>0.8783896184839218</v>
       </c>
       <c r="C4">
-        <v>5.379105460262934</v>
+        <v>5.380238404152841</v>
       </c>
     </row>
     <row r="5">
@@ -416,10 +416,10 @@
         <v>18172</v>
       </c>
       <c r="B5">
-        <v>0.8790113741662976</v>
+        <v>0.8792266968567582</v>
       </c>
       <c r="C5">
-        <v>5.404338996761497</v>
+        <v>5.405477255323372</v>
       </c>
     </row>
     <row r="6">
@@ -427,10 +427,10 @@
         <v>18264</v>
       </c>
       <c r="B6">
-        <v>0.9036501440277641</v>
+        <v>0.9038715022330908</v>
       </c>
       <c r="C6">
-        <v>5.481097403417228</v>
+        <v>5.482251828787592</v>
       </c>
     </row>
     <row r="7">
@@ -438,10 +438,10 @@
         <v>18354</v>
       </c>
       <c r="B7">
-        <v>0.9399196759482394</v>
+        <v>0.9401499187407559</v>
       </c>
       <c r="C7">
-        <v>5.581494284300094</v>
+        <v>5.582669855199878</v>
       </c>
     </row>
     <row r="8">
@@ -449,10 +449,10 @@
         <v>18445</v>
       </c>
       <c r="B8">
-        <v>0.9753568292029805</v>
+        <v>0.9755957526831484</v>
       </c>
       <c r="C8">
-        <v>5.815605754308256</v>
+        <v>5.816830633622137</v>
       </c>
     </row>
     <row r="9">
@@ -460,10 +460,10 @@
         <v>18537</v>
       </c>
       <c r="B9">
-        <v>1.018718710820987</v>
+        <v>1.018968256230846</v>
       </c>
       <c r="C9">
-        <v>5.973754838951565</v>
+        <v>5.975013027528568</v>
       </c>
     </row>
     <row r="10">
@@ -471,10 +471,10 @@
         <v>18629</v>
       </c>
       <c r="B10">
-        <v>1.076978651017729</v>
+        <v>1.077242467786796</v>
       </c>
       <c r="C10">
-        <v>6.278316641471992</v>
+        <v>6.279638976668879</v>
       </c>
     </row>
     <row r="11">
@@ -482,10 +482,10 @@
         <v>18719</v>
       </c>
       <c r="B11">
-        <v>1.166475519695628</v>
+        <v>1.166761259624187</v>
       </c>
       <c r="C11">
-        <v>6.601521156454883</v>
+        <v>6.602911564788306</v>
       </c>
     </row>
     <row r="12">
@@ -493,10 +493,10 @@
         <v>18810</v>
       </c>
       <c r="B12">
-        <v>1.272880019357605</v>
+        <v>1.273191824140178</v>
       </c>
       <c r="C12">
-        <v>6.8452007713945</v>
+        <v>6.84664250337883</v>
       </c>
     </row>
     <row r="13">
@@ -504,10 +504,10 @@
         <v>18902</v>
       </c>
       <c r="B13">
-        <v>1.371819826339079</v>
+        <v>1.372155867424002</v>
       </c>
       <c r="C13">
-        <v>7.193852093483353</v>
+        <v>7.195367258195111</v>
       </c>
     </row>
     <row r="14">
@@ -515,10 +515,10 @@
         <v>18994</v>
       </c>
       <c r="B14">
-        <v>1.430133567604444</v>
+        <v>1.43048389322769</v>
       </c>
       <c r="C14">
-        <v>7.434810925683653</v>
+        <v>7.436376840996729</v>
       </c>
     </row>
     <row r="15">
@@ -526,10 +526,10 @@
         <v>19085</v>
       </c>
       <c r="B15">
-        <v>1.467307585265254</v>
+        <v>1.467667017038582</v>
       </c>
       <c r="C15">
-        <v>7.476762323345125</v>
+        <v>7.478337074435823</v>
       </c>
     </row>
     <row r="16">
@@ -537,10 +537,10 @@
         <v>19176</v>
       </c>
       <c r="B16">
-        <v>1.487265091325445</v>
+        <v>1.487629411890917</v>
       </c>
       <c r="C16">
-        <v>7.507886996517491</v>
+        <v>7.509468303067745</v>
       </c>
     </row>
     <row r="17">
@@ -548,10 +548,10 @@
         <v>19268</v>
       </c>
       <c r="B17">
-        <v>1.497204554737963</v>
+        <v>1.497571310075119</v>
       </c>
       <c r="C17">
-        <v>7.477627920505485</v>
+        <v>7.479202853907727</v>
       </c>
     </row>
     <row r="18">
@@ -559,10 +559,10 @@
         <v>19360</v>
       </c>
       <c r="B18">
-        <v>1.505169125942702</v>
+        <v>1.505537832281802</v>
       </c>
       <c r="C18">
-        <v>7.458418168490763</v>
+        <v>7.459989055946827</v>
       </c>
     </row>
     <row r="19">
@@ -570,10 +570,10 @@
         <v>19450</v>
       </c>
       <c r="B19">
-        <v>1.524674650884924</v>
+        <v>1.525048135298839</v>
       </c>
       <c r="C19">
-        <v>7.451243514936206</v>
+        <v>7.452812891271144</v>
       </c>
     </row>
     <row r="20">
@@ -581,10 +581,10 @@
         <v>19541</v>
       </c>
       <c r="B20">
-        <v>1.540217789696486</v>
+        <v>1.540595081558821</v>
       </c>
       <c r="C20">
-        <v>7.452294034756862</v>
+        <v>7.453863632351639</v>
       </c>
     </row>
     <row r="21">
@@ -592,10 +592,10 @@
         <v>19633</v>
       </c>
       <c r="B21">
-        <v>1.563106905309422</v>
+        <v>1.56348980409119</v>
       </c>
       <c r="C21">
-        <v>7.41518049051058</v>
+        <v>7.416742271273451</v>
       </c>
     </row>
     <row r="22">
@@ -603,10 +603,10 @@
         <v>19725</v>
       </c>
       <c r="B22">
-        <v>1.600426708775696</v>
+        <v>1.600818749419249</v>
       </c>
       <c r="C22">
-        <v>7.478563447277432</v>
+        <v>7.480138577719749</v>
       </c>
     </row>
     <row r="23">
@@ -614,10 +614,10 @@
         <v>19815</v>
       </c>
       <c r="B23">
-        <v>1.638815538141273</v>
+        <v>1.639216982515273</v>
       </c>
       <c r="C23">
-        <v>7.538783355693199</v>
+        <v>7.540371169615656</v>
       </c>
     </row>
     <row r="24">
@@ -625,10 +625,10 @@
         <v>19906</v>
       </c>
       <c r="B24">
-        <v>1.658195248838765</v>
+        <v>1.658601440468114</v>
       </c>
       <c r="C24">
-        <v>7.577616004581508</v>
+        <v>7.579211997412637</v>
       </c>
     </row>
     <row r="25">
@@ -636,10 +636,10 @@
         <v>19998</v>
       </c>
       <c r="B25">
-        <v>1.686683298120805</v>
+        <v>1.687096468184788</v>
       </c>
       <c r="C25">
-        <v>7.601502883913799</v>
+        <v>7.603103907784789</v>
       </c>
     </row>
     <row r="26">
@@ -647,10 +647,10 @@
         <v>20090</v>
       </c>
       <c r="B26">
-        <v>1.717038346509408</v>
+        <v>1.717458952348263</v>
       </c>
       <c r="C26">
-        <v>7.565572360065231</v>
+        <v>7.567165816271344</v>
       </c>
     </row>
     <row r="27">
@@ -658,10 +658,10 @@
         <v>20180</v>
       </c>
       <c r="B27">
-        <v>1.752478245577401</v>
+        <v>1.752907532776522</v>
       </c>
       <c r="C27">
-        <v>7.609176509349805</v>
+        <v>7.610779149435072</v>
       </c>
     </row>
     <row r="28">
@@ -669,10 +669,10 @@
         <v>20271</v>
       </c>
       <c r="B28">
-        <v>1.800816495006601</v>
+        <v>1.801257623146835</v>
       </c>
       <c r="C28">
-        <v>7.652602509562819</v>
+        <v>7.654214296005595</v>
       </c>
     </row>
     <row r="29">
@@ -680,10 +680,10 @@
         <v>20363</v>
       </c>
       <c r="B29">
-        <v>1.853231789176701</v>
+        <v>1.853685756971226</v>
       </c>
       <c r="C29">
-        <v>7.740672190463073</v>
+        <v>7.742302526087974</v>
       </c>
     </row>
     <row r="30">
@@ -691,10 +691,10 @@
         <v>20455</v>
       </c>
       <c r="B30">
-        <v>1.902645501631008</v>
+        <v>1.903111573812146</v>
       </c>
       <c r="C30">
-        <v>7.857373560108076</v>
+        <v>7.859028475303812</v>
       </c>
     </row>
     <row r="31">
@@ -702,10 +702,10 @@
         <v>20546</v>
       </c>
       <c r="B31">
-        <v>1.949314120123532</v>
+        <v>1.949791624252867</v>
       </c>
       <c r="C31">
-        <v>7.94351998035441</v>
+        <v>7.945193039656294</v>
       </c>
     </row>
     <row r="32">
@@ -713,10 +713,10 @@
         <v>20637</v>
       </c>
       <c r="B32">
-        <v>1.993189062038751</v>
+        <v>1.993677313777066</v>
       </c>
       <c r="C32">
-        <v>8.068658760245116</v>
+        <v>8.070358176200001</v>
       </c>
     </row>
     <row r="33">
@@ -724,10 +724,10 @@
         <v>20729</v>
       </c>
       <c r="B33">
-        <v>2.033453253918812</v>
+        <v>2.033951368776512</v>
       </c>
       <c r="C33">
-        <v>8.15174042417056</v>
+        <v>8.1534573387345</v>
       </c>
     </row>
     <row r="34">
@@ -735,10 +735,10 @@
         <v>20821</v>
       </c>
       <c r="B34">
-        <v>2.072334428067237</v>
+        <v>2.072842067260198</v>
       </c>
       <c r="C34">
-        <v>8.1559848395515</v>
+        <v>8.1577026480716</v>
       </c>
     </row>
     <row r="35">
@@ -746,10 +746,10 @@
         <v>20911</v>
       </c>
       <c r="B35">
-        <v>2.121022966490148</v>
+        <v>2.12154253243104</v>
       </c>
       <c r="C35">
-        <v>8.303875150628873</v>
+        <v>8.305624107715506</v>
       </c>
     </row>
     <row r="36">
@@ -757,10 +757,10 @@
         <v>21002</v>
       </c>
       <c r="B36">
-        <v>2.184099996694995</v>
+        <v>2.184635013989816</v>
       </c>
       <c r="C36">
-        <v>8.573184394404857</v>
+        <v>8.574990073239089</v>
       </c>
     </row>
     <row r="37">
@@ -768,10 +768,10 @@
         <v>21094</v>
       </c>
       <c r="B37">
-        <v>2.265468072585544</v>
+        <v>2.266023021810182</v>
       </c>
       <c r="C37">
-        <v>8.884745216851888</v>
+        <v>8.886616516435284</v>
       </c>
     </row>
     <row r="38">
@@ -779,10 +779,10 @@
         <v>21186</v>
       </c>
       <c r="B38">
-        <v>2.35489201084165</v>
+        <v>2.355468865360739</v>
       </c>
       <c r="C38">
-        <v>9.249427777441564</v>
+        <v>9.251375886241998</v>
       </c>
     </row>
     <row r="39">
@@ -790,10 +790,10 @@
         <v>21276</v>
       </c>
       <c r="B39">
-        <v>2.434208166046114</v>
+        <v>2.434804449856379</v>
       </c>
       <c r="C39">
-        <v>9.523317194994364</v>
+        <v>9.525322990215788</v>
       </c>
     </row>
     <row r="40">
@@ -801,10 +801,10 @@
         <v>21367</v>
       </c>
       <c r="B40">
-        <v>2.492294934225937</v>
+        <v>2.492905446975181</v>
       </c>
       <c r="C40">
-        <v>9.636438472572603</v>
+        <v>9.638468093328067</v>
       </c>
     </row>
     <row r="41">
@@ -812,10 +812,10 @@
         <v>21459</v>
       </c>
       <c r="B41">
-        <v>2.538243862871465</v>
+        <v>2.538865631273628</v>
       </c>
       <c r="C41">
-        <v>9.722466406280482</v>
+        <v>9.724514146186532</v>
       </c>
     </row>
     <row r="42">
@@ -823,10 +823,10 @@
         <v>21551</v>
       </c>
       <c r="B42">
-        <v>2.598433323301405</v>
+        <v>2.599069835718194</v>
       </c>
       <c r="C42">
-        <v>9.95905314964229</v>
+        <v>9.961150719302992</v>
       </c>
     </row>
     <row r="43">
@@ -834,10 +834,10 @@
         <v>21641</v>
       </c>
       <c r="B43">
-        <v>2.67098523737608</v>
+        <v>2.671639522115043</v>
       </c>
       <c r="C43">
-        <v>10.05803982349138</v>
+        <v>10.06015824166456</v>
       </c>
     </row>
     <row r="44">
@@ -845,10 +845,10 @@
         <v>21732</v>
       </c>
       <c r="B44">
-        <v>2.727817676092117</v>
+        <v>2.728485882509422</v>
       </c>
       <c r="C44">
-        <v>10.15394319827598</v>
+        <v>10.15608181555908</v>
       </c>
     </row>
     <row r="45">
@@ -856,10 +856,10 @@
         <v>21824</v>
       </c>
       <c r="B45">
-        <v>2.78074265845672</v>
+        <v>2.781423829381573</v>
       </c>
       <c r="C45">
-        <v>10.26771918534334</v>
+        <v>10.269881766055</v>
       </c>
     </row>
     <row r="46">
@@ -867,10 +867,10 @@
         <v>21916</v>
       </c>
       <c r="B46">
-        <v>2.830324123032142</v>
+        <v>2.831017439436182</v>
       </c>
       <c r="C46">
-        <v>10.33506877431223</v>
+        <v>10.33724554015297</v>
       </c>
     </row>
     <row r="47">
@@ -878,10 +878,10 @@
         <v>22007</v>
       </c>
       <c r="B47">
-        <v>2.884656780301924</v>
+        <v>2.885363406037659</v>
       </c>
       <c r="C47">
-        <v>10.40526475750215</v>
+        <v>10.40745630797778</v>
       </c>
     </row>
     <row r="48">
@@ -889,10 +889,10 @@
         <v>22098</v>
       </c>
       <c r="B48">
-        <v>2.954168526113714</v>
+        <v>2.954892179451783</v>
       </c>
       <c r="C48">
-        <v>10.45950548204476</v>
+        <v>10.46170845666849</v>
       </c>
     </row>
     <row r="49">
@@ -900,10 +900,10 @@
         <v>22190</v>
       </c>
       <c r="B49">
-        <v>3.039594111373707</v>
+        <v>3.040338690569386</v>
       </c>
       <c r="C49">
-        <v>10.51484122522255</v>
+        <v>10.51705585462654</v>
       </c>
     </row>
     <row r="50">
@@ -911,10 +911,10 @@
         <v>22282</v>
       </c>
       <c r="B50">
-        <v>3.117284422996757</v>
+        <v>3.118048033216849</v>
       </c>
       <c r="C50">
-        <v>10.56540606555583</v>
+        <v>10.56763134489545</v>
       </c>
     </row>
     <row r="51">
@@ -922,10 +922,10 @@
         <v>22372</v>
       </c>
       <c r="B51">
-        <v>3.210535229522396</v>
+        <v>3.21132168246687</v>
       </c>
       <c r="C51">
-        <v>10.68602985827363</v>
+        <v>10.68828054332242</v>
       </c>
     </row>
     <row r="52">
@@ -933,10 +933,10 @@
         <v>22463</v>
       </c>
       <c r="B52">
-        <v>3.300776503151447</v>
+        <v>3.301585061604905</v>
       </c>
       <c r="C52">
-        <v>10.77228909525474</v>
+        <v>10.77455794817107</v>
       </c>
     </row>
     <row r="53">
@@ -944,10 +944,10 @@
         <v>22555</v>
       </c>
       <c r="B53">
-        <v>3.393809631341743</v>
+        <v>3.394640979197081</v>
       </c>
       <c r="C53">
-        <v>10.88273395134015</v>
+        <v>10.88502606608427</v>
       </c>
     </row>
     <row r="54">
@@ -955,10 +955,10 @@
         <v>22647</v>
       </c>
       <c r="B54">
-        <v>3.490978979330889</v>
+        <v>3.491834129796813</v>
       </c>
       <c r="C54">
-        <v>11.04504921387833</v>
+        <v>11.04737551536341</v>
       </c>
     </row>
     <row r="55">
@@ -966,10 +966,10 @@
         <v>22737</v>
       </c>
       <c r="B55">
-        <v>3.570989632658998</v>
+        <v>3.571864382540409</v>
       </c>
       <c r="C55">
-        <v>11.16931690265463</v>
+        <v>11.17166937732403</v>
       </c>
     </row>
     <row r="56">
@@ -977,10 +977,10 @@
         <v>22828</v>
       </c>
       <c r="B56">
-        <v>3.652674019449484</v>
+        <v>3.653568778744253</v>
       </c>
       <c r="C56">
-        <v>11.24190523763596</v>
+        <v>11.24427300081591</v>
       </c>
     </row>
     <row r="57">
@@ -988,10 +988,10 @@
         <v>22920</v>
       </c>
       <c r="B57">
-        <v>3.745767661910703</v>
+        <v>3.746685225430934</v>
       </c>
       <c r="C57">
-        <v>11.32162936636525</v>
+        <v>11.32401392099226</v>
       </c>
     </row>
     <row r="58">
@@ -999,10 +999,10 @@
         <v>23012</v>
       </c>
       <c r="B58">
-        <v>3.861150808029319</v>
+        <v>3.862096635813455</v>
       </c>
       <c r="C58">
-        <v>11.36324382132478</v>
+        <v>11.36563714076275</v>
       </c>
     </row>
     <row r="59">
@@ -1010,10 +1010,10 @@
         <v>23102</v>
       </c>
       <c r="B59">
-        <v>3.964889827254213</v>
+        <v>3.965861066956082</v>
       </c>
       <c r="C59">
-        <v>11.65885010188</v>
+        <v>11.66130568173131</v>
       </c>
     </row>
     <row r="60">
@@ -1021,10 +1021,10 @@
         <v>23193</v>
       </c>
       <c r="B60">
-        <v>4.06217172118787</v>
+        <v>4.063166791069586</v>
       </c>
       <c r="C60">
-        <v>11.89399448513409</v>
+        <v>11.89649959095105</v>
       </c>
     </row>
     <row r="61">
@@ -1032,10 +1032,10 @@
         <v>23285</v>
       </c>
       <c r="B61">
-        <v>4.158027573182953</v>
+        <v>4.15904612392118</v>
       </c>
       <c r="C61">
-        <v>11.97959219586727</v>
+        <v>11.98211533022152</v>
       </c>
     </row>
     <row r="62">
@@ -1043,10 +1043,10 @@
         <v>23377</v>
       </c>
       <c r="B62">
-        <v>4.247677006068724</v>
+        <v>4.248717517338582</v>
       </c>
       <c r="C62">
-        <v>11.99366530520569</v>
+        <v>11.99619140362959</v>
       </c>
     </row>
     <row r="63">
@@ -1054,10 +1054,10 @@
         <v>23468</v>
       </c>
       <c r="B63">
-        <v>4.337855984043556</v>
+        <v>4.338918585562451</v>
       </c>
       <c r="C63">
-        <v>12.05845053458965</v>
+        <v>12.06099027803879</v>
       </c>
     </row>
     <row r="64">
@@ -1065,10 +1065,10 @@
         <v>23559</v>
       </c>
       <c r="B64">
-        <v>4.414571731526155</v>
+        <v>4.415653125340159</v>
       </c>
       <c r="C64">
-        <v>12.15689450650436</v>
+        <v>12.15945498416243</v>
       </c>
     </row>
     <row r="65">
@@ -1076,10 +1076,10 @@
         <v>23651</v>
       </c>
       <c r="B65">
-        <v>4.50086404071391</v>
+        <v>4.50196657269828</v>
       </c>
       <c r="C65">
-        <v>12.24476622807491</v>
+        <v>12.24734521322103</v>
       </c>
     </row>
     <row r="66">
@@ -1087,10 +1087,10 @@
         <v>23743</v>
       </c>
       <c r="B66">
-        <v>4.574499308208217</v>
+        <v>4.575619877893095</v>
       </c>
       <c r="C66">
-        <v>12.33526975148622</v>
+        <v>12.33786779842889</v>
       </c>
     </row>
     <row r="67">
@@ -1098,10 +1098,10 @@
         <v>23833</v>
       </c>
       <c r="B67">
-        <v>4.653198304244458</v>
+        <v>4.654338152041156</v>
       </c>
       <c r="C67">
-        <v>12.38636748768417</v>
+        <v>12.38897629680067</v>
       </c>
     </row>
     <row r="68">
@@ -1109,10 +1109,10 @@
         <v>23924</v>
       </c>
       <c r="B68">
-        <v>4.725218500259279</v>
+        <v>4.726375990128457</v>
       </c>
       <c r="C68">
-        <v>12.44074756354867</v>
+        <v>12.44336782616336</v>
       </c>
     </row>
     <row r="69">
@@ -1120,10 +1120,10 @@
         <v>24016</v>
       </c>
       <c r="B69">
-        <v>4.799270462007076</v>
+        <v>4.800446091650216</v>
       </c>
       <c r="C69">
-        <v>12.55509486992497</v>
+        <v>12.55773921629914</v>
       </c>
     </row>
     <row r="70">
@@ -1131,10 +1131,10 @@
         <v>24108</v>
       </c>
       <c r="B70">
-        <v>4.865142510594774</v>
+        <v>4.86633427625975</v>
       </c>
       <c r="C70">
-        <v>12.70145809057556</v>
+        <v>12.70413326388141</v>
       </c>
     </row>
     <row r="71">
@@ -1142,10 +1142,10 @@
         <v>24198</v>
       </c>
       <c r="B71">
-        <v>4.941618493055852</v>
+        <v>4.942828992283081</v>
       </c>
       <c r="C71">
-        <v>12.743175911081</v>
+        <v>12.7458598709686</v>
       </c>
     </row>
     <row r="72">
@@ -1153,10 +1153,10 @@
         <v>24289</v>
       </c>
       <c r="B72">
-        <v>5.020682708510872</v>
+        <v>5.021912575314098</v>
       </c>
       <c r="C72">
-        <v>12.84264561721161</v>
+        <v>12.84535052734764</v>
       </c>
     </row>
     <row r="73">
@@ -1164,10 +1164,10 @@
         <v>24381</v>
       </c>
       <c r="B73">
-        <v>5.114968209752521</v>
+        <v>5.116221172739023</v>
       </c>
       <c r="C73">
-        <v>12.91538728159733</v>
+        <v>12.91810751253807</v>
       </c>
     </row>
     <row r="74">
@@ -1175,10 +1175,10 @@
         <v>24473</v>
       </c>
       <c r="B74">
-        <v>5.22712717204477</v>
+        <v>5.228407609498873</v>
       </c>
       <c r="C74">
-        <v>13.04967025242922</v>
+        <v>13.05241876596684</v>
       </c>
     </row>
     <row r="75">
@@ -1186,10 +1186,10 @@
         <v>24563</v>
       </c>
       <c r="B75">
-        <v>5.30122110721027</v>
+        <v>5.302519694720145</v>
       </c>
       <c r="C75">
-        <v>13.13310718069467</v>
+        <v>13.1358732676669</v>
       </c>
     </row>
     <row r="76">
@@ -1197,10 +1197,10 @@
         <v>24654</v>
       </c>
       <c r="B76">
-        <v>5.386765623108965</v>
+        <v>5.388085165609707</v>
       </c>
       <c r="C76">
-        <v>13.2272297658505</v>
+        <v>13.23001567686384</v>
       </c>
     </row>
     <row r="77">
@@ -1208,10 +1208,10 @@
         <v>24746</v>
       </c>
       <c r="B77">
-        <v>5.492593166478564</v>
+        <v>5.493938632502063</v>
       </c>
       <c r="C77">
-        <v>13.37605147744479</v>
+        <v>13.37886873319566</v>
       </c>
     </row>
     <row r="78">
@@ -1219,10 +1219,10 @@
         <v>24838</v>
       </c>
       <c r="B78">
-        <v>5.66501973035338</v>
+        <v>5.666407434000568</v>
       </c>
       <c r="C78">
-        <v>13.59338355592026</v>
+        <v>13.59624658602008</v>
       </c>
     </row>
     <row r="79">
@@ -1230,10 +1230,10 @@
         <v>24929</v>
       </c>
       <c r="B79">
-        <v>5.681509161855521</v>
+        <v>5.682900904755057</v>
       </c>
       <c r="C79">
-        <v>13.64404957108753</v>
+        <v>13.64692327243237</v>
       </c>
     </row>
     <row r="80">
@@ -1241,10 +1241,10 @@
         <v>25020</v>
       </c>
       <c r="B80">
-        <v>6.212445024981976</v>
+        <v>6.213966825969348</v>
       </c>
       <c r="C80">
-        <v>13.98507367700111</v>
+        <v>13.98801920463378</v>
       </c>
     </row>
     <row r="81">
@@ -1252,10 +1252,10 @@
         <v>25112</v>
       </c>
       <c r="B81">
-        <v>6.355833950303771</v>
+        <v>6.35739087585277</v>
       </c>
       <c r="C81">
-        <v>14.19085707077561</v>
+        <v>14.19384594038035</v>
       </c>
     </row>
     <row r="82">
@@ -1263,10 +1263,10 @@
         <v>25204</v>
       </c>
       <c r="B82">
-        <v>6.44747923805171</v>
+        <v>6.449058613037094</v>
       </c>
       <c r="C82">
-        <v>14.56050798512325</v>
+        <v>14.56357471037665</v>
       </c>
     </row>
     <row r="83">
@@ -1274,10 +1274,10 @@
         <v>25294</v>
       </c>
       <c r="B83">
-        <v>6.583276555270229</v>
+        <v>6.584889195176362</v>
       </c>
       <c r="C83">
-        <v>14.73249006891454</v>
+        <v>14.73559301692885</v>
       </c>
     </row>
     <row r="84">
@@ -1285,10 +1285,10 @@
         <v>25385</v>
       </c>
       <c r="B84">
-        <v>6.73631141531057</v>
+        <v>6.737961542647204</v>
       </c>
       <c r="C84">
-        <v>14.92140338605263</v>
+        <v>14.92454612287383</v>
       </c>
     </row>
     <row r="85">
@@ -1296,10 +1296,10 @@
         <v>25477</v>
       </c>
       <c r="B85">
-        <v>6.946074601726379</v>
+        <v>6.94777611266849</v>
       </c>
       <c r="C85">
-        <v>15.14901045020414</v>
+        <v>15.15220112548547</v>
       </c>
     </row>
     <row r="86">
@@ -1307,10 +1307,10 @@
         <v>25569</v>
       </c>
       <c r="B86">
-        <v>7.169001619705667</v>
+        <v>7.170757738866396</v>
       </c>
       <c r="C86">
-        <v>15.27253913580581</v>
+        <v>15.27575582862307</v>
       </c>
     </row>
     <row r="87">
@@ -1318,10 +1318,10 @@
         <v>25659</v>
       </c>
       <c r="B87">
-        <v>7.348796830624494</v>
+        <v>7.350596992433228</v>
       </c>
       <c r="C87">
-        <v>15.48810425214023</v>
+        <v>15.49136634714996</v>
       </c>
     </row>
     <row r="88">
@@ -1329,10 +1329,10 @@
         <v>25750</v>
       </c>
       <c r="B88">
-        <v>7.530582329473617</v>
+        <v>7.532427021471437</v>
       </c>
       <c r="C88">
-        <v>15.70222385283923</v>
+        <v>15.70553104558781</v>
       </c>
     </row>
     <row r="89">
@@ -1340,10 +1340,10 @@
         <v>25842</v>
       </c>
       <c r="B89">
-        <v>7.749818012545819</v>
+        <v>7.751716408532586</v>
       </c>
       <c r="C89">
-        <v>15.85345119532469</v>
+        <v>15.85679023948331</v>
       </c>
     </row>
     <row r="90">
@@ -1351,10 +1351,10 @@
         <v>25934</v>
       </c>
       <c r="B90">
-        <v>7.994880076155862</v>
+        <v>7.996838502563644</v>
       </c>
       <c r="C90">
-        <v>16.08833090952603</v>
+        <v>16.09171942390587</v>
       </c>
     </row>
     <row r="91">
@@ -1362,10 +1362,10 @@
         <v>26024</v>
       </c>
       <c r="B91">
-        <v>8.182512214360013</v>
+        <v>8.184516603150083</v>
       </c>
       <c r="C91">
-        <v>16.36425326283819</v>
+        <v>16.36769989181469</v>
       </c>
     </row>
     <row r="92">
@@ -1373,10 +1373,10 @@
         <v>26115</v>
       </c>
       <c r="B92">
-        <v>8.414451354192497</v>
+        <v>8.416512558811212</v>
       </c>
       <c r="C92">
-        <v>16.56082017630805</v>
+        <v>16.5643082060872</v>
       </c>
     </row>
     <row r="93">
@@ -1384,10 +1384,10 @@
         <v>26207</v>
       </c>
       <c r="B93">
-        <v>8.653062016075047</v>
+        <v>8.655181670778935</v>
       </c>
       <c r="C93">
-        <v>16.81356775921942</v>
+        <v>16.81710902253934</v>
       </c>
     </row>
     <row r="94">
@@ -1395,10 +1395,10 @@
         <v>26299</v>
       </c>
       <c r="B94">
-        <v>8.818316410513241</v>
+        <v>8.820476545945668</v>
       </c>
       <c r="C94">
-        <v>17.01065070885961</v>
+        <v>17.01423348166939</v>
       </c>
     </row>
     <row r="95">
@@ -1406,10 +1406,10 @@
         <v>26390</v>
       </c>
       <c r="B95">
-        <v>9.045638061353701</v>
+        <v>9.047853881514333</v>
       </c>
       <c r="C95">
-        <v>17.25689514938495</v>
+        <v>17.26052978604763</v>
       </c>
     </row>
     <row r="96">
@@ -1417,10 +1417,10 @@
         <v>26481</v>
       </c>
       <c r="B96">
-        <v>9.282918159061037</v>
+        <v>9.285192103371745</v>
       </c>
       <c r="C96">
-        <v>17.56441647101712</v>
+        <v>17.56811587763178</v>
       </c>
     </row>
     <row r="97">
@@ -1428,10 +1428,10 @@
         <v>26573</v>
       </c>
       <c r="B97">
-        <v>9.589189013209868</v>
+        <v>9.591537981651394</v>
       </c>
       <c r="C97">
-        <v>17.86349692495637</v>
+        <v>17.86725932371264</v>
       </c>
     </row>
     <row r="98">
@@ -1439,10 +1439,10 @@
         <v>26665</v>
       </c>
       <c r="B98">
-        <v>9.884268137281495</v>
+        <v>9.886689388326818</v>
       </c>
       <c r="C98">
-        <v>18.02626780600168</v>
+        <v>18.03006448746099</v>
       </c>
     </row>
     <row r="99">
@@ -1450,10 +1450,10 @@
         <v>26755</v>
       </c>
       <c r="B99">
-        <v>10.19446408791845</v>
+        <v>10.19696132458651</v>
       </c>
       <c r="C99">
-        <v>18.38435376659445</v>
+        <v>18.38822586789896</v>
       </c>
     </row>
     <row r="100">
@@ -1461,10 +1461,10 @@
         <v>26846</v>
       </c>
       <c r="B100">
-        <v>10.56660172148796</v>
+        <v>10.56919011701794</v>
       </c>
       <c r="C100">
-        <v>18.90107581841074</v>
+        <v>18.9050567513966</v>
       </c>
     </row>
     <row r="101">
@@ -1472,10 +1472,10 @@
         <v>26938</v>
       </c>
       <c r="B101">
-        <v>10.92923195285844</v>
+        <v>10.9319091783164</v>
       </c>
       <c r="C101">
-        <v>19.4386442520279</v>
+        <v>19.44273840734724</v>
       </c>
     </row>
     <row r="102">
@@ -1483,10 +1483,10 @@
         <v>27030</v>
       </c>
       <c r="B102">
-        <v>11.40870554987983</v>
+        <v>11.41150022722516</v>
       </c>
       <c r="C102">
-        <v>20.28138153470141</v>
+        <v>20.28565318682989</v>
       </c>
     </row>
     <row r="103">
@@ -1494,10 +1494,10 @@
         <v>27120</v>
       </c>
       <c r="B103">
-        <v>11.94411022935123</v>
+        <v>11.94703605946598</v>
       </c>
       <c r="C103">
-        <v>21.09532860594215</v>
+        <v>21.09977169110311</v>
       </c>
     </row>
     <row r="104">
@@ -1505,10 +1505,10 @@
         <v>27211</v>
       </c>
       <c r="B104">
-        <v>12.53639021089915</v>
+        <v>12.53946112596147</v>
       </c>
       <c r="C104">
-        <v>21.77831315241108</v>
+        <v>21.78290008735794</v>
       </c>
     </row>
     <row r="105">
@@ -1516,10 +1516,10 @@
         <v>27303</v>
       </c>
       <c r="B105">
-        <v>12.98755775747253</v>
+        <v>12.99073919057003</v>
       </c>
       <c r="C105">
-        <v>22.39797477436398</v>
+        <v>22.40269222206126</v>
       </c>
     </row>
     <row r="106">
@@ -1527,10 +1527,10 @@
         <v>27395</v>
       </c>
       <c r="B106">
-        <v>13.66199106665483</v>
+        <v>13.66533770898504</v>
       </c>
       <c r="C106">
-        <v>23.05334532262541</v>
+        <v>23.05820080406525</v>
       </c>
     </row>
     <row r="107">
@@ -1538,10 +1538,10 @@
         <v>27485</v>
       </c>
       <c r="B107">
-        <v>14.25519656124415</v>
+        <v>14.25868851523567</v>
       </c>
       <c r="C107">
-        <v>23.64716383456486</v>
+        <v>23.65214438569514</v>
       </c>
     </row>
     <row r="108">
@@ -1549,10 +1549,10 @@
         <v>27576</v>
       </c>
       <c r="B108">
-        <v>14.74039727508608</v>
+        <v>14.74400808387992</v>
       </c>
       <c r="C108">
-        <v>24.14456616677697</v>
+        <v>24.14965148048112</v>
       </c>
     </row>
     <row r="109">
@@ -1560,10 +1560,10 @@
         <v>27668</v>
       </c>
       <c r="B109">
-        <v>15.21636843856871</v>
+        <v>15.22009584129354</v>
       </c>
       <c r="C109">
-        <v>24.64524162921106</v>
+        <v>24.65043239487376</v>
       </c>
     </row>
     <row r="110">
@@ -1571,10 +1571,10 @@
         <v>27760</v>
       </c>
       <c r="B110">
-        <v>15.74579593409116</v>
+        <v>15.749653025414</v>
       </c>
       <c r="C110">
-        <v>25.27707784632297</v>
+        <v>25.28240168894184</v>
       </c>
     </row>
     <row r="111">
@@ -1582,10 +1582,10 @@
         <v>27851</v>
       </c>
       <c r="B111">
-        <v>16.31076932014757</v>
+        <v>16.31476480739235</v>
       </c>
       <c r="C111">
-        <v>25.82895998058633</v>
+        <v>25.83440006028152</v>
       </c>
     </row>
     <row r="112">
@@ -1593,10 +1593,10 @@
         <v>27942</v>
       </c>
       <c r="B112">
-        <v>16.86175078595569</v>
+        <v>16.8658812416606</v>
       </c>
       <c r="C112">
-        <v>26.44508488596128</v>
+        <v>26.45065473350583</v>
       </c>
     </row>
     <row r="113">
@@ -1604,10 +1604,10 @@
         <v>28034</v>
       </c>
       <c r="B113">
-        <v>17.39334566001908</v>
+        <v>17.39760633524319</v>
       </c>
       <c r="C113">
-        <v>27.11806101313462</v>
+        <v>27.12377260249794</v>
       </c>
     </row>
     <row r="114">
@@ -1615,10 +1615,10 @@
         <v>28126</v>
       </c>
       <c r="B114">
-        <v>17.87217710419705</v>
+        <v>17.87655507400672</v>
       </c>
       <c r="C114">
-        <v>27.59683517367687</v>
+        <v>27.60264760215997</v>
       </c>
     </row>
     <row r="115">
@@ -1626,10 +1626,10 @@
         <v>28216</v>
       </c>
       <c r="B115">
-        <v>18.2674985914661</v>
+        <v>18.27197339925619</v>
       </c>
       <c r="C115">
-        <v>28.37714801064812</v>
+        <v>28.38312478814193</v>
       </c>
     </row>
     <row r="116">
@@ -1637,10 +1637,10 @@
         <v>28307</v>
       </c>
       <c r="B116">
-        <v>18.75562376312065</v>
+        <v>18.76021814208847</v>
       </c>
       <c r="C116">
-        <v>28.99450413122559</v>
+        <v>29.00061093588652</v>
       </c>
     </row>
     <row r="117">
@@ -1648,10 +1648,10 @@
         <v>28399</v>
       </c>
       <c r="B117">
-        <v>19.31707850878407</v>
+        <v>19.32181042174742</v>
       </c>
       <c r="C117">
-        <v>29.48315171999855</v>
+        <v>29.48936144331465</v>
       </c>
     </row>
     <row r="118">
@@ -1659,10 +1659,10 @@
         <v>28491</v>
       </c>
       <c r="B118">
-        <v>19.83685818659943</v>
+        <v>19.84171742483065</v>
       </c>
       <c r="C118">
-        <v>29.92192993990717</v>
+        <v>29.9282320784226</v>
       </c>
     </row>
     <row r="119">
@@ -1670,10 +1670,10 @@
         <v>28581</v>
       </c>
       <c r="B119">
-        <v>20.42927431620927</v>
+        <v>20.43427867273889</v>
       </c>
       <c r="C119">
-        <v>30.65922622282446</v>
+        <v>30.66568365023039</v>
       </c>
     </row>
     <row r="120">
@@ -1681,10 +1681,10 @@
         <v>28672</v>
       </c>
       <c r="B120">
-        <v>21.06759569120547</v>
+        <v>21.07275641098577</v>
       </c>
       <c r="C120">
-        <v>31.53613180318635</v>
+        <v>31.54277392390729</v>
       </c>
     </row>
     <row r="121">
@@ -1692,10 +1692,10 @@
         <v>28764</v>
       </c>
       <c r="B121">
-        <v>21.66368344928861</v>
+        <v>21.66899018676969</v>
       </c>
       <c r="C121">
-        <v>32.27283364096644</v>
+        <v>32.27963092537621</v>
       </c>
     </row>
     <row r="122">
@@ -1703,10 +1703,10 @@
         <v>28856</v>
       </c>
       <c r="B122">
-        <v>22.27461276656224</v>
+        <v>22.28006915733353</v>
       </c>
       <c r="C122">
-        <v>33.01303709856683</v>
+        <v>33.01999028417445</v>
       </c>
     </row>
     <row r="123">
@@ -1714,10 +1714,10 @@
         <v>28946</v>
       </c>
       <c r="B123">
-        <v>23.03153768123375</v>
+        <v>23.03717948838746</v>
       </c>
       <c r="C123">
-        <v>33.91309449482218</v>
+        <v>33.92023724996606</v>
       </c>
     </row>
     <row r="124">
@@ -1725,10 +1725,10 @@
         <v>29037</v>
       </c>
       <c r="B124">
-        <v>23.78349368772271</v>
+        <v>23.78931969407473</v>
       </c>
       <c r="C124">
-        <v>35.08526235068669</v>
+        <v>35.09265198710481</v>
       </c>
     </row>
     <row r="125">
@@ -1736,10 +1736,10 @@
         <v>29129</v>
       </c>
       <c r="B125">
-        <v>24.64959534921233</v>
+        <v>24.65563351589065</v>
       </c>
       <c r="C125">
-        <v>35.9774917597757</v>
+        <v>35.98506931700424</v>
       </c>
     </row>
     <row r="126">
@@ -1747,10 +1747,10 @@
         <v>29221</v>
       </c>
       <c r="B126">
-        <v>25.47513062448815</v>
+        <v>25.48137101434784</v>
       </c>
       <c r="C126">
-        <v>37.32406866877337</v>
+        <v>37.33759769230829</v>
       </c>
     </row>
     <row r="127">
@@ -1758,10 +1758,10 @@
         <v>29312</v>
       </c>
       <c r="B127">
-        <v>26.42351320984924</v>
+        <v>26.42998591557635</v>
       </c>
       <c r="C127">
-        <v>38.42264568089002</v>
+        <v>38.43150195678975</v>
       </c>
     </row>
     <row r="128">
@@ -1769,10 +1769,10 @@
         <v>29403</v>
       </c>
       <c r="B128">
-        <v>27.30593697874337</v>
+        <v>27.3126258430614</v>
       </c>
       <c r="C128">
-        <v>39.569840711434</v>
+        <v>39.57609208029135</v>
       </c>
     </row>
     <row r="129">
@@ -1780,10 +1780,10 @@
         <v>29495</v>
       </c>
       <c r="B129">
-        <v>28.10851938451349</v>
+        <v>28.1154048494763</v>
       </c>
       <c r="C129">
-        <v>40.76430183627522</v>
+        <v>40.76886217431261</v>
       </c>
     </row>
     <row r="130">
@@ -1791,10 +1791,10 @@
         <v>29587</v>
       </c>
       <c r="B130">
-        <v>28.91467094497863</v>
+        <v>28.92175388488661</v>
       </c>
       <c r="C130">
-        <v>42.13520401748298</v>
+        <v>42.13493577417242</v>
       </c>
     </row>
     <row r="131">
@@ -1802,10 +1802,10 @@
         <v>29677</v>
       </c>
       <c r="B131">
-        <v>29.90874683657215</v>
+        <v>29.91607328538319</v>
       </c>
       <c r="C131">
-        <v>43.44769904633677</v>
+        <v>43.45068359963841</v>
       </c>
     </row>
     <row r="132">
@@ -1813,10 +1813,10 @@
         <v>29768</v>
       </c>
       <c r="B132">
-        <v>31.01600376567896</v>
+        <v>31.02360144822828</v>
       </c>
       <c r="C132">
-        <v>45.13858295982507</v>
+        <v>45.15767317074446</v>
       </c>
     </row>
     <row r="133">
@@ -1824,10 +1824,10 @@
         <v>29860</v>
       </c>
       <c r="B133">
-        <v>32.244893107301</v>
+        <v>32.25279181867326</v>
       </c>
       <c r="C133">
-        <v>46.56015578845248</v>
+        <v>46.57594071372603</v>
       </c>
     </row>
     <row r="134">
@@ -1835,10 +1835,10 @@
         <v>29952</v>
       </c>
       <c r="B134">
-        <v>33.58640738390994</v>
+        <v>33.59463471271745</v>
       </c>
       <c r="C134">
-        <v>47.88514129947569</v>
+        <v>47.89458482987693</v>
       </c>
     </row>
     <row r="135">
@@ -1846,10 +1846,10 @@
         <v>30042</v>
       </c>
       <c r="B135">
-        <v>34.46809357071259</v>
+        <v>34.47653687743286</v>
       </c>
       <c r="C135">
-        <v>49.22658811190679</v>
+        <v>49.24003526590838</v>
       </c>
     </row>
     <row r="136">
@@ -1857,10 +1857,10 @@
         <v>30133</v>
       </c>
       <c r="B136">
-        <v>35.06287441409685</v>
+        <v>35.07146341837598</v>
       </c>
       <c r="C136">
-        <v>50.02955304884757</v>
+        <v>50.03916268663499</v>
       </c>
     </row>
     <row r="137">
@@ -1868,10 +1868,10 @@
         <v>30225</v>
       </c>
       <c r="B137">
-        <v>35.7835509001213</v>
+        <v>35.79231644136512</v>
       </c>
       <c r="C137">
-        <v>51.04383519192312</v>
+        <v>51.0527226110736</v>
       </c>
     </row>
     <row r="138">
@@ -1879,10 +1879,10 @@
         <v>30317</v>
       </c>
       <c r="B138">
-        <v>36.8479153421768</v>
+        <v>36.85694161021214</v>
       </c>
       <c r="C138">
-        <v>52.39931855772426</v>
+        <v>52.40608533642133</v>
       </c>
     </row>
     <row r="139">
@@ -1890,10 +1890,10 @@
         <v>30407</v>
       </c>
       <c r="B139">
-        <v>37.59107680078307</v>
+        <v>37.60028511370363</v>
       </c>
       <c r="C139">
-        <v>53.77270391521779</v>
+        <v>53.79080866455478</v>
       </c>
     </row>
     <row r="140">
@@ -1901,10 +1901,10 @@
         <v>30498</v>
       </c>
       <c r="B140">
-        <v>38.57451818721826</v>
+        <v>38.58396740401272</v>
       </c>
       <c r="C140">
-        <v>54.95581949578163</v>
+        <v>54.96637101105529</v>
       </c>
     </row>
     <row r="141">
@@ -1912,10 +1912,10 @@
         <v>30590</v>
       </c>
       <c r="B141">
-        <v>39.42697627629011</v>
+        <v>39.43663431128036</v>
       </c>
       <c r="C141">
-        <v>56.08338814849182</v>
+        <v>56.0933678396291</v>
       </c>
     </row>
     <row r="142">
@@ -1923,10 +1923,10 @@
         <v>30682</v>
       </c>
       <c r="B142">
-        <v>40.20731836180652</v>
+        <v>40.21716754945108</v>
       </c>
       <c r="C142">
-        <v>57.14574465242721</v>
+        <v>57.15787544086481</v>
       </c>
     </row>
     <row r="143">
@@ -1934,10 +1934,10 @@
         <v>30773</v>
       </c>
       <c r="B143">
-        <v>41.13871877563336</v>
+        <v>41.14879611919137</v>
       </c>
       <c r="C143">
-        <v>58.07311274560944</v>
+        <v>58.09200523227659</v>
       </c>
     </row>
     <row r="144">
@@ -1945,10 +1945,10 @@
         <v>30864</v>
       </c>
       <c r="B144">
-        <v>41.39566941829618</v>
+        <v>41.40580970450238</v>
       </c>
       <c r="C144">
-        <v>59.08348416169177</v>
+        <v>59.09726290648647</v>
       </c>
     </row>
     <row r="145">
@@ -1956,10 +1956,10 @@
         <v>30956</v>
       </c>
       <c r="B145">
-        <v>42.34231025790423</v>
+        <v>42.3526824333197</v>
       </c>
       <c r="C145">
-        <v>60.07826459245612</v>
+        <v>60.08313631206514</v>
       </c>
     </row>
     <row r="146">
@@ -1967,10 +1967,10 @@
         <v>31048</v>
       </c>
       <c r="B146">
-        <v>43.10276707166051</v>
+        <v>43.11332552863265</v>
       </c>
       <c r="C146">
-        <v>61.02012703129161</v>
+        <v>61.04101471978073</v>
       </c>
     </row>
     <row r="147">
@@ -1978,10 +1978,10 @@
         <v>31138</v>
       </c>
       <c r="B147">
-        <v>43.7655500818136</v>
+        <v>43.77627089416035</v>
       </c>
       <c r="C147">
-        <v>62.03525712714041</v>
+        <v>62.04712710776796</v>
       </c>
     </row>
     <row r="148">
@@ -1989,10 +1989,10 @@
         <v>31229</v>
       </c>
       <c r="B148">
-        <v>44.28263335440145</v>
+        <v>44.29348083150445</v>
       </c>
       <c r="C148">
-        <v>62.66713656954676</v>
+        <v>62.67297877313824</v>
       </c>
     </row>
     <row r="149">
@@ -2000,10 +2000,10 @@
         <v>31321</v>
       </c>
       <c r="B149">
-        <v>44.81333771321702</v>
+        <v>44.82431519169855</v>
       </c>
       <c r="C149">
-        <v>63.14310369701091</v>
+        <v>63.15741565327828</v>
       </c>
     </row>
     <row r="150">
@@ -2011,10 +2011,10 @@
         <v>31413</v>
       </c>
       <c r="B150">
-        <v>45.1205786069892</v>
+        <v>45.13163134722252</v>
       </c>
       <c r="C150">
-        <v>63.29432061285887</v>
+        <v>63.31231079487506</v>
       </c>
     </row>
     <row r="151">
@@ -2022,10 +2022,10 @@
         <v>31503</v>
       </c>
       <c r="B151">
-        <v>45.89273693345482</v>
+        <v>45.90397882164822</v>
       </c>
       <c r="C151">
-        <v>63.62354205399981</v>
+        <v>63.64226734579579</v>
       </c>
     </row>
     <row r="152">
@@ -2033,10 +2033,10 @@
         <v>31594</v>
       </c>
       <c r="B152">
-        <v>45.93520860048989</v>
+        <v>45.94646089254596</v>
       </c>
       <c r="C152">
-        <v>63.99025652723022</v>
+        <v>63.99842976975236</v>
       </c>
     </row>
     <row r="153">
@@ -2044,10 +2044,10 @@
         <v>31686</v>
       </c>
       <c r="B153">
-        <v>46.22605818792051</v>
+        <v>46.23738172651277</v>
       </c>
       <c r="C153">
-        <v>64.5854870104491</v>
+        <v>64.59473676787752</v>
       </c>
     </row>
     <row r="154">
@@ -2055,10 +2055,10 @@
         <v>31778</v>
       </c>
       <c r="B154">
-        <v>47.05877812724765</v>
+        <v>47.07030564897711</v>
       </c>
       <c r="C154">
-        <v>65.11371275396336</v>
+        <v>65.12836233076757</v>
       </c>
     </row>
     <row r="155">
@@ -2066,10 +2066,10 @@
         <v>31868</v>
       </c>
       <c r="B155">
-        <v>47.27809960021165</v>
+        <v>47.28908811072836</v>
       </c>
       <c r="C155">
-        <v>65.58660274857067</v>
+        <v>65.59837685883969</v>
       </c>
     </row>
     <row r="156">
@@ -2077,10 +2077,10 @@
         <v>31959</v>
       </c>
       <c r="B156">
-        <v>47.77090186224559</v>
+        <v>47.78260382585723</v>
       </c>
       <c r="C156">
-        <v>65.9858203736229</v>
+        <v>65.99823562741534</v>
       </c>
     </row>
     <row r="157">
@@ -2088,10 +2088,10 @@
         <v>32051</v>
       </c>
       <c r="B157">
-        <v>48.32549396248586</v>
+        <v>48.3373317790189</v>
       </c>
       <c r="C157">
-        <v>66.34137582326737</v>
+        <v>66.35735230492867</v>
       </c>
     </row>
     <row r="158">
@@ -2099,10 +2099,10 @@
         <v>32143</v>
       </c>
       <c r="B158">
-        <v>48.93704185562461</v>
+        <v>48.94902947697425</v>
       </c>
       <c r="C158">
-        <v>66.71107811955578</v>
+        <v>66.72385881507844</v>
       </c>
     </row>
     <row r="159">
@@ -2110,10 +2110,10 @@
         <v>32234</v>
       </c>
       <c r="B159">
-        <v>49.30435716885243</v>
+        <v>49.31643476778804</v>
       </c>
       <c r="C159">
-        <v>67.16234040802483</v>
+        <v>67.17431356152257</v>
       </c>
     </row>
     <row r="160">
@@ -2121,10 +2121,10 @@
         <v>32325</v>
       </c>
       <c r="B160">
-        <v>49.90225809816246</v>
+        <v>49.91448215895342</v>
       </c>
       <c r="C160">
-        <v>67.77502042001855</v>
+        <v>67.79160756961586</v>
       </c>
     </row>
     <row r="161">
@@ -2132,10 +2132,10 @@
         <v>32417</v>
       </c>
       <c r="B161">
-        <v>50.4369598161509</v>
+        <v>50.44931485751378</v>
       </c>
       <c r="C161">
-        <v>68.39824696205088</v>
+        <v>68.41391971672677</v>
       </c>
     </row>
     <row r="162">
@@ -2143,10 +2143,10 @@
         <v>32509</v>
       </c>
       <c r="B162">
-        <v>51.03045308549098</v>
+        <v>51.04295350900848</v>
       </c>
       <c r="C162">
-        <v>69.12224304254148</v>
+        <v>69.13132746095333</v>
       </c>
     </row>
     <row r="163">
@@ -2154,10 +2154,10 @@
         <v>32599</v>
       </c>
       <c r="B163">
-        <v>51.71162594080948</v>
+        <v>51.72429322447941</v>
       </c>
       <c r="C163">
-        <v>69.86967214598778</v>
+        <v>69.88731843728408</v>
       </c>
     </row>
     <row r="164">
@@ -2165,10 +2165,10 @@
         <v>32690</v>
       </c>
       <c r="B164">
-        <v>52.16954266095195</v>
+        <v>52.18232211593512</v>
       </c>
       <c r="C164">
-        <v>70.39250280940207</v>
+        <v>70.40858674063428</v>
       </c>
     </row>
     <row r="165">
@@ -2176,10 +2176,10 @@
         <v>32782</v>
       </c>
       <c r="B165">
-        <v>53.04683928735976</v>
+        <v>53.05983364498865</v>
       </c>
       <c r="C165">
-        <v>70.98444696242713</v>
+        <v>71.0008671144107</v>
       </c>
     </row>
     <row r="166">
@@ -2187,10 +2187,10 @@
         <v>32874</v>
       </c>
       <c r="B166">
-        <v>53.6921234630972</v>
+        <v>53.70527588958495</v>
       </c>
       <c r="C166">
-        <v>71.34622064292283</v>
+        <v>71.35611115602332</v>
       </c>
     </row>
     <row r="167">
@@ -2198,10 +2198,10 @@
         <v>32964</v>
       </c>
       <c r="B167">
-        <v>54.56319992823489</v>
+        <v>54.57600307706848</v>
       </c>
       <c r="C167">
-        <v>71.76936907401796</v>
+        <v>71.78815104639689</v>
       </c>
     </row>
     <row r="168">
@@ -2209,10 +2209,10 @@
         <v>33055</v>
       </c>
       <c r="B168">
-        <v>55.27845937956217</v>
+        <v>55.29200039501195</v>
       </c>
       <c r="C168">
-        <v>72.32597460577537</v>
+        <v>72.34031784548137</v>
       </c>
     </row>
     <row r="169">
@@ -2220,10 +2220,10 @@
         <v>33147</v>
       </c>
       <c r="B169">
-        <v>55.88491615424768</v>
+        <v>55.89916761277917</v>
       </c>
       <c r="C169">
-        <v>72.94526100706054</v>
+        <v>72.95801120944552</v>
       </c>
     </row>
     <row r="170">
@@ -2231,10 +2231,10 @@
         <v>33239</v>
       </c>
       <c r="B170">
-        <v>56.06469011261444</v>
+        <v>56.07842372320205</v>
       </c>
       <c r="C170">
-        <v>73.27880021079118</v>
+        <v>73.29003383815747</v>
       </c>
     </row>
     <row r="171">
@@ -2242,10 +2242,10 @@
         <v>33329</v>
       </c>
       <c r="B171">
-        <v>57.00185631813828</v>
+        <v>57.01581949702808</v>
       </c>
       <c r="C171">
-        <v>73.6639175662358</v>
+        <v>73.68255051133491</v>
       </c>
     </row>
     <row r="172">
@@ -2253,10 +2253,10 @@
         <v>33420</v>
       </c>
       <c r="B172">
-        <v>57.42081608848101</v>
+        <v>57.434318455178</v>
       </c>
       <c r="C172">
-        <v>74.3045525422051</v>
+        <v>74.31551470262988</v>
       </c>
     </row>
     <row r="173">
@@ -2264,10 +2264,10 @@
         <v>33512</v>
       </c>
       <c r="B173">
-        <v>58.33194765456186</v>
+        <v>58.34680160718112</v>
       </c>
       <c r="C173">
-        <v>74.97218507941422</v>
+        <v>74.9941568822485</v>
       </c>
     </row>
     <row r="174">
@@ -2275,10 +2275,10 @@
         <v>33604</v>
       </c>
       <c r="B174">
-        <v>59.14173155134856</v>
+        <v>59.15621891423191</v>
       </c>
       <c r="C174">
-        <v>75.35460976625839</v>
+        <v>75.37271293021951</v>
       </c>
     </row>
     <row r="175">
@@ -2286,10 +2286,10 @@
         <v>33695</v>
       </c>
       <c r="B175">
-        <v>59.32241795315021</v>
+        <v>59.33694957698774</v>
       </c>
       <c r="C175">
-        <v>75.81443424397713</v>
+        <v>75.8279356452106</v>
       </c>
     </row>
     <row r="176">
@@ -2297,10 +2297,10 @@
         <v>33786</v>
       </c>
       <c r="B176">
-        <v>59.92873748171381</v>
+        <v>59.94341762962737</v>
       </c>
       <c r="C176">
-        <v>76.16158791379293</v>
+        <v>76.17636437838672</v>
       </c>
     </row>
     <row r="177">
@@ -2308,10 +2308,10 @@
         <v>33878</v>
       </c>
       <c r="B177">
-        <v>60.48989801961917</v>
+        <v>60.50471562945911</v>
       </c>
       <c r="C177">
-        <v>76.38433448680334</v>
+        <v>76.40608897416735</v>
       </c>
     </row>
     <row r="178">
@@ -2319,10 +2319,10 @@
         <v>33970</v>
       </c>
       <c r="B178">
-        <v>60.89416431466123</v>
+        <v>60.90908095360235</v>
       </c>
       <c r="C178">
-        <v>76.76736870055709</v>
+        <v>76.78160629372964</v>
       </c>
     </row>
     <row r="179">
@@ -2330,10 +2330,10 @@
         <v>34060</v>
       </c>
       <c r="B179">
-        <v>61.06094501528634</v>
+        <v>61.07590250884007</v>
       </c>
       <c r="C179">
-        <v>76.96097849409487</v>
+        <v>76.96848587263266</v>
       </c>
     </row>
     <row r="180">
@@ -2341,10 +2341,10 @@
         <v>34151</v>
       </c>
       <c r="B180">
-        <v>61.05736782992424</v>
+        <v>61.07232444721038</v>
       </c>
       <c r="C180">
-        <v>77.13566265778944</v>
+        <v>77.15121609548947</v>
       </c>
     </row>
     <row r="181">
@@ -2352,10 +2352,10 @@
         <v>34243</v>
       </c>
       <c r="B181">
-        <v>61.27087117449431</v>
+        <v>61.28588009157535</v>
       </c>
       <c r="C181">
-        <v>77.36840912604598</v>
+        <v>77.39331969850979</v>
       </c>
     </row>
     <row r="182">
@@ -2363,10 +2363,10 @@
         <v>34335</v>
       </c>
       <c r="B182">
-        <v>61.40594476550167</v>
+        <v>61.42098677021943</v>
       </c>
       <c r="C182">
-        <v>77.52894713900902</v>
+        <v>77.54140521641855</v>
       </c>
     </row>
     <row r="183">
@@ -2374,10 +2374,10 @@
         <v>34425</v>
       </c>
       <c r="B183">
-        <v>61.49298592718441</v>
+        <v>61.5080492535115</v>
       </c>
       <c r="C183">
-        <v>77.68469334311712</v>
+        <v>77.70837006570981</v>
       </c>
     </row>
     <row r="184">
@@ -2385,10 +2385,10 @@
         <v>34516</v>
       </c>
       <c r="B184">
-        <v>61.7832425543218</v>
+        <v>61.79837698193349</v>
       </c>
       <c r="C184">
-        <v>77.8552242036109</v>
+        <v>77.87536131935731</v>
       </c>
     </row>
     <row r="185">
@@ -2396,10 +2396,10 @@
         <v>34608</v>
       </c>
       <c r="B185">
-        <v>62.40401960382702</v>
+        <v>62.41930609703012</v>
       </c>
       <c r="C185">
-        <v>77.9619566229609</v>
+        <v>77.97405761382799</v>
       </c>
     </row>
     <row r="186">
@@ -2407,10 +2407,10 @@
         <v>34700</v>
       </c>
       <c r="B186">
-        <v>62.557340185875</v>
+        <v>62.5726642364991</v>
       </c>
       <c r="C186">
-        <v>78.1386672871464</v>
+        <v>78.15737066776083</v>
       </c>
     </row>
     <row r="187">
@@ -2418,10 +2418,10 @@
         <v>34790</v>
       </c>
       <c r="B187">
-        <v>62.97049114781765</v>
+        <v>62.98591640393158</v>
       </c>
       <c r="C187">
-        <v>78.18865018932436</v>
+        <v>78.21026107895538</v>
       </c>
     </row>
     <row r="188">
@@ -2429,10 +2429,10 @@
         <v>34881</v>
       </c>
       <c r="B188">
-        <v>63.13135103338902</v>
+        <v>63.14681569375227</v>
       </c>
       <c r="C188">
-        <v>78.59282147448329</v>
+        <v>78.61165264125655</v>
       </c>
     </row>
     <row r="189">
@@ -2440,10 +2440,10 @@
         <v>34973</v>
       </c>
       <c r="B189">
-        <v>63.23022086520162</v>
+        <v>63.24570974472608</v>
       </c>
       <c r="C189">
-        <v>78.93653848406356</v>
+        <v>78.94771264089768</v>
       </c>
     </row>
     <row r="190">
@@ -2451,10 +2451,10 @@
         <v>35065</v>
       </c>
       <c r="B190">
-        <v>63.64070196331011</v>
+        <v>63.65686434276218</v>
       </c>
       <c r="C190">
-        <v>79.41152648117928</v>
+        <v>79.43108116851637</v>
       </c>
     </row>
     <row r="191">
@@ -2462,10 +2462,10 @@
         <v>35156</v>
       </c>
       <c r="B191">
-        <v>64.02491259867533</v>
+        <v>64.04116914949839</v>
       </c>
       <c r="C191">
-        <v>79.7400855268869</v>
+        <v>79.75650830738941</v>
       </c>
     </row>
     <row r="192">
@@ -2473,10 +2473,10 @@
         <v>35247</v>
       </c>
       <c r="B192">
-        <v>64.32571149734902</v>
+        <v>64.33974956335383</v>
       </c>
       <c r="C192">
-        <v>79.63615672588575</v>
+        <v>79.65581154004586</v>
       </c>
     </row>
     <row r="193">
@@ -2484,10 +2484,10 @@
         <v>35339</v>
       </c>
       <c r="B193">
-        <v>64.34274216213333</v>
+        <v>64.35964826558683</v>
       </c>
       <c r="C193">
-        <v>79.93874828547052</v>
+        <v>79.96050961938984</v>
       </c>
     </row>
     <row r="194">
@@ -2495,10 +2495,10 @@
         <v>35431</v>
       </c>
       <c r="B194">
-        <v>64.70246514457264</v>
+        <v>64.71337780693368</v>
       </c>
       <c r="C194">
-        <v>80.19486413575584</v>
+        <v>80.21264024855979</v>
       </c>
     </row>
     <row r="195">
@@ -2506,10 +2506,10 @@
         <v>35521</v>
       </c>
       <c r="B195">
-        <v>64.96827269471819</v>
+        <v>64.98972023144634</v>
       </c>
       <c r="C195">
-        <v>80.09511977018468</v>
+        <v>80.11441211303776</v>
       </c>
     </row>
     <row r="196">
@@ -2517,10 +2517,10 @@
         <v>35612</v>
       </c>
       <c r="B196">
-        <v>65.22412903806631</v>
+        <v>65.23569971049112</v>
       </c>
       <c r="C196">
-        <v>80.3667458894832</v>
+        <v>80.38628385707754</v>
       </c>
     </row>
     <row r="197">
@@ -2528,10 +2528,10 @@
         <v>35704</v>
       </c>
       <c r="B197">
-        <v>65.32789264601671</v>
+        <v>65.34715627552988</v>
       </c>
       <c r="C197">
-        <v>80.58197809807127</v>
+        <v>80.59458039237609</v>
       </c>
     </row>
     <row r="198">
@@ -2539,10 +2539,10 @@
         <v>35796</v>
       </c>
       <c r="B198">
-        <v>65.75810348218468</v>
+        <v>65.78294969861557</v>
       </c>
       <c r="C198">
-        <v>80.63342808601507</v>
+        <v>80.64488014158297</v>
       </c>
     </row>
     <row r="199">
@@ -2550,10 +2550,10 @@
         <v>35886</v>
       </c>
       <c r="B199">
-        <v>65.93914632528988</v>
+        <v>65.95242194151794</v>
       </c>
       <c r="C199">
-        <v>80.66485224137753</v>
+        <v>80.67835151425832</v>
       </c>
     </row>
     <row r="200">
@@ -2561,10 +2561,10 @@
         <v>35977</v>
       </c>
       <c r="B200">
-        <v>66.43488153679168</v>
+        <v>66.4461974374931</v>
       </c>
       <c r="C200">
-        <v>80.45805192631228</v>
+        <v>80.47060181936784</v>
       </c>
     </row>
     <row r="201">
@@ -2572,10 +2572,10 @@
         <v>36069</v>
       </c>
       <c r="B201">
-        <v>66.66517864562557</v>
+        <v>66.68027860598229</v>
       </c>
       <c r="C201">
-        <v>80.09103113282801</v>
+        <v>80.11485771820368</v>
       </c>
     </row>
     <row r="202">
@@ -2583,10 +2583,10 @@
         <v>36161</v>
       </c>
       <c r="B202">
-        <v>66.97547543389301</v>
+        <v>66.99515499688353</v>
       </c>
       <c r="C202">
-        <v>79.92078411941101</v>
+        <v>79.94385856946612</v>
       </c>
     </row>
     <row r="203">
@@ -2594,10 +2594,10 @@
         <v>36251</v>
       </c>
       <c r="B203">
-        <v>67.08897025019613</v>
+        <v>67.10459271178534</v>
       </c>
       <c r="C203">
-        <v>79.93305806927702</v>
+        <v>79.95569795298461</v>
       </c>
     </row>
     <row r="204">
@@ -2605,10 +2605,10 @@
         <v>36342</v>
       </c>
       <c r="B204">
-        <v>67.47004451262026</v>
+        <v>67.48376272907127</v>
       </c>
       <c r="C204">
-        <v>79.86227170240045</v>
+        <v>79.88487494107919</v>
       </c>
     </row>
     <row r="205">
@@ -2616,10 +2616,10 @@
         <v>36434</v>
       </c>
       <c r="B205">
-        <v>68.02674430678253</v>
+        <v>68.04381275389872</v>
       </c>
       <c r="C205">
-        <v>80.32001259635884</v>
+        <v>80.349804489428</v>
       </c>
     </row>
     <row r="206">
@@ -2627,10 +2627,10 @@
         <v>36526</v>
       </c>
       <c r="B206">
-        <v>68.6085394584528</v>
+        <v>68.62786058462869</v>
       </c>
       <c r="C206">
-        <v>81.0427707796006</v>
+        <v>81.06844721285569</v>
       </c>
     </row>
     <row r="207">
@@ -2638,10 +2638,10 @@
         <v>36617</v>
       </c>
       <c r="B207">
-        <v>68.82480111289449</v>
+        <v>68.84101800271138</v>
       </c>
       <c r="C207">
-        <v>81.47567620848545</v>
+        <v>81.49580268044335</v>
       </c>
     </row>
     <row r="208">
@@ -2649,10 +2649,10 @@
         <v>36708</v>
       </c>
       <c r="B208">
-        <v>69.26050859471812</v>
+        <v>69.27385387101754</v>
       </c>
       <c r="C208">
-        <v>82.14653580701759</v>
+        <v>82.16026565934399</v>
       </c>
     </row>
     <row r="209">
@@ -2660,10 +2660,10 @@
         <v>36800</v>
       </c>
       <c r="B209">
-        <v>70.03652358656495</v>
+        <v>70.05544385403077</v>
       </c>
       <c r="C209">
-        <v>82.77226565675878</v>
+        <v>82.78199314313032</v>
       </c>
     </row>
     <row r="210">
@@ -2671,10 +2671,10 @@
         <v>36892</v>
       </c>
       <c r="B210">
-        <v>70.05785170852774</v>
+        <v>70.07665867153315</v>
       </c>
       <c r="C210">
-        <v>82.87089179897801</v>
+        <v>82.87362286249937</v>
       </c>
     </row>
     <row r="211">
@@ -2682,10 +2682,10 @@
         <v>36982</v>
       </c>
       <c r="B211">
-        <v>70.74064999358595</v>
+        <v>70.75746899888159</v>
       </c>
       <c r="C211">
-        <v>83.55726237045222</v>
+        <v>83.56768245909436</v>
       </c>
     </row>
     <row r="212">
@@ -2693,10 +2693,10 @@
         <v>37073</v>
       </c>
       <c r="B212">
-        <v>71.15251539115334</v>
+        <v>71.16780791266095</v>
       </c>
       <c r="C212">
-        <v>83.70949269435798</v>
+        <v>83.72641624737687</v>
       </c>
     </row>
     <row r="213">
@@ -2704,10 +2704,10 @@
         <v>37165</v>
       </c>
       <c r="B213">
-        <v>71.68855744544736</v>
+        <v>71.70754054217832</v>
       </c>
       <c r="C213">
-        <v>83.65405239116212</v>
+        <v>83.66743403663021</v>
       </c>
     </row>
     <row r="214">
@@ -2715,10 +2715,10 @@
         <v>37257</v>
       </c>
       <c r="B214">
-        <v>72.22934786783</v>
+        <v>72.24745071235017</v>
       </c>
       <c r="C214">
-        <v>84.04735139235621</v>
+        <v>84.06447670242761</v>
       </c>
     </row>
     <row r="215">
@@ -2726,10 +2726,10 @@
         <v>37347</v>
       </c>
       <c r="B215">
-        <v>73.05114317193993</v>
+        <v>73.07046323839531</v>
       </c>
       <c r="C215">
-        <v>84.14813382472656</v>
+        <v>84.17410860621891</v>
       </c>
     </row>
     <row r="216">
@@ -2737,10 +2737,10 @@
         <v>37438</v>
       </c>
       <c r="B216">
-        <v>73.48030480241511</v>
+        <v>73.49687706410836</v>
       </c>
       <c r="C216">
-        <v>84.34795798807059</v>
+        <v>84.37487475138022</v>
       </c>
     </row>
     <row r="217">
@@ -2748,10 +2748,10 @@
         <v>37530</v>
       </c>
       <c r="B217">
-        <v>73.8552925013058</v>
+        <v>73.87305367656244</v>
       </c>
       <c r="C217">
-        <v>84.62431156248101</v>
+        <v>84.64483835860031</v>
       </c>
     </row>
     <row r="218">
@@ -2759,10 +2759,10 @@
         <v>37622</v>
       </c>
       <c r="B218">
-        <v>74.36784119249992</v>
+        <v>74.38462396573949</v>
       </c>
       <c r="C218">
-        <v>85.28809011080976</v>
+        <v>85.31149555451067</v>
       </c>
     </row>
     <row r="219">
@@ -2770,10 +2770,10 @@
         <v>37712</v>
       </c>
       <c r="B219">
-        <v>74.96661414048667</v>
+        <v>74.98599229260356</v>
       </c>
       <c r="C219">
-        <v>85.32241694738167</v>
+        <v>85.33213820850372</v>
       </c>
     </row>
     <row r="220">
@@ -2781,10 +2781,10 @@
         <v>37803</v>
       </c>
       <c r="B220">
-        <v>75.68424609696692</v>
+        <v>75.70270809370854</v>
       </c>
       <c r="C220">
-        <v>85.80114205998916</v>
+        <v>85.81319175015972</v>
       </c>
     </row>
     <row r="221">
@@ -2792,10 +2792,10 @@
         <v>37895</v>
       </c>
       <c r="B221">
-        <v>76.07047794390105</v>
+        <v>76.0896197999767</v>
       </c>
       <c r="C221">
-        <v>86.3294654194511</v>
+        <v>86.35217102145744</v>
       </c>
     </row>
     <row r="222">
@@ -2803,10 +2803,10 @@
         <v>37987</v>
       </c>
       <c r="B222">
-        <v>76.92794857991299</v>
+        <v>76.94411521064252</v>
       </c>
       <c r="C222">
-        <v>86.7500869761202</v>
+        <v>86.76532472896574</v>
       </c>
     </row>
     <row r="223">
@@ -2814,10 +2814,10 @@
         <v>38078</v>
       </c>
       <c r="B223">
-        <v>77.56506273935433</v>
+        <v>77.58412994809714</v>
       </c>
       <c r="C223">
-        <v>87.32519006741934</v>
+        <v>87.34618427574617</v>
       </c>
     </row>
     <row r="224">
@@ -2825,10 +2825,10 @@
         <v>38169</v>
       </c>
       <c r="B224">
-        <v>78.10725825480183</v>
+        <v>78.1268982087648</v>
       </c>
       <c r="C224">
-        <v>87.68999910757522</v>
+        <v>87.70994289601443</v>
       </c>
     </row>
     <row r="225">
@@ -2836,10 +2836,10 @@
         <v>38261</v>
       </c>
       <c r="B225">
-        <v>78.72158748630159</v>
+        <v>78.74340154465921</v>
       </c>
       <c r="C225">
-        <v>88.0723148360849</v>
+        <v>88.09053715251778</v>
       </c>
     </row>
     <row r="226">
@@ -2847,10 +2847,10 @@
         <v>38353</v>
       </c>
       <c r="B226">
-        <v>78.97461746803255</v>
+        <v>78.98840814264548</v>
       </c>
       <c r="C226">
-        <v>88.36340030360947</v>
+        <v>88.38805960587929</v>
       </c>
     </row>
     <row r="227">
@@ -2858,10 +2858,10 @@
         <v>38443</v>
       </c>
       <c r="B227">
-        <v>79.55115556607203</v>
+        <v>79.57075291207639</v>
       </c>
       <c r="C227">
-        <v>88.74998471982977</v>
+        <v>88.76706696743396</v>
       </c>
     </row>
     <row r="228">
@@ -2869,10 +2869,10 @@
         <v>38534</v>
       </c>
       <c r="B228">
-        <v>80.3172462644836</v>
+        <v>80.33837877960609</v>
       </c>
       <c r="C228">
-        <v>89.43039179318109</v>
+        <v>89.44694989455851</v>
       </c>
     </row>
     <row r="229">
@@ -2880,10 +2880,10 @@
         <v>38626</v>
       </c>
       <c r="B229">
-        <v>81.17822636029005</v>
+        <v>81.20157626915694</v>
       </c>
       <c r="C229">
-        <v>89.64123182354533</v>
+        <v>89.65902019049835</v>
       </c>
     </row>
     <row r="230">
@@ -2891,10 +2891,10 @@
         <v>38718</v>
       </c>
       <c r="B230">
-        <v>81.68847456825574</v>
+        <v>81.69806931299007</v>
       </c>
       <c r="C230">
-        <v>90.21109867339769</v>
+        <v>90.23606278866662</v>
       </c>
     </row>
     <row r="231">
@@ -2902,10 +2902,10 @@
         <v>38808</v>
       </c>
       <c r="B231">
-        <v>82.20345101875428</v>
+        <v>82.22558018078814</v>
       </c>
       <c r="C231">
-        <v>90.77693810106739</v>
+        <v>90.80370473705814</v>
       </c>
     </row>
     <row r="232">
@@ -2913,10 +2913,10 @@
         <v>38899</v>
       </c>
       <c r="B232">
-        <v>82.73747895794398</v>
+        <v>82.75912353620538</v>
       </c>
       <c r="C232">
-        <v>91.33582513416241</v>
+        <v>91.35614952636904</v>
       </c>
     </row>
     <row r="233">
@@ -2924,10 +2924,10 @@
         <v>38991</v>
       </c>
       <c r="B233">
-        <v>83.83362222750137</v>
+        <v>83.86107453575544</v>
       </c>
       <c r="C233">
-        <v>91.385083796586</v>
+        <v>91.39601396264936</v>
       </c>
     </row>
     <row r="234">
@@ -2935,10 +2935,10 @@
         <v>39083</v>
       </c>
       <c r="B234">
-        <v>84.05554142053978</v>
+        <v>84.05799815792227</v>
       </c>
       <c r="C234">
-        <v>91.77120767993301</v>
+        <v>91.78672512047567</v>
       </c>
     </row>
     <row r="235">
@@ -2946,10 +2946,10 @@
         <v>39173</v>
       </c>
       <c r="B235">
-        <v>84.31112162227548</v>
+        <v>84.33854258227018</v>
       </c>
       <c r="C235">
-        <v>92.44724951650544</v>
+        <v>92.45941368128913</v>
       </c>
     </row>
     <row r="236">
@@ -2957,10 +2957,10 @@
         <v>39264</v>
       </c>
       <c r="B236">
-        <v>84.73243731710983</v>
+        <v>84.76102366312884</v>
       </c>
       <c r="C236">
-        <v>93.11065019570255</v>
+        <v>93.13228040511643</v>
       </c>
     </row>
     <row r="237">
@@ -2968,10 +2968,10 @@
         <v>39356</v>
       </c>
       <c r="B237">
-        <v>85.51360619993726</v>
+        <v>85.53844245934037</v>
       </c>
       <c r="C237">
-        <v>94.10563356270202</v>
+        <v>94.12995042153757</v>
       </c>
     </row>
     <row r="238">
@@ -2979,10 +2979,10 @@
         <v>39448</v>
       </c>
       <c r="B238">
-        <v>86.32092164224055</v>
+        <v>86.31976899172467</v>
       </c>
       <c r="C238">
-        <v>95.01005446739214</v>
+        <v>95.01572221641349</v>
       </c>
     </row>
     <row r="239">
@@ -2990,10 +2990,10 @@
         <v>39539</v>
       </c>
       <c r="B239">
-        <v>86.50779096821758</v>
+        <v>86.53285502546971</v>
       </c>
       <c r="C239">
-        <v>95.91857334890183</v>
+        <v>95.93634057079967</v>
       </c>
     </row>
     <row r="240">
@@ -3001,10 +3001,10 @@
         <v>39630</v>
       </c>
       <c r="B240">
-        <v>87.09153219086672</v>
+        <v>87.11340044545842</v>
       </c>
       <c r="C240">
-        <v>95.90825520609003</v>
+        <v>95.92481196635411</v>
       </c>
     </row>
     <row r="241">
@@ -3012,10 +3012,10 @@
         <v>39722</v>
       </c>
       <c r="B241">
-        <v>86.98908827558827</v>
+        <v>87.02792918058888</v>
       </c>
       <c r="C241">
-        <v>94.97182322328237</v>
+        <v>95.01341628749503</v>
       </c>
     </row>
     <row r="242">
@@ -3023,10 +3023,10 @@
         <v>39814</v>
       </c>
       <c r="B242">
-        <v>87.11617305506985</v>
+        <v>87.12762696108605</v>
       </c>
       <c r="C242">
-        <v>94.2724739809278</v>
+        <v>94.32551675365498</v>
       </c>
     </row>
     <row r="243">
@@ -3034,10 +3034,10 @@
         <v>39904</v>
       </c>
       <c r="B243">
-        <v>87.34453333293945</v>
+        <v>87.36791055644504</v>
       </c>
       <c r="C243">
-        <v>93.8630100822831</v>
+        <v>93.87567914592353</v>
       </c>
     </row>
     <row r="244">
@@ -3045,10 +3045,10 @@
         <v>39995</v>
       </c>
       <c r="B244">
-        <v>87.95814500398764</v>
+        <v>87.97722898223992</v>
       </c>
       <c r="C244">
-        <v>93.78692842146252</v>
+        <v>93.79221330239743</v>
       </c>
     </row>
     <row r="245">
@@ -3056,10 +3056,10 @@
         <v>40087</v>
       </c>
       <c r="B245">
-        <v>88.67820972016162</v>
+        <v>88.70988920682412</v>
       </c>
       <c r="C245">
-        <v>93.88869719184616</v>
+        <v>93.8965128201431</v>
       </c>
     </row>
     <row r="246">
@@ -3067,10 +3067,10 @@
         <v>40179</v>
       </c>
       <c r="B246">
-        <v>89.54105867424326</v>
+        <v>89.55752754629478</v>
       </c>
       <c r="C246">
-        <v>94.47910215401004</v>
+        <v>94.49498766784167</v>
       </c>
     </row>
     <row r="247">
@@ -3078,10 +3078,10 @@
         <v>40269</v>
       </c>
       <c r="B247">
-        <v>90.20003328152984</v>
+        <v>90.21713175708109</v>
       </c>
       <c r="C247">
-        <v>94.99580118705565</v>
+        <v>95.01212312915789</v>
       </c>
     </row>
     <row r="248">
@@ -3089,10 +3089,10 @@
         <v>40360</v>
       </c>
       <c r="B248">
-        <v>90.52011307519844</v>
+        <v>90.54378044854926</v>
       </c>
       <c r="C248">
-        <v>95.18477440335397</v>
+        <v>95.19795374486583</v>
       </c>
     </row>
     <row r="249">
@@ -3100,10 +3100,10 @@
         <v>40452</v>
       </c>
       <c r="B249">
-        <v>90.76666039711061</v>
+        <v>90.79728542675714</v>
       </c>
       <c r="C249">
-        <v>95.51147028085587</v>
+        <v>95.54689622111961</v>
       </c>
     </row>
     <row r="250">
@@ -3111,10 +3111,10 @@
         <v>40544</v>
       </c>
       <c r="B250">
-        <v>91.41293024111388</v>
+        <v>91.43134234454757</v>
       </c>
       <c r="C250">
-        <v>96.22526200429733</v>
+        <v>96.24542654813581</v>
       </c>
     </row>
     <row r="251">
@@ -3122,10 +3122,10 @@
         <v>40634</v>
       </c>
       <c r="B251">
-        <v>91.51809684993415</v>
+        <v>91.54002527285303</v>
       </c>
       <c r="C251">
-        <v>96.69899348102768</v>
+        <v>96.71376999262326</v>
       </c>
     </row>
     <row r="252">
@@ -3133,10 +3133,10 @@
         <v>40725</v>
       </c>
       <c r="B252">
-        <v>91.59813196396489</v>
+        <v>91.62158434013369</v>
       </c>
       <c r="C252">
-        <v>96.92376750743826</v>
+        <v>96.9486526862072</v>
       </c>
     </row>
     <row r="253">
@@ -3144,10 +3144,10 @@
         <v>40817</v>
       </c>
       <c r="B253">
-        <v>92.19956626312225</v>
+        <v>92.22558233040836</v>
       </c>
       <c r="C253">
-        <v>97.30196037332557</v>
+        <v>97.32141517748215</v>
       </c>
     </row>
     <row r="254">
@@ -3155,10 +3155,10 @@
         <v>40909</v>
       </c>
       <c r="B254">
-        <v>92.63405376181585</v>
+        <v>92.65717871960642</v>
       </c>
       <c r="C254">
-        <v>97.92840589949982</v>
+        <v>97.9636898550644</v>
       </c>
     </row>
     <row r="255">
@@ -3166,10 +3166,10 @@
         <v>41000</v>
       </c>
       <c r="B255">
-        <v>92.88791007473431</v>
+        <v>92.91124740934606</v>
       </c>
       <c r="C255">
-        <v>98.1502497506134</v>
+        <v>98.17785196359756</v>
       </c>
     </row>
     <row r="256">
@@ -3177,10 +3177,10 @@
         <v>41091</v>
       </c>
       <c r="B256">
-        <v>93.28507278446978</v>
+        <v>93.30207973862441</v>
       </c>
       <c r="C256">
-        <v>98.18408287138631</v>
+        <v>98.19370949431949</v>
       </c>
     </row>
     <row r="257">
@@ -3188,10 +3188,10 @@
         <v>41183</v>
       </c>
       <c r="B257">
-        <v>93.7756516719792</v>
+        <v>93.80296275255972</v>
       </c>
       <c r="C257">
-        <v>98.32478292045798</v>
+        <v>98.33652641975867</v>
       </c>
     </row>
     <row r="258">
@@ -3199,10 +3199,10 @@
         <v>41275</v>
       </c>
       <c r="B258">
-        <v>93.79401521119287</v>
+        <v>93.81503904131414</v>
       </c>
       <c r="C258">
-        <v>98.70390590396265</v>
+        <v>98.7317997545383</v>
       </c>
     </row>
     <row r="259">
@@ -3210,10 +3210,10 @@
         <v>41365</v>
       </c>
       <c r="B259">
-        <v>94.36422182506342</v>
+        <v>94.38793550326936</v>
       </c>
       <c r="C259">
-        <v>98.68467557849651</v>
+        <v>98.71182316700286</v>
       </c>
     </row>
     <row r="260">
@@ -3221,10 +3221,10 @@
         <v>41456</v>
       </c>
       <c r="B260">
-        <v>94.83460759713613</v>
+        <v>94.85246661919929</v>
       </c>
       <c r="C260">
-        <v>98.88124558435372</v>
+        <v>98.89178200877488</v>
       </c>
     </row>
     <row r="261">
@@ -3232,10 +3232,10 @@
         <v>41548</v>
       </c>
       <c r="B261">
-        <v>94.84177192882588</v>
+        <v>94.87170680273742</v>
       </c>
       <c r="C261">
-        <v>98.85053612435574</v>
+        <v>98.86852475540199</v>
       </c>
     </row>
     <row r="262">
@@ -3243,10 +3243,10 @@
         <v>41640</v>
       </c>
       <c r="B262">
-        <v>95.1450408777077</v>
+        <v>95.16837922718223</v>
       </c>
       <c r="C262">
-        <v>99.06212530492053</v>
+        <v>99.07839819524293</v>
       </c>
     </row>
     <row r="263">
@@ -3254,10 +3254,10 @@
         <v>41730</v>
       </c>
       <c r="B263">
-        <v>95.4436451756894</v>
+        <v>95.46608507857792</v>
       </c>
       <c r="C263">
-        <v>98.88794518840032</v>
+        <v>98.91124143930024</v>
       </c>
     </row>
     <row r="264">
@@ -3265,10 +3265,10 @@
         <v>41821</v>
       </c>
       <c r="B264">
-        <v>95.78759029921345</v>
+        <v>95.80615039817231</v>
       </c>
       <c r="C264">
-        <v>98.79520288195174</v>
+        <v>98.81984234927184</v>
       </c>
     </row>
     <row r="265">
@@ -3276,10 +3276,10 @@
         <v>41913</v>
       </c>
       <c r="B265">
-        <v>96.06157591041169</v>
+        <v>96.09039463996955</v>
       </c>
       <c r="C265">
-        <v>98.7960468284631</v>
+        <v>98.81443410473214</v>
       </c>
     </row>
     <row r="266">
@@ -3287,10 +3287,10 @@
         <v>42005</v>
       </c>
       <c r="B266">
-        <v>96.29547973868512</v>
+        <v>96.31873248140724</v>
       </c>
       <c r="C266">
-        <v>98.81242469353822</v>
+        <v>98.84194168091371</v>
       </c>
     </row>
     <row r="267">
@@ -3298,10 +3298,10 @@
         <v>42095</v>
       </c>
       <c r="B267">
-        <v>96.71770320410995</v>
+        <v>96.73684774208488</v>
       </c>
       <c r="C267">
-        <v>99.29393136241579</v>
+        <v>99.30101294949046</v>
       </c>
     </row>
     <row r="268">
@@ -3309,10 +3309,10 @@
         <v>42186</v>
       </c>
       <c r="B268">
-        <v>97.10220429547637</v>
+        <v>97.12842396200664</v>
       </c>
       <c r="C268">
-        <v>99.24242561086196</v>
+        <v>99.26603896794172</v>
       </c>
     </row>
     <row r="269">
@@ -3320,10 +3320,10 @@
         <v>42278</v>
       </c>
       <c r="B269">
-        <v>97.58651595042708</v>
+        <v>97.61285042977222</v>
       </c>
       <c r="C269">
-        <v>99.22724347971629</v>
+        <v>99.24841314006133</v>
       </c>
     </row>
     <row r="270">
@@ -3331,10 +3331,10 @@
         <v>42370</v>
       </c>
       <c r="B270">
-        <v>98.17429380511271</v>
+        <v>98.19873176657666</v>
       </c>
       <c r="C270">
-        <v>99.06839119939586</v>
+        <v>99.03850301008606</v>
       </c>
     </row>
     <row r="271">
@@ -3342,10 +3342,10 @@
         <v>42461</v>
       </c>
       <c r="B271">
-        <v>98.04573787064433</v>
+        <v>98.0570756671241</v>
       </c>
       <c r="C271">
-        <v>99.34220506187171</v>
+        <v>99.36030972176387</v>
       </c>
     </row>
     <row r="272">
@@ -3353,10 +3353,10 @@
         <v>42552</v>
       </c>
       <c r="B272">
-        <v>98.35996862786484</v>
+        <v>98.39140109455428</v>
       </c>
       <c r="C272">
-        <v>99.42646655590795</v>
+        <v>99.462650973962</v>
       </c>
     </row>
     <row r="273">
@@ -3364,10 +3364,10 @@
         <v>42644</v>
       </c>
       <c r="B273">
-        <v>98.91113723459651</v>
+        <v>98.93975160773351</v>
       </c>
       <c r="C273">
-        <v>99.63600387854346</v>
+        <v>99.69406524068</v>
       </c>
     </row>
     <row r="274">
@@ -3375,10 +3375,10 @@
         <v>42736</v>
       </c>
       <c r="B274">
-        <v>99.79714644362268</v>
+        <v>99.82317488300983</v>
       </c>
       <c r="C274">
-        <v>100.0524603942098</v>
+        <v>100.011992360116</v>
       </c>
     </row>
     <row r="275">
@@ -3397,10 +3397,10 @@
         <v>42917</v>
       </c>
       <c r="B276">
-        <v>100.3615738671262</v>
+        <v>100.4001652328461</v>
       </c>
       <c r="C276">
-        <v>100.0439751843059</v>
+        <v>100.1045025954967</v>
       </c>
     </row>
     <row r="277">
@@ -3408,10 +3408,10 @@
         <v>43009</v>
       </c>
       <c r="B277">
-        <v>101.195241366691</v>
+        <v>101.2283875711727</v>
       </c>
       <c r="C277">
-        <v>100.5905809971437</v>
+        <v>100.6534356730375</v>
       </c>
     </row>
     <row r="278">
@@ -3419,10 +3419,10 @@
         <v>43101</v>
       </c>
       <c r="B278">
-        <v>101.2087168529435</v>
+        <v>101.2437418367398</v>
       </c>
       <c r="C278">
-        <v>101.2674450582879</v>
+        <v>101.269986150668</v>
       </c>
     </row>
     <row r="279">
@@ -3430,10 +3430,10 @@
         <v>43191</v>
       </c>
       <c r="B279">
-        <v>101.7162582497874</v>
+        <v>101.7027118594449</v>
       </c>
       <c r="C279">
-        <v>101.8433383184556</v>
+        <v>101.8854215063295</v>
       </c>
     </row>
     <row r="280">
@@ -3441,10 +3441,10 @@
         <v>43282</v>
       </c>
       <c r="B280">
-        <v>102.3257475915487</v>
+        <v>102.3645354813408</v>
       </c>
       <c r="C280">
-        <v>102.119486592023</v>
+        <v>102.1654535153637</v>
       </c>
     </row>
     <row r="281">
@@ -3452,10 +3452,10 @@
         <v>43374</v>
       </c>
       <c r="B281">
-        <v>102.8432591869217</v>
+        <v>102.8834206228294</v>
       </c>
       <c r="C281">
-        <v>102.2287339862874</v>
+        <v>102.2250598750145</v>
       </c>
     </row>
     <row r="282">
@@ -3463,10 +3463,10 @@
         <v>43466</v>
       </c>
       <c r="B282">
-        <v>101.4742354335517</v>
+        <v>101.5141311080007</v>
       </c>
       <c r="C282">
-        <v>102.2237701537</v>
+        <v>102.2018890871676</v>
       </c>
     </row>
     <row r="283">
@@ -3474,10 +3474,10 @@
         <v>43556</v>
       </c>
       <c r="B283">
-        <v>101.1043185977434</v>
+        <v>101.0734798261951</v>
       </c>
       <c r="C283">
-        <v>102.5960904164361</v>
+        <v>102.608754006546</v>
       </c>
     </row>
     <row r="284">
@@ -3485,10 +3485,10 @@
         <v>43647</v>
       </c>
       <c r="B284">
-        <v>101.3074314814449</v>
+        <v>101.3390640203707</v>
       </c>
       <c r="C284">
-        <v>102.822015215222</v>
+        <v>102.8917788098255</v>
       </c>
     </row>
     <row r="285">
@@ -3496,10 +3496,10 @@
         <v>43739</v>
       </c>
       <c r="B285">
-        <v>101.0307787680512</v>
+        <v>101.0900204772598</v>
       </c>
       <c r="C285">
-        <v>103.1846460591515</v>
+        <v>103.210764037145</v>
       </c>
     </row>
     <row r="286">
@@ -3507,10 +3507,10 @@
         <v>43831</v>
       </c>
       <c r="B286">
-        <v>97.33284694670377</v>
+        <v>97.35964483710117</v>
       </c>
       <c r="C286">
-        <v>103.5174823801417</v>
+        <v>103.4770570257857</v>
       </c>
     </row>
     <row r="287">
@@ -3518,10 +3518,10 @@
         <v>43922</v>
       </c>
       <c r="B287">
-        <v>85.96181432337926</v>
+        <v>85.91274405075835</v>
       </c>
       <c r="C287">
-        <v>103.5944757923636</v>
+        <v>103.6020154286757</v>
       </c>
     </row>
     <row r="288">
@@ -3529,10 +3529,10 @@
         <v>44013</v>
       </c>
       <c r="B288">
-        <v>99.19393515917464</v>
+        <v>99.19110146266709</v>
       </c>
       <c r="C288">
-        <v>103.6081143644015</v>
+        <v>103.6906822603219</v>
       </c>
     </row>
     <row r="289">
@@ -3540,10 +3540,10 @@
         <v>44105</v>
       </c>
       <c r="B289">
-        <v>97.56972434121603</v>
+        <v>97.6850354211625</v>
       </c>
       <c r="C289">
-        <v>103.7404082041653</v>
+        <v>103.7747177482538</v>
       </c>
     </row>
     <row r="290">
@@ -3551,10 +3551,10 @@
         <v>44197</v>
       </c>
       <c r="B290">
-        <v>97.70807666653921</v>
+        <v>97.71863576438459</v>
       </c>
       <c r="C290">
-        <v>104.3511384616094</v>
+        <v>104.347620819556</v>
       </c>
     </row>
     <row r="291">
@@ -3562,10 +3562,10 @@
         <v>44287</v>
       </c>
       <c r="B291">
-        <v>98.78568676741693</v>
+        <v>98.71937155492184</v>
       </c>
       <c r="C291">
-        <v>104.6558823369027</v>
+        <v>104.7190842006649</v>
       </c>
     </row>
     <row r="292">
@@ -3573,10 +3573,10 @@
         <v>44378</v>
       </c>
       <c r="B292">
-        <v>101.8150422111389</v>
+        <v>101.8401053503415</v>
       </c>
       <c r="C292">
-        <v>105.3801306291325</v>
+        <v>105.4462297079327</v>
       </c>
     </row>
     <row r="293">
@@ -3584,10 +3584,10 @@
         <v>44470</v>
       </c>
       <c r="B293">
-        <v>102.4245916124575</v>
+        <v>102.549955309785</v>
       </c>
       <c r="C293">
-        <v>106.2061457923502</v>
+        <v>106.1702182688898</v>
       </c>
     </row>
     <row r="294">
@@ -3595,10 +3595,10 @@
         <v>44562</v>
       </c>
       <c r="B294">
-        <v>103.8027925876426</v>
+        <v>103.8046581563721</v>
       </c>
       <c r="C294">
-        <v>107.3509503836638</v>
+        <v>107.3790779746158</v>
       </c>
     </row>
     <row r="295">
@@ -3606,10 +3606,10 @@
         <v>44652</v>
       </c>
       <c r="B295">
-        <v>104.5078433050086</v>
+        <v>104.4274186843537</v>
       </c>
       <c r="C295">
-        <v>109.2877821642938</v>
+        <v>109.3575688067031</v>
       </c>
     </row>
     <row r="296">
@@ -3617,10 +3617,10 @@
         <v>44743</v>
       </c>
       <c r="B296">
-        <v>104.6527936254914</v>
+        <v>104.662328969476</v>
       </c>
       <c r="C296">
-        <v>111.1118798993653</v>
+        <v>111.216384537951</v>
       </c>
     </row>
     <row r="297">
@@ -3628,10 +3628,10 @@
         <v>44835</v>
       </c>
       <c r="B297">
-        <v>106.7790050297514</v>
+        <v>106.9496734728535</v>
       </c>
       <c r="C297">
-        <v>113.2787923525218</v>
+        <v>113.1809637412933</v>
       </c>
     </row>
     <row r="298">
@@ -3639,18 +3639,21 @@
         <v>44927</v>
       </c>
       <c r="B298">
-        <v>107.9790291168578</v>
+        <v>107.9946445438968</v>
       </c>
       <c r="C298">
-        <v>115.5941037192763</v>
+        <v>115.4648732951276</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2">
         <v>45017</v>
       </c>
+      <c r="B299">
+        <v>108.8535181174555</v>
+      </c>
       <c r="C299">
-        <v>117.0290906371843</v>
+        <v>117.0569476550662</v>
       </c>
     </row>
   </sheetData>

--- a/Conjoncture - comptes trimestriels/data/smpt.xlsx
+++ b/Conjoncture - comptes trimestriels/data/smpt.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C299"/>
+  <dimension ref="A1:C300"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -383,10 +383,10 @@
         <v>17899</v>
       </c>
       <c r="B2">
-        <v>0.8488207280433295</v>
+        <v>0.8486392491682327</v>
       </c>
       <c r="C2">
-        <v>5.189921053298163</v>
+        <v>5.18946688386686</v>
       </c>
     </row>
     <row r="3">
@@ -394,10 +394,10 @@
         <v>17989</v>
       </c>
       <c r="B3">
-        <v>0.8726351281478683</v>
+        <v>0.8724485577258769</v>
       </c>
       <c r="C3">
-        <v>5.226305227461935</v>
+        <v>5.225847874055477</v>
       </c>
     </row>
     <row r="4">
@@ -405,10 +405,10 @@
         <v>18080</v>
       </c>
       <c r="B4">
-        <v>0.8783896184839218</v>
+        <v>0.8782018177450936</v>
       </c>
       <c r="C4">
-        <v>5.380238404152841</v>
+        <v>5.379767580070704</v>
       </c>
     </row>
     <row r="5">
@@ -416,10 +416,10 @@
         <v>18172</v>
       </c>
       <c r="B5">
-        <v>0.8792266968567582</v>
+        <v>0.8790387171495844</v>
       </c>
       <c r="C5">
-        <v>5.405477255323372</v>
+        <v>5.405004222592091</v>
       </c>
     </row>
     <row r="6">
@@ -427,10 +427,10 @@
         <v>18264</v>
       </c>
       <c r="B6">
-        <v>0.9038715022330908</v>
+        <v>0.9036782534373936</v>
       </c>
       <c r="C6">
-        <v>5.482251828787592</v>
+        <v>5.481772077521673</v>
       </c>
     </row>
     <row r="7">
@@ -438,10 +438,10 @@
         <v>18354</v>
       </c>
       <c r="B7">
-        <v>0.9401499187407559</v>
+        <v>0.9399489135767226</v>
       </c>
       <c r="C7">
-        <v>5.582669855199878</v>
+        <v>5.582181316363304</v>
       </c>
     </row>
     <row r="8">
@@ -449,10 +449,10 @@
         <v>18445</v>
       </c>
       <c r="B8">
-        <v>0.9755957526831484</v>
+        <v>0.9753871691579156</v>
       </c>
       <c r="C8">
-        <v>5.816830633622137</v>
+        <v>5.816321603401113</v>
       </c>
     </row>
     <row r="9">
@@ -460,10 +460,10 @@
         <v>18537</v>
       </c>
       <c r="B9">
-        <v>1.018968256230846</v>
+        <v>1.018750399613081</v>
       </c>
       <c r="C9">
-        <v>5.975013027528568</v>
+        <v>5.974490154783323</v>
       </c>
     </row>
     <row r="10">
@@ -471,10 +471,10 @@
         <v>18629</v>
       </c>
       <c r="B10">
-        <v>1.077242467786796</v>
+        <v>1.077012152073711</v>
       </c>
       <c r="C10">
-        <v>6.279638976668879</v>
+        <v>6.279089446139699</v>
       </c>
     </row>
     <row r="11">
@@ -482,10 +482,10 @@
         <v>18719</v>
       </c>
       <c r="B11">
-        <v>1.166761259624187</v>
+        <v>1.166511804687582</v>
       </c>
       <c r="C11">
-        <v>6.602911564788306</v>
+        <v>6.602333744709825</v>
       </c>
     </row>
     <row r="12">
@@ -493,10 +493,10 @@
         <v>18810</v>
       </c>
       <c r="B12">
-        <v>1.273191824140178</v>
+        <v>1.272919614223062</v>
       </c>
       <c r="C12">
-        <v>6.84664250337883</v>
+        <v>6.846043354432216</v>
       </c>
     </row>
     <row r="13">
@@ -504,10 +504,10 @@
         <v>18902</v>
       </c>
       <c r="B13">
-        <v>1.372155867424002</v>
+        <v>1.37186249887744</v>
       </c>
       <c r="C13">
-        <v>7.195367258195111</v>
+        <v>7.194737592382835</v>
       </c>
     </row>
     <row r="14">
@@ -515,10 +515,10 @@
         <v>18994</v>
       </c>
       <c r="B14">
-        <v>1.43048389322769</v>
+        <v>1.430178054080258</v>
       </c>
       <c r="C14">
-        <v>7.436376840996729</v>
+        <v>7.435726084461872</v>
       </c>
     </row>
     <row r="15">
@@ -526,10 +526,10 @@
         <v>19085</v>
       </c>
       <c r="B15">
-        <v>1.467667017038582</v>
+        <v>1.467353228095324</v>
       </c>
       <c r="C15">
-        <v>7.478337074435823</v>
+        <v>7.477682645965465</v>
       </c>
     </row>
     <row r="16">
@@ -537,10 +537,10 @@
         <v>19176</v>
       </c>
       <c r="B16">
-        <v>1.487629411890917</v>
+        <v>1.48731135496404</v>
       </c>
       <c r="C16">
-        <v>7.509468303067745</v>
+        <v>7.508811150306929</v>
       </c>
     </row>
     <row r="17">
@@ -548,10 +548,10 @@
         <v>19268</v>
       </c>
       <c r="B17">
-        <v>1.497571310075119</v>
+        <v>1.497251127558657</v>
       </c>
       <c r="C17">
-        <v>7.479202853907727</v>
+        <v>7.4785483496731</v>
       </c>
     </row>
     <row r="18">
@@ -559,10 +559,10 @@
         <v>19360</v>
       </c>
       <c r="B18">
-        <v>1.505537832281802</v>
+        <v>1.505215946513475</v>
       </c>
       <c r="C18">
-        <v>7.459989055946827</v>
+        <v>7.459336233109587</v>
       </c>
     </row>
     <row r="19">
@@ -570,10 +570,10 @@
         <v>19450</v>
       </c>
       <c r="B19">
-        <v>1.525048135298839</v>
+        <v>1.524722078204663</v>
       </c>
       <c r="C19">
-        <v>7.452812891271144</v>
+        <v>7.452160696419299</v>
       </c>
     </row>
     <row r="20">
@@ -581,10 +581,10 @@
         <v>19541</v>
       </c>
       <c r="B20">
-        <v>1.540595081558821</v>
+        <v>1.540265700509156</v>
       </c>
       <c r="C20">
-        <v>7.453863632351639</v>
+        <v>7.453211345549556</v>
       </c>
     </row>
     <row r="21">
@@ -592,10 +592,10 @@
         <v>19633</v>
       </c>
       <c r="B21">
-        <v>1.56348980409119</v>
+        <v>1.563155528122782</v>
       </c>
       <c r="C21">
-        <v>7.416742271273451</v>
+        <v>7.41609323295767</v>
       </c>
     </row>
     <row r="22">
@@ -603,10 +603,10 @@
         <v>19725</v>
       </c>
       <c r="B22">
-        <v>1.600818749419249</v>
+        <v>1.6004764924782</v>
       </c>
       <c r="C22">
-        <v>7.480138577719749</v>
+        <v>7.479483991600032</v>
       </c>
     </row>
     <row r="23">
@@ -614,10 +614,10 @@
         <v>19815</v>
       </c>
       <c r="B23">
-        <v>1.639216982515273</v>
+        <v>1.638866515986596</v>
       </c>
       <c r="C23">
-        <v>7.540371169615656</v>
+        <v>7.539711312548324</v>
       </c>
     </row>
     <row r="24">
@@ -625,10 +625,10 @@
         <v>19906</v>
       </c>
       <c r="B24">
-        <v>1.658601440468114</v>
+        <v>1.658246829519411</v>
       </c>
       <c r="C24">
-        <v>7.579211997412637</v>
+        <v>7.578548741388655</v>
       </c>
     </row>
     <row r="25">
@@ -636,10 +636,10 @@
         <v>19998</v>
       </c>
       <c r="B25">
-        <v>1.687096468184788</v>
+        <v>1.686735764965474</v>
       </c>
       <c r="C25">
-        <v>7.603103907784789</v>
+        <v>7.602438560982308</v>
       </c>
     </row>
     <row r="26">
@@ -647,10 +647,10 @@
         <v>20090</v>
       </c>
       <c r="B26">
-        <v>1.717458952348263</v>
+        <v>1.717091757593942</v>
       </c>
       <c r="C26">
-        <v>7.567165816271344</v>
+        <v>7.566503614407375</v>
       </c>
     </row>
     <row r="27">
@@ -658,10 +658,10 @@
         <v>20180</v>
       </c>
       <c r="B27">
-        <v>1.752907532776522</v>
+        <v>1.752532759073799</v>
       </c>
       <c r="C27">
-        <v>7.610779149435072</v>
+        <v>7.610113130973025</v>
       </c>
     </row>
     <row r="28">
@@ -669,10 +669,10 @@
         <v>20271</v>
       </c>
       <c r="B28">
-        <v>1.801257623146835</v>
+        <v>1.800872512137634</v>
       </c>
       <c r="C28">
-        <v>7.654214296005595</v>
+        <v>7.653544476538557</v>
       </c>
     </row>
     <row r="29">
@@ -680,10 +680,10 @@
         <v>20363</v>
       </c>
       <c r="B29">
-        <v>1.853685756971226</v>
+        <v>1.853289436765034</v>
       </c>
       <c r="C29">
-        <v>7.742302526087974</v>
+        <v>7.741624998029428</v>
       </c>
     </row>
     <row r="30">
@@ -691,10 +691,10 @@
         <v>20455</v>
       </c>
       <c r="B30">
-        <v>1.903111573812146</v>
+        <v>1.902704686307885</v>
       </c>
       <c r="C30">
-        <v>7.859028475303812</v>
+        <v>7.858340732570046</v>
       </c>
     </row>
     <row r="31">
@@ -702,10 +702,10 @@
         <v>20546</v>
       </c>
       <c r="B31">
-        <v>1.949791624252867</v>
+        <v>1.949374756498639</v>
       </c>
       <c r="C31">
-        <v>7.945193039656294</v>
+        <v>7.9444977566708</v>
       </c>
     </row>
     <row r="32">
@@ -713,10 +713,10 @@
         <v>20637</v>
       </c>
       <c r="B32">
-        <v>1.993677313777066</v>
+        <v>1.993251063210536</v>
       </c>
       <c r="C32">
-        <v>8.070358176200001</v>
+        <v>8.069651940026915</v>
       </c>
     </row>
     <row r="33">
@@ -724,10 +724,10 @@
         <v>20729</v>
       </c>
       <c r="B33">
-        <v>2.033951368776512</v>
+        <v>2.033516507569414</v>
       </c>
       <c r="C33">
-        <v>8.1534573387345</v>
+        <v>8.152743830562667</v>
       </c>
     </row>
     <row r="34">
@@ -735,10 +735,10 @@
         <v>20821</v>
       </c>
       <c r="B34">
-        <v>2.072842067260198</v>
+        <v>2.072398891175788</v>
       </c>
       <c r="C34">
-        <v>8.1577026480716</v>
+        <v>8.156988768393207</v>
       </c>
     </row>
     <row r="35">
@@ -746,10 +746,10 @@
         <v>20911</v>
       </c>
       <c r="B35">
-        <v>2.12154253243104</v>
+        <v>2.121088944129605</v>
       </c>
       <c r="C35">
-        <v>8.305624107715506</v>
+        <v>8.304897283446142</v>
       </c>
     </row>
     <row r="36">
@@ -757,10 +757,10 @@
         <v>21002</v>
       </c>
       <c r="B36">
-        <v>2.184635013989816</v>
+        <v>2.184167936441239</v>
       </c>
       <c r="C36">
-        <v>8.574990073239089</v>
+        <v>8.574239676783153</v>
       </c>
     </row>
     <row r="37">
@@ -768,10 +768,10 @@
         <v>21094</v>
       </c>
       <c r="B37">
-        <v>2.266023021810182</v>
+        <v>2.26553854340932</v>
       </c>
       <c r="C37">
-        <v>8.886616516435284</v>
+        <v>8.88583884958293</v>
       </c>
     </row>
     <row r="38">
@@ -779,10 +779,10 @@
         <v>21186</v>
       </c>
       <c r="B38">
-        <v>2.355468865360739</v>
+        <v>2.354965263332786</v>
       </c>
       <c r="C38">
-        <v>9.251375886241998</v>
+        <v>9.250566299336556</v>
       </c>
     </row>
     <row r="39">
@@ -790,10 +790,10 @@
         <v>21276</v>
       </c>
       <c r="B39">
-        <v>2.434804449856379</v>
+        <v>2.434283885786674</v>
       </c>
       <c r="C39">
-        <v>9.525322990215788</v>
+        <v>9.524489430228842</v>
       </c>
     </row>
     <row r="40">
@@ -801,10 +801,10 @@
         <v>21367</v>
       </c>
       <c r="B40">
-        <v>2.492905446975181</v>
+        <v>2.492372460843607</v>
       </c>
       <c r="C40">
-        <v>9.638468093328067</v>
+        <v>9.637624632025355</v>
       </c>
     </row>
     <row r="41">
@@ -812,10 +812,10 @@
         <v>21459</v>
       </c>
       <c r="B41">
-        <v>2.538865631273628</v>
+        <v>2.538322818800319</v>
       </c>
       <c r="C41">
-        <v>9.724514146186532</v>
+        <v>9.723663155003022</v>
       </c>
     </row>
     <row r="42">
@@ -823,10 +823,10 @@
         <v>21551</v>
       </c>
       <c r="B42">
-        <v>2.599069835718194</v>
+        <v>2.598514151514804</v>
       </c>
       <c r="C42">
-        <v>9.961150719302992</v>
+        <v>9.960279020078504</v>
       </c>
     </row>
     <row r="43">
@@ -834,10 +834,10 @@
         <v>21641</v>
       </c>
       <c r="B43">
-        <v>2.671639522115043</v>
+        <v>2.671068322426913</v>
       </c>
       <c r="C43">
-        <v>10.06015824166456</v>
+        <v>10.05927787830247</v>
       </c>
     </row>
     <row r="44">
@@ -845,10 +845,10 @@
         <v>21732</v>
       </c>
       <c r="B44">
-        <v>2.728485882509422</v>
+        <v>2.727902529002237</v>
       </c>
       <c r="C44">
-        <v>10.15608181555908</v>
+        <v>10.1551930579354</v>
       </c>
     </row>
     <row r="45">
@@ -856,10 +856,10 @@
         <v>21824</v>
       </c>
       <c r="B45">
-        <v>2.781423829381573</v>
+        <v>2.780829157678766</v>
       </c>
       <c r="C45">
-        <v>10.269881766055</v>
+        <v>10.26898304980993</v>
       </c>
     </row>
     <row r="46">
@@ -867,10 +867,10 @@
         <v>21916</v>
       </c>
       <c r="B46">
-        <v>2.831017439436182</v>
+        <v>2.830412164560918</v>
       </c>
       <c r="C46">
-        <v>10.33724554015297</v>
+        <v>10.3363409289113</v>
       </c>
     </row>
     <row r="47">
@@ -878,10 +878,10 @@
         <v>22007</v>
       </c>
       <c r="B47">
-        <v>2.885363406037659</v>
+        <v>2.88474651193049</v>
       </c>
       <c r="C47">
-        <v>10.40745630797778</v>
+        <v>10.40654555259939</v>
       </c>
     </row>
     <row r="48">
@@ -889,10 +889,10 @@
         <v>22098</v>
       </c>
       <c r="B48">
-        <v>2.954892179451783</v>
+        <v>2.954260420010664</v>
       </c>
       <c r="C48">
-        <v>10.46170845666849</v>
+        <v>10.46079295369043</v>
       </c>
     </row>
     <row r="49">
@@ -900,10 +900,10 @@
         <v>22190</v>
       </c>
       <c r="B49">
-        <v>3.040338690569386</v>
+        <v>3.039688662563179</v>
       </c>
       <c r="C49">
-        <v>10.51705585462654</v>
+        <v>10.51613550820365</v>
       </c>
     </row>
     <row r="50">
@@ -911,10 +911,10 @@
         <v>22282</v>
       </c>
       <c r="B50">
-        <v>3.118048033216849</v>
+        <v>3.117381390861319</v>
       </c>
       <c r="C50">
-        <v>10.56763134489545</v>
+        <v>10.56670657261687</v>
       </c>
     </row>
     <row r="51">
@@ -922,10 +922,10 @@
         <v>22372</v>
       </c>
       <c r="B51">
-        <v>3.21132168246687</v>
+        <v>3.210635098094866</v>
       </c>
       <c r="C51">
-        <v>10.68828054332242</v>
+        <v>10.6873452130455</v>
       </c>
     </row>
     <row r="52">
@@ -933,10 +933,10 @@
         <v>22463</v>
       </c>
       <c r="B52">
-        <v>3.301585061604905</v>
+        <v>3.300879178815736</v>
       </c>
       <c r="C52">
-        <v>10.77455794817107</v>
+        <v>10.77361506776777</v>
       </c>
     </row>
     <row r="53">
@@ -944,10 +944,10 @@
         <v>22555</v>
       </c>
       <c r="B53">
-        <v>3.394640979197081</v>
+        <v>3.393915200942724</v>
       </c>
       <c r="C53">
-        <v>10.88502606608427</v>
+        <v>10.88407351862789</v>
       </c>
     </row>
     <row r="54">
@@ -955,10 +955,10 @@
         <v>22647</v>
       </c>
       <c r="B54">
-        <v>3.491834129796813</v>
+        <v>3.491087571531959</v>
       </c>
       <c r="C54">
-        <v>11.04737551536341</v>
+        <v>11.04640876072424</v>
       </c>
     </row>
     <row r="55">
@@ -966,10 +966,10 @@
         <v>22737</v>
       </c>
       <c r="B55">
-        <v>3.571864382540409</v>
+        <v>3.57110071371291</v>
       </c>
       <c r="C55">
-        <v>11.17166937732403</v>
+        <v>11.17069174574241</v>
       </c>
     </row>
     <row r="56">
@@ -977,10 +977,10 @@
         <v>22828</v>
       </c>
       <c r="B56">
-        <v>3.653568778744253</v>
+        <v>3.652787641420259</v>
       </c>
       <c r="C56">
-        <v>11.24427300081591</v>
+        <v>11.24328901569904</v>
       </c>
     </row>
     <row r="57">
@@ -988,10 +988,10 @@
         <v>22920</v>
       </c>
       <c r="B57">
-        <v>3.746685225430934</v>
+        <v>3.74588417970056</v>
       </c>
       <c r="C57">
-        <v>11.32401392099226</v>
+        <v>11.32302295775607</v>
       </c>
     </row>
     <row r="58">
@@ -999,10 +999,10 @@
         <v>23012</v>
       </c>
       <c r="B58">
-        <v>3.862096635813455</v>
+        <v>3.861270914987107</v>
       </c>
       <c r="C58">
-        <v>11.36563714076275</v>
+        <v>11.36464253508308</v>
       </c>
     </row>
     <row r="59">
@@ -1010,10 +1010,10 @@
         <v>23102</v>
       </c>
       <c r="B59">
-        <v>3.965861066956082</v>
+        <v>3.965013161171688</v>
       </c>
       <c r="C59">
-        <v>11.66130568173131</v>
+        <v>11.66028520212954</v>
       </c>
     </row>
     <row r="60">
@@ -1021,10 +1021,10 @@
         <v>23193</v>
       </c>
       <c r="B60">
-        <v>4.063166791069586</v>
+        <v>4.062298081206346</v>
       </c>
       <c r="C60">
-        <v>11.89649959095105</v>
+        <v>11.89545852955566</v>
       </c>
     </row>
     <row r="61">
@@ -1032,10 +1032,10 @@
         <v>23285</v>
       </c>
       <c r="B61">
-        <v>4.15904612392118</v>
+        <v>4.158156914943232</v>
       </c>
       <c r="C61">
-        <v>11.98211533022152</v>
+        <v>11.98106677660202</v>
       </c>
     </row>
     <row r="62">
@@ -1043,10 +1043,10 @@
         <v>23377</v>
       </c>
       <c r="B62">
-        <v>4.248717517338582</v>
+        <v>4.247809136510716</v>
       </c>
       <c r="C62">
-        <v>11.99619140362959</v>
+        <v>11.99514161821443</v>
       </c>
     </row>
     <row r="63">
@@ -1054,10 +1054,10 @@
         <v>23468</v>
       </c>
       <c r="B63">
-        <v>4.338918585562451</v>
+        <v>4.337990919639566</v>
       </c>
       <c r="C63">
-        <v>12.06099027803879</v>
+        <v>12.05993482208112</v>
       </c>
     </row>
     <row r="64">
@@ -1065,10 +1065,10 @@
         <v>23559</v>
       </c>
       <c r="B64">
-        <v>4.415653125340159</v>
+        <v>4.414709053481958</v>
       </c>
       <c r="C64">
-        <v>12.15945498416243</v>
+        <v>12.15839091156896</v>
       </c>
     </row>
     <row r="65">
@@ -1076,10 +1076,10 @@
         <v>23651</v>
       </c>
       <c r="B65">
-        <v>4.50196657269828</v>
+        <v>4.501004046922998</v>
       </c>
       <c r="C65">
-        <v>12.24734521322103</v>
+        <v>12.2462734493631</v>
       </c>
     </row>
     <row r="66">
@@ -1087,10 +1087,10 @@
         <v>23743</v>
       </c>
       <c r="B66">
-        <v>4.575619877893095</v>
+        <v>4.574641604954091</v>
       </c>
       <c r="C66">
-        <v>12.33786779842889</v>
+        <v>12.33678811294929</v>
       </c>
     </row>
     <row r="67">
@@ -1098,10 +1098,10 @@
         <v>23833</v>
       </c>
       <c r="B67">
-        <v>4.654338152041156</v>
+        <v>4.653343049042082</v>
       </c>
       <c r="C67">
-        <v>12.38897629680067</v>
+        <v>12.3878921388219</v>
       </c>
     </row>
     <row r="68">
@@ -1109,10 +1109,10 @@
         <v>23924</v>
       </c>
       <c r="B68">
-        <v>4.726375990128457</v>
+        <v>4.72536548535444</v>
       </c>
       <c r="C68">
-        <v>12.44336782616336</v>
+        <v>12.44227890838772</v>
       </c>
     </row>
     <row r="69">
@@ -1120,10 +1120,10 @@
         <v>24016</v>
       </c>
       <c r="B69">
-        <v>4.800446091650216</v>
+        <v>4.799419750600931</v>
       </c>
       <c r="C69">
-        <v>12.55773921629914</v>
+        <v>12.55664028989549</v>
       </c>
     </row>
     <row r="70">
@@ -1131,10 +1131,10 @@
         <v>24108</v>
       </c>
       <c r="B70">
-        <v>4.86633427625975</v>
+        <v>4.865293848238705</v>
       </c>
       <c r="C70">
-        <v>12.70413326388141</v>
+        <v>12.70302152655046</v>
       </c>
     </row>
     <row r="71">
@@ -1142,10 +1142,10 @@
         <v>24198</v>
       </c>
       <c r="B71">
-        <v>4.942828992283081</v>
+        <v>4.941772209601321</v>
       </c>
       <c r="C71">
-        <v>12.7458598709686</v>
+        <v>12.74474448214676</v>
       </c>
     </row>
     <row r="72">
@@ -1153,10 +1153,10 @@
         <v>24289</v>
       </c>
       <c r="B72">
-        <v>5.021912575314098</v>
+        <v>5.020838884468796</v>
       </c>
       <c r="C72">
-        <v>12.84535052734764</v>
+        <v>12.8442264321092</v>
       </c>
     </row>
     <row r="73">
@@ -1164,10 +1164,10 @@
         <v>24381</v>
       </c>
       <c r="B73">
-        <v>5.116221172739023</v>
+        <v>5.115127318604104</v>
       </c>
       <c r="C73">
-        <v>12.91810751253807</v>
+        <v>12.91697705034371</v>
       </c>
     </row>
     <row r="74">
@@ -1175,10 +1175,10 @@
         <v>24473</v>
       </c>
       <c r="B74">
-        <v>5.228407609498873</v>
+        <v>5.227289769771152</v>
       </c>
       <c r="C74">
-        <v>13.05241876596684</v>
+        <v>13.05127655020918</v>
       </c>
     </row>
     <row r="75">
@@ -1186,10 +1186,10 @@
         <v>24563</v>
       </c>
       <c r="B75">
-        <v>5.302519694720145</v>
+        <v>5.301386009740992</v>
       </c>
       <c r="C75">
-        <v>13.1358732676669</v>
+        <v>13.1347237488148</v>
       </c>
     </row>
     <row r="76">
@@ -1197,10 +1197,10 @@
         <v>24654</v>
       </c>
       <c r="B76">
-        <v>5.388085165609707</v>
+        <v>5.386933186631726</v>
       </c>
       <c r="C76">
-        <v>13.23001567686384</v>
+        <v>13.22885791961967</v>
       </c>
     </row>
     <row r="77">
@@ -1208,10 +1208,10 @@
         <v>24746</v>
       </c>
       <c r="B77">
-        <v>5.493938632502063</v>
+        <v>5.492764021927727</v>
       </c>
       <c r="C77">
-        <v>13.37886873319566</v>
+        <v>13.3776979498366</v>
       </c>
     </row>
     <row r="78">
@@ -1219,10 +1219,10 @@
         <v>24838</v>
       </c>
       <c r="B78">
-        <v>5.666407434000568</v>
+        <v>5.665195949392586</v>
       </c>
       <c r="C78">
-        <v>13.59624658602008</v>
+        <v>13.59505677994858</v>
       </c>
     </row>
     <row r="79">
@@ -1230,10 +1230,10 @@
         <v>24929</v>
       </c>
       <c r="B79">
-        <v>5.682900904755057</v>
+        <v>5.681685893823528</v>
       </c>
       <c r="C79">
-        <v>13.64692327243237</v>
+        <v>13.64572903164951</v>
       </c>
     </row>
     <row r="80">
@@ -1241,10 +1241,10 @@
         <v>25020</v>
       </c>
       <c r="B80">
-        <v>6.213966825969348</v>
+        <v>6.21263827251606</v>
       </c>
       <c r="C80">
-        <v>13.98801920463378</v>
+        <v>13.9867951145827</v>
       </c>
     </row>
     <row r="81">
@@ -1252,10 +1252,10 @@
         <v>25112</v>
       </c>
       <c r="B81">
-        <v>6.35739087585277</v>
+        <v>6.356031658168066</v>
       </c>
       <c r="C81">
-        <v>14.19384594038035</v>
+        <v>14.19260383845384</v>
       </c>
     </row>
     <row r="82">
@@ -1263,10 +1263,10 @@
         <v>25204</v>
       </c>
       <c r="B82">
-        <v>6.449058613037094</v>
+        <v>6.447679796681814</v>
       </c>
       <c r="C82">
-        <v>14.56357471037665</v>
+        <v>14.56230025352537</v>
       </c>
     </row>
     <row r="83">
@@ -1274,10 +1274,10 @@
         <v>25294</v>
       </c>
       <c r="B83">
-        <v>6.584889195176362</v>
+        <v>6.583481338082048</v>
       </c>
       <c r="C83">
-        <v>14.73559301692885</v>
+        <v>14.73430350677413</v>
       </c>
     </row>
     <row r="84">
@@ -1285,10 +1285,10 @@
         <v>25385</v>
       </c>
       <c r="B84">
-        <v>6.737961542647204</v>
+        <v>6.736520958504046</v>
       </c>
       <c r="C84">
-        <v>14.92454612287383</v>
+        <v>14.9232400774532</v>
       </c>
     </row>
     <row r="85">
@@ -1296,10 +1296,10 @@
         <v>25477</v>
       </c>
       <c r="B85">
-        <v>6.94777611266849</v>
+        <v>6.946290669922226</v>
       </c>
       <c r="C85">
-        <v>15.15220112548547</v>
+        <v>15.15087515800013</v>
       </c>
     </row>
     <row r="86">
@@ -1307,10 +1307,10 @@
         <v>25569</v>
       </c>
       <c r="B86">
-        <v>7.170757738866396</v>
+        <v>7.169224622384849</v>
       </c>
       <c r="C86">
-        <v>15.27575582862307</v>
+        <v>15.27441904887899</v>
       </c>
     </row>
     <row r="87">
@@ -1318,10 +1318,10 @@
         <v>25659</v>
       </c>
       <c r="B87">
-        <v>7.350596992433228</v>
+        <v>7.349025426106672</v>
       </c>
       <c r="C87">
-        <v>15.49136634714996</v>
+        <v>15.49001069935268</v>
       </c>
     </row>
     <row r="88">
@@ -1329,10 +1329,10 @@
         <v>25750</v>
       </c>
       <c r="B88">
-        <v>7.532427021471437</v>
+        <v>7.530816579669721</v>
       </c>
       <c r="C88">
-        <v>15.70553104558781</v>
+        <v>15.70415665626088</v>
       </c>
     </row>
     <row r="89">
@@ -1340,10 +1340,10 @@
         <v>25842</v>
       </c>
       <c r="B89">
-        <v>7.751716408532586</v>
+        <v>7.750059082400681</v>
       </c>
       <c r="C89">
-        <v>15.85679023948331</v>
+        <v>15.85540261348064</v>
       </c>
     </row>
     <row r="90">
@@ -1351,10 +1351,10 @@
         <v>25934</v>
       </c>
       <c r="B90">
-        <v>7.996838502563644</v>
+        <v>7.995128769038261</v>
       </c>
       <c r="C90">
-        <v>16.09171942390587</v>
+        <v>16.09031123927562</v>
       </c>
     </row>
     <row r="91">
@@ -1362,10 +1362,10 @@
         <v>26024</v>
       </c>
       <c r="B91">
-        <v>8.184516603150083</v>
+        <v>8.18276674382493</v>
       </c>
       <c r="C91">
-        <v>16.36769989181469</v>
+        <v>16.36626755616349</v>
       </c>
     </row>
     <row r="92">
@@ -1373,10 +1373,10 @@
         <v>26115</v>
       </c>
       <c r="B92">
-        <v>8.416512558811212</v>
+        <v>8.414713098476481</v>
       </c>
       <c r="C92">
-        <v>16.5643082060872</v>
+        <v>16.56285866526363</v>
       </c>
     </row>
     <row r="93">
@@ -1384,10 +1384,10 @@
         <v>26207</v>
       </c>
       <c r="B93">
-        <v>8.655181670778935</v>
+        <v>8.653331182705921</v>
       </c>
       <c r="C93">
-        <v>16.81710902253934</v>
+        <v>16.81563735914359</v>
       </c>
     </row>
     <row r="94">
@@ -1395,10 +1395,10 @@
         <v>26299</v>
       </c>
       <c r="B94">
-        <v>8.820476545945668</v>
+        <v>8.818590717632938</v>
       </c>
       <c r="C94">
-        <v>17.01423348166939</v>
+        <v>17.01274456793351</v>
       </c>
     </row>
     <row r="95">
@@ -1406,10 +1406,10 @@
         <v>26390</v>
       </c>
       <c r="B95">
-        <v>9.047853881514333</v>
+        <v>9.045919439658464</v>
       </c>
       <c r="C95">
-        <v>17.26052978604763</v>
+        <v>17.25901931894873</v>
       </c>
     </row>
     <row r="96">
@@ -1417,10 +1417,10 @@
         <v>26481</v>
       </c>
       <c r="B96">
-        <v>9.285192103371745</v>
+        <v>9.28320691832347</v>
       </c>
       <c r="C96">
-        <v>17.56811587763178</v>
+        <v>17.56657849370719</v>
       </c>
     </row>
     <row r="97">
@@ -1428,10 +1428,10 @@
         <v>26573</v>
       </c>
       <c r="B97">
-        <v>9.591537981651394</v>
+        <v>9.589487299492193</v>
       </c>
       <c r="C97">
-        <v>17.86725932371264</v>
+        <v>17.86569576177736</v>
       </c>
     </row>
     <row r="98">
@@ -1439,10 +1439,10 @@
         <v>26665</v>
       </c>
       <c r="B98">
-        <v>9.886689388326818</v>
+        <v>9.884575602447956</v>
       </c>
       <c r="C98">
-        <v>18.03006448746099</v>
+        <v>18.02848667846341</v>
       </c>
     </row>
     <row r="99">
@@ -1450,10 +1450,10 @@
         <v>26755</v>
       </c>
       <c r="B99">
-        <v>10.19696132458651</v>
+        <v>10.19478120220089</v>
       </c>
       <c r="C99">
-        <v>18.38822586789896</v>
+        <v>18.38661671623763</v>
       </c>
     </row>
     <row r="100">
@@ -1461,10 +1461,10 @@
         <v>26846</v>
       </c>
       <c r="B100">
-        <v>10.56919011701794</v>
+        <v>10.56693041167646</v>
       </c>
       <c r="C100">
-        <v>18.9050567513966</v>
+        <v>18.90340237192042</v>
       </c>
     </row>
     <row r="101">
@@ -1472,10 +1472,10 @@
         <v>26938</v>
       </c>
       <c r="B101">
-        <v>10.9319091783164</v>
+        <v>10.92957192321082</v>
       </c>
       <c r="C101">
-        <v>19.44273840734724</v>
+        <v>19.44103697540738</v>
       </c>
     </row>
     <row r="102">
@@ -1483,10 +1483,10 @@
         <v>27030</v>
       </c>
       <c r="B102">
-        <v>11.41150022722516</v>
+        <v>11.40906043498637</v>
       </c>
       <c r="C102">
-        <v>20.28565318682989</v>
+        <v>20.28387799150864</v>
       </c>
     </row>
     <row r="103">
@@ -1494,10 +1494,10 @@
         <v>27120</v>
       </c>
       <c r="B103">
-        <v>11.94703605946598</v>
+        <v>11.94448176903317</v>
       </c>
       <c r="C103">
-        <v>21.09977169110311</v>
+        <v>21.09792525235941</v>
       </c>
     </row>
     <row r="104">
@@ -1505,10 +1505,10 @@
         <v>27211</v>
       </c>
       <c r="B104">
-        <v>12.53946112596147</v>
+        <v>12.5367801743491</v>
       </c>
       <c r="C104">
-        <v>21.78290008735794</v>
+        <v>21.780993868122</v>
       </c>
     </row>
     <row r="105">
@@ -1516,10 +1516,10 @@
         <v>27303</v>
       </c>
       <c r="B105">
-        <v>12.99073919057003</v>
+        <v>12.98796175517396</v>
       </c>
       <c r="C105">
-        <v>22.40269222206126</v>
+        <v>22.4007317648825</v>
       </c>
     </row>
     <row r="106">
@@ -1527,10 +1527,10 @@
         <v>27395</v>
       </c>
       <c r="B106">
-        <v>13.66533770898504</v>
+        <v>13.66241604362826</v>
       </c>
       <c r="C106">
-        <v>23.05820080406525</v>
+        <v>23.05618298340121</v>
       </c>
     </row>
     <row r="107">
@@ -1538,10 +1538,10 @@
         <v>27485</v>
       </c>
       <c r="B107">
-        <v>14.25868851523567</v>
+        <v>14.25563999077507</v>
       </c>
       <c r="C107">
-        <v>23.65214438569514</v>
+        <v>23.65007458909237</v>
       </c>
     </row>
     <row r="108">
@@ -1549,10 +1549,10 @@
         <v>27576</v>
       </c>
       <c r="B108">
-        <v>14.74400808387992</v>
+        <v>14.74085579752183</v>
       </c>
       <c r="C108">
-        <v>24.14965148048112</v>
+        <v>24.14753814708618</v>
       </c>
     </row>
     <row r="109">
@@ -1560,10 +1560,10 @@
         <v>27668</v>
       </c>
       <c r="B109">
-        <v>15.22009584129354</v>
+        <v>15.2168417668101</v>
       </c>
       <c r="C109">
-        <v>24.65043239487376</v>
+        <v>24.64827523819504</v>
       </c>
     </row>
     <row r="110">
@@ -1571,10 +1571,10 @@
         <v>27760</v>
       </c>
       <c r="B110">
-        <v>15.749653025414</v>
+        <v>15.74628573097857</v>
       </c>
       <c r="C110">
-        <v>25.28240168894184</v>
+        <v>25.2801892286984</v>
       </c>
     </row>
     <row r="111">
@@ -1582,10 +1582,10 @@
         <v>27851</v>
       </c>
       <c r="B111">
-        <v>16.31476480739235</v>
+        <v>16.31127669138988</v>
       </c>
       <c r="C111">
-        <v>25.83440006028152</v>
+        <v>25.83213929472018</v>
       </c>
     </row>
     <row r="112">
@@ -1593,10 +1593,10 @@
         <v>27942</v>
       </c>
       <c r="B112">
-        <v>16.8658812416606</v>
+        <v>16.86227529631298</v>
       </c>
       <c r="C112">
-        <v>26.45065473350583</v>
+        <v>26.44834003956452</v>
       </c>
     </row>
     <row r="113">
@@ -1604,10 +1604,10 @@
         <v>28034</v>
       </c>
       <c r="B113">
-        <v>17.39760633524319</v>
+        <v>17.39388670644198</v>
       </c>
       <c r="C113">
-        <v>27.12377260249794</v>
+        <v>27.12139900408457</v>
       </c>
     </row>
     <row r="114">
@@ -1615,10 +1615,10 @@
         <v>28126</v>
       </c>
       <c r="B114">
-        <v>17.87655507400672</v>
+        <v>17.87273304539897</v>
       </c>
       <c r="C114">
-        <v>27.60264760215997</v>
+        <v>27.60023209744705</v>
       </c>
     </row>
     <row r="115">
@@ -1626,10 +1626,10 @@
         <v>28216</v>
       </c>
       <c r="B115">
-        <v>18.27197339925619</v>
+        <v>18.26806682974305</v>
       </c>
       <c r="C115">
-        <v>28.38312478814193</v>
+        <v>28.38064098395468</v>
       </c>
     </row>
     <row r="116">
@@ -1637,10 +1637,10 @@
         <v>28307</v>
       </c>
       <c r="B116">
-        <v>18.76021814208847</v>
+        <v>18.75620718527213</v>
       </c>
       <c r="C116">
-        <v>29.00061093588652</v>
+        <v>28.99807309555312</v>
       </c>
     </row>
     <row r="117">
@@ -1648,10 +1648,10 @@
         <v>28399</v>
       </c>
       <c r="B117">
-        <v>19.32181042174742</v>
+        <v>19.3176793958378</v>
       </c>
       <c r="C117">
-        <v>29.48936144331465</v>
+        <v>29.4867808324771</v>
       </c>
     </row>
     <row r="118">
@@ -1659,10 +1659,10 @@
         <v>28491</v>
       </c>
       <c r="B118">
-        <v>19.84171742483065</v>
+        <v>19.83747524218916</v>
       </c>
       <c r="C118">
-        <v>29.9282320784226</v>
+        <v>29.92561306206313</v>
       </c>
     </row>
     <row r="119">
@@ -1670,10 +1670,10 @@
         <v>28581</v>
       </c>
       <c r="B119">
-        <v>20.43427867273889</v>
+        <v>20.42990979980209</v>
       </c>
       <c r="C119">
-        <v>30.66568365023039</v>
+        <v>30.66300009956345</v>
       </c>
     </row>
     <row r="120">
@@ -1681,10 +1681,10 @@
         <v>28672</v>
       </c>
       <c r="B120">
-        <v>21.07275641098577</v>
+        <v>21.06825103075375</v>
       </c>
       <c r="C120">
-        <v>31.54277392390729</v>
+        <v>31.54001361916515</v>
       </c>
     </row>
     <row r="121">
@@ -1692,10 +1692,10 @@
         <v>28764</v>
       </c>
       <c r="B121">
-        <v>21.66899018676969</v>
+        <v>21.66435733105157</v>
       </c>
       <c r="C121">
-        <v>32.27963092537621</v>
+        <v>32.27680613835739</v>
       </c>
     </row>
     <row r="122">
@@ -1703,10 +1703,10 @@
         <v>28856</v>
       </c>
       <c r="B122">
-        <v>22.28006915733353</v>
+        <v>22.27530565220911</v>
       </c>
       <c r="C122">
-        <v>33.01999028417445</v>
+        <v>33.01710070838804</v>
       </c>
     </row>
     <row r="123">
@@ -1714,10 +1714,10 @@
         <v>28946</v>
       </c>
       <c r="B123">
-        <v>23.03717948838746</v>
+        <v>23.03225411217924</v>
       </c>
       <c r="C123">
-        <v>33.92023724996606</v>
+        <v>33.91726889366483</v>
       </c>
     </row>
     <row r="124">
@@ -1725,10 +1725,10 @@
         <v>29037</v>
       </c>
       <c r="B124">
-        <v>23.78931969407473</v>
+        <v>23.78423350940137</v>
       </c>
       <c r="C124">
-        <v>35.09265198710481</v>
+        <v>35.08958103291644</v>
       </c>
     </row>
     <row r="125">
@@ -1736,10 +1736,10 @@
         <v>29129</v>
       </c>
       <c r="B125">
-        <v>24.65563351589065</v>
+        <v>24.65036211229808</v>
       </c>
       <c r="C125">
-        <v>35.98506931700424</v>
+        <v>35.98192026747164</v>
       </c>
     </row>
     <row r="126">
@@ -1747,10 +1747,10 @@
         <v>29221</v>
       </c>
       <c r="B126">
-        <v>25.48137101434784</v>
+        <v>25.47592306710194</v>
       </c>
       <c r="C126">
-        <v>37.33759769230829</v>
+        <v>37.33408590535932</v>
       </c>
     </row>
     <row r="127">
@@ -1758,10 +1758,10 @@
         <v>29312</v>
       </c>
       <c r="B127">
-        <v>26.42998591557635</v>
+        <v>26.42433515334316</v>
       </c>
       <c r="C127">
-        <v>38.43150195678975</v>
+        <v>38.42916062794775</v>
       </c>
     </row>
     <row r="128">
@@ -1769,10 +1769,10 @@
         <v>29403</v>
       </c>
       <c r="B128">
-        <v>27.3126258430614</v>
+        <v>27.30736599791774</v>
       </c>
       <c r="C128">
-        <v>39.57609208029135</v>
+        <v>39.57210896173811</v>
       </c>
     </row>
     <row r="129">
@@ -1780,10 +1780,10 @@
         <v>29495</v>
       </c>
       <c r="B129">
-        <v>28.1154048494763</v>
+        <v>28.1093937426826</v>
       </c>
       <c r="C129">
-        <v>40.76886217431261</v>
+        <v>40.76506785877795</v>
       </c>
     </row>
     <row r="130">
@@ -1791,10 +1791,10 @@
         <v>29587</v>
       </c>
       <c r="B130">
-        <v>28.92175388488661</v>
+        <v>28.91498993226168</v>
       </c>
       <c r="C130">
-        <v>42.13493577417242</v>
+        <v>42.13068643183726</v>
       </c>
     </row>
     <row r="131">
@@ -1802,10 +1802,10 @@
         <v>29677</v>
       </c>
       <c r="B131">
-        <v>29.91607328538319</v>
+        <v>29.90967719354922</v>
       </c>
       <c r="C131">
-        <v>43.45068359963841</v>
+        <v>43.44745145233906</v>
       </c>
     </row>
     <row r="132">
@@ -1813,10 +1813,10 @@
         <v>29768</v>
       </c>
       <c r="B132">
-        <v>31.02360144822828</v>
+        <v>31.01638345014097</v>
       </c>
       <c r="C132">
-        <v>45.15767317074446</v>
+        <v>45.15426056563937</v>
       </c>
     </row>
     <row r="133">
@@ -1824,10 +1824,10 @@
         <v>29860</v>
       </c>
       <c r="B133">
-        <v>32.25279181867326</v>
+        <v>32.24706700860489</v>
       </c>
       <c r="C133">
-        <v>46.57594071372603</v>
+        <v>46.57179189715635</v>
       </c>
     </row>
     <row r="134">
@@ -1835,10 +1835,10 @@
         <v>29952</v>
       </c>
       <c r="B134">
-        <v>33.59463471271745</v>
+        <v>33.58979048852323</v>
       </c>
       <c r="C134">
-        <v>47.89458482987693</v>
+        <v>47.8906361901678</v>
       </c>
     </row>
     <row r="135">
@@ -1846,10 +1846,10 @@
         <v>30042</v>
       </c>
       <c r="B135">
-        <v>34.47653687743286</v>
+        <v>34.47033317047819</v>
       </c>
       <c r="C135">
-        <v>49.24003526590838</v>
+        <v>49.23638405033823</v>
       </c>
     </row>
     <row r="136">
@@ -1857,10 +1857,10 @@
         <v>30133</v>
       </c>
       <c r="B136">
-        <v>35.07146341837598</v>
+        <v>35.0627996982831</v>
       </c>
       <c r="C136">
-        <v>50.03916268663499</v>
+        <v>50.03485695347655</v>
       </c>
     </row>
     <row r="137">
@@ -1868,10 +1868,10 @@
         <v>30225</v>
       </c>
       <c r="B137">
-        <v>35.79231644136512</v>
+        <v>35.78233241156454</v>
       </c>
       <c r="C137">
-        <v>51.0527226110736</v>
+        <v>51.04860818472145</v>
       </c>
     </row>
     <row r="138">
@@ -1879,10 +1879,10 @@
         <v>30317</v>
       </c>
       <c r="B138">
-        <v>36.85694161021214</v>
+        <v>36.84964538327409</v>
       </c>
       <c r="C138">
-        <v>52.40608533642133</v>
+        <v>52.40168148524238</v>
       </c>
     </row>
     <row r="139">
@@ -1890,10 +1890,10 @@
         <v>30407</v>
       </c>
       <c r="B139">
-        <v>37.60028511370363</v>
+        <v>37.59341649710528</v>
       </c>
       <c r="C139">
-        <v>53.79080866455478</v>
+        <v>53.78651940527303</v>
       </c>
     </row>
     <row r="140">
@@ -1901,10 +1901,10 @@
         <v>30498</v>
       </c>
       <c r="B140">
-        <v>38.58396740401272</v>
+        <v>38.57546497967667</v>
       </c>
       <c r="C140">
-        <v>54.96637101105529</v>
+        <v>54.96115364593115</v>
       </c>
     </row>
     <row r="141">
@@ -1912,10 +1912,10 @@
         <v>30590</v>
       </c>
       <c r="B141">
-        <v>39.43663431128036</v>
+        <v>39.4270276100861</v>
       </c>
       <c r="C141">
-        <v>56.0933678396291</v>
+        <v>56.08766595561868</v>
       </c>
     </row>
     <row r="142">
@@ -1923,10 +1923,10 @@
         <v>30682</v>
       </c>
       <c r="B142">
-        <v>40.21716754945108</v>
+        <v>40.20856907148593</v>
       </c>
       <c r="C142">
-        <v>57.15787544086481</v>
+        <v>57.15331984076333</v>
       </c>
     </row>
     <row r="143">
@@ -1934,10 +1934,10 @@
         <v>30773</v>
       </c>
       <c r="B143">
-        <v>41.14879611919137</v>
+        <v>41.14118312688181</v>
       </c>
       <c r="C143">
-        <v>58.09200523227659</v>
+        <v>58.08785342692298</v>
       </c>
     </row>
     <row r="144">
@@ -1945,10 +1945,10 @@
         <v>30864</v>
       </c>
       <c r="B144">
-        <v>41.40580970450238</v>
+        <v>41.39576786743835</v>
       </c>
       <c r="C144">
-        <v>59.09726290648647</v>
+        <v>59.09158969894563</v>
       </c>
     </row>
     <row r="145">
@@ -1956,10 +1956,10 @@
         <v>30956</v>
       </c>
       <c r="B145">
-        <v>42.3526824333197</v>
+        <v>42.34303064603712</v>
       </c>
       <c r="C145">
-        <v>60.08313631206514</v>
+        <v>60.07629145323109</v>
       </c>
     </row>
     <row r="146">
@@ -1967,10 +1967,10 @@
         <v>31048</v>
       </c>
       <c r="B146">
-        <v>43.11332552863265</v>
+        <v>43.10530500209852</v>
       </c>
       <c r="C146">
-        <v>61.04101471978073</v>
+        <v>61.03493193873406</v>
       </c>
     </row>
     <row r="147">
@@ -1978,10 +1978,10 @@
         <v>31138</v>
       </c>
       <c r="B147">
-        <v>43.77627089416035</v>
+        <v>43.76691147569267</v>
       </c>
       <c r="C147">
-        <v>62.04712710776796</v>
+        <v>62.04199067299718</v>
       </c>
     </row>
     <row r="148">
@@ -1989,10 +1989,10 @@
         <v>31229</v>
       </c>
       <c r="B148">
-        <v>44.29348083150445</v>
+        <v>44.28281124439287</v>
       </c>
       <c r="C148">
-        <v>62.67297877313824</v>
+        <v>62.66775349213435</v>
       </c>
     </row>
     <row r="149">
@@ -2000,10 +2000,10 @@
         <v>31321</v>
       </c>
       <c r="B149">
-        <v>44.82431519169855</v>
+        <v>44.81413231627105</v>
       </c>
       <c r="C149">
-        <v>63.15741565327828</v>
+        <v>63.15188875465011</v>
       </c>
     </row>
     <row r="150">
@@ -2011,10 +2011,10 @@
         <v>31413</v>
       </c>
       <c r="B150">
-        <v>45.13163134722252</v>
+        <v>45.12078480513704</v>
       </c>
       <c r="C150">
-        <v>63.31231079487506</v>
+        <v>63.30660711815423</v>
       </c>
     </row>
     <row r="151">
@@ -2022,10 +2022,10 @@
         <v>31503</v>
       </c>
       <c r="B151">
-        <v>45.90397882164822</v>
+        <v>45.89237170922252</v>
       </c>
       <c r="C151">
-        <v>63.64226734579579</v>
+        <v>63.63612468327151</v>
       </c>
     </row>
     <row r="152">
@@ -2033,10 +2033,10 @@
         <v>31594</v>
       </c>
       <c r="B152">
-        <v>45.94646089254596</v>
+        <v>45.93723383225557</v>
       </c>
       <c r="C152">
-        <v>63.99842976975236</v>
+        <v>63.99299714394193</v>
       </c>
     </row>
     <row r="153">
@@ -2044,10 +2044,10 @@
         <v>31686</v>
       </c>
       <c r="B153">
-        <v>46.23738172651277</v>
+        <v>46.22868754995207</v>
       </c>
       <c r="C153">
-        <v>64.59473676787752</v>
+        <v>64.58945555578957</v>
       </c>
     </row>
     <row r="154">
@@ -2055,10 +2055,10 @@
         <v>31778</v>
       </c>
       <c r="B154">
-        <v>47.07030564897711</v>
+        <v>47.06083662247611</v>
       </c>
       <c r="C154">
-        <v>65.12836233076757</v>
+        <v>65.12266295480835</v>
       </c>
     </row>
     <row r="155">
@@ -2066,10 +2066,10 @@
         <v>31868</v>
       </c>
       <c r="B155">
-        <v>47.28908811072836</v>
+        <v>47.27897764778707</v>
       </c>
       <c r="C155">
-        <v>65.59837685883969</v>
+        <v>65.59281814184284</v>
       </c>
     </row>
     <row r="156">
@@ -2077,10 +2077,10 @@
         <v>31959</v>
       </c>
       <c r="B156">
-        <v>47.78260382585723</v>
+        <v>47.77238784867263</v>
       </c>
       <c r="C156">
-        <v>65.99823562741534</v>
+        <v>65.9920892410086</v>
       </c>
     </row>
     <row r="157">
@@ -2088,10 +2088,10 @@
         <v>32051</v>
       </c>
       <c r="B157">
-        <v>48.3373317790189</v>
+        <v>48.32699720034213</v>
       </c>
       <c r="C157">
-        <v>66.35735230492867</v>
+        <v>66.35154538018942</v>
       </c>
     </row>
     <row r="158">
@@ -2099,10 +2099,10 @@
         <v>32143</v>
       </c>
       <c r="B158">
-        <v>48.94902947697425</v>
+        <v>48.93856411660654</v>
       </c>
       <c r="C158">
-        <v>66.72385881507844</v>
+        <v>66.71691460447602</v>
       </c>
     </row>
     <row r="159">
@@ -2110,10 +2110,10 @@
         <v>32234</v>
       </c>
       <c r="B159">
-        <v>49.31643476778804</v>
+        <v>49.30589085573482</v>
       </c>
       <c r="C159">
-        <v>67.17431356152257</v>
+        <v>67.1680662858722</v>
       </c>
     </row>
     <row r="160">
@@ -2121,10 +2121,10 @@
         <v>32325</v>
       </c>
       <c r="B160">
-        <v>49.91448215895342</v>
+        <v>49.90322859821287</v>
       </c>
       <c r="C160">
-        <v>67.79160756961586</v>
+        <v>67.78657837259261</v>
       </c>
     </row>
     <row r="161">
@@ -2132,10 +2132,10 @@
         <v>32417</v>
       </c>
       <c r="B161">
-        <v>50.44931485751378</v>
+        <v>50.43968502441876</v>
       </c>
       <c r="C161">
-        <v>68.41391971672677</v>
+        <v>68.40756521330896</v>
       </c>
     </row>
     <row r="162">
@@ -2143,10 +2143,10 @@
         <v>32509</v>
       </c>
       <c r="B162">
-        <v>51.04295350900848</v>
+        <v>51.03548369039225</v>
       </c>
       <c r="C162">
-        <v>69.13132746095333</v>
+        <v>69.12543624318832</v>
       </c>
     </row>
     <row r="163">
@@ -2154,10 +2154,10 @@
         <v>32599</v>
       </c>
       <c r="B163">
-        <v>51.72429322447941</v>
+        <v>51.71494718956409</v>
       </c>
       <c r="C163">
-        <v>69.88731843728408</v>
+        <v>69.88083200295905</v>
       </c>
     </row>
     <row r="164">
@@ -2165,10 +2165,10 @@
         <v>32690</v>
       </c>
       <c r="B164">
-        <v>52.18232211593512</v>
+        <v>52.1677476261511</v>
       </c>
       <c r="C164">
-        <v>70.40858674063428</v>
+        <v>70.4022757815779</v>
       </c>
     </row>
     <row r="165">
@@ -2176,10 +2176,10 @@
         <v>32782</v>
       </c>
       <c r="B165">
-        <v>53.05983364498865</v>
+        <v>53.04622818249481</v>
       </c>
       <c r="C165">
-        <v>71.0008671144107</v>
+        <v>70.99391269502136</v>
       </c>
     </row>
     <row r="166">
@@ -2187,10 +2187,10 @@
         <v>32874</v>
       </c>
       <c r="B166">
-        <v>53.70527588958495</v>
+        <v>53.68985404841013</v>
       </c>
       <c r="C166">
-        <v>71.35611115602332</v>
+        <v>71.34992509531467</v>
       </c>
     </row>
     <row r="167">
@@ -2198,10 +2198,10 @@
         <v>32964</v>
       </c>
       <c r="B167">
-        <v>54.57600307706848</v>
+        <v>54.563772126781</v>
       </c>
       <c r="C167">
-        <v>71.78815104639689</v>
+        <v>71.78168034951807</v>
       </c>
     </row>
     <row r="168">
@@ -2209,10 +2209,10 @@
         <v>33055</v>
       </c>
       <c r="B168">
-        <v>55.29200039501195</v>
+        <v>55.28242672417598</v>
       </c>
       <c r="C168">
-        <v>72.34031784548137</v>
+        <v>72.33375180932406</v>
       </c>
     </row>
     <row r="169">
@@ -2220,10 +2220,10 @@
         <v>33147</v>
       </c>
       <c r="B169">
-        <v>55.89916761277917</v>
+        <v>55.88946336567828</v>
       </c>
       <c r="C169">
-        <v>72.95801120944552</v>
+        <v>72.95149390605218</v>
       </c>
     </row>
     <row r="170">
@@ -2231,10 +2231,10 @@
         <v>33239</v>
       </c>
       <c r="B170">
-        <v>56.07842372320205</v>
+        <v>56.06867849791826</v>
       </c>
       <c r="C170">
-        <v>73.29003383815747</v>
+        <v>73.2835072791531</v>
       </c>
     </row>
     <row r="171">
@@ -2242,10 +2242,10 @@
         <v>33329</v>
       </c>
       <c r="B171">
-        <v>57.01581949702808</v>
+        <v>57.00475322522855</v>
       </c>
       <c r="C171">
-        <v>73.68255051133491</v>
+        <v>73.67571544581146</v>
       </c>
     </row>
     <row r="172">
@@ -2253,10 +2253,10 @@
         <v>33420</v>
       </c>
       <c r="B172">
-        <v>57.434318455178</v>
+        <v>57.42147560985129</v>
       </c>
       <c r="C172">
-        <v>74.31551470262988</v>
+        <v>74.30913727914692</v>
       </c>
     </row>
     <row r="173">
@@ -2264,10 +2264,10 @@
         <v>33512</v>
       </c>
       <c r="B173">
-        <v>58.34680160718112</v>
+        <v>58.33150282366962</v>
       </c>
       <c r="C173">
-        <v>74.9941568822485</v>
+        <v>74.9883593116855</v>
       </c>
     </row>
     <row r="174">
@@ -2275,10 +2275,10 @@
         <v>33604</v>
       </c>
       <c r="B174">
-        <v>59.15621891423191</v>
+        <v>59.13960343723092</v>
       </c>
       <c r="C174">
-        <v>75.37271293021951</v>
+        <v>75.36611707224485</v>
       </c>
     </row>
     <row r="175">
@@ -2286,10 +2286,10 @@
         <v>33695</v>
       </c>
       <c r="B175">
-        <v>59.33694957698774</v>
+        <v>59.32369479281119</v>
       </c>
       <c r="C175">
-        <v>75.8279356452106</v>
+        <v>75.8214509759249</v>
       </c>
     </row>
     <row r="176">
@@ -2297,10 +2297,10 @@
         <v>33786</v>
       </c>
       <c r="B176">
-        <v>59.94341762962737</v>
+        <v>59.93288359651095</v>
       </c>
       <c r="C176">
-        <v>76.17636437838672</v>
+        <v>76.16981315619707</v>
       </c>
     </row>
     <row r="177">
@@ -2308,10 +2308,10 @@
         <v>33878</v>
       </c>
       <c r="B177">
-        <v>60.50471562945911</v>
+        <v>60.49465094049972</v>
       </c>
       <c r="C177">
-        <v>76.40608897416735</v>
+        <v>76.39874730015815</v>
       </c>
     </row>
     <row r="178">
@@ -2319,10 +2319,10 @@
         <v>33970</v>
       </c>
       <c r="B178">
-        <v>60.90908095360235</v>
+        <v>60.89837217814896</v>
       </c>
       <c r="C178">
-        <v>76.78160629372964</v>
+        <v>76.77410389427219</v>
       </c>
     </row>
     <row r="179">
@@ -2330,10 +2330,10 @@
         <v>34060</v>
       </c>
       <c r="B179">
-        <v>61.07590250884007</v>
+        <v>61.06226254745716</v>
       </c>
       <c r="C179">
-        <v>76.96848587263266</v>
+        <v>76.96225149357799</v>
       </c>
     </row>
     <row r="180">
@@ -2341,10 +2341,10 @@
         <v>34151</v>
       </c>
       <c r="B180">
-        <v>61.07232444721038</v>
+        <v>61.05868331563074</v>
       </c>
       <c r="C180">
-        <v>77.15121609548947</v>
+        <v>77.14485575240064</v>
       </c>
     </row>
     <row r="181">
@@ -2352,10 +2352,10 @@
         <v>34243</v>
       </c>
       <c r="B181">
-        <v>61.28588009157535</v>
+        <v>61.2721926905732</v>
       </c>
       <c r="C181">
-        <v>77.39331969850979</v>
+        <v>77.38715453975861</v>
       </c>
     </row>
     <row r="182">
@@ -2363,10 +2363,10 @@
         <v>34335</v>
       </c>
       <c r="B182">
-        <v>61.42098677021943</v>
+        <v>61.40493396182162</v>
       </c>
       <c r="C182">
-        <v>77.54140521641855</v>
+        <v>77.53408025679185</v>
       </c>
     </row>
     <row r="183">
@@ -2374,10 +2374,10 @@
         <v>34425</v>
       </c>
       <c r="B183">
-        <v>61.5080492535115</v>
+        <v>61.49315078563791</v>
       </c>
       <c r="C183">
-        <v>77.70837006570981</v>
+        <v>77.70227656599234</v>
       </c>
     </row>
     <row r="184">
@@ -2385,10 +2385,10 @@
         <v>34516</v>
       </c>
       <c r="B184">
-        <v>61.79837698193349</v>
+        <v>61.7863243085806</v>
       </c>
       <c r="C184">
-        <v>77.87536131935731</v>
+        <v>77.86815896436462</v>
       </c>
     </row>
     <row r="185">
@@ -2396,10 +2396,10 @@
         <v>34608</v>
       </c>
       <c r="B185">
-        <v>62.41930609703012</v>
+        <v>62.40942661813706</v>
       </c>
       <c r="C185">
-        <v>77.97405761382799</v>
+        <v>77.96697977931245</v>
       </c>
     </row>
     <row r="186">
@@ -2407,10 +2407,10 @@
         <v>34700</v>
       </c>
       <c r="B186">
-        <v>62.5726642364991</v>
+        <v>62.5610151915099</v>
       </c>
       <c r="C186">
-        <v>78.15737066776083</v>
+        <v>78.15011976079198</v>
       </c>
     </row>
     <row r="187">
@@ -2418,10 +2418,10 @@
         <v>34790</v>
       </c>
       <c r="B187">
-        <v>62.98591640393158</v>
+        <v>62.97302495264331</v>
       </c>
       <c r="C187">
-        <v>78.21026107895538</v>
+        <v>78.20251820472713</v>
       </c>
     </row>
     <row r="188">
@@ -2429,10 +2429,10 @@
         <v>34881</v>
       </c>
       <c r="B188">
-        <v>63.14681569375227</v>
+        <v>63.13159254251545</v>
       </c>
       <c r="C188">
-        <v>78.61165264125655</v>
+        <v>78.60497258306646</v>
       </c>
     </row>
     <row r="189">
@@ -2440,10 +2440,10 @@
         <v>34973</v>
       </c>
       <c r="B189">
-        <v>63.24570974472608</v>
+        <v>63.23161448860789</v>
       </c>
       <c r="C189">
-        <v>78.94771264089768</v>
+        <v>78.94090189320416</v>
       </c>
     </row>
     <row r="190">
@@ -2451,10 +2451,10 @@
         <v>35065</v>
       </c>
       <c r="B190">
-        <v>63.65686434276218</v>
+        <v>63.64268160396242</v>
       </c>
       <c r="C190">
-        <v>79.43108116851637</v>
+        <v>79.42432568617508</v>
       </c>
     </row>
     <row r="191">
@@ -2462,10 +2462,10 @@
         <v>35156</v>
       </c>
       <c r="B191">
-        <v>64.04116914949839</v>
+        <v>64.02690419078276</v>
       </c>
       <c r="C191">
-        <v>79.75650830738941</v>
+        <v>79.74873983994974</v>
       </c>
     </row>
     <row r="192">
@@ -2473,10 +2473,10 @@
         <v>35247</v>
       </c>
       <c r="B192">
-        <v>64.33974956335383</v>
+        <v>64.32599364883738</v>
       </c>
       <c r="C192">
-        <v>79.65581154004586</v>
+        <v>79.648564767286</v>
       </c>
     </row>
     <row r="193">
@@ -2484,10 +2484,10 @@
         <v>35339</v>
       </c>
       <c r="B193">
-        <v>64.35964826558683</v>
+        <v>64.34646032465054</v>
       </c>
       <c r="C193">
-        <v>79.96050961938984</v>
+        <v>79.95373622338677</v>
       </c>
     </row>
     <row r="194">
@@ -2495,10 +2495,10 @@
         <v>35431</v>
       </c>
       <c r="B194">
-        <v>64.71337780693368</v>
+        <v>64.70109526206429</v>
       </c>
       <c r="C194">
-        <v>80.21264024855979</v>
+        <v>80.20609952284555</v>
       </c>
     </row>
     <row r="195">
@@ -2506,10 +2506,10 @@
         <v>35521</v>
       </c>
       <c r="B195">
-        <v>64.98972023144634</v>
+        <v>64.97582535243268</v>
       </c>
       <c r="C195">
-        <v>80.11441211303776</v>
+        <v>80.10751603909291</v>
       </c>
     </row>
     <row r="196">
@@ -2517,10 +2517,10 @@
         <v>35612</v>
       </c>
       <c r="B196">
-        <v>65.23569971049112</v>
+        <v>65.22061682388703</v>
       </c>
       <c r="C196">
-        <v>80.38628385707754</v>
+        <v>80.37856771679186</v>
       </c>
     </row>
     <row r="197">
@@ -2528,10 +2528,10 @@
         <v>35704</v>
       </c>
       <c r="B197">
-        <v>65.34715627552988</v>
+        <v>65.33318497626745</v>
       </c>
       <c r="C197">
-        <v>80.59458039237609</v>
+        <v>80.58785678180466</v>
       </c>
     </row>
     <row r="198">
@@ -2539,10 +2539,10 @@
         <v>35796</v>
       </c>
       <c r="B198">
-        <v>65.78294969861557</v>
+        <v>65.76664059265771</v>
       </c>
       <c r="C198">
-        <v>80.64488014158297</v>
+        <v>80.6369671627121</v>
       </c>
     </row>
     <row r="199">
@@ -2550,10 +2550,10 @@
         <v>35886</v>
       </c>
       <c r="B199">
-        <v>65.95242194151794</v>
+        <v>65.93553759516462</v>
       </c>
       <c r="C199">
-        <v>80.67835151425832</v>
+        <v>80.67148424531766</v>
       </c>
     </row>
     <row r="200">
@@ -2561,10 +2561,10 @@
         <v>35977</v>
       </c>
       <c r="B200">
-        <v>66.4461974374931</v>
+        <v>66.43516358578503</v>
       </c>
       <c r="C200">
-        <v>80.47060181936784</v>
+        <v>80.46428793803803</v>
       </c>
     </row>
     <row r="201">
@@ -2572,10 +2572,10 @@
         <v>36069</v>
       </c>
       <c r="B201">
-        <v>66.68027860598229</v>
+        <v>66.66876983435594</v>
       </c>
       <c r="C201">
-        <v>80.11485771820368</v>
+        <v>80.10823405168426</v>
       </c>
     </row>
     <row r="202">
@@ -2583,10 +2583,10 @@
         <v>36161</v>
       </c>
       <c r="B202">
-        <v>66.99515499688353</v>
+        <v>66.97646795913377</v>
       </c>
       <c r="C202">
-        <v>79.94385856946612</v>
+        <v>79.93629609603927</v>
       </c>
     </row>
     <row r="203">
@@ -2594,10 +2594,10 @@
         <v>36251</v>
       </c>
       <c r="B203">
-        <v>67.10459271178534</v>
+        <v>67.09024567053527</v>
       </c>
       <c r="C203">
-        <v>79.95569795298461</v>
+        <v>79.94990693537831</v>
       </c>
     </row>
     <row r="204">
@@ -2605,10 +2605,10 @@
         <v>36342</v>
       </c>
       <c r="B204">
-        <v>67.48376272907127</v>
+        <v>67.47040563914395</v>
       </c>
       <c r="C204">
-        <v>79.88487494107919</v>
+        <v>79.87751601731784</v>
       </c>
     </row>
     <row r="205">
@@ -2616,10 +2616,10 @@
         <v>36434</v>
       </c>
       <c r="B205">
-        <v>68.04381275389872</v>
+        <v>68.03192132405034</v>
       </c>
       <c r="C205">
-        <v>80.349804489428</v>
+        <v>80.34315207678578</v>
       </c>
     </row>
     <row r="206">
@@ -2627,10 +2627,10 @@
         <v>36526</v>
       </c>
       <c r="B206">
-        <v>68.62786058462869</v>
+        <v>68.61371519012492</v>
       </c>
       <c r="C206">
-        <v>81.06844721285569</v>
+        <v>81.06104308353068</v>
       </c>
     </row>
     <row r="207">
@@ -2638,10 +2638,10 @@
         <v>36617</v>
       </c>
       <c r="B207">
-        <v>68.84101800271138</v>
+        <v>68.82682205296862</v>
       </c>
       <c r="C207">
-        <v>81.49580268044335</v>
+        <v>81.4885449761224</v>
       </c>
     </row>
     <row r="208">
@@ -2649,10 +2649,10 @@
         <v>36708</v>
       </c>
       <c r="B208">
-        <v>69.27385387101754</v>
+        <v>69.2580087509328</v>
       </c>
       <c r="C208">
-        <v>82.16026565934399</v>
+        <v>82.1539430286757</v>
       </c>
     </row>
     <row r="209">
@@ -2660,10 +2660,10 @@
         <v>36800</v>
       </c>
       <c r="B209">
-        <v>70.05544385403077</v>
+        <v>70.0404659173181</v>
       </c>
       <c r="C209">
-        <v>82.78199314313032</v>
+        <v>82.77270070129997</v>
       </c>
     </row>
     <row r="210">
@@ -2671,10 +2671,10 @@
         <v>36892</v>
       </c>
       <c r="B210">
-        <v>70.07665867153315</v>
+        <v>70.06730380730856</v>
       </c>
       <c r="C210">
-        <v>82.87362286249937</v>
+        <v>82.86573637998261</v>
       </c>
     </row>
     <row r="211">
@@ -2682,10 +2682,10 @@
         <v>36982</v>
       </c>
       <c r="B211">
-        <v>70.75746899888159</v>
+        <v>70.74336000943835</v>
       </c>
       <c r="C211">
-        <v>83.56768245909436</v>
+        <v>83.56097859541556</v>
       </c>
     </row>
     <row r="212">
@@ -2693,10 +2693,10 @@
         <v>37073</v>
       </c>
       <c r="B212">
-        <v>71.16780791266095</v>
+        <v>71.15066259749523</v>
       </c>
       <c r="C212">
-        <v>83.72641624737687</v>
+        <v>83.72004234242014</v>
       </c>
     </row>
     <row r="213">
@@ -2704,10 +2704,10 @@
         <v>37165</v>
       </c>
       <c r="B213">
-        <v>71.70754054217832</v>
+        <v>71.68713530342477</v>
       </c>
       <c r="C213">
-        <v>83.66743403663021</v>
+        <v>83.65960470982627</v>
       </c>
     </row>
     <row r="214">
@@ -2715,10 +2715,10 @@
         <v>37257</v>
       </c>
       <c r="B214">
-        <v>72.24745071235017</v>
+        <v>72.23099119245917</v>
       </c>
       <c r="C214">
-        <v>84.06447670242761</v>
+        <v>84.05695570425563</v>
       </c>
     </row>
     <row r="215">
@@ -2726,10 +2726,10 @@
         <v>37347</v>
       </c>
       <c r="B215">
-        <v>73.07046323839531</v>
+        <v>73.06040441933686</v>
       </c>
       <c r="C215">
-        <v>84.17410860621891</v>
+        <v>84.16668164565846</v>
       </c>
     </row>
     <row r="216">
@@ -2737,10 +2737,10 @@
         <v>37438</v>
       </c>
       <c r="B216">
-        <v>73.49687706410836</v>
+        <v>73.47964639273233</v>
       </c>
       <c r="C216">
-        <v>84.37487475138022</v>
+        <v>84.36877002714436</v>
       </c>
     </row>
     <row r="217">
@@ -2748,10 +2748,10 @@
         <v>37530</v>
       </c>
       <c r="B217">
-        <v>73.87305367656244</v>
+        <v>73.85371983505269</v>
       </c>
       <c r="C217">
-        <v>84.64483835860031</v>
+        <v>84.63575102232413</v>
       </c>
     </row>
     <row r="218">
@@ -2759,10 +2759,10 @@
         <v>37622</v>
       </c>
       <c r="B218">
-        <v>74.38462396573949</v>
+        <v>74.36821413255473</v>
       </c>
       <c r="C218">
-        <v>85.31149555451067</v>
+        <v>85.30269599030002</v>
       </c>
     </row>
     <row r="219">
@@ -2770,10 +2770,10 @@
         <v>37712</v>
       </c>
       <c r="B219">
-        <v>74.98599229260356</v>
+        <v>74.97604484665044</v>
       </c>
       <c r="C219">
-        <v>85.33213820850372</v>
+        <v>85.32521501226033</v>
       </c>
     </row>
     <row r="220">
@@ -2781,10 +2781,10 @@
         <v>37803</v>
       </c>
       <c r="B220">
-        <v>75.70270809370854</v>
+        <v>75.68601514948078</v>
       </c>
       <c r="C220">
-        <v>85.81319175015972</v>
+        <v>85.80608240595441</v>
       </c>
     </row>
     <row r="221">
@@ -2792,10 +2792,10 @@
         <v>37895</v>
       </c>
       <c r="B221">
-        <v>76.0896197999767</v>
+        <v>76.06827657223717</v>
       </c>
       <c r="C221">
-        <v>86.35217102145744</v>
+        <v>86.34460828775588</v>
       </c>
     </row>
     <row r="222">
@@ -2803,10 +2803,10 @@
         <v>37987</v>
       </c>
       <c r="B222">
-        <v>76.94411521064252</v>
+        <v>76.92462114218647</v>
       </c>
       <c r="C222">
-        <v>86.76532472896574</v>
+        <v>86.75600144636883</v>
       </c>
     </row>
     <row r="223">
@@ -2814,10 +2814,10 @@
         <v>38078</v>
       </c>
       <c r="B223">
-        <v>77.58412994809714</v>
+        <v>77.5715991696626</v>
       </c>
       <c r="C223">
-        <v>87.34618427574617</v>
+        <v>87.33993366308268</v>
       </c>
     </row>
     <row r="224">
@@ -2825,10 +2825,10 @@
         <v>38169</v>
       </c>
       <c r="B224">
-        <v>78.1268982087648</v>
+        <v>78.11272801516431</v>
       </c>
       <c r="C224">
-        <v>87.70994289601443</v>
+        <v>87.70350324721578</v>
       </c>
     </row>
     <row r="225">
@@ -2836,10 +2836,10 @@
         <v>38261</v>
       </c>
       <c r="B225">
-        <v>78.74340154465921</v>
+        <v>78.72353026648788</v>
       </c>
       <c r="C225">
-        <v>88.09053715251778</v>
+        <v>88.08109755925071</v>
       </c>
     </row>
     <row r="226">
@@ -2847,10 +2847,10 @@
         <v>38353</v>
       </c>
       <c r="B226">
-        <v>78.98840814264548</v>
+        <v>78.97808386900593</v>
       </c>
       <c r="C226">
-        <v>88.38805960587929</v>
+        <v>88.38058815510263</v>
       </c>
     </row>
     <row r="227">
@@ -2858,10 +2858,10 @@
         <v>38443</v>
       </c>
       <c r="B227">
-        <v>79.57075291207639</v>
+        <v>79.55626033120838</v>
       </c>
       <c r="C227">
-        <v>88.76706696743396</v>
+        <v>88.76021764157959</v>
       </c>
     </row>
     <row r="228">
@@ -2869,10 +2869,10 @@
         <v>38534</v>
       </c>
       <c r="B228">
-        <v>80.33837877960609</v>
+        <v>80.32170516700265</v>
       </c>
       <c r="C228">
-        <v>89.44694989455851</v>
+        <v>89.44052892725946</v>
       </c>
     </row>
     <row r="229">
@@ -2880,10 +2880,10 @@
         <v>38626</v>
       </c>
       <c r="B229">
-        <v>81.20157626915694</v>
+        <v>81.17468931929905</v>
       </c>
       <c r="C229">
-        <v>89.65902019049835</v>
+        <v>89.64827237666852</v>
       </c>
     </row>
     <row r="230">
@@ -2891,10 +2891,10 @@
         <v>38718</v>
       </c>
       <c r="B230">
-        <v>81.69806931299007</v>
+        <v>81.67610254917847</v>
       </c>
       <c r="C230">
-        <v>90.23606278866662</v>
+        <v>90.22892154078622</v>
       </c>
     </row>
     <row r="231">
@@ -2902,10 +2902,10 @@
         <v>38808</v>
       </c>
       <c r="B231">
-        <v>82.22558018078814</v>
+        <v>82.20600808189747</v>
       </c>
       <c r="C231">
-        <v>90.80370473705814</v>
+        <v>90.79675405122516</v>
       </c>
     </row>
     <row r="232">
@@ -2913,10 +2913,10 @@
         <v>38899</v>
       </c>
       <c r="B232">
-        <v>82.75912353620538</v>
+        <v>82.74242076172729</v>
       </c>
       <c r="C232">
-        <v>91.35614952636904</v>
+        <v>91.348989863304</v>
       </c>
     </row>
     <row r="233">
@@ -2924,10 +2924,10 @@
         <v>38991</v>
       </c>
       <c r="B233">
-        <v>83.86107453575544</v>
+        <v>83.84907202970057</v>
       </c>
       <c r="C233">
-        <v>91.39601396264936</v>
+        <v>91.38525043888581</v>
       </c>
     </row>
     <row r="234">
@@ -2935,10 +2935,10 @@
         <v>39083</v>
       </c>
       <c r="B234">
-        <v>84.05799815792227</v>
+        <v>84.04248427232265</v>
       </c>
       <c r="C234">
-        <v>91.78672512047567</v>
+        <v>91.77811429324264</v>
       </c>
     </row>
     <row r="235">
@@ -2946,10 +2946,10 @@
         <v>39173</v>
       </c>
       <c r="B235">
-        <v>84.33854258227018</v>
+        <v>84.31904319073432</v>
       </c>
       <c r="C235">
-        <v>92.45941368128913</v>
+        <v>92.45254069073778</v>
       </c>
     </row>
     <row r="236">
@@ -2957,10 +2957,10 @@
         <v>39264</v>
       </c>
       <c r="B236">
-        <v>84.76102366312884</v>
+        <v>84.73607364753261</v>
       </c>
       <c r="C236">
-        <v>93.13228040511643</v>
+        <v>93.12483644314916</v>
       </c>
     </row>
     <row r="237">
@@ -2968,10 +2968,10 @@
         <v>39356</v>
       </c>
       <c r="B237">
-        <v>85.53844245934037</v>
+        <v>85.52598625233222</v>
       </c>
       <c r="C237">
-        <v>94.12995042153757</v>
+        <v>94.12013974935465</v>
       </c>
     </row>
     <row r="238">
@@ -2979,10 +2979,10 @@
         <v>39448</v>
       </c>
       <c r="B238">
-        <v>86.31976899172467</v>
+        <v>86.31051496073651</v>
       </c>
       <c r="C238">
-        <v>95.01572221641349</v>
+        <v>95.00737246164488</v>
       </c>
     </row>
     <row r="239">
@@ -2990,10 +2990,10 @@
         <v>39539</v>
       </c>
       <c r="B239">
-        <v>86.53285502546971</v>
+        <v>86.51290209587718</v>
       </c>
       <c r="C239">
-        <v>95.93634057079967</v>
+        <v>95.92849851020769</v>
       </c>
     </row>
     <row r="240">
@@ -3001,10 +3001,10 @@
         <v>39630</v>
       </c>
       <c r="B240">
-        <v>87.11340044545842</v>
+        <v>87.09380495236893</v>
       </c>
       <c r="C240">
-        <v>95.92481196635411</v>
+        <v>95.91635187121128</v>
       </c>
     </row>
     <row r="241">
@@ -3012,10 +3012,10 @@
         <v>39722</v>
       </c>
       <c r="B241">
-        <v>87.02792918058888</v>
+        <v>87.00249595122007</v>
       </c>
       <c r="C241">
-        <v>95.01341628749503</v>
+        <v>95.00425682243738</v>
       </c>
     </row>
     <row r="242">
@@ -3023,10 +3023,10 @@
         <v>39814</v>
       </c>
       <c r="B242">
-        <v>87.12762696108605</v>
+        <v>87.1055567443439</v>
       </c>
       <c r="C242">
-        <v>94.32551675365498</v>
+        <v>94.31664932209051</v>
       </c>
     </row>
     <row r="243">
@@ -3034,10 +3034,10 @@
         <v>39904</v>
       </c>
       <c r="B243">
-        <v>87.36791055644504</v>
+        <v>87.35022163220142</v>
       </c>
       <c r="C243">
-        <v>93.87567914592353</v>
+        <v>93.86807434880316</v>
       </c>
     </row>
     <row r="244">
@@ -3045,10 +3045,10 @@
         <v>39995</v>
       </c>
       <c r="B244">
-        <v>87.97722898223992</v>
+        <v>87.96239509307728</v>
       </c>
       <c r="C244">
-        <v>93.79221330239743</v>
+        <v>93.78520857056715</v>
       </c>
     </row>
     <row r="245">
@@ -3056,10 +3056,10 @@
         <v>40087</v>
       </c>
       <c r="B245">
-        <v>88.70988920682412</v>
+        <v>88.68893346094082</v>
       </c>
       <c r="C245">
-        <v>93.8965128201431</v>
+        <v>93.88780829528763</v>
       </c>
     </row>
     <row r="246">
@@ -3067,10 +3067,10 @@
         <v>40179</v>
       </c>
       <c r="B246">
-        <v>89.55752754629478</v>
+        <v>89.53539565030655</v>
       </c>
       <c r="C246">
-        <v>94.49498766784167</v>
+        <v>94.48618274225042</v>
       </c>
     </row>
     <row r="247">
@@ -3078,10 +3078,10 @@
         <v>40269</v>
       </c>
       <c r="B247">
-        <v>90.21713175708109</v>
+        <v>90.20082359520035</v>
       </c>
       <c r="C247">
-        <v>95.01212312915789</v>
+        <v>95.0039841026079</v>
       </c>
     </row>
     <row r="248">
@@ -3089,10 +3089,10 @@
         <v>40360</v>
       </c>
       <c r="B248">
-        <v>90.54378044854926</v>
+        <v>90.52442208125221</v>
       </c>
       <c r="C248">
-        <v>95.19795374486583</v>
+        <v>95.1896270838688</v>
       </c>
     </row>
     <row r="249">
@@ -3100,10 +3100,10 @@
         <v>40452</v>
       </c>
       <c r="B249">
-        <v>90.79728542675714</v>
+        <v>90.77688498948177</v>
       </c>
       <c r="C249">
-        <v>95.54689622111961</v>
+        <v>95.53910935401075</v>
       </c>
     </row>
     <row r="250">
@@ -3111,10 +3111,10 @@
         <v>40544</v>
       </c>
       <c r="B250">
-        <v>91.43134234454757</v>
+        <v>91.40687672111825</v>
       </c>
       <c r="C250">
-        <v>96.24542654813581</v>
+        <v>96.23693814637882</v>
       </c>
     </row>
     <row r="251">
@@ -3122,10 +3122,10 @@
         <v>40634</v>
       </c>
       <c r="B251">
-        <v>91.54002527285303</v>
+        <v>91.52094365927718</v>
       </c>
       <c r="C251">
-        <v>96.71376999262326</v>
+        <v>96.70561587594672</v>
       </c>
     </row>
     <row r="252">
@@ -3133,10 +3133,10 @@
         <v>40725</v>
       </c>
       <c r="B252">
-        <v>91.62158434013369</v>
+        <v>91.60150689929583</v>
       </c>
       <c r="C252">
-        <v>96.9486526862072</v>
+        <v>96.93997434432674</v>
       </c>
     </row>
     <row r="253">
@@ -3144,10 +3144,10 @@
         <v>40817</v>
       </c>
       <c r="B253">
-        <v>92.22558233040836</v>
+        <v>92.21074228639337</v>
       </c>
       <c r="C253">
-        <v>97.32141517748215</v>
+        <v>97.31285857736033</v>
       </c>
     </row>
     <row r="254">
@@ -3155,10 +3155,10 @@
         <v>40909</v>
       </c>
       <c r="B254">
-        <v>92.65717871960642</v>
+        <v>92.63054995075855</v>
       </c>
       <c r="C254">
-        <v>97.9636898550644</v>
+        <v>97.95624194321584</v>
       </c>
     </row>
     <row r="255">
@@ -3166,10 +3166,10 @@
         <v>41000</v>
       </c>
       <c r="B255">
-        <v>92.91124740934606</v>
+        <v>92.89333010976429</v>
       </c>
       <c r="C255">
-        <v>98.17785196359756</v>
+        <v>98.16998468882242</v>
       </c>
     </row>
     <row r="256">
@@ -3177,10 +3177,10 @@
         <v>41091</v>
       </c>
       <c r="B256">
-        <v>93.30207973862441</v>
+        <v>93.28456619142985</v>
       </c>
       <c r="C256">
-        <v>98.19370949431949</v>
+        <v>98.18550134201426</v>
       </c>
     </row>
     <row r="257">
@@ -3188,10 +3188,10 @@
         <v>41183</v>
       </c>
       <c r="B257">
-        <v>93.80296275255972</v>
+        <v>93.78583238875335</v>
       </c>
       <c r="C257">
-        <v>98.33652641975867</v>
+        <v>98.32613025236412</v>
       </c>
     </row>
     <row r="258">
@@ -3199,10 +3199,10 @@
         <v>41275</v>
       </c>
       <c r="B258">
-        <v>93.81503904131414</v>
+        <v>93.79059030698264</v>
       </c>
       <c r="C258">
-        <v>98.7317997545383</v>
+        <v>98.72280913246685</v>
       </c>
     </row>
     <row r="259">
@@ -3210,10 +3210,10 @@
         <v>41365</v>
       </c>
       <c r="B259">
-        <v>94.38793550326936</v>
+        <v>94.3706851229628</v>
       </c>
       <c r="C259">
-        <v>98.71182316700286</v>
+        <v>98.70105336621135</v>
       </c>
     </row>
     <row r="260">
@@ -3221,10 +3221,10 @@
         <v>41456</v>
       </c>
       <c r="B260">
-        <v>94.85246661919929</v>
+        <v>94.83511642527392</v>
       </c>
       <c r="C260">
-        <v>98.89178200877488</v>
+        <v>98.88383780079147</v>
       </c>
     </row>
     <row r="261">
@@ -3232,10 +3232,10 @@
         <v>41548</v>
       </c>
       <c r="B261">
-        <v>94.87170680273742</v>
+        <v>94.84996149092252</v>
       </c>
       <c r="C261">
-        <v>98.86852475540199</v>
+        <v>98.86163605166423</v>
       </c>
     </row>
     <row r="262">
@@ -3243,10 +3243,10 @@
         <v>41640</v>
       </c>
       <c r="B262">
-        <v>95.16837922718223</v>
+        <v>95.14660358228411</v>
       </c>
       <c r="C262">
-        <v>99.07839819524293</v>
+        <v>99.07150414739614</v>
       </c>
     </row>
     <row r="263">
@@ -3254,10 +3254,10 @@
         <v>41730</v>
       </c>
       <c r="B263">
-        <v>95.46608507857792</v>
+        <v>95.4500860418234</v>
       </c>
       <c r="C263">
-        <v>98.91124143930024</v>
+        <v>98.90293882328419</v>
       </c>
     </row>
     <row r="264">
@@ -3265,10 +3265,10 @@
         <v>41821</v>
       </c>
       <c r="B264">
-        <v>95.80615039817231</v>
+        <v>95.78858765507395</v>
       </c>
       <c r="C264">
-        <v>98.81984234927184</v>
+        <v>98.8101436724272</v>
       </c>
     </row>
     <row r="265">
@@ -3276,10 +3276,10 @@
         <v>41913</v>
       </c>
       <c r="B265">
-        <v>96.09039463996955</v>
+        <v>96.06445413447273</v>
       </c>
       <c r="C265">
-        <v>98.81443410473214</v>
+        <v>98.80473739265058</v>
       </c>
     </row>
     <row r="266">
@@ -3287,10 +3287,10 @@
         <v>42005</v>
       </c>
       <c r="B266">
-        <v>96.31873248140724</v>
+        <v>96.29371435732395</v>
       </c>
       <c r="C266">
-        <v>98.84194168091371</v>
+        <v>98.83120492830074</v>
       </c>
     </row>
     <row r="267">
@@ -3298,10 +3298,10 @@
         <v>42095</v>
       </c>
       <c r="B267">
-        <v>96.73684774208488</v>
+        <v>96.71661237726561</v>
       </c>
       <c r="C267">
-        <v>99.30101294949046</v>
+        <v>99.28956843274614</v>
       </c>
     </row>
     <row r="268">
@@ -3309,10 +3309,10 @@
         <v>42186</v>
       </c>
       <c r="B268">
-        <v>97.12842396200664</v>
+        <v>97.11009077332551</v>
       </c>
       <c r="C268">
-        <v>99.26603896794172</v>
+        <v>99.25697930370173</v>
       </c>
     </row>
     <row r="269">
@@ -3320,10 +3320,10 @@
         <v>42278</v>
       </c>
       <c r="B269">
-        <v>97.61285042977222</v>
+        <v>97.59251136079732</v>
       </c>
       <c r="C269">
-        <v>99.24841314006133</v>
+        <v>99.24460655995659</v>
       </c>
     </row>
     <row r="270">
@@ -3331,10 +3331,10 @@
         <v>42370</v>
       </c>
       <c r="B270">
-        <v>98.19873176657666</v>
+        <v>98.1759886007292</v>
       </c>
       <c r="C270">
-        <v>99.03850301008606</v>
+        <v>99.04252473143509</v>
       </c>
     </row>
     <row r="271">
@@ -3342,10 +3342,10 @@
         <v>42461</v>
       </c>
       <c r="B271">
-        <v>98.0570756671241</v>
+        <v>98.05028672304671</v>
       </c>
       <c r="C271">
-        <v>99.36030972176387</v>
+        <v>99.34165322313908</v>
       </c>
     </row>
     <row r="272">
@@ -3353,10 +3353,10 @@
         <v>42552</v>
       </c>
       <c r="B272">
-        <v>98.39140109455428</v>
+        <v>98.37229535501157</v>
       </c>
       <c r="C272">
-        <v>99.462650973962</v>
+        <v>99.45153009060735</v>
       </c>
     </row>
     <row r="273">
@@ -3364,10 +3364,10 @@
         <v>42644</v>
       </c>
       <c r="B273">
-        <v>98.93975160773351</v>
+        <v>98.90427706072245</v>
       </c>
       <c r="C273">
-        <v>99.69406524068</v>
+        <v>99.68499074622957</v>
       </c>
     </row>
     <row r="274">
@@ -3375,10 +3375,10 @@
         <v>42736</v>
       </c>
       <c r="B274">
-        <v>99.82317488300983</v>
+        <v>99.79100041125871</v>
       </c>
       <c r="C274">
-        <v>100.011992360116</v>
+        <v>100.0052482074686</v>
       </c>
     </row>
     <row r="275">
@@ -3397,10 +3397,10 @@
         <v>42917</v>
       </c>
       <c r="B276">
-        <v>100.4001652328461</v>
+        <v>100.3868246317988</v>
       </c>
       <c r="C276">
-        <v>100.1045025954967</v>
+        <v>100.101645718722</v>
       </c>
     </row>
     <row r="277">
@@ -3408,10 +3408,10 @@
         <v>43009</v>
       </c>
       <c r="B277">
-        <v>101.2283875711727</v>
+        <v>101.1880792198653</v>
       </c>
       <c r="C277">
-        <v>100.6534356730375</v>
+        <v>100.6275112571777</v>
       </c>
     </row>
     <row r="278">
@@ -3419,10 +3419,10 @@
         <v>43101</v>
       </c>
       <c r="B278">
-        <v>101.2437418367398</v>
+        <v>101.2052167733296</v>
       </c>
       <c r="C278">
-        <v>101.269986150668</v>
+        <v>101.2534192413517</v>
       </c>
     </row>
     <row r="279">
@@ -3430,10 +3430,10 @@
         <v>43191</v>
       </c>
       <c r="B279">
-        <v>101.7027118594449</v>
+        <v>101.7161106601846</v>
       </c>
       <c r="C279">
-        <v>101.8854215063295</v>
+        <v>101.8668506892039</v>
       </c>
     </row>
     <row r="280">
@@ -3441,10 +3441,10 @@
         <v>43282</v>
       </c>
       <c r="B280">
-        <v>102.3645354813408</v>
+        <v>102.350493662293</v>
       </c>
       <c r="C280">
-        <v>102.1654535153637</v>
+        <v>102.1542348628747</v>
       </c>
     </row>
     <row r="281">
@@ -3452,10 +3452,10 @@
         <v>43374</v>
       </c>
       <c r="B281">
-        <v>102.8834206228294</v>
+        <v>102.8353220165298</v>
       </c>
       <c r="C281">
-        <v>102.2250598750145</v>
+        <v>102.2357171968646</v>
       </c>
     </row>
     <row r="282">
@@ -3463,10 +3463,10 @@
         <v>43466</v>
       </c>
       <c r="B282">
-        <v>101.5141311080007</v>
+        <v>101.461732750486</v>
       </c>
       <c r="C282">
-        <v>102.2018890871676</v>
+        <v>102.2035090014158</v>
       </c>
     </row>
     <row r="283">
@@ -3474,10 +3474,10 @@
         <v>43556</v>
       </c>
       <c r="B283">
-        <v>101.0734798261951</v>
+        <v>101.084677442844</v>
       </c>
       <c r="C283">
-        <v>102.608754006546</v>
+        <v>102.5944029480282</v>
       </c>
     </row>
     <row r="284">
@@ -3485,10 +3485,10 @@
         <v>43647</v>
       </c>
       <c r="B284">
-        <v>101.3390640203707</v>
+        <v>101.3293104594114</v>
       </c>
       <c r="C284">
-        <v>102.8917788098255</v>
+        <v>102.8826275860999</v>
       </c>
     </row>
     <row r="285">
@@ -3496,10 +3496,10 @@
         <v>43739</v>
       </c>
       <c r="B285">
-        <v>101.0900204772598</v>
+        <v>101.0528059855579</v>
       </c>
       <c r="C285">
-        <v>103.210764037145</v>
+        <v>103.1963409932544</v>
       </c>
     </row>
     <row r="286">
@@ -3507,10 +3507,10 @@
         <v>43831</v>
       </c>
       <c r="B286">
-        <v>97.35964483710117</v>
+        <v>97.36419918205101</v>
       </c>
       <c r="C286">
-        <v>103.4770570257857</v>
+        <v>103.4651477947219</v>
       </c>
     </row>
     <row r="287">
@@ -3518,10 +3518,10 @@
         <v>43922</v>
       </c>
       <c r="B287">
-        <v>85.91274405075835</v>
+        <v>85.86881199454449</v>
       </c>
       <c r="C287">
-        <v>103.6020154286757</v>
+        <v>103.6071434698978</v>
       </c>
     </row>
     <row r="288">
@@ -3529,10 +3529,10 @@
         <v>44013</v>
       </c>
       <c r="B288">
-        <v>99.19110146266709</v>
+        <v>99.19201612566756</v>
       </c>
       <c r="C288">
-        <v>103.6906822603219</v>
+        <v>103.64685052215</v>
       </c>
     </row>
     <row r="289">
@@ -3540,10 +3540,10 @@
         <v>44105</v>
       </c>
       <c r="B289">
-        <v>97.6850354211625</v>
+        <v>97.64132805061494</v>
       </c>
       <c r="C289">
-        <v>103.7747177482538</v>
+        <v>103.7928486934079</v>
       </c>
     </row>
     <row r="290">
@@ -3551,10 +3551,10 @@
         <v>44197</v>
       </c>
       <c r="B290">
-        <v>97.71863576438459</v>
+        <v>97.72639657567603</v>
       </c>
       <c r="C290">
-        <v>104.347620819556</v>
+        <v>104.33525667428</v>
       </c>
     </row>
     <row r="291">
@@ -3562,10 +3562,10 @@
         <v>44287</v>
       </c>
       <c r="B291">
-        <v>98.71937155492184</v>
+        <v>98.72711120133927</v>
       </c>
       <c r="C291">
-        <v>104.7190842006649</v>
+        <v>104.7026782679764</v>
       </c>
     </row>
     <row r="292">
@@ -3573,10 +3573,10 @@
         <v>44378</v>
       </c>
       <c r="B292">
-        <v>101.8401053503415</v>
+        <v>101.8142328323101</v>
       </c>
       <c r="C292">
-        <v>105.4462297079327</v>
+        <v>105.4410501467152</v>
       </c>
     </row>
     <row r="293">
@@ -3584,10 +3584,10 @@
         <v>44470</v>
       </c>
       <c r="B293">
-        <v>102.549955309785</v>
+        <v>102.4758041052214</v>
       </c>
       <c r="C293">
-        <v>106.1702182688898</v>
+        <v>106.1729232895291</v>
       </c>
     </row>
     <row r="294">
@@ -3595,10 +3595,10 @@
         <v>44562</v>
       </c>
       <c r="B294">
-        <v>103.8046581563721</v>
+        <v>103.8106126244964</v>
       </c>
       <c r="C294">
-        <v>107.3790779746158</v>
+        <v>107.3764084269686</v>
       </c>
     </row>
     <row r="295">
@@ -3606,10 +3606,10 @@
         <v>44652</v>
       </c>
       <c r="B295">
-        <v>104.4274186843537</v>
+        <v>104.442419285234</v>
       </c>
       <c r="C295">
-        <v>109.3575688067031</v>
+        <v>109.3326203326845</v>
       </c>
     </row>
     <row r="296">
@@ -3617,10 +3617,10 @@
         <v>44743</v>
       </c>
       <c r="B296">
-        <v>104.662328969476</v>
+        <v>104.6260302644137</v>
       </c>
       <c r="C296">
-        <v>111.216384537951</v>
+        <v>111.190145889789</v>
       </c>
     </row>
     <row r="297">
@@ -3628,10 +3628,10 @@
         <v>44835</v>
       </c>
       <c r="B297">
-        <v>106.9496734728535</v>
+        <v>106.8746719334606</v>
       </c>
       <c r="C297">
-        <v>113.1809637412933</v>
+        <v>113.1851949125848</v>
       </c>
     </row>
     <row r="298">
@@ -3639,10 +3639,10 @@
         <v>44927</v>
       </c>
       <c r="B298">
-        <v>107.9946445438968</v>
+        <v>108.2193766337159</v>
       </c>
       <c r="C298">
-        <v>115.4648732951276</v>
+        <v>115.4207509252739</v>
       </c>
     </row>
     <row r="299">
@@ -3650,10 +3650,18 @@
         <v>45017</v>
       </c>
       <c r="B299">
-        <v>108.8535181174555</v>
+        <v>108.9655538459786</v>
       </c>
       <c r="C299">
-        <v>117.0569476550662</v>
+        <v>117.0195997976178</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2">
+        <v>45108</v>
+      </c>
+      <c r="C300">
+        <v>118.1942499103857</v>
       </c>
     </row>
   </sheetData>

--- a/Conjoncture - comptes trimestriels/data/smpt.xlsx
+++ b/Conjoncture - comptes trimestriels/data/smpt.xlsx
@@ -383,10 +383,10 @@
         <v>17899</v>
       </c>
       <c r="B2">
-        <v>0.8486392491682327</v>
+        <v>0.8487030417456893</v>
       </c>
       <c r="C2">
-        <v>5.18946688386686</v>
+        <v>5.189477122925738</v>
       </c>
     </row>
     <row r="3">
@@ -394,10 +394,10 @@
         <v>17989</v>
       </c>
       <c r="B3">
-        <v>0.8724485577258769</v>
+        <v>0.8725141400593007</v>
       </c>
       <c r="C3">
-        <v>5.225847874055477</v>
+        <v>5.225858184895736</v>
       </c>
     </row>
     <row r="4">
@@ -405,10 +405,10 @@
         <v>18080</v>
       </c>
       <c r="B4">
-        <v>0.8782018177450936</v>
+        <v>0.8782678325535485</v>
       </c>
       <c r="C4">
-        <v>5.379767580070704</v>
+        <v>5.379778194601683</v>
       </c>
     </row>
     <row r="5">
@@ -416,10 +416,10 @@
         <v>18172</v>
       </c>
       <c r="B5">
-        <v>0.8790387171495844</v>
+        <v>0.8791047948681274</v>
       </c>
       <c r="C5">
-        <v>5.405004222592091</v>
+        <v>5.405014886916137</v>
       </c>
     </row>
     <row r="6">
@@ -427,10 +427,10 @@
         <v>18264</v>
       </c>
       <c r="B6">
-        <v>0.9036782534373936</v>
+        <v>0.9037461833204795</v>
       </c>
       <c r="C6">
-        <v>5.481772077521673</v>
+        <v>5.481782893312257</v>
       </c>
     </row>
     <row r="7">
@@ -438,10 +438,10 @@
         <v>18354</v>
       </c>
       <c r="B7">
-        <v>0.9399489135767226</v>
+        <v>0.9400195699409354</v>
       </c>
       <c r="C7">
-        <v>5.582181316363304</v>
+        <v>5.582192330265975</v>
       </c>
     </row>
     <row r="8">
@@ -449,10 +449,10 @@
         <v>18445</v>
       </c>
       <c r="B8">
-        <v>0.9753871691579156</v>
+        <v>0.9754604894310465</v>
       </c>
       <c r="C8">
-        <v>5.816321603401113</v>
+        <v>5.81633307927343</v>
       </c>
     </row>
     <row r="9">
@@ -460,10 +460,10 @@
         <v>18537</v>
       </c>
       <c r="B9">
-        <v>1.018750399613081</v>
+        <v>1.018826979518901</v>
       </c>
       <c r="C9">
-        <v>5.974490154783323</v>
+        <v>5.974501942729528</v>
       </c>
     </row>
     <row r="10">
@@ -471,10 +471,10 @@
         <v>18629</v>
       </c>
       <c r="B10">
-        <v>1.077012152073711</v>
+        <v>1.077093111540529</v>
       </c>
       <c r="C10">
-        <v>6.279089446139699</v>
+        <v>6.279101835074435</v>
       </c>
     </row>
     <row r="11">
@@ -482,10 +482,10 @@
         <v>18719</v>
       </c>
       <c r="B11">
-        <v>1.166511804687582</v>
+        <v>1.166599491881791</v>
       </c>
       <c r="C11">
-        <v>6.602333744709825</v>
+        <v>6.602346771420556</v>
       </c>
     </row>
     <row r="12">
@@ -493,10 +493,10 @@
         <v>18810</v>
       </c>
       <c r="B12">
-        <v>1.272919614223062</v>
+        <v>1.273015300138091</v>
       </c>
       <c r="C12">
-        <v>6.846043354432216</v>
+        <v>6.846056861993312</v>
       </c>
     </row>
     <row r="13">
@@ -504,10 +504,10 @@
         <v>18902</v>
       </c>
       <c r="B13">
-        <v>1.37186249887744</v>
+        <v>1.371965622371675</v>
       </c>
       <c r="C13">
-        <v>7.194737592382835</v>
+        <v>7.194751787933838</v>
       </c>
     </row>
     <row r="14">
@@ -515,10 +515,10 @@
         <v>18994</v>
       </c>
       <c r="B14">
-        <v>1.430178054080258</v>
+        <v>1.430285561179866</v>
       </c>
       <c r="C14">
-        <v>7.435726084461872</v>
+        <v>7.435740755494347</v>
       </c>
     </row>
     <row r="15">
@@ -526,10 +526,10 @@
         <v>19085</v>
       </c>
       <c r="B15">
-        <v>1.467353228095324</v>
+        <v>1.467463529668756</v>
       </c>
       <c r="C15">
-        <v>7.477682645965465</v>
+        <v>7.477697399780182</v>
       </c>
     </row>
     <row r="16">
@@ -537,10 +537,10 @@
         <v>19176</v>
       </c>
       <c r="B16">
-        <v>1.48731135496404</v>
+        <v>1.487423156798455</v>
       </c>
       <c r="C16">
-        <v>7.508811150306929</v>
+        <v>7.508825965539629</v>
       </c>
     </row>
     <row r="17">
@@ -548,10 +548,10 @@
         <v>19268</v>
       </c>
       <c r="B17">
-        <v>1.497251127558657</v>
+        <v>1.497363676570055</v>
       </c>
       <c r="C17">
-        <v>7.4785483496731</v>
+        <v>7.478563105195891</v>
       </c>
     </row>
     <row r="18">
@@ -559,10 +559,10 @@
         <v>19360</v>
       </c>
       <c r="B18">
-        <v>1.505215946513475</v>
+        <v>1.50532909424374</v>
       </c>
       <c r="C18">
-        <v>7.459336233109587</v>
+        <v>7.45935095072598</v>
       </c>
     </row>
     <row r="19">
@@ -570,10 +570,10 @@
         <v>19450</v>
       </c>
       <c r="B19">
-        <v>1.524722078204663</v>
+        <v>1.524836692219239</v>
       </c>
       <c r="C19">
-        <v>7.452160696419299</v>
+        <v>7.452175399878026</v>
       </c>
     </row>
     <row r="20">
@@ -581,10 +581,10 @@
         <v>19541</v>
       </c>
       <c r="B20">
-        <v>1.540265700509156</v>
+        <v>1.540381482944507</v>
       </c>
       <c r="C20">
-        <v>7.453211345549556</v>
+        <v>7.453226051081263</v>
       </c>
     </row>
     <row r="21">
@@ -592,10 +592,10 @@
         <v>19633</v>
       </c>
       <c r="B21">
-        <v>1.563155528122782</v>
+        <v>1.563273031196322</v>
       </c>
       <c r="C21">
-        <v>7.41609323295767</v>
+        <v>7.416107865253618</v>
       </c>
     </row>
     <row r="22">
@@ -603,10 +603,10 @@
         <v>19725</v>
       </c>
       <c r="B22">
-        <v>1.6004764924782</v>
+        <v>1.600596800984688</v>
       </c>
       <c r="C22">
-        <v>7.479483991600032</v>
+        <v>7.479498748968888</v>
       </c>
     </row>
     <row r="23">
@@ -614,10 +614,10 @@
         <v>19815</v>
       </c>
       <c r="B23">
-        <v>1.638866515986596</v>
+        <v>1.638989710287666</v>
       </c>
       <c r="C23">
-        <v>7.539711312548324</v>
+        <v>7.539726188748477</v>
       </c>
     </row>
     <row r="24">
@@ -625,10 +625,10 @@
         <v>19906</v>
       </c>
       <c r="B24">
-        <v>1.658246829519411</v>
+        <v>1.658371480646988</v>
       </c>
       <c r="C24">
-        <v>7.578548741388655</v>
+        <v>7.578563694216857</v>
       </c>
     </row>
     <row r="25">
@@ -636,10 +636,10 @@
         <v>19998</v>
       </c>
       <c r="B25">
-        <v>1.686735764965474</v>
+        <v>1.686862557618584</v>
       </c>
       <c r="C25">
-        <v>7.602438560982308</v>
+        <v>7.602453560946233</v>
       </c>
     </row>
     <row r="26">
@@ -647,10 +647,10 @@
         <v>20090</v>
       </c>
       <c r="B26">
-        <v>1.717091757593942</v>
+        <v>1.717220832120077</v>
       </c>
       <c r="C26">
-        <v>7.566503614407375</v>
+        <v>7.566518543469983</v>
       </c>
     </row>
     <row r="27">
@@ -658,10 +658,10 @@
         <v>20180</v>
       </c>
       <c r="B27">
-        <v>1.752532759073799</v>
+        <v>1.752664497715263</v>
       </c>
       <c r="C27">
-        <v>7.610113130973025</v>
+        <v>7.610128146079232</v>
       </c>
     </row>
     <row r="28">
@@ -669,10 +669,10 @@
         <v>20271</v>
       </c>
       <c r="B28">
-        <v>1.800872512137634</v>
+        <v>1.801007884499132</v>
       </c>
       <c r="C28">
-        <v>7.653544476538557</v>
+        <v>7.653559577336823</v>
       </c>
     </row>
     <row r="29">
@@ -680,10 +680,10 @@
         <v>20363</v>
       </c>
       <c r="B29">
-        <v>1.853289436765034</v>
+        <v>1.853428749329307</v>
       </c>
       <c r="C29">
-        <v>7.741624998029428</v>
+        <v>7.741640272614648</v>
       </c>
     </row>
     <row r="30">
@@ -691,10 +691,10 @@
         <v>20455</v>
       </c>
       <c r="B30">
-        <v>1.902704686307885</v>
+        <v>1.902847713437726</v>
       </c>
       <c r="C30">
-        <v>7.858340732570046</v>
+        <v>7.858356237440825</v>
       </c>
     </row>
     <row r="31">
@@ -702,10 +702,10 @@
         <v>20546</v>
       </c>
       <c r="B31">
-        <v>1.949374756498639</v>
+        <v>1.949521291837733</v>
       </c>
       <c r="C31">
-        <v>7.9444977566708</v>
+        <v>7.944513431533384</v>
       </c>
     </row>
     <row r="32">
@@ -713,10 +713,10 @@
         <v>20637</v>
       </c>
       <c r="B32">
-        <v>1.993251063210536</v>
+        <v>1.993400896750483</v>
       </c>
       <c r="C32">
-        <v>8.069651940026915</v>
+        <v>8.069667861824508</v>
       </c>
     </row>
     <row r="33">
@@ -724,10 +724,10 @@
         <v>20729</v>
       </c>
       <c r="B33">
-        <v>2.033516507569414</v>
+        <v>2.033669367880135</v>
       </c>
       <c r="C33">
-        <v>8.152743830562667</v>
+        <v>8.152759916304415</v>
       </c>
     </row>
     <row r="34">
@@ -735,10 +735,10 @@
         <v>20821</v>
       </c>
       <c r="B34">
-        <v>2.072398891175788</v>
+        <v>2.072554674292014</v>
       </c>
       <c r="C34">
-        <v>8.156988768393207</v>
+        <v>8.157004862510414</v>
       </c>
     </row>
     <row r="35">
@@ -746,10 +746,10 @@
         <v>20911</v>
       </c>
       <c r="B35">
-        <v>2.121088944129605</v>
+        <v>2.121248387298058</v>
       </c>
       <c r="C35">
-        <v>8.304897283446142</v>
+        <v>8.304913669393708</v>
       </c>
     </row>
     <row r="36">
@@ -757,10 +757,10 @@
         <v>21002</v>
       </c>
       <c r="B36">
-        <v>2.184167936441239</v>
+        <v>2.184332121284681</v>
       </c>
       <c r="C36">
-        <v>8.574239676783153</v>
+        <v>8.574256594155754</v>
       </c>
     </row>
     <row r="37">
@@ -768,10 +768,10 @@
         <v>21094</v>
       </c>
       <c r="B37">
-        <v>2.26553854340932</v>
+        <v>2.265708844916294</v>
       </c>
       <c r="C37">
-        <v>8.88583884958293</v>
+        <v>8.885856381755156</v>
       </c>
     </row>
     <row r="38">
@@ -779,10 +779,10 @@
         <v>21186</v>
       </c>
       <c r="B38">
-        <v>2.354965263332786</v>
+        <v>2.35514228708477</v>
       </c>
       <c r="C38">
-        <v>9.250566299336556</v>
+        <v>9.25058455113296</v>
       </c>
     </row>
     <row r="39">
@@ -790,10 +790,10 @@
         <v>21276</v>
       </c>
       <c r="B39">
-        <v>2.434283885786674</v>
+        <v>2.434466871953632</v>
       </c>
       <c r="C39">
-        <v>9.524489430228842</v>
+        <v>9.524508222488286</v>
       </c>
     </row>
     <row r="40">
@@ -801,10 +801,10 @@
         <v>21367</v>
       </c>
       <c r="B40">
-        <v>2.492372460843607</v>
+        <v>2.492559813553743</v>
       </c>
       <c r="C40">
-        <v>9.637624632025355</v>
+        <v>9.637643647505802</v>
       </c>
     </row>
     <row r="41">
@@ -812,10 +812,10 @@
         <v>21459</v>
       </c>
       <c r="B41">
-        <v>2.538322818800319</v>
+        <v>2.538513625618631</v>
       </c>
       <c r="C41">
-        <v>9.723663155003022</v>
+        <v>9.723682340241465</v>
       </c>
     </row>
     <row r="42">
@@ -823,10 +823,10 @@
         <v>21551</v>
       </c>
       <c r="B42">
-        <v>2.598514151514804</v>
+        <v>2.598709482941491</v>
       </c>
       <c r="C42">
-        <v>9.960279020078504</v>
+        <v>9.960298672171024</v>
       </c>
     </row>
     <row r="43">
@@ -834,10 +834,10 @@
         <v>21641</v>
       </c>
       <c r="B43">
-        <v>2.671068322426913</v>
+        <v>2.671269107781841</v>
       </c>
       <c r="C43">
-        <v>10.05927787830247</v>
+        <v>10.05929772572433</v>
       </c>
     </row>
     <row r="44">
@@ -845,10 +845,10 @@
         <v>21732</v>
       </c>
       <c r="B44">
-        <v>2.727902529002237</v>
+        <v>2.728107586608925</v>
       </c>
       <c r="C44">
-        <v>10.1551930579354</v>
+        <v>10.15521309460236</v>
       </c>
     </row>
     <row r="45">
@@ -856,10 +856,10 @@
         <v>21824</v>
       </c>
       <c r="B45">
-        <v>2.780829157678766</v>
+        <v>2.781038193802901</v>
       </c>
       <c r="C45">
-        <v>10.26898304980993</v>
+        <v>10.26900331098982</v>
       </c>
     </row>
     <row r="46">
@@ -867,10 +867,10 @@
         <v>21916</v>
       </c>
       <c r="B46">
-        <v>2.830412164560918</v>
+        <v>2.830624927861011</v>
       </c>
       <c r="C46">
-        <v>10.3363409289113</v>
+        <v>10.33636132299141</v>
       </c>
     </row>
     <row r="47">
@@ -878,10 +878,10 @@
         <v>22007</v>
       </c>
       <c r="B47">
-        <v>2.88474651193049</v>
+        <v>2.88496335956685</v>
       </c>
       <c r="C47">
-        <v>10.40654555259939</v>
+        <v>10.40656608519648</v>
       </c>
     </row>
     <row r="48">
@@ -889,10 +889,10 @@
         <v>22098</v>
       </c>
       <c r="B48">
-        <v>2.954260420010664</v>
+        <v>2.954482493037401</v>
       </c>
       <c r="C48">
-        <v>10.46079295369043</v>
+        <v>10.46081359332015</v>
       </c>
     </row>
     <row r="49">
@@ -900,10 +900,10 @@
         <v>22190</v>
       </c>
       <c r="B49">
-        <v>3.039688662563179</v>
+        <v>3.039917157267661</v>
       </c>
       <c r="C49">
-        <v>10.51613550820365</v>
+        <v>10.51615625702681</v>
       </c>
     </row>
     <row r="50">
@@ -911,10 +911,10 @@
         <v>22282</v>
       </c>
       <c r="B50">
-        <v>3.117381390861319</v>
+        <v>3.117615725761611</v>
       </c>
       <c r="C50">
-        <v>10.56670657261687</v>
+        <v>10.56672742121908</v>
       </c>
     </row>
     <row r="51">
@@ -922,10 +922,10 @@
         <v>22372</v>
       </c>
       <c r="B51">
-        <v>3.210635098094866</v>
+        <v>3.21087644291645</v>
       </c>
       <c r="C51">
-        <v>10.6873452130455</v>
+        <v>10.68736629967335</v>
       </c>
     </row>
     <row r="52">
@@ -933,10 +933,10 @@
         <v>22463</v>
       </c>
       <c r="B52">
-        <v>3.300879178815736</v>
+        <v>3.301127307323692</v>
       </c>
       <c r="C52">
-        <v>10.77361506776777</v>
+        <v>10.77363632461003</v>
       </c>
     </row>
     <row r="53">
@@ -944,10 +944,10 @@
         <v>22555</v>
       </c>
       <c r="B53">
-        <v>3.393915200942724</v>
+        <v>3.394170323008489</v>
       </c>
       <c r="C53">
-        <v>10.88407351862789</v>
+        <v>10.88409499340981</v>
       </c>
     </row>
     <row r="54">
@@ -955,10 +955,10 @@
         <v>22647</v>
       </c>
       <c r="B54">
-        <v>3.491087571531959</v>
+        <v>3.491349998086626</v>
       </c>
       <c r="C54">
-        <v>11.04640876072424</v>
+        <v>11.04643055580112</v>
       </c>
     </row>
     <row r="55">
@@ -966,10 +966,10 @@
         <v>22737</v>
       </c>
       <c r="B55">
-        <v>3.57110071371291</v>
+        <v>3.571369154889898</v>
       </c>
       <c r="C55">
-        <v>11.17069174574241</v>
+        <v>11.17071378603539</v>
       </c>
     </row>
     <row r="56">
@@ -977,10 +977,10 @@
         <v>22828</v>
       </c>
       <c r="B56">
-        <v>3.652787641420259</v>
+        <v>3.653062223038746</v>
       </c>
       <c r="C56">
-        <v>11.24328901569904</v>
+        <v>11.24331119922979</v>
       </c>
     </row>
     <row r="57">
@@ -988,10 +988,10 @@
         <v>22920</v>
       </c>
       <c r="B57">
-        <v>3.74588417970056</v>
+        <v>3.74616575942588</v>
       </c>
       <c r="C57">
-        <v>11.32302295775607</v>
+        <v>11.32304529860559</v>
       </c>
     </row>
     <row r="58">
@@ -999,10 +999,10 @@
         <v>23012</v>
       </c>
       <c r="B58">
-        <v>3.861270914987107</v>
+        <v>3.86156116838296</v>
       </c>
       <c r="C58">
-        <v>11.36464253508308</v>
+        <v>11.36466495804996</v>
       </c>
     </row>
     <row r="59">
@@ -1010,10 +1010,10 @@
         <v>23102</v>
       </c>
       <c r="B59">
-        <v>3.965013161171688</v>
+        <v>3.965311212916819</v>
       </c>
       <c r="C59">
-        <v>11.66028520212954</v>
+        <v>11.66030820841311</v>
       </c>
     </row>
     <row r="60">
@@ -1021,10 +1021,10 @@
         <v>23193</v>
       </c>
       <c r="B60">
-        <v>4.062298081206346</v>
+        <v>4.062603445900768</v>
       </c>
       <c r="C60">
-        <v>11.89545852955566</v>
+        <v>11.89548199984712</v>
       </c>
     </row>
     <row r="61">
@@ -1032,10 +1032,10 @@
         <v>23285</v>
       </c>
       <c r="B61">
-        <v>4.158156914943232</v>
+        <v>4.158469485387426</v>
       </c>
       <c r="C61">
-        <v>11.98106677660202</v>
+        <v>11.98109041580252</v>
       </c>
     </row>
     <row r="62">
@@ -1043,10 +1043,10 @@
         <v>23377</v>
       </c>
       <c r="B62">
-        <v>4.247809136510716</v>
+        <v>4.248128446150975</v>
       </c>
       <c r="C62">
-        <v>11.99514161821443</v>
+        <v>11.99516528518524</v>
       </c>
     </row>
     <row r="63">
@@ -1054,10 +1054,10 @@
         <v>23468</v>
       </c>
       <c r="B63">
-        <v>4.337990919639566</v>
+        <v>4.33831700828326</v>
       </c>
       <c r="C63">
-        <v>12.05993482208112</v>
+        <v>12.05995861689193</v>
       </c>
     </row>
     <row r="64">
@@ -1065,10 +1065,10 @@
         <v>23559</v>
       </c>
       <c r="B64">
-        <v>4.414709053481958</v>
+        <v>4.415040909060778</v>
       </c>
       <c r="C64">
-        <v>12.15839091156896</v>
+        <v>12.1584149006382</v>
       </c>
     </row>
     <row r="65">
@@ -1076,10 +1076,10 @@
         <v>23651</v>
       </c>
       <c r="B65">
-        <v>4.501004046922998</v>
+        <v>4.5013423893336</v>
       </c>
       <c r="C65">
-        <v>12.2462734493631</v>
+        <v>12.24629761182867</v>
       </c>
     </row>
     <row r="66">
@@ -1087,10 +1087,10 @@
         <v>23743</v>
       </c>
       <c r="B66">
-        <v>4.574641604954091</v>
+        <v>4.574985482731611</v>
       </c>
       <c r="C66">
-        <v>12.33678811294929</v>
+        <v>12.33681245400449</v>
       </c>
     </row>
     <row r="67">
@@ -1098,10 +1098,10 @@
         <v>23833</v>
       </c>
       <c r="B67">
-        <v>4.653343049042082</v>
+        <v>4.653692842841012</v>
       </c>
       <c r="C67">
-        <v>12.3878921388219</v>
+        <v>12.3879165807077</v>
       </c>
     </row>
     <row r="68">
@@ -1109,10 +1109,10 @@
         <v>23924</v>
       </c>
       <c r="B68">
-        <v>4.72536548535444</v>
+        <v>4.725720693110893</v>
       </c>
       <c r="C68">
-        <v>12.44227890838772</v>
+        <v>12.44230345758115</v>
       </c>
     </row>
     <row r="69">
@@ -1120,10 +1120,10 @@
         <v>24016</v>
       </c>
       <c r="B69">
-        <v>4.799419750600931</v>
+        <v>4.799780525048362</v>
       </c>
       <c r="C69">
-        <v>12.55664028989549</v>
+        <v>12.55666506472923</v>
       </c>
     </row>
     <row r="70">
@@ -1131,10 +1131,10 @@
         <v>24108</v>
       </c>
       <c r="B70">
-        <v>4.865293848238705</v>
+        <v>4.865659574470396</v>
       </c>
       <c r="C70">
-        <v>12.70302152655046</v>
+        <v>12.70304659020117</v>
       </c>
     </row>
     <row r="71">
@@ -1142,10 +1142,10 @@
         <v>24198</v>
       </c>
       <c r="B71">
-        <v>4.941772209601321</v>
+        <v>4.942143684744337</v>
       </c>
       <c r="C71">
-        <v>12.74474448214676</v>
+        <v>12.7447696281188</v>
       </c>
     </row>
     <row r="72">
@@ -1153,10 +1153,10 @@
         <v>24289</v>
       </c>
       <c r="B72">
-        <v>5.020838884468796</v>
+        <v>5.021216303087778</v>
       </c>
       <c r="C72">
-        <v>12.8442264321092</v>
+        <v>12.84425177436374</v>
       </c>
     </row>
     <row r="73">
@@ -1164,10 +1164,10 @@
         <v>24381</v>
       </c>
       <c r="B73">
-        <v>5.115127318604104</v>
+        <v>5.115511824925243</v>
       </c>
       <c r="C73">
-        <v>12.91697705034371</v>
+        <v>12.91700253613859</v>
       </c>
     </row>
     <row r="74">
@@ -1175,10 +1175,10 @@
         <v>24473</v>
       </c>
       <c r="B74">
-        <v>5.227289769771152</v>
+        <v>5.227682707392</v>
       </c>
       <c r="C74">
-        <v>13.05127655020918</v>
+        <v>13.05130230098321</v>
       </c>
     </row>
     <row r="75">
@@ -1186,10 +1186,10 @@
         <v>24563</v>
       </c>
       <c r="B75">
-        <v>5.301386009740992</v>
+        <v>5.301784517208075</v>
       </c>
       <c r="C75">
-        <v>13.1347237488148</v>
+        <v>13.13474966423403</v>
       </c>
     </row>
     <row r="76">
@@ -1197,10 +1197,10 @@
         <v>24654</v>
       </c>
       <c r="B76">
-        <v>5.386933186631726</v>
+        <v>5.3873381247169</v>
       </c>
       <c r="C76">
-        <v>13.22885791961967</v>
+        <v>13.22888402076998</v>
       </c>
     </row>
     <row r="77">
@@ -1208,10 +1208,10 @@
         <v>24746</v>
       </c>
       <c r="B77">
-        <v>5.492764021927727</v>
+        <v>5.493176915362319</v>
       </c>
       <c r="C77">
-        <v>13.3776979498366</v>
+        <v>13.37772434465519</v>
       </c>
     </row>
     <row r="78">
@@ -1219,10 +1219,10 @@
         <v>24838</v>
       </c>
       <c r="B78">
-        <v>5.665195949392586</v>
+        <v>5.665621804609349</v>
       </c>
       <c r="C78">
-        <v>13.59505677994858</v>
+        <v>13.59508360362622</v>
       </c>
     </row>
     <row r="79">
@@ -1230,10 +1230,10 @@
         <v>24929</v>
       </c>
       <c r="B79">
-        <v>5.681685893823528</v>
+        <v>5.682112988596509</v>
       </c>
       <c r="C79">
-        <v>13.64572903164951</v>
+        <v>13.64575595530585</v>
       </c>
     </row>
     <row r="80">
@@ -1241,10 +1241,10 @@
         <v>25020</v>
       </c>
       <c r="B80">
-        <v>6.21263827251606</v>
+        <v>6.213105279207769</v>
       </c>
       <c r="C80">
-        <v>13.9867951145827</v>
+        <v>13.98682271117825</v>
       </c>
     </row>
     <row r="81">
@@ -1252,10 +1252,10 @@
         <v>25112</v>
       </c>
       <c r="B81">
-        <v>6.356031658168066</v>
+        <v>6.356509443802265</v>
       </c>
       <c r="C81">
-        <v>14.19260383845384</v>
+        <v>14.19263184111955</v>
       </c>
     </row>
     <row r="82">
@@ -1263,10 +1263,10 @@
         <v>25204</v>
       </c>
       <c r="B82">
-        <v>6.447679796681814</v>
+        <v>6.448164471546014</v>
       </c>
       <c r="C82">
-        <v>14.56230025352537</v>
+        <v>14.56232898561925</v>
       </c>
     </row>
     <row r="83">
@@ -1274,10 +1274,10 @@
         <v>25294</v>
       </c>
       <c r="B83">
-        <v>6.583481338082048</v>
+        <v>6.583976221206539</v>
       </c>
       <c r="C83">
-        <v>14.73430350677413</v>
+        <v>14.73433257823841</v>
       </c>
     </row>
     <row r="84">
@@ -1285,10 +1285,10 @@
         <v>25385</v>
       </c>
       <c r="B84">
-        <v>6.736520958504046</v>
+        <v>6.737027345682642</v>
       </c>
       <c r="C84">
-        <v>14.9232400774532</v>
+        <v>14.9232695216981</v>
       </c>
     </row>
     <row r="85">
@@ -1296,10 +1296,10 @@
         <v>25477</v>
       </c>
       <c r="B85">
-        <v>6.946290669922226</v>
+        <v>6.946812825580276</v>
       </c>
       <c r="C85">
-        <v>15.15087515800013</v>
+        <v>15.1509050513796</v>
       </c>
     </row>
     <row r="86">
@@ -1307,10 +1307,10 @@
         <v>25569</v>
       </c>
       <c r="B86">
-        <v>7.169224622384849</v>
+        <v>7.169763536084016</v>
       </c>
       <c r="C86">
-        <v>15.27441904887899</v>
+        <v>15.27444918601629</v>
       </c>
     </row>
     <row r="87">
@@ -1318,10 +1318,10 @@
         <v>25659</v>
       </c>
       <c r="B87">
-        <v>7.349025426106672</v>
+        <v>7.349577855509606</v>
       </c>
       <c r="C87">
-        <v>15.49001069935268</v>
+        <v>15.4900412618623</v>
       </c>
     </row>
     <row r="88">
@@ -1329,10 +1329,10 @@
         <v>25750</v>
       </c>
       <c r="B88">
-        <v>7.530816579669721</v>
+        <v>7.531382674391877</v>
       </c>
       <c r="C88">
-        <v>15.70415665626088</v>
+        <v>15.7041876412904</v>
       </c>
     </row>
     <row r="89">
@@ -1340,10 +1340,10 @@
         <v>25842</v>
       </c>
       <c r="B89">
-        <v>7.750059082400681</v>
+        <v>7.750641657676089</v>
       </c>
       <c r="C89">
-        <v>15.85540261348064</v>
+        <v>15.85543389692546</v>
       </c>
     </row>
     <row r="90">
@@ -1351,10 +1351,10 @@
         <v>25934</v>
       </c>
       <c r="B90">
-        <v>7.995128769038261</v>
+        <v>7.995729766307447</v>
       </c>
       <c r="C90">
-        <v>16.09031123927562</v>
+        <v>16.09034298620605</v>
       </c>
     </row>
     <row r="91">
@@ -1362,10 +1362,10 @@
         <v>26024</v>
       </c>
       <c r="B91">
-        <v>8.18276674382493</v>
+        <v>8.183381845921405</v>
       </c>
       <c r="C91">
-        <v>16.36626755616349</v>
+        <v>16.36629984756853</v>
       </c>
     </row>
     <row r="92">
@@ -1373,10 +1373,10 @@
         <v>26115</v>
       </c>
       <c r="B92">
-        <v>8.414713098476481</v>
+        <v>8.415345636080222</v>
       </c>
       <c r="C92">
-        <v>16.56285866526363</v>
+        <v>16.56289134455206</v>
       </c>
     </row>
     <row r="93">
@@ -1384,10 +1384,10 @@
         <v>26207</v>
       </c>
       <c r="B93">
-        <v>8.653331182705921</v>
+        <v>8.653981657333711</v>
       </c>
       <c r="C93">
-        <v>16.81563735914359</v>
+        <v>16.81567053717611</v>
       </c>
     </row>
     <row r="94">
@@ -1395,10 +1395,10 @@
         <v>26299</v>
       </c>
       <c r="B94">
-        <v>8.818590717632938</v>
+        <v>8.819253614891066</v>
       </c>
       <c r="C94">
-        <v>17.01274456793351</v>
+        <v>17.01277813486768</v>
       </c>
     </row>
     <row r="95">
@@ -1406,10 +1406,10 @@
         <v>26390</v>
       </c>
       <c r="B95">
-        <v>9.045919439658464</v>
+        <v>9.046599425314426</v>
       </c>
       <c r="C95">
-        <v>17.25901931894873</v>
+        <v>17.25905337179442</v>
       </c>
     </row>
     <row r="96">
@@ -1417,10 +1417,10 @@
         <v>26481</v>
       </c>
       <c r="B96">
-        <v>9.28320691832347</v>
+        <v>9.283904740981287</v>
       </c>
       <c r="C96">
-        <v>17.56657849370719</v>
+        <v>17.5666131533814</v>
       </c>
     </row>
     <row r="97">
@@ -1428,10 +1428,10 @@
         <v>26573</v>
       </c>
       <c r="B97">
-        <v>9.589487299492193</v>
+        <v>9.590208145378028</v>
       </c>
       <c r="C97">
-        <v>17.86569576177736</v>
+        <v>17.86573101162382</v>
       </c>
     </row>
     <row r="98">
@@ -1439,10 +1439,10 @@
         <v>26665</v>
       </c>
       <c r="B98">
-        <v>9.884575602447956</v>
+        <v>9.885318630248477</v>
       </c>
       <c r="C98">
-        <v>18.02848667846341</v>
+        <v>18.02852224950389</v>
       </c>
     </row>
     <row r="99">
@@ -1450,10 +1450,10 @@
         <v>26755</v>
       </c>
       <c r="B99">
-        <v>10.19478120220089</v>
+        <v>10.1955475482898</v>
       </c>
       <c r="C99">
-        <v>18.38661671623763</v>
+        <v>18.38665299388528</v>
       </c>
     </row>
     <row r="100">
@@ -1461,10 +1461,10 @@
         <v>26846</v>
       </c>
       <c r="B100">
-        <v>10.56693041167646</v>
+        <v>10.56772473238155</v>
       </c>
       <c r="C100">
-        <v>18.90340237192042</v>
+        <v>18.90343966921015</v>
       </c>
     </row>
     <row r="101">
@@ -1472,10 +1472,10 @@
         <v>26938</v>
       </c>
       <c r="B101">
-        <v>10.92957192321082</v>
+        <v>10.93039350383435</v>
       </c>
       <c r="C101">
-        <v>19.44103697540738</v>
+        <v>19.44107533347511</v>
       </c>
     </row>
     <row r="102">
@@ -1483,10 +1483,10 @@
         <v>27030</v>
       </c>
       <c r="B102">
-        <v>11.40906043498637</v>
+        <v>11.40991805896761</v>
       </c>
       <c r="C102">
-        <v>20.28387799150864</v>
+        <v>20.2839180125408</v>
       </c>
     </row>
     <row r="103">
@@ -1494,10 +1494,10 @@
         <v>27120</v>
       </c>
       <c r="B103">
-        <v>11.94448176903317</v>
+        <v>11.94537964086643</v>
       </c>
       <c r="C103">
-        <v>21.09792525235941</v>
+        <v>21.09796687954457</v>
       </c>
     </row>
     <row r="104">
@@ -1505,10 +1505,10 @@
         <v>27211</v>
       </c>
       <c r="B104">
-        <v>12.5367801743491</v>
+        <v>12.53772256950831</v>
       </c>
       <c r="C104">
-        <v>21.780993868122</v>
+        <v>21.78103684303322</v>
       </c>
     </row>
     <row r="105">
@@ -1516,10 +1516,10 @@
         <v>27303</v>
       </c>
       <c r="B105">
-        <v>12.98796175517396</v>
+        <v>12.9889380658467</v>
       </c>
       <c r="C105">
-        <v>22.4007317648825</v>
+        <v>22.40077596256534</v>
       </c>
     </row>
     <row r="106">
@@ -1527,10 +1527,10 @@
         <v>27395</v>
       </c>
       <c r="B106">
-        <v>13.66241604362826</v>
+        <v>13.66344305332002</v>
       </c>
       <c r="C106">
-        <v>23.05618298340121</v>
+        <v>23.05622847431971</v>
       </c>
     </row>
     <row r="107">
@@ -1538,10 +1538,10 @@
         <v>27485</v>
       </c>
       <c r="B107">
-        <v>14.25563999077507</v>
+        <v>14.25671159336616</v>
       </c>
       <c r="C107">
-        <v>23.65007458909237</v>
+        <v>23.65012125178656</v>
       </c>
     </row>
     <row r="108">
@@ -1549,10 +1549,10 @@
         <v>27576</v>
       </c>
       <c r="B108">
-        <v>14.74085579752183</v>
+        <v>14.74196387399385</v>
       </c>
       <c r="C108">
-        <v>24.14753814708618</v>
+        <v>24.14758579129904</v>
       </c>
     </row>
     <row r="109">
@@ -1560,10 +1560,10 @@
         <v>27668</v>
       </c>
       <c r="B109">
-        <v>15.2168417668101</v>
+        <v>15.21798562335221</v>
       </c>
       <c r="C109">
-        <v>24.64827523819504</v>
+        <v>24.6483238703854</v>
       </c>
     </row>
     <row r="110">
@@ -1571,10 +1571,10 @@
         <v>27760</v>
       </c>
       <c r="B110">
-        <v>15.74628573097857</v>
+        <v>15.74746938605124</v>
       </c>
       <c r="C110">
-        <v>25.2801892286984</v>
+        <v>25.28023910768438</v>
       </c>
     </row>
     <row r="111">
@@ -1582,10 +1582,10 @@
         <v>27851</v>
       </c>
       <c r="B111">
-        <v>16.31127669138988</v>
+        <v>16.31250281707611</v>
       </c>
       <c r="C111">
-        <v>25.83213929472018</v>
+        <v>25.83219026272924</v>
       </c>
     </row>
     <row r="112">
@@ -1593,10 +1593,10 @@
         <v>27942</v>
       </c>
       <c r="B112">
-        <v>16.86227529631298</v>
+        <v>16.86354284080139</v>
       </c>
       <c r="C112">
-        <v>26.44834003956452</v>
+        <v>26.44839222336624</v>
       </c>
     </row>
     <row r="113">
@@ -1604,10 +1604,10 @@
         <v>28034</v>
       </c>
       <c r="B113">
-        <v>17.39388670644198</v>
+        <v>17.39519421238879</v>
       </c>
       <c r="C113">
-        <v>27.12139900408457</v>
+        <v>27.12145251586284</v>
       </c>
     </row>
     <row r="114">
@@ -1615,10 +1615,10 @@
         <v>28126</v>
       </c>
       <c r="B114">
-        <v>17.87273304539897</v>
+        <v>17.8740765464311</v>
       </c>
       <c r="C114">
-        <v>27.60023209744705</v>
+        <v>27.60028655398523</v>
       </c>
     </row>
     <row r="115">
@@ -1626,10 +1626,10 @@
         <v>28216</v>
       </c>
       <c r="B115">
-        <v>18.26806682974305</v>
+        <v>18.26944004818582</v>
       </c>
       <c r="C115">
-        <v>28.38064098395468</v>
+        <v>28.3806969802758</v>
       </c>
     </row>
     <row r="116">
@@ -1637,10 +1637,10 @@
         <v>28307</v>
       </c>
       <c r="B116">
-        <v>18.75620718527213</v>
+        <v>18.75761709743543</v>
       </c>
       <c r="C116">
-        <v>28.99807309555312</v>
+        <v>28.99813031009643</v>
       </c>
     </row>
     <row r="117">
@@ -1648,10 +1648,10 @@
         <v>28399</v>
       </c>
       <c r="B117">
-        <v>19.3176793958378</v>
+        <v>19.31913151410873</v>
       </c>
       <c r="C117">
-        <v>29.4867808324771</v>
+        <v>29.48683901126345</v>
       </c>
     </row>
     <row r="118">
@@ -1659,10 +1659,10 @@
         <v>28491</v>
       </c>
       <c r="B118">
-        <v>19.83747524218916</v>
+        <v>19.83896643373747</v>
       </c>
       <c r="C118">
-        <v>29.92561306206313</v>
+        <v>29.92567210668582</v>
       </c>
     </row>
     <row r="119">
@@ -1670,10 +1670,10 @@
         <v>28581</v>
       </c>
       <c r="B119">
-        <v>20.42990979980209</v>
+        <v>20.43144552491098</v>
       </c>
       <c r="C119">
-        <v>30.66300009956345</v>
+        <v>30.66306059908497</v>
       </c>
     </row>
     <row r="120">
@@ -1681,10 +1681,10 @@
         <v>28672</v>
       </c>
       <c r="B120">
-        <v>21.06825103075375</v>
+        <v>21.06983474024759</v>
       </c>
       <c r="C120">
-        <v>31.54001361916515</v>
+        <v>31.54007584907503</v>
       </c>
     </row>
     <row r="121">
@@ -1692,10 +1692,10 @@
         <v>28764</v>
       </c>
       <c r="B121">
-        <v>21.66435733105157</v>
+        <v>21.66598585011246</v>
       </c>
       <c r="C121">
-        <v>32.27680613835739</v>
+        <v>32.27686982199308</v>
       </c>
     </row>
     <row r="122">
@@ -1703,10 +1703,10 @@
         <v>28856</v>
       </c>
       <c r="B122">
-        <v>22.27530565220911</v>
+        <v>22.27698009651814</v>
       </c>
       <c r="C122">
-        <v>33.01710070838804</v>
+        <v>33.01716585265925</v>
       </c>
     </row>
     <row r="123">
@@ -1714,10 +1714,10 @@
         <v>28946</v>
       </c>
       <c r="B123">
-        <v>23.03225411217924</v>
+        <v>23.03398545662965</v>
       </c>
       <c r="C123">
-        <v>33.91726889366483</v>
+        <v>33.91733581400963</v>
       </c>
     </row>
     <row r="124">
@@ -1725,10 +1725,10 @@
         <v>29037</v>
       </c>
       <c r="B124">
-        <v>23.78423350940137</v>
+        <v>23.78602138046659</v>
       </c>
       <c r="C124">
-        <v>35.08958103291644</v>
+        <v>35.08965026628748</v>
       </c>
     </row>
     <row r="125">
@@ -1736,10 +1736,10 @@
         <v>29129</v>
       </c>
       <c r="B125">
-        <v>24.65036211229808</v>
+        <v>24.65221509062299</v>
       </c>
       <c r="C125">
-        <v>35.98192026747164</v>
+        <v>35.98199126146937</v>
       </c>
     </row>
     <row r="126">
@@ -1747,10 +1747,10 @@
         <v>29221</v>
       </c>
       <c r="B126">
-        <v>25.47592306710194</v>
+        <v>25.477838103199</v>
       </c>
       <c r="C126">
-        <v>37.33408590535932</v>
+        <v>37.33415956724257</v>
       </c>
     </row>
     <row r="127">
@@ -1758,10 +1758,10 @@
         <v>29312</v>
       </c>
       <c r="B127">
-        <v>26.42433515334316</v>
+        <v>26.42632148198476</v>
       </c>
       <c r="C127">
-        <v>38.42916062794775</v>
+        <v>38.4297455380024</v>
       </c>
     </row>
     <row r="128">
@@ -1769,10 +1769,10 @@
         <v>29403</v>
       </c>
       <c r="B128">
-        <v>27.30736599791774</v>
+        <v>27.30941870436782</v>
       </c>
       <c r="C128">
-        <v>39.57210896173811</v>
+        <v>39.57218656832875</v>
       </c>
     </row>
     <row r="129">
@@ -1780,10 +1780,10 @@
         <v>29495</v>
       </c>
       <c r="B129">
-        <v>28.1093937426826</v>
+        <v>28.1115067379033</v>
       </c>
       <c r="C129">
-        <v>40.76506785877795</v>
+        <v>40.76503496708425</v>
       </c>
     </row>
     <row r="130">
@@ -1791,10 +1791,10 @@
         <v>29587</v>
       </c>
       <c r="B130">
-        <v>28.91498993226168</v>
+        <v>28.91716348449453</v>
       </c>
       <c r="C130">
-        <v>42.13068643183726</v>
+        <v>42.13104485017086</v>
       </c>
     </row>
     <row r="131">
@@ -1802,10 +1802,10 @@
         <v>29677</v>
       </c>
       <c r="B131">
-        <v>29.90967719354922</v>
+        <v>29.91192551685143</v>
       </c>
       <c r="C131">
-        <v>43.44745145233906</v>
+        <v>43.44773966371862</v>
       </c>
     </row>
     <row r="132">
@@ -1813,10 +1813,10 @@
         <v>29768</v>
       </c>
       <c r="B132">
-        <v>31.01638345014097</v>
+        <v>31.0187149650286</v>
       </c>
       <c r="C132">
-        <v>45.15426056563937</v>
+        <v>45.15387991942394</v>
       </c>
     </row>
     <row r="133">
@@ -1824,10 +1824,10 @@
         <v>29860</v>
       </c>
       <c r="B133">
-        <v>32.24706700860489</v>
+        <v>32.24949103450507</v>
       </c>
       <c r="C133">
-        <v>46.57179189715635</v>
+        <v>46.57184730348948</v>
       </c>
     </row>
     <row r="134">
@@ -1835,10 +1835,10 @@
         <v>29952</v>
       </c>
       <c r="B134">
-        <v>33.58979048852323</v>
+        <v>33.59231544752505</v>
       </c>
       <c r="C134">
-        <v>47.8906361901678</v>
+        <v>47.89040968506652</v>
       </c>
     </row>
     <row r="135">
@@ -1846,10 +1846,10 @@
         <v>30042</v>
       </c>
       <c r="B135">
-        <v>34.47033317047819</v>
+        <v>34.47292432025223</v>
       </c>
       <c r="C135">
-        <v>49.23638405033823</v>
+        <v>49.23616680271851</v>
       </c>
     </row>
     <row r="136">
@@ -1857,10 +1857,10 @@
         <v>30133</v>
       </c>
       <c r="B136">
-        <v>35.0627996982831</v>
+        <v>35.06543538402094</v>
       </c>
       <c r="C136">
-        <v>50.03485695347655</v>
+        <v>50.03523801866807</v>
       </c>
     </row>
     <row r="137">
@@ -1868,10 +1868,10 @@
         <v>30225</v>
       </c>
       <c r="B137">
-        <v>35.78233241156454</v>
+        <v>35.78502218488598</v>
       </c>
       <c r="C137">
-        <v>51.04860818472145</v>
+        <v>51.04782648096665</v>
       </c>
     </row>
     <row r="138">
@@ -1879,10 +1879,10 @@
         <v>30317</v>
       </c>
       <c r="B138">
-        <v>36.84964538327409</v>
+        <v>36.85241538697079</v>
       </c>
       <c r="C138">
-        <v>52.40168148524238</v>
+        <v>52.40182131889812</v>
       </c>
     </row>
     <row r="139">
@@ -1890,10 +1890,10 @@
         <v>30407</v>
       </c>
       <c r="B139">
-        <v>37.59341649710528</v>
+        <v>37.59624241039658</v>
       </c>
       <c r="C139">
-        <v>53.78651940527303</v>
+        <v>53.78695797778254</v>
       </c>
     </row>
     <row r="140">
@@ -1901,10 +1901,10 @@
         <v>30498</v>
       </c>
       <c r="B140">
-        <v>38.57546497967667</v>
+        <v>38.5783647139749</v>
       </c>
       <c r="C140">
-        <v>54.96115364593115</v>
+        <v>54.96167047875579</v>
       </c>
     </row>
     <row r="141">
@@ -1912,10 +1912,10 @@
         <v>30590</v>
       </c>
       <c r="B141">
-        <v>39.4270276100861</v>
+        <v>39.42999135671361</v>
       </c>
       <c r="C141">
-        <v>56.08766595561868</v>
+        <v>56.08751222565039</v>
       </c>
     </row>
     <row r="142">
@@ -1923,10 +1923,10 @@
         <v>30682</v>
       </c>
       <c r="B142">
-        <v>40.20856907148593</v>
+        <v>40.21159156692132</v>
       </c>
       <c r="C142">
-        <v>57.15331984076333</v>
+        <v>57.15317589096234</v>
       </c>
     </row>
     <row r="143">
@@ -1934,10 +1934,10 @@
         <v>30773</v>
       </c>
       <c r="B143">
-        <v>41.14118312688181</v>
+        <v>41.14427572731698</v>
       </c>
       <c r="C143">
-        <v>58.08785342692298</v>
+        <v>58.08832367394392</v>
       </c>
     </row>
     <row r="144">
@@ -1945,10 +1945,10 @@
         <v>30864</v>
       </c>
       <c r="B144">
-        <v>41.39576786743835</v>
+        <v>41.39887960511799</v>
       </c>
       <c r="C144">
-        <v>59.09158969894563</v>
+        <v>59.0924362753322</v>
       </c>
     </row>
     <row r="145">
@@ -1956,10 +1956,10 @@
         <v>30956</v>
       </c>
       <c r="B145">
-        <v>42.34303064603712</v>
+        <v>42.34621358986735</v>
       </c>
       <c r="C145">
-        <v>60.07629145323109</v>
+        <v>60.07654081715819</v>
       </c>
     </row>
     <row r="146">
@@ -1967,10 +1967,10 @@
         <v>31048</v>
       </c>
       <c r="B146">
-        <v>43.10530500209852</v>
+        <v>43.10854524642004</v>
       </c>
       <c r="C146">
-        <v>61.03493193873406</v>
+        <v>61.03505236348592</v>
       </c>
     </row>
     <row r="147">
@@ -1978,10 +1978,10 @@
         <v>31138</v>
       </c>
       <c r="B147">
-        <v>43.76691147569267</v>
+        <v>43.77020145325744</v>
       </c>
       <c r="C147">
-        <v>62.04199067299718</v>
+        <v>62.04233587189675</v>
       </c>
     </row>
     <row r="148">
@@ -1989,10 +1989,10 @@
         <v>31229</v>
       </c>
       <c r="B148">
-        <v>44.28281124439287</v>
+        <v>44.2861400023652</v>
       </c>
       <c r="C148">
-        <v>62.66775349213435</v>
+        <v>62.66771809061395</v>
       </c>
     </row>
     <row r="149">
@@ -2000,10 +2000,10 @@
         <v>31321</v>
       </c>
       <c r="B149">
-        <v>44.81413231627105</v>
+        <v>44.81750101387694</v>
       </c>
       <c r="C149">
-        <v>63.15188875465011</v>
+        <v>63.15217627247448</v>
       </c>
     </row>
     <row r="150">
@@ -2011,10 +2011,10 @@
         <v>31413</v>
       </c>
       <c r="B150">
-        <v>45.12078480513704</v>
+        <v>45.12417655394245</v>
       </c>
       <c r="C150">
-        <v>63.30660711815423</v>
+        <v>63.30673202502658</v>
       </c>
     </row>
     <row r="151">
@@ -2022,10 +2022,10 @@
         <v>31503</v>
       </c>
       <c r="B151">
-        <v>45.89237170922252</v>
+        <v>45.89582145854745</v>
       </c>
       <c r="C151">
-        <v>63.63612468327151</v>
+        <v>63.63629012946287</v>
       </c>
     </row>
     <row r="152">
@@ -2033,10 +2033,10 @@
         <v>31594</v>
       </c>
       <c r="B152">
-        <v>45.93723383225557</v>
+        <v>45.94068695388559</v>
       </c>
       <c r="C152">
-        <v>63.99299714394193</v>
+        <v>63.99275413659272</v>
       </c>
     </row>
     <row r="153">
@@ -2044,10 +2044,10 @@
         <v>31686</v>
       </c>
       <c r="B153">
-        <v>46.22868754995207</v>
+        <v>46.23216258028343</v>
       </c>
       <c r="C153">
-        <v>64.58945555578957</v>
+        <v>64.58975716869951</v>
       </c>
     </row>
     <row r="154">
@@ -2055,10 +2055,10 @@
         <v>31778</v>
       </c>
       <c r="B154">
-        <v>47.06083662247611</v>
+        <v>47.06437420581126</v>
       </c>
       <c r="C154">
-        <v>65.12266295480835</v>
+        <v>65.12316280265568</v>
       </c>
     </row>
     <row r="155">
@@ -2066,10 +2066,10 @@
         <v>31868</v>
       </c>
       <c r="B155">
-        <v>47.27897764778707</v>
+        <v>47.28253162887695</v>
       </c>
       <c r="C155">
-        <v>65.59281814184284</v>
+        <v>65.59276576927391</v>
       </c>
     </row>
     <row r="156">
@@ -2077,10 +2077,10 @@
         <v>31959</v>
       </c>
       <c r="B156">
-        <v>47.77238784867263</v>
+        <v>47.77597891961957</v>
       </c>
       <c r="C156">
-        <v>65.9920892410086</v>
+        <v>65.99240541818428</v>
       </c>
     </row>
     <row r="157">
@@ -2088,10 +2088,10 @@
         <v>32051</v>
       </c>
       <c r="B157">
-        <v>48.32699720034213</v>
+        <v>48.33062996151264</v>
       </c>
       <c r="C157">
-        <v>66.35154538018942</v>
+        <v>66.35167629486622</v>
       </c>
     </row>
     <row r="158">
@@ -2099,10 +2099,10 @@
         <v>32143</v>
       </c>
       <c r="B158">
-        <v>48.93856411660654</v>
+        <v>48.94224284952525</v>
       </c>
       <c r="C158">
-        <v>66.71691460447602</v>
+        <v>66.71722391785858</v>
       </c>
     </row>
     <row r="159">
@@ -2110,10 +2110,10 @@
         <v>32234</v>
       </c>
       <c r="B159">
-        <v>49.30589085573482</v>
+        <v>49.30959720076254</v>
       </c>
       <c r="C159">
-        <v>67.1680662858722</v>
+        <v>67.16800418378828</v>
       </c>
     </row>
     <row r="160">
@@ -2121,10 +2121,10 @@
         <v>32325</v>
       </c>
       <c r="B160">
-        <v>49.90322859821287</v>
+        <v>49.90697984537567</v>
       </c>
       <c r="C160">
-        <v>67.78657837259261</v>
+        <v>67.78671211865606</v>
       </c>
     </row>
     <row r="161">
@@ -2132,10 +2132,10 @@
         <v>32417</v>
       </c>
       <c r="B161">
-        <v>50.43968502441876</v>
+        <v>50.44347659724191</v>
       </c>
       <c r="C161">
-        <v>68.40756521330896</v>
+        <v>68.40733257914754</v>
       </c>
     </row>
     <row r="162">
@@ -2143,10 +2143,10 @@
         <v>32509</v>
       </c>
       <c r="B162">
-        <v>51.03548369039225</v>
+        <v>51.03932004965744</v>
       </c>
       <c r="C162">
-        <v>69.12543624318832</v>
+        <v>69.12557263088046</v>
       </c>
     </row>
     <row r="163">
@@ -2154,10 +2154,10 @@
         <v>32599</v>
       </c>
       <c r="B163">
-        <v>51.71494718956409</v>
+        <v>51.71883462439283</v>
       </c>
       <c r="C163">
-        <v>69.88083200295905</v>
+        <v>69.88112374933969</v>
       </c>
     </row>
     <row r="164">
@@ -2165,10 +2165,10 @@
         <v>32690</v>
       </c>
       <c r="B164">
-        <v>52.1677476261511</v>
+        <v>52.17166909818346</v>
       </c>
       <c r="C164">
-        <v>70.4022757815779</v>
+        <v>70.40241468853368</v>
       </c>
     </row>
     <row r="165">
@@ -2176,10 +2176,10 @@
         <v>32782</v>
       </c>
       <c r="B165">
-        <v>53.04622818249481</v>
+        <v>53.05021569028852</v>
       </c>
       <c r="C165">
-        <v>70.99391269502136</v>
+        <v>70.99390713574188</v>
       </c>
     </row>
     <row r="166">
@@ -2187,10 +2187,10 @@
         <v>32874</v>
       </c>
       <c r="B166">
-        <v>53.68985404841013</v>
+        <v>53.69388993783708</v>
       </c>
       <c r="C166">
-        <v>71.34992509531467</v>
+        <v>71.35020819569097</v>
       </c>
     </row>
     <row r="167">
@@ -2198,10 +2198,10 @@
         <v>32964</v>
       </c>
       <c r="B167">
-        <v>54.563772126781</v>
+        <v>54.56787370900589</v>
       </c>
       <c r="C167">
-        <v>71.78168034951807</v>
+        <v>71.7819613722281</v>
       </c>
     </row>
     <row r="168">
@@ -2209,10 +2209,10 @@
         <v>33055</v>
       </c>
       <c r="B168">
-        <v>55.28242672417598</v>
+        <v>55.28658232797612</v>
       </c>
       <c r="C168">
-        <v>72.33375180932406</v>
+        <v>72.33362116966893</v>
       </c>
     </row>
     <row r="169">
@@ -2220,10 +2220,10 @@
         <v>33147</v>
       </c>
       <c r="B169">
-        <v>55.88946336567828</v>
+        <v>55.89366460068391</v>
       </c>
       <c r="C169">
-        <v>72.95149390605218</v>
+        <v>72.95214391011872</v>
       </c>
     </row>
     <row r="170">
@@ -2231,10 +2231,10 @@
         <v>33239</v>
       </c>
       <c r="B170">
-        <v>56.06867849791826</v>
+        <v>56.07289320460248</v>
       </c>
       <c r="C170">
-        <v>73.2835072791531</v>
+        <v>73.28378299767877</v>
       </c>
     </row>
     <row r="171">
@@ -2242,10 +2242,10 @@
         <v>33329</v>
       </c>
       <c r="B171">
-        <v>57.00475322522855</v>
+        <v>57.00903829705275</v>
       </c>
       <c r="C171">
-        <v>73.67571544581146</v>
+        <v>73.67598985081719</v>
       </c>
     </row>
     <row r="172">
@@ -2253,10 +2253,10 @@
         <v>33420</v>
       </c>
       <c r="B172">
-        <v>57.42147560985129</v>
+        <v>57.42635536936594</v>
       </c>
       <c r="C172">
-        <v>74.30913727914692</v>
+        <v>74.3091579750843</v>
       </c>
     </row>
     <row r="173">
@@ -2264,10 +2264,10 @@
         <v>33512</v>
       </c>
       <c r="B173">
-        <v>58.33150282366962</v>
+        <v>58.33588762783192</v>
       </c>
       <c r="C173">
-        <v>74.9883593116855</v>
+        <v>74.98862923371318</v>
       </c>
     </row>
     <row r="174">
@@ -2275,10 +2275,10 @@
         <v>33604</v>
       </c>
       <c r="B174">
-        <v>59.13960343723092</v>
+        <v>59.14404898666398</v>
       </c>
       <c r="C174">
-        <v>75.36611707224485</v>
+        <v>75.36638560751302</v>
       </c>
     </row>
     <row r="175">
@@ -2286,10 +2286,10 @@
         <v>33695</v>
       </c>
       <c r="B175">
-        <v>59.32369479281119</v>
+        <v>59.32758566352692</v>
       </c>
       <c r="C175">
-        <v>75.8214509759249</v>
+        <v>75.82160057516471</v>
       </c>
     </row>
     <row r="176">
@@ -2297,10 +2297,10 @@
         <v>33786</v>
       </c>
       <c r="B176">
-        <v>59.93288359651095</v>
+        <v>59.93795930514736</v>
       </c>
       <c r="C176">
-        <v>76.16981315619707</v>
+        <v>76.1701188583836</v>
       </c>
     </row>
     <row r="177">
@@ -2308,10 +2308,10 @@
         <v>33878</v>
       </c>
       <c r="B177">
-        <v>60.49465094049972</v>
+        <v>60.49919834943657</v>
       </c>
       <c r="C177">
-        <v>76.39874730015815</v>
+        <v>76.39889803843037</v>
       </c>
     </row>
     <row r="178">
@@ -2319,10 +2319,10 @@
         <v>33970</v>
       </c>
       <c r="B178">
-        <v>60.89837217814896</v>
+        <v>60.90294993498494</v>
       </c>
       <c r="C178">
-        <v>76.77410389427219</v>
+        <v>76.77414253745343</v>
       </c>
     </row>
     <row r="179">
@@ -2330,10 +2330,10 @@
         <v>34060</v>
       </c>
       <c r="B179">
-        <v>61.06226254745716</v>
+        <v>61.0668526240027</v>
       </c>
       <c r="C179">
-        <v>76.96225149357799</v>
+        <v>76.96218106800863</v>
       </c>
     </row>
     <row r="180">
@@ -2341,10 +2341,10 @@
         <v>34151</v>
       </c>
       <c r="B180">
-        <v>61.05868331563074</v>
+        <v>61.06327312312387</v>
       </c>
       <c r="C180">
-        <v>77.14485575240064</v>
+        <v>77.14450652950421</v>
       </c>
     </row>
     <row r="181">
@@ -2352,10 +2352,10 @@
         <v>34243</v>
       </c>
       <c r="B181">
-        <v>61.2721926905732</v>
+        <v>61.27679854765792</v>
       </c>
       <c r="C181">
-        <v>77.38715453975861</v>
+        <v>77.38730722820418</v>
       </c>
     </row>
     <row r="182">
@@ -2363,10 +2363,10 @@
         <v>34335</v>
       </c>
       <c r="B182">
-        <v>61.40493396182162</v>
+        <v>61.4095497971248</v>
       </c>
       <c r="C182">
-        <v>77.53408025679185</v>
+        <v>77.5345169067553</v>
       </c>
     </row>
     <row r="183">
@@ -2374,10 +2374,10 @@
         <v>34425</v>
       </c>
       <c r="B183">
-        <v>61.49315078563791</v>
+        <v>61.49777325223769</v>
       </c>
       <c r="C183">
-        <v>77.70227656599234</v>
+        <v>77.70242987618828</v>
       </c>
     </row>
     <row r="184">
@@ -2385,10 +2385,10 @@
         <v>34516</v>
       </c>
       <c r="B184">
-        <v>61.7863243085806</v>
+        <v>61.79096881316023</v>
       </c>
       <c r="C184">
-        <v>77.86815896436462</v>
+        <v>77.86802974698442</v>
       </c>
     </row>
     <row r="185">
@@ -2396,10 +2396,10 @@
         <v>34608</v>
       </c>
       <c r="B185">
-        <v>62.40942661813706</v>
+        <v>62.41411796158537</v>
       </c>
       <c r="C185">
-        <v>77.96697977931245</v>
+        <v>77.96723736859803</v>
       </c>
     </row>
     <row r="186">
@@ -2407,10 +2407,10 @@
         <v>34700</v>
       </c>
       <c r="B186">
-        <v>62.5610151915099</v>
+        <v>62.56571792993649</v>
       </c>
       <c r="C186">
-        <v>78.15011976079198</v>
+        <v>78.15078815793876</v>
       </c>
     </row>
     <row r="187">
@@ -2418,10 +2418,10 @@
         <v>34790</v>
       </c>
       <c r="B187">
-        <v>62.97302495264331</v>
+        <v>62.97775866202089</v>
       </c>
       <c r="C187">
-        <v>78.20251820472713</v>
+        <v>78.20265021597848</v>
       </c>
     </row>
     <row r="188">
@@ -2429,10 +2429,10 @@
         <v>34881</v>
       </c>
       <c r="B188">
-        <v>63.13159254251545</v>
+        <v>63.13633817148697</v>
       </c>
       <c r="C188">
-        <v>78.60497258306646</v>
+        <v>78.60492843488124</v>
       </c>
     </row>
     <row r="189">
@@ -2440,10 +2440,10 @@
         <v>34973</v>
       </c>
       <c r="B189">
-        <v>63.23161448860789</v>
+        <v>63.23636763627214</v>
       </c>
       <c r="C189">
-        <v>78.94090189320416</v>
+        <v>78.9408660222677</v>
       </c>
     </row>
     <row r="190">
@@ -2451,10 +2451,10 @@
         <v>35065</v>
       </c>
       <c r="B190">
-        <v>63.64268160396242</v>
+        <v>63.64803852072887</v>
       </c>
       <c r="C190">
-        <v>79.42432568617508</v>
+        <v>79.42466300287012</v>
       </c>
     </row>
     <row r="191">
@@ -2462,10 +2462,10 @@
         <v>35156</v>
       </c>
       <c r="B191">
-        <v>64.02690419078276</v>
+        <v>64.03114419660771</v>
       </c>
       <c r="C191">
-        <v>79.74873983994974</v>
+        <v>79.74900540662389</v>
       </c>
     </row>
     <row r="192">
@@ -2473,10 +2473,10 @@
         <v>35247</v>
       </c>
       <c r="B192">
-        <v>64.32599364883738</v>
+        <v>64.33254798808214</v>
       </c>
       <c r="C192">
-        <v>79.648564767286</v>
+        <v>79.6484458078439</v>
       </c>
     </row>
     <row r="193">
@@ -2484,10 +2484,10 @@
         <v>35339</v>
       </c>
       <c r="B193">
-        <v>64.34646032465054</v>
+        <v>64.35015273383419</v>
       </c>
       <c r="C193">
-        <v>79.95373622338677</v>
+        <v>79.95369031659516</v>
       </c>
     </row>
     <row r="194">
@@ -2495,10 +2495,10 @@
         <v>35431</v>
       </c>
       <c r="B194">
-        <v>64.70109526206429</v>
+        <v>64.70554593969375</v>
       </c>
       <c r="C194">
-        <v>80.20609952284555</v>
+        <v>80.20650274157899</v>
       </c>
     </row>
     <row r="195">
@@ -2506,10 +2506,10 @@
         <v>35521</v>
       </c>
       <c r="B195">
-        <v>64.97582535243268</v>
+        <v>64.97972707363895</v>
       </c>
       <c r="C195">
-        <v>80.10751603909291</v>
+        <v>80.10769805814691</v>
       </c>
     </row>
     <row r="196">
@@ -2517,10 +2517,10 @@
         <v>35612</v>
       </c>
       <c r="B196">
-        <v>65.22061682388703</v>
+        <v>65.22639383585464</v>
       </c>
       <c r="C196">
-        <v>80.37856771679186</v>
+        <v>80.3783714308879</v>
       </c>
     </row>
     <row r="197">
@@ -2528,10 +2528,10 @@
         <v>35704</v>
       </c>
       <c r="B197">
-        <v>65.33318497626745</v>
+        <v>65.33764083289995</v>
       </c>
       <c r="C197">
-        <v>80.58785678180466</v>
+        <v>80.58810232655898</v>
       </c>
     </row>
     <row r="198">
@@ -2539,10 +2539,10 @@
         <v>35796</v>
       </c>
       <c r="B198">
-        <v>65.76664059265771</v>
+        <v>65.77270670046303</v>
       </c>
       <c r="C198">
-        <v>80.6369671627121</v>
+        <v>80.63734733732029</v>
       </c>
     </row>
     <row r="199">
@@ -2550,10 +2550,10 @@
         <v>35886</v>
       </c>
       <c r="B199">
-        <v>65.93553759516462</v>
+        <v>65.93882368799798</v>
       </c>
       <c r="C199">
-        <v>80.67148424531766</v>
+        <v>80.67167952142897</v>
       </c>
     </row>
     <row r="200">
@@ -2561,10 +2561,10 @@
         <v>35977</v>
       </c>
       <c r="B200">
-        <v>66.43516358578503</v>
+        <v>66.4404408375903</v>
       </c>
       <c r="C200">
-        <v>80.46428793803803</v>
+        <v>80.46402507692191</v>
       </c>
     </row>
     <row r="201">
@@ -2572,10 +2572,10 @@
         <v>36069</v>
       </c>
       <c r="B201">
-        <v>66.66876983435594</v>
+        <v>66.67364187017955</v>
       </c>
       <c r="C201">
-        <v>80.10823405168426</v>
+        <v>80.10847761074446</v>
       </c>
     </row>
     <row r="202">
@@ -2583,10 +2583,10 @@
         <v>36161</v>
       </c>
       <c r="B202">
-        <v>66.97646795913377</v>
+        <v>66.98054825205001</v>
       </c>
       <c r="C202">
-        <v>79.93629609603927</v>
+        <v>79.93660770203228</v>
       </c>
     </row>
     <row r="203">
@@ -2594,10 +2594,10 @@
         <v>36251</v>
       </c>
       <c r="B203">
-        <v>67.09024567053527</v>
+        <v>67.09474850116956</v>
       </c>
       <c r="C203">
-        <v>79.94990693537831</v>
+        <v>79.94982693402292</v>
       </c>
     </row>
     <row r="204">
@@ -2605,10 +2605,10 @@
         <v>36342</v>
       </c>
       <c r="B204">
-        <v>67.47040563914395</v>
+        <v>67.47601296797737</v>
       </c>
       <c r="C204">
-        <v>79.87751601731784</v>
+        <v>79.87733910155779</v>
       </c>
     </row>
     <row r="205">
@@ -2616,10 +2616,10 @@
         <v>36434</v>
       </c>
       <c r="B205">
-        <v>68.03192132405034</v>
+        <v>68.03850254150942</v>
       </c>
       <c r="C205">
-        <v>80.34315207678578</v>
+        <v>80.34312109964752</v>
       </c>
     </row>
     <row r="206">
@@ -2627,10 +2627,10 @@
         <v>36526</v>
       </c>
       <c r="B206">
-        <v>68.61371519012492</v>
+        <v>68.61887291261435</v>
       </c>
       <c r="C206">
-        <v>81.06104308353068</v>
+        <v>81.06143540089002</v>
       </c>
     </row>
     <row r="207">
@@ -2638,10 +2638,10 @@
         <v>36617</v>
       </c>
       <c r="B207">
-        <v>68.82682205296862</v>
+        <v>68.83147341424075</v>
       </c>
       <c r="C207">
-        <v>81.4885449761224</v>
+        <v>81.48875683707465</v>
       </c>
     </row>
     <row r="208">
@@ -2649,10 +2649,10 @@
         <v>36708</v>
       </c>
       <c r="B208">
-        <v>69.2580087509328</v>
+        <v>69.2632149052464</v>
       </c>
       <c r="C208">
-        <v>82.1539430286757</v>
+        <v>82.1545287411025</v>
       </c>
     </row>
     <row r="209">
@@ -2660,10 +2660,10 @@
         <v>36800</v>
       </c>
       <c r="B209">
-        <v>70.0404659173181</v>
+        <v>70.04624480910219</v>
       </c>
       <c r="C209">
-        <v>82.77270070129997</v>
+        <v>82.77328746043565</v>
       </c>
     </row>
     <row r="210">
@@ -2671,10 +2671,10 @@
         <v>36892</v>
       </c>
       <c r="B210">
-        <v>70.06730380730856</v>
+        <v>70.07410571429902</v>
       </c>
       <c r="C210">
-        <v>82.86573637998261</v>
+        <v>82.86638674680862</v>
       </c>
     </row>
     <row r="211">
@@ -2682,10 +2682,10 @@
         <v>36982</v>
       </c>
       <c r="B211">
-        <v>70.74336000943835</v>
+        <v>70.74714914172947</v>
       </c>
       <c r="C211">
-        <v>83.56097859541556</v>
+        <v>83.56136583058704</v>
       </c>
     </row>
     <row r="212">
@@ -2693,10 +2693,10 @@
         <v>37073</v>
       </c>
       <c r="B212">
-        <v>71.15066259749523</v>
+        <v>71.15550272262247</v>
       </c>
       <c r="C212">
-        <v>83.72004234242014</v>
+        <v>83.71992055919722</v>
       </c>
     </row>
     <row r="213">
@@ -2704,10 +2704,10 @@
         <v>37165</v>
       </c>
       <c r="B213">
-        <v>71.68713530342477</v>
+        <v>71.69303150255001</v>
       </c>
       <c r="C213">
-        <v>83.65960470982627</v>
+        <v>83.65983322591704</v>
       </c>
     </row>
     <row r="214">
@@ -2715,10 +2715,10 @@
         <v>37257</v>
       </c>
       <c r="B214">
-        <v>72.23099119245917</v>
+        <v>72.23591432431039</v>
       </c>
       <c r="C214">
-        <v>84.05695570425563</v>
+        <v>84.05712155252827</v>
       </c>
     </row>
     <row r="215">
@@ -2726,10 +2726,10 @@
         <v>37347</v>
       </c>
       <c r="B215">
-        <v>73.06040441933686</v>
+        <v>73.06488473762485</v>
       </c>
       <c r="C215">
-        <v>84.16668164565846</v>
+        <v>84.1667868164018</v>
       </c>
     </row>
     <row r="216">
@@ -2737,10 +2737,10 @@
         <v>37438</v>
       </c>
       <c r="B216">
-        <v>73.47964639273233</v>
+        <v>73.48618126683344</v>
       </c>
       <c r="C216">
-        <v>84.36877002714436</v>
+        <v>84.36836246213247</v>
       </c>
     </row>
     <row r="217">
@@ -2748,10 +2748,10 @@
         <v>37530</v>
       </c>
       <c r="B217">
-        <v>73.85371983505269</v>
+        <v>73.86028286848401</v>
       </c>
       <c r="C217">
-        <v>84.63575102232413</v>
+        <v>84.63591801258677</v>
       </c>
     </row>
     <row r="218">
@@ -2759,10 +2759,10 @@
         <v>37622</v>
       </c>
       <c r="B218">
-        <v>74.36821413255473</v>
+        <v>74.37422589288694</v>
       </c>
       <c r="C218">
-        <v>85.30269599030002</v>
+        <v>85.30315627839921</v>
       </c>
     </row>
     <row r="219">
@@ -2770,10 +2770,10 @@
         <v>37712</v>
       </c>
       <c r="B219">
-        <v>74.97604484665044</v>
+        <v>74.97863827558231</v>
       </c>
       <c r="C219">
-        <v>85.32521501226033</v>
+        <v>85.3250916085852</v>
       </c>
     </row>
     <row r="220">
@@ -2781,10 +2781,10 @@
         <v>37803</v>
       </c>
       <c r="B220">
-        <v>75.68601514948078</v>
+        <v>75.692289764655</v>
       </c>
       <c r="C220">
-        <v>85.80608240595441</v>
+        <v>85.80635762444636</v>
       </c>
     </row>
     <row r="221">
@@ -2792,10 +2792,10 @@
         <v>37895</v>
       </c>
       <c r="B221">
-        <v>76.06827657223717</v>
+        <v>76.07602488074457</v>
       </c>
       <c r="C221">
-        <v>86.34460828775588</v>
+        <v>86.34477864967319</v>
       </c>
     </row>
     <row r="222">
@@ -2803,10 +2803,10 @@
         <v>37987</v>
       </c>
       <c r="B222">
-        <v>76.92462114218647</v>
+        <v>76.93040359905177</v>
       </c>
       <c r="C222">
-        <v>86.75600144636883</v>
+        <v>86.75612399536632</v>
       </c>
     </row>
     <row r="223">
@@ -2814,10 +2814,10 @@
         <v>38078</v>
       </c>
       <c r="B223">
-        <v>77.5715991696626</v>
+        <v>77.57540170753632</v>
       </c>
       <c r="C223">
-        <v>87.33993366308268</v>
+        <v>87.34040818448908</v>
       </c>
     </row>
     <row r="224">
@@ -2825,10 +2825,10 @@
         <v>38169</v>
       </c>
       <c r="B224">
-        <v>78.11272801516431</v>
+        <v>78.1185997825344</v>
       </c>
       <c r="C224">
-        <v>87.70350324721578</v>
+        <v>87.7037209455157</v>
       </c>
     </row>
     <row r="225">
@@ -2836,10 +2836,10 @@
         <v>38261</v>
       </c>
       <c r="B225">
-        <v>78.72353026648788</v>
+        <v>78.73096598514583</v>
       </c>
       <c r="C225">
-        <v>88.08109755925071</v>
+        <v>88.08161750255672</v>
       </c>
     </row>
     <row r="226">
@@ -2847,10 +2847,10 @@
         <v>38353</v>
       </c>
       <c r="B226">
-        <v>78.97808386900593</v>
+        <v>78.98503053705285</v>
       </c>
       <c r="C226">
-        <v>88.38058815510263</v>
+        <v>88.38063918926755</v>
       </c>
     </row>
     <row r="227">
@@ -2858,10 +2858,10 @@
         <v>38443</v>
       </c>
       <c r="B227">
-        <v>79.55626033120838</v>
+        <v>79.55871270811195</v>
       </c>
       <c r="C227">
-        <v>88.76021764157959</v>
+        <v>88.76051118059604</v>
       </c>
     </row>
     <row r="228">
@@ -2869,10 +2869,10 @@
         <v>38534</v>
       </c>
       <c r="B228">
-        <v>80.32170516700265</v>
+        <v>80.32678804956491</v>
       </c>
       <c r="C228">
-        <v>89.44052892725946</v>
+        <v>89.44077868615619</v>
       </c>
     </row>
     <row r="229">
@@ -2880,10 +2880,10 @@
         <v>38626</v>
       </c>
       <c r="B229">
-        <v>81.17468931929905</v>
+        <v>81.18379967864777</v>
       </c>
       <c r="C229">
-        <v>89.64827237666852</v>
+        <v>89.64848483214173</v>
       </c>
     </row>
     <row r="230">
@@ -2891,10 +2891,10 @@
         <v>38718</v>
       </c>
       <c r="B230">
-        <v>81.67610254917847</v>
+        <v>81.67824221405576</v>
       </c>
       <c r="C230">
-        <v>90.22892154078622</v>
+        <v>90.2290664751151</v>
       </c>
     </row>
     <row r="231">
@@ -2902,10 +2902,10 @@
         <v>38808</v>
       </c>
       <c r="B231">
-        <v>82.20600808189747</v>
+        <v>82.21567410708556</v>
       </c>
       <c r="C231">
-        <v>90.79675405122516</v>
+        <v>90.79740024464428</v>
       </c>
     </row>
     <row r="232">
@@ -2913,10 +2913,10 @@
         <v>38899</v>
       </c>
       <c r="B232">
-        <v>82.74242076172729</v>
+        <v>82.74025118785117</v>
       </c>
       <c r="C232">
-        <v>91.348989863304</v>
+        <v>91.34914151925935</v>
       </c>
     </row>
     <row r="233">
@@ -2924,10 +2924,10 @@
         <v>38991</v>
       </c>
       <c r="B233">
-        <v>83.84907202970057</v>
+        <v>83.86327838233142</v>
       </c>
       <c r="C233">
-        <v>91.38525043888581</v>
+        <v>91.385028262104</v>
       </c>
     </row>
     <row r="234">
@@ -2935,10 +2935,10 @@
         <v>39083</v>
       </c>
       <c r="B234">
-        <v>84.04248427232265</v>
+        <v>84.04880178202167</v>
       </c>
       <c r="C234">
-        <v>91.77811429324264</v>
+        <v>91.77842599004181</v>
       </c>
     </row>
     <row r="235">
@@ -2946,10 +2946,10 @@
         <v>39173</v>
       </c>
       <c r="B235">
-        <v>84.31904319073432</v>
+        <v>84.31948264191209</v>
       </c>
       <c r="C235">
-        <v>92.45254069073778</v>
+        <v>92.45257156694012</v>
       </c>
     </row>
     <row r="236">
@@ -2957,10 +2957,10 @@
         <v>39264</v>
       </c>
       <c r="B236">
-        <v>84.73607364753261</v>
+        <v>84.74149296267663</v>
       </c>
       <c r="C236">
-        <v>93.12483644314916</v>
+        <v>93.1249777535256</v>
       </c>
     </row>
     <row r="237">
@@ -2968,10 +2968,10 @@
         <v>39356</v>
       </c>
       <c r="B237">
-        <v>85.52598625233222</v>
+        <v>85.53873376664329</v>
       </c>
       <c r="C237">
-        <v>94.12013974935465</v>
+        <v>94.12074068989851</v>
       </c>
     </row>
     <row r="238">
@@ -2979,10 +2979,10 @@
         <v>39448</v>
       </c>
       <c r="B238">
-        <v>86.31051496073651</v>
+        <v>86.3228147041162</v>
       </c>
       <c r="C238">
-        <v>95.00737246164488</v>
+        <v>95.00745975394457</v>
       </c>
     </row>
     <row r="239">
@@ -2990,10 +2990,10 @@
         <v>39539</v>
       </c>
       <c r="B239">
-        <v>86.51290209587718</v>
+        <v>86.51406515220906</v>
       </c>
       <c r="C239">
-        <v>95.92849851020769</v>
+        <v>95.92878603397261</v>
       </c>
     </row>
     <row r="240">
@@ -3001,10 +3001,10 @@
         <v>39630</v>
       </c>
       <c r="B240">
-        <v>87.09380495236893</v>
+        <v>87.10374899432645</v>
       </c>
       <c r="C240">
-        <v>95.91635187121128</v>
+        <v>95.91649730012483</v>
       </c>
     </row>
     <row r="241">
@@ -3012,10 +3012,10 @@
         <v>39722</v>
       </c>
       <c r="B241">
-        <v>87.00249595122007</v>
+        <v>87.0056224320783</v>
       </c>
       <c r="C241">
-        <v>95.00425682243738</v>
+        <v>95.00485234637809</v>
       </c>
     </row>
     <row r="242">
@@ -3023,10 +3023,10 @@
         <v>39814</v>
       </c>
       <c r="B242">
-        <v>87.1055567443439</v>
+        <v>87.11308807390495</v>
       </c>
       <c r="C242">
-        <v>94.31664932209051</v>
+        <v>94.31673382488874</v>
       </c>
     </row>
     <row r="243">
@@ -3034,10 +3034,10 @@
         <v>39904</v>
       </c>
       <c r="B243">
-        <v>87.35022163220142</v>
+        <v>87.36520714446702</v>
       </c>
       <c r="C243">
-        <v>93.86807434880316</v>
+        <v>93.86837043456096</v>
       </c>
     </row>
     <row r="244">
@@ -3045,10 +3045,10 @@
         <v>39995</v>
       </c>
       <c r="B244">
-        <v>87.96239509307728</v>
+        <v>87.96651452566719</v>
       </c>
       <c r="C244">
-        <v>93.78520857056715</v>
+        <v>93.78491749829244</v>
       </c>
     </row>
     <row r="245">
@@ -3056,10 +3056,10 @@
         <v>40087</v>
       </c>
       <c r="B245">
-        <v>88.68893346094082</v>
+        <v>88.68963139747207</v>
       </c>
       <c r="C245">
-        <v>93.88780829528763</v>
+        <v>93.88808468224255</v>
       </c>
     </row>
     <row r="246">
@@ -3067,10 +3067,10 @@
         <v>40179</v>
       </c>
       <c r="B246">
-        <v>89.53539565030655</v>
+        <v>89.54312057922292</v>
       </c>
       <c r="C246">
-        <v>94.48618274225042</v>
+        <v>94.48668055384665</v>
       </c>
     </row>
     <row r="247">
@@ -3078,10 +3078,10 @@
         <v>40269</v>
       </c>
       <c r="B247">
-        <v>90.20082359520035</v>
+        <v>90.21604903937934</v>
       </c>
       <c r="C247">
-        <v>95.0039841026079</v>
+        <v>95.00421393825866</v>
       </c>
     </row>
     <row r="248">
@@ -3089,10 +3089,10 @@
         <v>40360</v>
       </c>
       <c r="B248">
-        <v>90.52442208125221</v>
+        <v>90.52429482756892</v>
       </c>
       <c r="C248">
-        <v>95.1896270838688</v>
+        <v>95.1900380725255</v>
       </c>
     </row>
     <row r="249">
@@ -3100,10 +3100,10 @@
         <v>40452</v>
       </c>
       <c r="B249">
-        <v>90.77688498948177</v>
+        <v>90.78173283783397</v>
       </c>
       <c r="C249">
-        <v>95.53910935401075</v>
+        <v>95.53936974189719</v>
       </c>
     </row>
     <row r="250">
@@ -3111,10 +3111,10 @@
         <v>40544</v>
       </c>
       <c r="B250">
-        <v>91.40687672111825</v>
+        <v>91.41178066976599</v>
       </c>
       <c r="C250">
-        <v>96.23693814637882</v>
+        <v>96.23780123547989</v>
       </c>
     </row>
     <row r="251">
@@ -3122,10 +3122,10 @@
         <v>40634</v>
       </c>
       <c r="B251">
-        <v>91.52094365927718</v>
+        <v>91.52733353912843</v>
       </c>
       <c r="C251">
-        <v>96.70561587594672</v>
+        <v>96.7058224689938</v>
       </c>
     </row>
     <row r="252">
@@ -3133,10 +3133,10 @@
         <v>40725</v>
       </c>
       <c r="B252">
-        <v>91.60150689929583</v>
+        <v>91.61034732208077</v>
       </c>
       <c r="C252">
-        <v>96.93997434432674</v>
+        <v>96.93979518632867</v>
       </c>
     </row>
     <row r="253">
@@ -3144,10 +3144,10 @@
         <v>40817</v>
       </c>
       <c r="B253">
-        <v>92.21074228639337</v>
+        <v>92.21816163367998</v>
       </c>
       <c r="C253">
-        <v>97.31285857736033</v>
+        <v>97.31307344534129</v>
       </c>
     </row>
     <row r="254">
@@ -3155,10 +3155,10 @@
         <v>40909</v>
       </c>
       <c r="B254">
-        <v>92.63054995075855</v>
+        <v>92.63653887661279</v>
       </c>
       <c r="C254">
-        <v>97.95624194321584</v>
+        <v>97.9560884953269</v>
       </c>
     </row>
     <row r="255">
@@ -3166,10 +3166,10 @@
         <v>41000</v>
       </c>
       <c r="B255">
-        <v>92.89333010976429</v>
+        <v>92.8993392506903</v>
       </c>
       <c r="C255">
-        <v>98.16998468882242</v>
+        <v>98.16981887134408</v>
       </c>
     </row>
     <row r="256">
@@ -3177,10 +3177,10 @@
         <v>41091</v>
       </c>
       <c r="B256">
-        <v>93.28456619142985</v>
+        <v>93.29401316316023</v>
       </c>
       <c r="C256">
-        <v>98.18550134201426</v>
+        <v>98.1856848396062</v>
       </c>
     </row>
     <row r="257">
@@ -3188,10 +3188,10 @@
         <v>41183</v>
       </c>
       <c r="B257">
-        <v>93.78583238875335</v>
+        <v>93.79190729666198</v>
       </c>
       <c r="C257">
-        <v>98.32613025236412</v>
+        <v>98.32668854574796</v>
       </c>
     </row>
     <row r="258">
@@ -3199,10 +3199,10 @@
         <v>41275</v>
       </c>
       <c r="B258">
-        <v>93.79059030698264</v>
+        <v>93.79764058600605</v>
       </c>
       <c r="C258">
-        <v>98.72280913246685</v>
+        <v>98.72300577194974</v>
       </c>
     </row>
     <row r="259">
@@ -3210,10 +3210,10 @@
         <v>41365</v>
       </c>
       <c r="B259">
-        <v>94.3706851229628</v>
+        <v>94.37582561321287</v>
       </c>
       <c r="C259">
-        <v>98.70105336621135</v>
+        <v>98.70124463702223</v>
       </c>
     </row>
     <row r="260">
@@ -3221,10 +3221,10 @@
         <v>41456</v>
       </c>
       <c r="B260">
-        <v>94.83511642527392</v>
+        <v>94.8446865515841</v>
       </c>
       <c r="C260">
-        <v>98.88383780079147</v>
+        <v>98.88367808462714</v>
       </c>
     </row>
     <row r="261">
@@ -3232,10 +3232,10 @@
         <v>41548</v>
       </c>
       <c r="B261">
-        <v>94.84996149092252</v>
+        <v>94.85608690041937</v>
       </c>
       <c r="C261">
-        <v>98.86163605166423</v>
+        <v>98.86183169673265</v>
       </c>
     </row>
     <row r="262">
@@ -3243,10 +3243,10 @@
         <v>41640</v>
       </c>
       <c r="B262">
-        <v>95.14660358228411</v>
+        <v>95.1532690435531</v>
       </c>
       <c r="C262">
-        <v>99.07150414739614</v>
+        <v>99.07205310369234</v>
       </c>
     </row>
     <row r="263">
@@ -3254,10 +3254,10 @@
         <v>41730</v>
       </c>
       <c r="B263">
-        <v>95.4500860418234</v>
+        <v>95.45531491456708</v>
       </c>
       <c r="C263">
-        <v>98.90293882328419</v>
+        <v>98.90313420448361</v>
       </c>
     </row>
     <row r="264">
@@ -3265,10 +3265,10 @@
         <v>41821</v>
       </c>
       <c r="B264">
-        <v>95.78858765507395</v>
+        <v>95.80065636552932</v>
       </c>
       <c r="C264">
-        <v>98.8101436724272</v>
+        <v>98.81033832974224</v>
       </c>
     </row>
     <row r="265">
@@ -3276,10 +3276,10 @@
         <v>41913</v>
       </c>
       <c r="B265">
-        <v>96.06445413447273</v>
+        <v>96.0692389769312</v>
       </c>
       <c r="C265">
-        <v>98.80473739265058</v>
+        <v>98.80458600376818</v>
       </c>
     </row>
     <row r="266">
@@ -3287,10 +3287,10 @@
         <v>42005</v>
       </c>
       <c r="B266">
-        <v>96.29371435732395</v>
+        <v>96.301927789441</v>
       </c>
       <c r="C266">
-        <v>98.83120492830074</v>
+        <v>98.83140081665245</v>
       </c>
     </row>
     <row r="267">
@@ -3298,10 +3298,10 @@
         <v>42095</v>
       </c>
       <c r="B267">
-        <v>96.71661237726561</v>
+        <v>96.72343548543277</v>
       </c>
       <c r="C267">
-        <v>99.28956843274614</v>
+        <v>99.28978932498825</v>
       </c>
     </row>
     <row r="268">
@@ -3309,10 +3309,10 @@
         <v>42186</v>
       </c>
       <c r="B268">
-        <v>97.11009077332551</v>
+        <v>97.1217702795559</v>
       </c>
       <c r="C268">
-        <v>99.25697930370173</v>
+        <v>99.2575200982575</v>
       </c>
     </row>
     <row r="269">
@@ -3320,10 +3320,10 @@
         <v>42278</v>
       </c>
       <c r="B269">
-        <v>97.59251136079732</v>
+        <v>97.5959604628888</v>
       </c>
       <c r="C269">
-        <v>99.24460655995659</v>
+        <v>99.24479010148755</v>
       </c>
     </row>
     <row r="270">
@@ -3331,10 +3331,10 @@
         <v>42370</v>
       </c>
       <c r="B270">
-        <v>98.1759886007292</v>
+        <v>98.18235057027779</v>
       </c>
       <c r="C270">
-        <v>99.04252473143509</v>
+        <v>99.04306027014178</v>
       </c>
     </row>
     <row r="271">
@@ -3342,10 +3342,10 @@
         <v>42461</v>
       </c>
       <c r="B271">
-        <v>98.05028672304671</v>
+        <v>98.06302824027547</v>
       </c>
       <c r="C271">
-        <v>99.34165322313908</v>
+        <v>99.3418894555809</v>
       </c>
     </row>
     <row r="272">
@@ -3353,10 +3353,10 @@
         <v>42552</v>
       </c>
       <c r="B272">
-        <v>98.37229535501157</v>
+        <v>98.37100232729922</v>
       </c>
       <c r="C272">
-        <v>99.45153009060735</v>
+        <v>99.45136703046906</v>
       </c>
     </row>
     <row r="273">
@@ -3364,10 +3364,10 @@
         <v>42644</v>
       </c>
       <c r="B273">
-        <v>98.90427706072245</v>
+        <v>98.91604450200771</v>
       </c>
       <c r="C273">
-        <v>99.68499074622957</v>
+        <v>99.68514673420442</v>
       </c>
     </row>
     <row r="274">
@@ -3375,10 +3375,10 @@
         <v>42736</v>
       </c>
       <c r="B274">
-        <v>99.79100041125871</v>
+        <v>99.79370523770771</v>
       </c>
       <c r="C274">
-        <v>100.0052482074686</v>
+        <v>100.0057421393981</v>
       </c>
     </row>
     <row r="275">
@@ -3397,10 +3397,10 @@
         <v>42917</v>
       </c>
       <c r="B276">
-        <v>100.3868246317988</v>
+        <v>100.3990607554662</v>
       </c>
       <c r="C276">
-        <v>100.101645718722</v>
+        <v>100.1014514845771</v>
       </c>
     </row>
     <row r="277">
@@ -3408,10 +3408,10 @@
         <v>43009</v>
       </c>
       <c r="B277">
-        <v>101.1880792198653</v>
+        <v>101.2037275624249</v>
       </c>
       <c r="C277">
-        <v>100.6275112571777</v>
+        <v>100.6283086615361</v>
       </c>
     </row>
     <row r="278">
@@ -3419,10 +3419,10 @@
         <v>43101</v>
       </c>
       <c r="B278">
-        <v>101.2052167733296</v>
+        <v>101.2035349607754</v>
       </c>
       <c r="C278">
-        <v>101.2534192413517</v>
+        <v>101.2532143201268</v>
       </c>
     </row>
     <row r="279">
@@ -3430,10 +3430,10 @@
         <v>43191</v>
       </c>
       <c r="B279">
-        <v>101.7161106601846</v>
+        <v>101.7158481224675</v>
       </c>
       <c r="C279">
-        <v>101.8668506892039</v>
+        <v>101.8675122001909</v>
       </c>
     </row>
     <row r="280">
@@ -3441,10 +3441,10 @@
         <v>43282</v>
       </c>
       <c r="B280">
-        <v>102.350493662293</v>
+        <v>102.3636723414485</v>
       </c>
       <c r="C280">
-        <v>102.1542348628747</v>
+        <v>102.1542940363568</v>
       </c>
     </row>
     <row r="281">
@@ -3452,10 +3452,10 @@
         <v>43374</v>
       </c>
       <c r="B281">
-        <v>102.8353220165298</v>
+        <v>102.8542059689907</v>
       </c>
       <c r="C281">
-        <v>102.2357171968646</v>
+        <v>102.2366340734824</v>
       </c>
     </row>
     <row r="282">
@@ -3463,10 +3463,10 @@
         <v>43466</v>
       </c>
       <c r="B282">
-        <v>101.461732750486</v>
+        <v>101.4456990750787</v>
       </c>
       <c r="C282">
-        <v>102.2035090014158</v>
+        <v>102.2026705054403</v>
       </c>
     </row>
     <row r="283">
@@ -3474,10 +3474,10 @@
         <v>43556</v>
       </c>
       <c r="B283">
-        <v>101.084677442844</v>
+        <v>101.0753516031973</v>
       </c>
       <c r="C283">
-        <v>102.5944029480282</v>
+        <v>102.5952643059863</v>
       </c>
     </row>
     <row r="284">
@@ -3485,10 +3485,10 @@
         <v>43647</v>
       </c>
       <c r="B284">
-        <v>101.3293104594114</v>
+        <v>101.3566636066574</v>
       </c>
       <c r="C284">
-        <v>102.8826275860999</v>
+        <v>102.8823595735206</v>
       </c>
     </row>
     <row r="285">
@@ -3496,10 +3496,10 @@
         <v>43739</v>
       </c>
       <c r="B285">
-        <v>101.0528059855579</v>
+        <v>101.0803236382015</v>
       </c>
       <c r="C285">
-        <v>103.1963409932544</v>
+        <v>103.1972961908302</v>
       </c>
     </row>
     <row r="286">
@@ -3507,10 +3507,10 @@
         <v>43831</v>
       </c>
       <c r="B286">
-        <v>97.36419918205101</v>
+        <v>97.33148014554892</v>
       </c>
       <c r="C286">
-        <v>103.4651477947219</v>
+        <v>103.4641614507136</v>
       </c>
     </row>
     <row r="287">
@@ -3518,10 +3518,10 @@
         <v>43922</v>
       </c>
       <c r="B287">
-        <v>85.86881199454449</v>
+        <v>85.83385313810351</v>
       </c>
       <c r="C287">
-        <v>103.6071434698978</v>
+        <v>103.6094364633104</v>
       </c>
     </row>
     <row r="288">
@@ -3529,10 +3529,10 @@
         <v>44013</v>
       </c>
       <c r="B288">
-        <v>99.19201612566756</v>
+        <v>99.26097740462409</v>
       </c>
       <c r="C288">
-        <v>103.64685052215</v>
+        <v>103.6436630871348</v>
       </c>
     </row>
     <row r="289">
@@ -3540,10 +3540,10 @@
         <v>44105</v>
       </c>
       <c r="B289">
-        <v>97.64132805061494</v>
+        <v>97.66820056979779</v>
       </c>
       <c r="C289">
-        <v>103.7928486934079</v>
+        <v>103.7955385741272</v>
       </c>
     </row>
     <row r="290">
@@ -3551,10 +3551,10 @@
         <v>44197</v>
       </c>
       <c r="B290">
-        <v>97.72639657567603</v>
+        <v>97.65370536609946</v>
       </c>
       <c r="C290">
-        <v>104.33525667428</v>
+        <v>104.33456195056</v>
       </c>
     </row>
     <row r="291">
@@ -3562,10 +3562,10 @@
         <v>44287</v>
       </c>
       <c r="B291">
-        <v>98.72711120133927</v>
+        <v>98.66235214052463</v>
       </c>
       <c r="C291">
-        <v>104.7026782679764</v>
+        <v>104.7061265604165</v>
       </c>
     </row>
     <row r="292">
@@ -3573,10 +3573,10 @@
         <v>44378</v>
       </c>
       <c r="B292">
-        <v>101.8142328323101</v>
+        <v>101.9483964079498</v>
       </c>
       <c r="C292">
-        <v>105.4410501467152</v>
+        <v>105.4389547994154</v>
       </c>
     </row>
     <row r="293">
@@ -3584,10 +3584,10 @@
         <v>44470</v>
       </c>
       <c r="B293">
-        <v>102.4758041052214</v>
+        <v>102.5053694683767</v>
       </c>
       <c r="C293">
-        <v>106.1729232895291</v>
+        <v>106.1723697945148</v>
       </c>
     </row>
     <row r="294">
@@ -3595,10 +3595,10 @@
         <v>44562</v>
       </c>
       <c r="B294">
-        <v>103.8106126244964</v>
+        <v>103.7385580011679</v>
       </c>
       <c r="C294">
-        <v>107.3764084269686</v>
+        <v>107.3701517505474</v>
       </c>
     </row>
     <row r="295">
@@ -3606,10 +3606,10 @@
         <v>44652</v>
       </c>
       <c r="B295">
-        <v>104.442419285234</v>
+        <v>104.4024471701864</v>
       </c>
       <c r="C295">
-        <v>109.3326203326845</v>
+        <v>109.336752549737</v>
       </c>
     </row>
     <row r="296">
@@ -3617,10 +3617,10 @@
         <v>44743</v>
       </c>
       <c r="B296">
-        <v>104.6260302644137</v>
+        <v>104.7688762870786</v>
       </c>
       <c r="C296">
-        <v>111.190145889789</v>
+        <v>111.1880528573855</v>
       </c>
     </row>
     <row r="297">
@@ -3628,10 +3628,10 @@
         <v>44835</v>
       </c>
       <c r="B297">
-        <v>106.8746719334606</v>
+        <v>106.8745886329225</v>
       </c>
       <c r="C297">
-        <v>113.1851949125848</v>
+        <v>113.18902728244</v>
       </c>
     </row>
     <row r="298">
@@ -3639,10 +3639,10 @@
         <v>44927</v>
       </c>
       <c r="B298">
-        <v>108.2193766337159</v>
+        <v>108.1156625788259</v>
       </c>
       <c r="C298">
-        <v>115.4207509252739</v>
+        <v>115.4161586674342</v>
       </c>
     </row>
     <row r="299">
@@ -3650,18 +3650,21 @@
         <v>45017</v>
       </c>
       <c r="B299">
-        <v>108.9655538459786</v>
+        <v>108.7867814371502</v>
       </c>
       <c r="C299">
-        <v>117.0195997976178</v>
+        <v>117.0286599117481</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2">
         <v>45108</v>
       </c>
+      <c r="B300">
+        <v>108.8654155644608</v>
+      </c>
       <c r="C300">
-        <v>118.1942499103857</v>
+        <v>118.2025797171333</v>
       </c>
     </row>
   </sheetData>

--- a/Conjoncture - comptes trimestriels/data/smpt.xlsx
+++ b/Conjoncture - comptes trimestriels/data/smpt.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C300"/>
+  <dimension ref="A1:C301"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -383,10 +383,10 @@
         <v>17899</v>
       </c>
       <c r="B2">
-        <v>0.8487030417456893</v>
+        <v>0.848603381923972</v>
       </c>
       <c r="C2">
-        <v>5.189477122925738</v>
+        <v>5.189544045164789</v>
       </c>
     </row>
     <row r="3">
@@ -394,10 +394,10 @@
         <v>17989</v>
       </c>
       <c r="B3">
-        <v>0.8725141400593007</v>
+        <v>0.8724116841950383</v>
       </c>
       <c r="C3">
-        <v>5.225858184895736</v>
+        <v>5.225925576296143</v>
       </c>
     </row>
     <row r="4">
@@ -405,10 +405,10 @@
         <v>18080</v>
       </c>
       <c r="B4">
-        <v>0.8782678325535485</v>
+        <v>0.8781647010560669</v>
       </c>
       <c r="C4">
-        <v>5.379778194601683</v>
+        <v>5.379847570917224</v>
       </c>
     </row>
     <row r="5">
@@ -416,10 +416,10 @@
         <v>18172</v>
       </c>
       <c r="B5">
-        <v>0.8791047948681274</v>
+        <v>0.8790015650894911</v>
       </c>
       <c r="C5">
-        <v>5.405014886916137</v>
+        <v>5.405084588677946</v>
       </c>
     </row>
     <row r="6">
@@ -427,10 +427,10 @@
         <v>18264</v>
       </c>
       <c r="B6">
-        <v>0.9037461833204795</v>
+        <v>0.9036400600016304</v>
       </c>
       <c r="C6">
-        <v>5.481782893312257</v>
+        <v>5.481853585055668</v>
       </c>
     </row>
     <row r="7">
@@ -438,10 +438,10 @@
         <v>18354</v>
       </c>
       <c r="B7">
-        <v>0.9400195699409354</v>
+        <v>0.9399091871826051</v>
       </c>
       <c r="C7">
-        <v>5.582192330265975</v>
+        <v>5.582264316865145</v>
       </c>
     </row>
     <row r="8">
@@ -449,10 +449,10 @@
         <v>18445</v>
       </c>
       <c r="B8">
-        <v>0.9754604894310465</v>
+        <v>0.9753459449865384</v>
       </c>
       <c r="C8">
-        <v>5.81633307927343</v>
+        <v>5.816408085294944</v>
       </c>
     </row>
     <row r="9">
@@ -460,10 +460,10 @@
         <v>18537</v>
       </c>
       <c r="B9">
-        <v>1.018826979518901</v>
+        <v>1.018707342719991</v>
       </c>
       <c r="C9">
-        <v>5.974501942729528</v>
+        <v>5.974578988458366</v>
       </c>
     </row>
     <row r="10">
@@ -471,10 +471,10 @@
         <v>18629</v>
       </c>
       <c r="B10">
-        <v>1.077093111540529</v>
+        <v>1.076966632781541</v>
       </c>
       <c r="C10">
-        <v>6.279101835074435</v>
+        <v>6.27918280884965</v>
       </c>
     </row>
     <row r="11">
@@ -482,10 +482,10 @@
         <v>18719</v>
       </c>
       <c r="B11">
-        <v>1.166599491881791</v>
+        <v>1.166462502744651</v>
       </c>
       <c r="C11">
-        <v>6.602346771420556</v>
+        <v>6.602431913684114</v>
       </c>
     </row>
     <row r="12">
@@ -493,10 +493,10 @@
         <v>18810</v>
       </c>
       <c r="B12">
-        <v>1.273015300138091</v>
+        <v>1.272865815015952</v>
       </c>
       <c r="C12">
-        <v>6.846056861993312</v>
+        <v>6.846145147083122</v>
       </c>
     </row>
     <row r="13">
@@ -504,10 +504,10 @@
         <v>18902</v>
       </c>
       <c r="B13">
-        <v>1.371965622371675</v>
+        <v>1.371804517906859</v>
       </c>
       <c r="C13">
-        <v>7.194751787933838</v>
+        <v>7.194844569708891</v>
       </c>
     </row>
     <row r="14">
@@ -515,10 +515,10 @@
         <v>18994</v>
       </c>
       <c r="B14">
-        <v>1.430285561179866</v>
+        <v>1.430117608436656</v>
       </c>
       <c r="C14">
-        <v>7.435740755494347</v>
+        <v>7.43583664500471</v>
       </c>
     </row>
     <row r="15">
@@ -526,10 +526,10 @@
         <v>19085</v>
       </c>
       <c r="B15">
-        <v>1.467463529668756</v>
+        <v>1.467291211264614</v>
       </c>
       <c r="C15">
-        <v>7.477697399780182</v>
+        <v>7.47779383035326</v>
       </c>
     </row>
     <row r="16">
@@ -537,10 +537,10 @@
         <v>19176</v>
       </c>
       <c r="B16">
-        <v>1.487423156798455</v>
+        <v>1.487248494614707</v>
       </c>
       <c r="C16">
-        <v>7.508825965539629</v>
+        <v>7.508922797539146</v>
       </c>
     </row>
     <row r="17">
@@ -548,10 +548,10 @@
         <v>19268</v>
       </c>
       <c r="B17">
-        <v>1.497363676570055</v>
+        <v>1.497187847110617</v>
       </c>
       <c r="C17">
-        <v>7.478563105195891</v>
+        <v>7.478659546932896</v>
       </c>
     </row>
     <row r="18">
@@ -559,10 +559,10 @@
         <v>19360</v>
       </c>
       <c r="B18">
-        <v>1.50532909424374</v>
+        <v>1.505152329436995</v>
       </c>
       <c r="C18">
-        <v>7.45935095072598</v>
+        <v>7.459447144707698</v>
       </c>
     </row>
     <row r="19">
@@ -570,10 +570,10 @@
         <v>19450</v>
       </c>
       <c r="B19">
-        <v>1.524836692219239</v>
+        <v>1.524657636712872</v>
       </c>
       <c r="C19">
-        <v>7.452175399878026</v>
+        <v>7.45227150132558</v>
       </c>
     </row>
     <row r="20">
@@ -581,10 +581,10 @@
         <v>19541</v>
       </c>
       <c r="B20">
-        <v>1.540381482944507</v>
+        <v>1.540200602075209</v>
       </c>
       <c r="C20">
-        <v>7.453226051081263</v>
+        <v>7.45332216607776</v>
       </c>
     </row>
     <row r="21">
@@ -592,10 +592,10 @@
         <v>19633</v>
       </c>
       <c r="B21">
-        <v>1.563273031196322</v>
+        <v>1.563089462263584</v>
       </c>
       <c r="C21">
-        <v>7.416107865253618</v>
+        <v>7.41620350158299</v>
       </c>
     </row>
     <row r="22">
@@ -603,10 +603,10 @@
         <v>19725</v>
       </c>
       <c r="B22">
-        <v>1.600596800984688</v>
+        <v>1.600408849270152</v>
       </c>
       <c r="C22">
-        <v>7.479498748968888</v>
+        <v>7.479595202771729</v>
       </c>
     </row>
     <row r="23">
@@ -614,10 +614,10 @@
         <v>19815</v>
       </c>
       <c r="B23">
-        <v>1.638989710287666</v>
+        <v>1.638797250246533</v>
       </c>
       <c r="C23">
-        <v>7.539726188748477</v>
+        <v>7.539823419229783</v>
       </c>
     </row>
     <row r="24">
@@ -625,10 +625,10 @@
         <v>19906</v>
       </c>
       <c r="B24">
-        <v>1.658371480646988</v>
+        <v>1.65817674468167</v>
       </c>
       <c r="C24">
-        <v>7.578563694216857</v>
+        <v>7.578661425537217</v>
       </c>
     </row>
     <row r="25">
@@ -636,10 +636,10 @@
         <v>19998</v>
       </c>
       <c r="B25">
-        <v>1.686862557618584</v>
+        <v>1.686664476059446</v>
       </c>
       <c r="C25">
-        <v>7.602453560946233</v>
+        <v>7.602551600344524</v>
       </c>
     </row>
     <row r="26">
@@ -647,10 +647,10 @@
         <v>20090</v>
       </c>
       <c r="B26">
-        <v>1.717220832120077</v>
+        <v>1.717019185709542</v>
       </c>
       <c r="C26">
-        <v>7.566518543469983</v>
+        <v>7.566616119458999</v>
       </c>
     </row>
     <row r="27">
@@ -658,10 +658,10 @@
         <v>20180</v>
       </c>
       <c r="B27">
-        <v>1.752664497715263</v>
+        <v>1.752458689296085</v>
       </c>
       <c r="C27">
-        <v>7.610128146079232</v>
+        <v>7.610226284447112</v>
       </c>
     </row>
     <row r="28">
@@ -669,10 +669,10 @@
         <v>20271</v>
       </c>
       <c r="B28">
-        <v>1.801007884499132</v>
+        <v>1.800796399308374</v>
       </c>
       <c r="C28">
-        <v>7.653559577336823</v>
+        <v>7.653658275785914</v>
       </c>
     </row>
     <row r="29">
@@ -680,10 +680,10 @@
         <v>20363</v>
       </c>
       <c r="B29">
-        <v>1.853428749329307</v>
+        <v>1.853211108564943</v>
       </c>
       <c r="C29">
-        <v>7.741640272614648</v>
+        <v>7.741740106931035</v>
       </c>
     </row>
     <row r="30">
@@ -691,10 +691,10 @@
         <v>20455</v>
       </c>
       <c r="B30">
-        <v>1.902847713437726</v>
+        <v>1.902624269601014</v>
       </c>
       <c r="C30">
-        <v>7.858356237440825</v>
+        <v>7.858457576898002</v>
       </c>
     </row>
     <row r="31">
@@ -702,10 +702,10 @@
         <v>20546</v>
       </c>
       <c r="B31">
-        <v>1.949521291837733</v>
+        <v>1.949292367308396</v>
       </c>
       <c r="C31">
-        <v>7.944513431533384</v>
+        <v>7.944615882052853</v>
       </c>
     </row>
     <row r="32">
@@ -713,10 +713,10 @@
         <v>20637</v>
       </c>
       <c r="B32">
-        <v>1.993400896750483</v>
+        <v>1.993166819613711</v>
       </c>
       <c r="C32">
-        <v>8.069667861824508</v>
+        <v>8.069771926305171</v>
       </c>
     </row>
     <row r="33">
@@ -724,10 +724,10 @@
         <v>20729</v>
       </c>
       <c r="B33">
-        <v>2.033669367880135</v>
+        <v>2.033430562177002</v>
       </c>
       <c r="C33">
-        <v>8.152759916304415</v>
+        <v>8.152865052320072</v>
       </c>
     </row>
     <row r="34">
@@ -735,10 +735,10 @@
         <v>20821</v>
       </c>
       <c r="B34">
-        <v>2.072554674292014</v>
+        <v>2.07231130244205</v>
       </c>
       <c r="C34">
-        <v>8.157004862510414</v>
+        <v>8.157110053267868</v>
       </c>
     </row>
     <row r="35">
@@ -746,10 +746,10 @@
         <v>20911</v>
       </c>
       <c r="B35">
-        <v>2.121248387298058</v>
+        <v>2.120999297539099</v>
       </c>
       <c r="C35">
-        <v>8.304913669393708</v>
+        <v>8.305020767547283</v>
       </c>
     </row>
     <row r="36">
@@ -757,10 +757,10 @@
         <v>21002</v>
       </c>
       <c r="B36">
-        <v>2.184332121284681</v>
+        <v>2.184075623853812</v>
       </c>
       <c r="C36">
-        <v>8.574256594155754</v>
+        <v>8.574367165690399</v>
       </c>
     </row>
     <row r="37">
@@ -768,10 +768,10 @@
         <v>21094</v>
       </c>
       <c r="B37">
-        <v>2.265708844916294</v>
+        <v>2.265442791740517</v>
       </c>
       <c r="C37">
-        <v>8.885856381755156</v>
+        <v>8.885970971605129</v>
       </c>
     </row>
     <row r="38">
@@ -779,10 +779,10 @@
         <v>21186</v>
       </c>
       <c r="B38">
-        <v>2.35514228708477</v>
+        <v>2.354865732095681</v>
       </c>
       <c r="C38">
-        <v>9.25058455113296</v>
+        <v>9.250703844428994</v>
       </c>
     </row>
     <row r="39">
@@ -790,10 +790,10 @@
         <v>21276</v>
       </c>
       <c r="B39">
-        <v>2.434466871953632</v>
+        <v>2.434181002194126</v>
       </c>
       <c r="C39">
-        <v>9.524508222488286</v>
+        <v>9.524631048237588</v>
       </c>
     </row>
     <row r="40">
@@ -801,10 +801,10 @@
         <v>21367</v>
       </c>
       <c r="B40">
-        <v>2.492559813553743</v>
+        <v>2.492267122171221</v>
       </c>
       <c r="C40">
-        <v>9.637643647505802</v>
+        <v>9.63776793222212</v>
       </c>
     </row>
     <row r="41">
@@ -812,10 +812,10 @@
         <v>21459</v>
       </c>
       <c r="B41">
-        <v>2.538513625618631</v>
+        <v>2.538215538062781</v>
       </c>
       <c r="C41">
-        <v>9.723682340241465</v>
+        <v>9.72380773449191</v>
       </c>
     </row>
     <row r="42">
@@ -823,10 +823,10 @@
         <v>21551</v>
       </c>
       <c r="B42">
-        <v>2.598709482941491</v>
+        <v>2.598404326825598</v>
       </c>
       <c r="C42">
-        <v>9.960298672171024</v>
+        <v>9.960427117768329</v>
       </c>
     </row>
     <row r="43">
@@ -834,10 +834,10 @@
         <v>21641</v>
       </c>
       <c r="B43">
-        <v>2.671269107781841</v>
+        <v>2.670955431277874</v>
       </c>
       <c r="C43">
-        <v>10.05929772572433</v>
+        <v>10.05942744798944</v>
       </c>
     </row>
     <row r="44">
@@ -845,10 +845,10 @@
         <v>21732</v>
       </c>
       <c r="B44">
-        <v>2.728107586608925</v>
+        <v>2.727787235788515</v>
       </c>
       <c r="C44">
-        <v>10.15521309460236</v>
+        <v>10.15534405376881</v>
       </c>
     </row>
     <row r="45">
@@ -856,10 +856,10 @@
         <v>21824</v>
       </c>
       <c r="B45">
-        <v>2.781038193802901</v>
+        <v>2.780711627551868</v>
       </c>
       <c r="C45">
-        <v>10.26900331098982</v>
+        <v>10.26913573756732</v>
       </c>
     </row>
     <row r="46">
@@ -867,10 +867,10 @@
         <v>21916</v>
       </c>
       <c r="B46">
-        <v>2.830624927861011</v>
+        <v>2.830292538837072</v>
       </c>
       <c r="C46">
-        <v>10.33636132299141</v>
+        <v>10.3364946182015</v>
       </c>
     </row>
     <row r="47">
@@ -878,10 +878,10 @@
         <v>22007</v>
       </c>
       <c r="B47">
-        <v>2.88496335956685</v>
+        <v>2.884624589797057</v>
       </c>
       <c r="C47">
-        <v>10.40656608519648</v>
+        <v>10.40670028575017</v>
       </c>
     </row>
     <row r="48">
@@ -889,10 +889,10 @@
         <v>22098</v>
       </c>
       <c r="B48">
-        <v>2.954482493037401</v>
+        <v>2.954135559912338</v>
       </c>
       <c r="C48">
-        <v>10.46081359332015</v>
+        <v>10.46094849343656</v>
       </c>
     </row>
     <row r="49">
@@ -900,10 +900,10 @@
         <v>22190</v>
       </c>
       <c r="B49">
-        <v>3.039917157267661</v>
+        <v>3.03956019188987</v>
       </c>
       <c r="C49">
-        <v>10.51615625702681</v>
+        <v>10.51629187082879</v>
       </c>
     </row>
     <row r="50">
@@ -911,10 +911,10 @@
         <v>22282</v>
       </c>
       <c r="B50">
-        <v>3.117615725761611</v>
+        <v>3.117249636550038</v>
       </c>
       <c r="C50">
-        <v>10.56672742121908</v>
+        <v>10.56686368717453</v>
       </c>
     </row>
     <row r="51">
@@ -922,10 +922,10 @@
         <v>22372</v>
       </c>
       <c r="B51">
-        <v>3.21087644291645</v>
+        <v>3.210499402469889</v>
       </c>
       <c r="C51">
-        <v>10.68736629967335</v>
+        <v>10.68750412135854</v>
       </c>
     </row>
     <row r="52">
@@ -933,10 +933,10 @@
         <v>22463</v>
       </c>
       <c r="B52">
-        <v>3.301127307323692</v>
+        <v>3.300739669077177</v>
       </c>
       <c r="C52">
-        <v>10.77363632461003</v>
+        <v>10.77377525881255</v>
       </c>
     </row>
     <row r="53">
@@ -944,10 +944,10 @@
         <v>22555</v>
       </c>
       <c r="B53">
-        <v>3.394170323008489</v>
+        <v>3.393771759090804</v>
       </c>
       <c r="C53">
-        <v>10.88409499340981</v>
+        <v>10.88423535206054</v>
       </c>
     </row>
     <row r="54">
@@ -955,10 +955,10 @@
         <v>22647</v>
       </c>
       <c r="B54">
-        <v>3.491349998086626</v>
+        <v>3.490940022746315</v>
       </c>
       <c r="C54">
-        <v>11.04643055580112</v>
+        <v>11.04657300789192</v>
       </c>
     </row>
     <row r="55">
@@ -966,10 +966,10 @@
         <v>22737</v>
       </c>
       <c r="B55">
-        <v>3.571369154889898</v>
+        <v>3.570949783218352</v>
       </c>
       <c r="C55">
-        <v>11.17071378603539</v>
+        <v>11.17085784085259</v>
       </c>
     </row>
     <row r="56">
@@ -977,10 +977,10 @@
         <v>22828</v>
       </c>
       <c r="B56">
-        <v>3.653062223038746</v>
+        <v>3.652633258475214</v>
       </c>
       <c r="C56">
-        <v>11.24331119922979</v>
+        <v>11.24345619024565</v>
       </c>
     </row>
     <row r="57">
@@ -988,10 +988,10 @@
         <v>22920</v>
       </c>
       <c r="B57">
-        <v>3.74616575942588</v>
+        <v>3.745725862084472</v>
       </c>
       <c r="C57">
-        <v>11.32304529860559</v>
+        <v>11.32319131785306</v>
       </c>
     </row>
     <row r="58">
@@ -999,10 +999,10 @@
         <v>23012</v>
       </c>
       <c r="B58">
-        <v>3.86156116838296</v>
+        <v>3.861107720617766</v>
       </c>
       <c r="C58">
-        <v>11.36466495804996</v>
+        <v>11.36481151401447</v>
       </c>
     </row>
     <row r="59">
@@ -1010,10 +1010,10 @@
         <v>23102</v>
       </c>
       <c r="B59">
-        <v>3.965311212916819</v>
+        <v>3.964845582196655</v>
       </c>
       <c r="C59">
-        <v>11.66030820841311</v>
+        <v>11.66045857692131</v>
       </c>
     </row>
     <row r="60">
@@ -1021,10 +1021,10 @@
         <v>23193</v>
       </c>
       <c r="B60">
-        <v>4.062603445900768</v>
+        <v>4.062126390540752</v>
       </c>
       <c r="C60">
-        <v>11.89548199984712</v>
+        <v>11.89563540109953</v>
       </c>
     </row>
     <row r="61">
@@ -1032,10 +1032,10 @@
         <v>23285</v>
       </c>
       <c r="B61">
-        <v>4.158469485387426</v>
+        <v>4.157981172859786</v>
       </c>
       <c r="C61">
-        <v>11.98109041580252</v>
+        <v>11.98124492104031</v>
       </c>
     </row>
     <row r="62">
@@ -1043,10 +1043,10 @@
         <v>23377</v>
       </c>
       <c r="B62">
-        <v>4.248128446150975</v>
+        <v>4.247629605328271</v>
       </c>
       <c r="C62">
-        <v>11.99516528518524</v>
+        <v>11.99531997192914</v>
       </c>
     </row>
     <row r="63">
@@ -1054,10 +1054,10 @@
         <v>23468</v>
       </c>
       <c r="B63">
-        <v>4.33831700828326</v>
+        <v>4.33780757697651</v>
       </c>
       <c r="C63">
-        <v>12.05995861689193</v>
+        <v>12.06011413919493</v>
       </c>
     </row>
     <row r="64">
@@ -1065,10 +1065,10 @@
         <v>23559</v>
       </c>
       <c r="B64">
-        <v>4.415040909060778</v>
+        <v>4.414522468371597</v>
       </c>
       <c r="C64">
-        <v>12.1584149006382</v>
+        <v>12.15857169260956</v>
       </c>
     </row>
     <row r="65">
@@ -1076,10 +1076,10 @@
         <v>23651</v>
       </c>
       <c r="B65">
-        <v>4.5013423893336</v>
+        <v>4.500813814604933</v>
       </c>
       <c r="C65">
-        <v>12.24629761182867</v>
+        <v>12.24645553711417</v>
       </c>
     </row>
     <row r="66">
@@ -1087,10 +1087,10 @@
         <v>23743</v>
       </c>
       <c r="B66">
-        <v>4.574985482731611</v>
+        <v>4.574448260387467</v>
       </c>
       <c r="C66">
-        <v>12.33681245400449</v>
+        <v>12.33697154654746</v>
       </c>
     </row>
     <row r="67">
@@ -1098,10 +1098,10 @@
         <v>23833</v>
       </c>
       <c r="B67">
-        <v>4.653692842841012</v>
+        <v>4.653146378204699</v>
       </c>
       <c r="C67">
-        <v>12.3879165807077</v>
+        <v>12.38807633227711</v>
       </c>
     </row>
     <row r="68">
@@ -1109,10 +1109,10 @@
         <v>23924</v>
       </c>
       <c r="B68">
-        <v>4.725720693110893</v>
+        <v>4.725165770530678</v>
       </c>
       <c r="C68">
-        <v>12.44230345758115</v>
+        <v>12.44246391051053</v>
       </c>
     </row>
     <row r="69">
@@ -1120,10 +1120,10 @@
         <v>24016</v>
       </c>
       <c r="B69">
-        <v>4.799780525048362</v>
+        <v>4.799216905916722</v>
       </c>
       <c r="C69">
-        <v>12.55666506472923</v>
+        <v>12.55682699243818</v>
       </c>
     </row>
     <row r="70">
@@ -1131,10 +1131,10 @@
         <v>24108</v>
       </c>
       <c r="B70">
-        <v>4.865659574470396</v>
+        <v>4.865088219424075</v>
       </c>
       <c r="C70">
-        <v>12.70304659020117</v>
+        <v>12.70321040561078</v>
       </c>
     </row>
     <row r="71">
@@ -1142,10 +1142,10 @@
         <v>24198</v>
       </c>
       <c r="B71">
-        <v>4.942143684744337</v>
+        <v>4.941563348473231</v>
       </c>
       <c r="C71">
-        <v>12.7447696281188</v>
+        <v>12.7449339815786</v>
       </c>
     </row>
     <row r="72">
@@ -1153,10 +1153,10 @@
         <v>24289</v>
       </c>
       <c r="B72">
-        <v>5.021216303087778</v>
+        <v>5.020626681633682</v>
       </c>
       <c r="C72">
-        <v>12.84425177436374</v>
+        <v>12.84441741072119</v>
       </c>
     </row>
     <row r="73">
@@ -1164,10 +1164,10 @@
         <v>24381</v>
       </c>
       <c r="B73">
-        <v>5.115511824925243</v>
+        <v>5.114911130723162</v>
       </c>
       <c r="C73">
-        <v>12.91700253613859</v>
+        <v>12.91716911067222</v>
       </c>
     </row>
     <row r="74">
@@ -1175,10 +1175,10 @@
         <v>24473</v>
       </c>
       <c r="B74">
-        <v>5.227682707392</v>
+        <v>5.227068841409451</v>
       </c>
       <c r="C74">
-        <v>13.05130230098321</v>
+        <v>13.05147060741405</v>
       </c>
     </row>
     <row r="75">
@@ -1186,10 +1186,10 @@
         <v>24563</v>
       </c>
       <c r="B75">
-        <v>5.301784517208075</v>
+        <v>5.301161949744806</v>
       </c>
       <c r="C75">
-        <v>13.13474966423403</v>
+        <v>13.13491904678184</v>
       </c>
     </row>
     <row r="76">
@@ -1197,10 +1197,10 @@
         <v>24654</v>
       </c>
       <c r="B76">
-        <v>5.3873381247169</v>
+        <v>5.386705511033866</v>
       </c>
       <c r="C76">
-        <v>13.22888402076998</v>
+        <v>13.22905461725163</v>
       </c>
     </row>
     <row r="77">
@@ -1208,10 +1208,10 @@
         <v>24746</v>
       </c>
       <c r="B77">
-        <v>5.493176915362319</v>
+        <v>5.492531873451168</v>
       </c>
       <c r="C77">
-        <v>13.37772434465519</v>
+        <v>13.37789686054558</v>
       </c>
     </row>
     <row r="78">
@@ -1219,10 +1219,10 @@
         <v>24838</v>
       </c>
       <c r="B78">
-        <v>5.665621804609349</v>
+        <v>5.664956513180907</v>
       </c>
       <c r="C78">
-        <v>13.59508360362622</v>
+        <v>13.59525892252894</v>
       </c>
     </row>
     <row r="79">
@@ -1230,10 +1230,10 @@
         <v>24929</v>
       </c>
       <c r="B79">
-        <v>5.682112988596509</v>
+        <v>5.681445760673939</v>
       </c>
       <c r="C79">
-        <v>13.64575595530585</v>
+        <v>13.64593192766693</v>
       </c>
     </row>
     <row r="80">
@@ -1241,10 +1241,10 @@
         <v>25020</v>
       </c>
       <c r="B80">
-        <v>6.213105279207769</v>
+        <v>6.212375698973011</v>
       </c>
       <c r="C80">
-        <v>13.98682271117825</v>
+        <v>13.98700308185354</v>
       </c>
     </row>
     <row r="81">
@@ -1252,10 +1252,10 @@
         <v>25112</v>
       </c>
       <c r="B81">
-        <v>6.356509443802265</v>
+        <v>6.355763024186976</v>
       </c>
       <c r="C81">
-        <v>14.19263184111955</v>
+        <v>14.19281486585949</v>
       </c>
     </row>
     <row r="82">
@@ -1263,10 +1263,10 @@
         <v>25204</v>
       </c>
       <c r="B82">
-        <v>6.448164471546014</v>
+        <v>6.447407289245456</v>
       </c>
       <c r="C82">
-        <v>14.56232898561925</v>
+        <v>14.56251677788396</v>
       </c>
     </row>
     <row r="83">
@@ -1274,10 +1274,10 @@
         <v>25294</v>
       </c>
       <c r="B83">
-        <v>6.583976221206539</v>
+        <v>6.583203091072532</v>
       </c>
       <c r="C83">
-        <v>14.73433257823841</v>
+        <v>14.73452258861975</v>
       </c>
     </row>
     <row r="84">
@@ -1285,10 +1285,10 @@
         <v>25385</v>
       </c>
       <c r="B84">
-        <v>6.737027345682642</v>
+        <v>6.736236243363986</v>
       </c>
       <c r="C84">
-        <v>14.9232695216981</v>
+        <v>14.92346196856445</v>
       </c>
     </row>
     <row r="85">
@@ -1296,10 +1296,10 @@
         <v>25477</v>
       </c>
       <c r="B85">
-        <v>6.946812825580276</v>
+        <v>6.945997088987324</v>
       </c>
       <c r="C85">
-        <v>15.1509050513796</v>
+        <v>15.15110043377857</v>
       </c>
     </row>
     <row r="86">
@@ -1307,10 +1307,10 @@
         <v>25569</v>
       </c>
       <c r="B86">
-        <v>7.169763536084016</v>
+        <v>7.168921619276116</v>
       </c>
       <c r="C86">
-        <v>15.27444918601629</v>
+        <v>15.27464616161047</v>
       </c>
     </row>
     <row r="87">
@@ -1318,10 +1318,10 @@
         <v>25659</v>
       </c>
       <c r="B87">
-        <v>7.349577855509606</v>
+        <v>7.348714823821548</v>
       </c>
       <c r="C87">
-        <v>15.4900412618623</v>
+        <v>15.49024101767963</v>
       </c>
     </row>
     <row r="88">
@@ -1329,10 +1329,10 @@
         <v>25750</v>
       </c>
       <c r="B88">
-        <v>7.531382674391877</v>
+        <v>7.530498294087229</v>
       </c>
       <c r="C88">
-        <v>15.7041876412904</v>
+        <v>15.70439015868754</v>
       </c>
     </row>
     <row r="89">
@@ -1340,10 +1340,10 @@
         <v>25842</v>
       </c>
       <c r="B89">
-        <v>7.750641657676089</v>
+        <v>7.749731530661333</v>
       </c>
       <c r="C89">
-        <v>15.85543389692546</v>
+        <v>15.85563836475764</v>
       </c>
     </row>
     <row r="90">
@@ -1351,10 +1351,10 @@
         <v>25934</v>
       </c>
       <c r="B90">
-        <v>7.995729766307447</v>
+        <v>7.99479085957115</v>
       </c>
       <c r="C90">
-        <v>16.09034298620605</v>
+        <v>16.09055048336892</v>
       </c>
     </row>
     <row r="91">
@@ -1362,10 +1362,10 @@
         <v>26024</v>
       </c>
       <c r="B91">
-        <v>8.183381845921405</v>
+        <v>8.182420903947953</v>
       </c>
       <c r="C91">
-        <v>16.36629984756853</v>
+        <v>16.36651090340419</v>
       </c>
     </row>
     <row r="92">
@@ -1373,10 +1373,10 @@
         <v>26115</v>
       </c>
       <c r="B92">
-        <v>8.415345636080222</v>
+        <v>8.414357455521735</v>
       </c>
       <c r="C92">
-        <v>16.56289134455206</v>
+        <v>16.563104935584</v>
       </c>
     </row>
     <row r="93">
@@ -1384,10 +1384,10 @@
         <v>26207</v>
       </c>
       <c r="B93">
-        <v>8.653981657333711</v>
+        <v>8.652965454696636</v>
       </c>
       <c r="C93">
-        <v>16.81567053717611</v>
+        <v>16.81588738798725</v>
       </c>
     </row>
     <row r="94">
@@ -1395,10 +1395,10 @@
         <v>26299</v>
       </c>
       <c r="B94">
-        <v>8.819253614891066</v>
+        <v>8.818218005025532</v>
       </c>
       <c r="C94">
-        <v>17.01277813486768</v>
+        <v>17.01299752753062</v>
       </c>
     </row>
     <row r="95">
@@ -1406,10 +1406,10 @@
         <v>26390</v>
       </c>
       <c r="B95">
-        <v>9.046599425314426</v>
+        <v>9.045537119134844</v>
       </c>
       <c r="C95">
-        <v>17.25905337179442</v>
+        <v>17.25927594036311</v>
       </c>
     </row>
     <row r="96">
@@ -1417,10 +1417,10 @@
         <v>26481</v>
       </c>
       <c r="B96">
-        <v>9.283904740981287</v>
+        <v>9.282814568982582</v>
       </c>
       <c r="C96">
-        <v>17.5666131533814</v>
+        <v>17.56683968816649</v>
       </c>
     </row>
     <row r="97">
@@ -1428,10 +1428,10 @@
         <v>26573</v>
       </c>
       <c r="B97">
-        <v>9.590208145378028</v>
+        <v>9.589082005389141</v>
       </c>
       <c r="C97">
-        <v>17.86573101162382</v>
+        <v>17.8659614037603</v>
       </c>
     </row>
     <row r="98">
@@ -1439,10 +1439,10 @@
         <v>26665</v>
       </c>
       <c r="B98">
-        <v>9.885318630248477</v>
+        <v>9.884157836609415</v>
       </c>
       <c r="C98">
-        <v>18.02852224950389</v>
+        <v>18.02875474095671</v>
       </c>
     </row>
     <row r="99">
@@ -1450,10 +1450,10 @@
         <v>26755</v>
       </c>
       <c r="B99">
-        <v>10.1955475482898</v>
+        <v>10.1943503257031</v>
       </c>
       <c r="C99">
-        <v>18.38665299388528</v>
+        <v>18.38689010370538</v>
       </c>
     </row>
     <row r="100">
@@ -1461,10 +1461,10 @@
         <v>26846</v>
       </c>
       <c r="B100">
-        <v>10.56772473238155</v>
+        <v>10.56648380650879</v>
       </c>
       <c r="C100">
-        <v>18.90343966921015</v>
+        <v>18.90368344338594</v>
       </c>
     </row>
     <row r="101">
@@ -1472,10 +1472,10 @@
         <v>26938</v>
       </c>
       <c r="B101">
-        <v>10.93039350383435</v>
+        <v>10.9291099912106</v>
       </c>
       <c r="C101">
-        <v>19.44107533347511</v>
+        <v>19.44132604087011</v>
       </c>
     </row>
     <row r="102">
@@ -1483,10 +1483,10 @@
         <v>27030</v>
       </c>
       <c r="B102">
-        <v>11.40991805896761</v>
+        <v>11.40857823768309</v>
       </c>
       <c r="C102">
-        <v>20.2839180125408</v>
+        <v>20.28417958903068</v>
       </c>
     </row>
     <row r="103">
@@ -1494,10 +1494,10 @@
         <v>27120</v>
       </c>
       <c r="B103">
-        <v>11.94537964086643</v>
+        <v>11.94397694245862</v>
       </c>
       <c r="C103">
-        <v>21.09796687954457</v>
+        <v>21.09823895381131</v>
       </c>
     </row>
     <row r="104">
@@ -1505,10 +1505,10 @@
         <v>27211</v>
       </c>
       <c r="B104">
-        <v>12.53772256950831</v>
+        <v>12.53625031462697</v>
       </c>
       <c r="C104">
-        <v>21.78103684303322</v>
+        <v>21.78131772600464</v>
       </c>
     </row>
     <row r="105">
@@ -1516,10 +1516,10 @@
         <v>27303</v>
       </c>
       <c r="B105">
-        <v>12.9889380658467</v>
+        <v>12.98741282652474</v>
       </c>
       <c r="C105">
-        <v>22.40077596256534</v>
+        <v>22.40106483754222</v>
       </c>
     </row>
     <row r="106">
@@ -1527,10 +1527,10 @@
         <v>27395</v>
       </c>
       <c r="B106">
-        <v>13.66344305332002</v>
+        <v>13.66183860956082</v>
       </c>
       <c r="C106">
-        <v>23.05622847431971</v>
+        <v>23.0565258018533</v>
       </c>
     </row>
     <row r="107">
@@ -1538,10 +1538,10 @@
         <v>27485</v>
       </c>
       <c r="B107">
-        <v>14.25671159336616</v>
+        <v>14.25503748444256</v>
       </c>
       <c r="C107">
-        <v>23.65012125178656</v>
+        <v>23.65042623801745</v>
       </c>
     </row>
     <row r="108">
@@ -1549,10 +1549,10 @@
         <v>27576</v>
       </c>
       <c r="B108">
-        <v>14.74196387399385</v>
+        <v>14.74023278382546</v>
       </c>
       <c r="C108">
-        <v>24.14758579129904</v>
+        <v>24.14789719271204</v>
       </c>
     </row>
     <row r="109">
@@ -1560,10 +1560,10 @@
         <v>27668</v>
       </c>
       <c r="B109">
-        <v>15.21798562335221</v>
+        <v>15.2161986358436</v>
       </c>
       <c r="C109">
-        <v>24.6483238703854</v>
+        <v>24.6486417291953</v>
       </c>
     </row>
     <row r="110">
@@ -1571,10 +1571,10 @@
         <v>27760</v>
       </c>
       <c r="B110">
-        <v>15.74746938605124</v>
+        <v>15.74562022337087</v>
       </c>
       <c r="C110">
-        <v>25.28023910768438</v>
+        <v>25.28056511551999</v>
       </c>
     </row>
     <row r="111">
@@ -1582,10 +1582,10 @@
         <v>27851</v>
       </c>
       <c r="B111">
-        <v>16.31250281707611</v>
+        <v>16.31058730476786</v>
       </c>
       <c r="C111">
-        <v>25.83219026272924</v>
+        <v>25.83252338839316</v>
       </c>
     </row>
     <row r="112">
@@ -1593,10 +1593,10 @@
         <v>27942</v>
       </c>
       <c r="B112">
-        <v>16.86354284080139</v>
+        <v>16.8615626220554</v>
       </c>
       <c r="C112">
-        <v>26.44839222336624</v>
+        <v>26.44873329542128</v>
       </c>
     </row>
     <row r="113">
@@ -1604,10 +1604,10 @@
         <v>28034</v>
       </c>
       <c r="B113">
-        <v>17.39519421238879</v>
+        <v>17.39315156393737</v>
       </c>
       <c r="C113">
-        <v>27.12145251586284</v>
+        <v>27.12180226754026</v>
       </c>
     </row>
     <row r="114">
@@ -1615,10 +1615,10 @@
         <v>28126</v>
       </c>
       <c r="B114">
-        <v>17.8740765464311</v>
+        <v>17.87197766473236</v>
       </c>
       <c r="C114">
-        <v>27.60028655398523</v>
+        <v>27.60064248059034</v>
       </c>
     </row>
     <row r="115">
@@ -1626,10 +1626,10 @@
         <v>28216</v>
       </c>
       <c r="B115">
-        <v>18.26944004818582</v>
+        <v>18.26729474052399</v>
       </c>
       <c r="C115">
-        <v>28.3806969802758</v>
+        <v>28.38106297086459</v>
       </c>
     </row>
     <row r="116">
@@ -1637,10 +1637,10 @@
         <v>28307</v>
       </c>
       <c r="B116">
-        <v>18.75761709743543</v>
+        <v>18.75541446508486</v>
       </c>
       <c r="C116">
-        <v>28.99813031009643</v>
+        <v>28.99850426295578</v>
       </c>
     </row>
     <row r="117">
@@ -1648,10 +1648,10 @@
         <v>28399</v>
       </c>
       <c r="B117">
-        <v>19.31913151410873</v>
+        <v>19.31686294535413</v>
       </c>
       <c r="C117">
-        <v>29.48683901126345</v>
+        <v>29.48721926639174</v>
       </c>
     </row>
     <row r="118">
@@ -1659,10 +1659,10 @@
         <v>28491</v>
       </c>
       <c r="B118">
-        <v>19.83896643373747</v>
+        <v>19.83663682283638</v>
       </c>
       <c r="C118">
-        <v>29.92567210668582</v>
+        <v>29.92605802089934</v>
       </c>
     </row>
     <row r="119">
@@ -1670,10 +1670,10 @@
         <v>28581</v>
       </c>
       <c r="B119">
-        <v>20.43144552491098</v>
+        <v>20.42904634154732</v>
       </c>
       <c r="C119">
-        <v>30.66306059908497</v>
+        <v>30.66345602248174</v>
       </c>
     </row>
     <row r="120">
@@ -1681,10 +1681,10 @@
         <v>28672</v>
       </c>
       <c r="B120">
-        <v>21.06983474024759</v>
+        <v>21.06736059337814</v>
       </c>
       <c r="C120">
-        <v>31.54007584907503</v>
+        <v>31.54048258224788</v>
       </c>
     </row>
     <row r="121">
@@ -1692,10 +1692,10 @@
         <v>28764</v>
       </c>
       <c r="B121">
-        <v>21.66598585011246</v>
+        <v>21.6634416995899</v>
       </c>
       <c r="C121">
-        <v>32.27686982199308</v>
+        <v>32.27728605668241</v>
       </c>
     </row>
     <row r="122">
@@ -1703,10 +1703,10 @@
         <v>28856</v>
       </c>
       <c r="B122">
-        <v>22.27698009651814</v>
+        <v>22.274364199372</v>
       </c>
       <c r="C122">
-        <v>33.01716585265925</v>
+        <v>33.01759163402674</v>
       </c>
     </row>
     <row r="123">
@@ -1714,10 +1714,10 @@
         <v>28946</v>
       </c>
       <c r="B123">
-        <v>23.03398545662965</v>
+        <v>23.03128066735574</v>
       </c>
       <c r="C123">
-        <v>33.91733581400963</v>
+        <v>33.91777320375075</v>
       </c>
     </row>
     <row r="124">
@@ -1725,10 +1725,10 @@
         <v>29037</v>
       </c>
       <c r="B124">
-        <v>23.78602138046659</v>
+        <v>23.78322828260604</v>
       </c>
       <c r="C124">
-        <v>35.08965026628748</v>
+        <v>35.0901027739116</v>
       </c>
     </row>
     <row r="125">
@@ -1736,10 +1736,10 @@
         <v>29129</v>
       </c>
       <c r="B125">
-        <v>24.65221509062299</v>
+        <v>24.64948040198795</v>
       </c>
       <c r="C125">
-        <v>35.98199126146937</v>
+        <v>35.98245527650666</v>
       </c>
     </row>
     <row r="126">
@@ -1747,10 +1747,10 @@
         <v>29221</v>
       </c>
       <c r="B126">
-        <v>25.477838103199</v>
+        <v>25.47426686779589</v>
       </c>
       <c r="C126">
-        <v>37.33415956724257</v>
+        <v>37.33448243791493</v>
       </c>
     </row>
     <row r="127">
@@ -1758,10 +1758,10 @@
         <v>29312</v>
       </c>
       <c r="B127">
-        <v>26.42632148198476</v>
+        <v>26.42321834418744</v>
       </c>
       <c r="C127">
-        <v>38.4297455380024</v>
+        <v>38.43013252677847</v>
       </c>
     </row>
     <row r="128">
@@ -1769,10 +1769,10 @@
         <v>29403</v>
       </c>
       <c r="B128">
-        <v>27.30941870436782</v>
+        <v>27.30621186797699</v>
       </c>
       <c r="C128">
-        <v>39.57218656832875</v>
+        <v>39.57243695630245</v>
       </c>
     </row>
     <row r="129">
@@ -1780,10 +1780,10 @@
         <v>29495</v>
       </c>
       <c r="B129">
-        <v>28.1115067379033</v>
+        <v>28.10820571550571</v>
       </c>
       <c r="C129">
-        <v>40.76503496708425</v>
+        <v>40.76567398761865</v>
       </c>
     </row>
     <row r="130">
@@ -1791,10 +1791,10 @@
         <v>29587</v>
       </c>
       <c r="B130">
-        <v>28.91716348449453</v>
+        <v>28.91434827995236</v>
       </c>
       <c r="C130">
-        <v>42.13104485017086</v>
+        <v>42.13131286582759</v>
       </c>
     </row>
     <row r="131">
@@ -1802,10 +1802,10 @@
         <v>29677</v>
       </c>
       <c r="B131">
-        <v>29.91192551685143</v>
+        <v>29.90841307843939</v>
       </c>
       <c r="C131">
-        <v>43.44773966371862</v>
+        <v>43.44837721588848</v>
       </c>
     </row>
     <row r="132">
@@ -1813,10 +1813,10 @@
         <v>29768</v>
       </c>
       <c r="B132">
-        <v>31.0187149650286</v>
+        <v>31.01507256073491</v>
       </c>
       <c r="C132">
-        <v>45.15387991942394</v>
+        <v>45.15469708025029</v>
       </c>
     </row>
     <row r="133">
@@ -1824,10 +1824,10 @@
         <v>29860</v>
       </c>
       <c r="B133">
-        <v>32.24949103450507</v>
+        <v>32.24570410507405</v>
       </c>
       <c r="C133">
-        <v>46.57184730348948</v>
+        <v>46.57244788274332</v>
       </c>
     </row>
     <row r="134">
@@ -1835,10 +1835,10 @@
         <v>29952</v>
       </c>
       <c r="B134">
-        <v>33.59231544752505</v>
+        <v>33.58837083556551</v>
       </c>
       <c r="C134">
-        <v>47.89040968506652</v>
+        <v>47.89072586581693</v>
       </c>
     </row>
     <row r="135">
@@ -1846,10 +1846,10 @@
         <v>30042</v>
       </c>
       <c r="B135">
-        <v>34.47292432025223</v>
+        <v>34.46887630189617</v>
       </c>
       <c r="C135">
-        <v>49.23616680271851</v>
+        <v>49.23680962796627</v>
       </c>
     </row>
     <row r="136">
@@ -1857,10 +1857,10 @@
         <v>30133</v>
       </c>
       <c r="B136">
-        <v>35.06543538402094</v>
+        <v>35.0613177894479</v>
       </c>
       <c r="C136">
-        <v>50.03523801866807</v>
+        <v>50.03590523101563</v>
       </c>
     </row>
     <row r="137">
@@ -1868,10 +1868,10 @@
         <v>30225</v>
       </c>
       <c r="B137">
-        <v>35.78502218488598</v>
+        <v>35.78082009209771</v>
       </c>
       <c r="C137">
-        <v>51.04782648096665</v>
+        <v>51.04936721776918</v>
       </c>
     </row>
     <row r="138">
@@ -1879,10 +1879,10 @@
         <v>30317</v>
       </c>
       <c r="B138">
-        <v>36.85241538697079</v>
+        <v>36.8480879544453</v>
       </c>
       <c r="C138">
-        <v>52.40182131889812</v>
+        <v>52.40278382360339</v>
       </c>
     </row>
     <row r="139">
@@ -1890,10 +1890,10 @@
         <v>30407</v>
       </c>
       <c r="B139">
-        <v>37.59624241039658</v>
+        <v>37.59124247355123</v>
       </c>
       <c r="C139">
-        <v>53.78695797778254</v>
+        <v>53.78737279019442</v>
       </c>
     </row>
     <row r="140">
@@ -1901,10 +1901,10 @@
         <v>30498</v>
       </c>
       <c r="B140">
-        <v>38.5783647139749</v>
+        <v>38.57383461008646</v>
       </c>
       <c r="C140">
-        <v>54.96167047875579</v>
+        <v>54.9618339835524</v>
       </c>
     </row>
     <row r="141">
@@ -1912,10 +1912,10 @@
         <v>30590</v>
       </c>
       <c r="B141">
-        <v>39.42999135671361</v>
+        <v>39.42536124969661</v>
       </c>
       <c r="C141">
-        <v>56.08751222565039</v>
+        <v>56.08892837454702</v>
       </c>
     </row>
     <row r="142">
@@ -1923,10 +1923,10 @@
         <v>30682</v>
       </c>
       <c r="B142">
-        <v>40.21159156692132</v>
+        <v>40.20686967970116</v>
       </c>
       <c r="C142">
-        <v>57.15317589096234</v>
+        <v>57.15410250057502</v>
       </c>
     </row>
     <row r="143">
@@ -1934,10 +1934,10 @@
         <v>30773</v>
       </c>
       <c r="B143">
-        <v>41.14427572731698</v>
+        <v>41.13944431870645</v>
       </c>
       <c r="C143">
-        <v>58.08832367394392</v>
+        <v>58.08896695991006</v>
       </c>
     </row>
     <row r="144">
@@ -1945,10 +1945,10 @@
         <v>30864</v>
       </c>
       <c r="B144">
-        <v>41.39887960511799</v>
+        <v>41.394018299387</v>
       </c>
       <c r="C144">
-        <v>59.0924362753322</v>
+        <v>59.09235789646949</v>
       </c>
     </row>
     <row r="145">
@@ -1956,10 +1956,10 @@
         <v>30956</v>
       </c>
       <c r="B145">
-        <v>42.34621358986735</v>
+        <v>42.3412410424754</v>
       </c>
       <c r="C145">
-        <v>60.07654081715819</v>
+        <v>60.07744638519139</v>
       </c>
     </row>
     <row r="146">
@@ -1967,10 +1967,10 @@
         <v>31048</v>
       </c>
       <c r="B146">
-        <v>43.10854524642004</v>
+        <v>43.10348318145451</v>
       </c>
       <c r="C146">
-        <v>61.03505236348592</v>
+        <v>61.03598015700206</v>
       </c>
     </row>
     <row r="147">
@@ -1978,10 +1978,10 @@
         <v>31138</v>
       </c>
       <c r="B147">
-        <v>43.77020145325744</v>
+        <v>43.76506169263588</v>
       </c>
       <c r="C147">
-        <v>62.04233587189675</v>
+        <v>62.04298367199633</v>
       </c>
     </row>
     <row r="148">
@@ -1989,10 +1989,10 @@
         <v>31229</v>
       </c>
       <c r="B148">
-        <v>44.2861400023652</v>
+        <v>44.28093965713242</v>
       </c>
       <c r="C148">
-        <v>62.66771809061395</v>
+        <v>62.66836719218667</v>
       </c>
     </row>
     <row r="149">
@@ -2000,10 +2000,10 @@
         <v>31321</v>
       </c>
       <c r="B149">
-        <v>44.81750101387694</v>
+        <v>44.81223827303454</v>
       </c>
       <c r="C149">
-        <v>63.15217627247448</v>
+        <v>63.15277821667776</v>
       </c>
     </row>
     <row r="150">
@@ -2011,10 +2011,10 @@
         <v>31413</v>
       </c>
       <c r="B150">
-        <v>45.12417655394245</v>
+        <v>45.11947644908422</v>
       </c>
       <c r="C150">
-        <v>63.30673202502658</v>
+        <v>63.30733885032435</v>
       </c>
     </row>
     <row r="151">
@@ -2022,10 +2022,10 @@
         <v>31503</v>
       </c>
       <c r="B151">
-        <v>45.89582145854745</v>
+        <v>45.89102966539746</v>
       </c>
       <c r="C151">
-        <v>63.63629012946287</v>
+        <v>63.63764422105665</v>
       </c>
     </row>
     <row r="152">
@@ -2033,10 +2033,10 @@
         <v>31594</v>
       </c>
       <c r="B152">
-        <v>45.94068695388559</v>
+        <v>45.93529232178673</v>
       </c>
       <c r="C152">
-        <v>63.99275413659272</v>
+        <v>63.99364643527918</v>
       </c>
     </row>
     <row r="153">
@@ -2044,10 +2044,10 @@
         <v>31686</v>
       </c>
       <c r="B153">
-        <v>46.23216258028343</v>
+        <v>46.22673372136138</v>
       </c>
       <c r="C153">
-        <v>64.58975716869951</v>
+        <v>64.59113577042423</v>
       </c>
     </row>
     <row r="154">
@@ -2055,10 +2055,10 @@
         <v>31778</v>
       </c>
       <c r="B154">
-        <v>47.06437420581126</v>
+        <v>47.05884762358888</v>
       </c>
       <c r="C154">
-        <v>65.12316280265568</v>
+        <v>65.1241813999405</v>
       </c>
     </row>
     <row r="155">
@@ -2066,10 +2066,10 @@
         <v>31868</v>
       </c>
       <c r="B155">
-        <v>47.28253162887695</v>
+        <v>47.27697942929629</v>
       </c>
       <c r="C155">
-        <v>65.59276576927391</v>
+        <v>65.59342984918932</v>
       </c>
     </row>
     <row r="156">
@@ -2077,10 +2077,10 @@
         <v>31959</v>
       </c>
       <c r="B156">
-        <v>47.77597891961957</v>
+        <v>47.77036877648669</v>
       </c>
       <c r="C156">
-        <v>65.99240541818428</v>
+        <v>65.99288344665095</v>
       </c>
     </row>
     <row r="157">
@@ -2088,10 +2088,10 @@
         <v>32051</v>
       </c>
       <c r="B157">
-        <v>48.33062996151264</v>
+        <v>48.32495468791453</v>
       </c>
       <c r="C157">
-        <v>66.35167629486622</v>
+        <v>66.35272552811035</v>
       </c>
     </row>
     <row r="158">
@@ -2099,10 +2099,10 @@
         <v>32143</v>
       </c>
       <c r="B158">
-        <v>48.94224284952525</v>
+        <v>48.93649575665894</v>
       </c>
       <c r="C158">
-        <v>66.71722391785858</v>
+        <v>66.7180973315988</v>
       </c>
     </row>
     <row r="159">
@@ -2110,10 +2110,10 @@
         <v>32234</v>
       </c>
       <c r="B159">
-        <v>49.30959720076254</v>
+        <v>49.30380697093624</v>
       </c>
       <c r="C159">
-        <v>67.16800418378828</v>
+        <v>67.16906499639295</v>
       </c>
     </row>
     <row r="160">
@@ -2121,10 +2121,10 @@
         <v>32325</v>
       </c>
       <c r="B160">
-        <v>49.90697984537567</v>
+        <v>49.90111946728204</v>
       </c>
       <c r="C160">
-        <v>67.78671211865606</v>
+        <v>67.78772466434857</v>
       </c>
     </row>
     <row r="161">
@@ -2132,10 +2132,10 @@
         <v>32417</v>
       </c>
       <c r="B161">
-        <v>50.44347659724191</v>
+        <v>50.4375532204691</v>
       </c>
       <c r="C161">
-        <v>68.40733257914754</v>
+        <v>68.40882608804661</v>
       </c>
     </row>
     <row r="162">
@@ -2143,10 +2143,10 @@
         <v>32509</v>
       </c>
       <c r="B162">
-        <v>51.03932004965744</v>
+        <v>51.03332670535853</v>
       </c>
       <c r="C162">
-        <v>69.12557263088046</v>
+        <v>69.1264640575091</v>
       </c>
     </row>
     <row r="163">
@@ -2154,10 +2154,10 @@
         <v>32599</v>
       </c>
       <c r="B163">
-        <v>51.71883462439283</v>
+        <v>51.71276148740077</v>
       </c>
       <c r="C163">
-        <v>69.88112374933969</v>
+        <v>69.88202491937243</v>
       </c>
     </row>
     <row r="164">
@@ -2165,10 +2165,10 @@
         <v>32690</v>
       </c>
       <c r="B164">
-        <v>52.17166909818346</v>
+        <v>52.16554278664069</v>
       </c>
       <c r="C164">
-        <v>70.40241468853368</v>
+        <v>70.4036216063427</v>
       </c>
     </row>
     <row r="165">
@@ -2176,10 +2176,10 @@
         <v>32782</v>
       </c>
       <c r="B165">
-        <v>53.05021569028852</v>
+        <v>53.04398621451466</v>
       </c>
       <c r="C165">
-        <v>70.99390713574188</v>
+        <v>70.9944520844931</v>
       </c>
     </row>
     <row r="166">
@@ -2187,10 +2187,10 @@
         <v>32874</v>
       </c>
       <c r="B166">
-        <v>53.69388993783708</v>
+        <v>53.68758487795711</v>
       </c>
       <c r="C166">
-        <v>71.35020819569097</v>
+        <v>71.35098598518076</v>
       </c>
     </row>
     <row r="167">
@@ -2198,10 +2198,10 @@
         <v>32964</v>
       </c>
       <c r="B167">
-        <v>54.56787370900589</v>
+        <v>54.56146602068872</v>
       </c>
       <c r="C167">
-        <v>71.7819613722281</v>
+        <v>71.78302644949139</v>
       </c>
     </row>
     <row r="168">
@@ -2209,10 +2209,10 @@
         <v>33055</v>
       </c>
       <c r="B168">
-        <v>55.28658232797612</v>
+        <v>55.28009024456514</v>
       </c>
       <c r="C168">
-        <v>72.33362116966893</v>
+        <v>72.33496400594568</v>
       </c>
     </row>
     <row r="169">
@@ -2220,10 +2220,10 @@
         <v>33147</v>
       </c>
       <c r="B169">
-        <v>55.89366460068391</v>
+        <v>55.88674984047402</v>
       </c>
       <c r="C169">
-        <v>72.95214391011872</v>
+        <v>72.95268640986112</v>
       </c>
     </row>
     <row r="170">
@@ -2231,10 +2231,10 @@
         <v>33239</v>
       </c>
       <c r="B170">
-        <v>56.07289320460248</v>
+        <v>56.06630878783351</v>
       </c>
       <c r="C170">
-        <v>73.28378299767877</v>
+        <v>73.28485917469514</v>
       </c>
     </row>
     <row r="171">
@@ -2242,10 +2242,10 @@
         <v>33329</v>
       </c>
       <c r="B171">
-        <v>57.00903829705275</v>
+        <v>57.00234395248992</v>
       </c>
       <c r="C171">
-        <v>73.67598985081719</v>
+        <v>73.67706899826847</v>
       </c>
     </row>
     <row r="172">
@@ -2253,10 +2253,10 @@
         <v>33420</v>
       </c>
       <c r="B172">
-        <v>57.42635536936594</v>
+        <v>57.41961202091955</v>
       </c>
       <c r="C172">
-        <v>74.3091579750843</v>
+        <v>74.31024500197087</v>
       </c>
     </row>
     <row r="173">
@@ -2264,10 +2264,10 @@
         <v>33512</v>
       </c>
       <c r="B173">
-        <v>58.33588762783192</v>
+        <v>58.32903747663091</v>
       </c>
       <c r="C173">
-        <v>74.98862923371318</v>
+        <v>74.9899788591196</v>
       </c>
     </row>
     <row r="174">
@@ -2275,10 +2275,10 @@
         <v>33604</v>
       </c>
       <c r="B174">
-        <v>59.14404898666398</v>
+        <v>59.13672876037266</v>
       </c>
       <c r="C174">
-        <v>75.36638560751302</v>
+        <v>75.36774137560519</v>
       </c>
     </row>
     <row r="175">
@@ -2286,10 +2286,10 @@
         <v>33695</v>
       </c>
       <c r="B175">
-        <v>59.32758566352692</v>
+        <v>59.32118751135599</v>
       </c>
       <c r="C175">
-        <v>75.82160057516471</v>
+        <v>75.82308166504598</v>
       </c>
     </row>
     <row r="176">
@@ -2297,10 +2297,10 @@
         <v>33786</v>
       </c>
       <c r="B176">
-        <v>59.93795930514736</v>
+        <v>59.93092102904295</v>
       </c>
       <c r="C176">
-        <v>76.1701188583836</v>
+        <v>76.17133105809204</v>
       </c>
     </row>
     <row r="177">
@@ -2308,10 +2308,10 @@
         <v>33878</v>
       </c>
       <c r="B177">
-        <v>60.49919834943657</v>
+        <v>60.49190873834236</v>
       </c>
       <c r="C177">
-        <v>76.39889803843037</v>
+        <v>76.40015438150255</v>
       </c>
     </row>
     <row r="178">
@@ -2319,10 +2319,10 @@
         <v>33970</v>
       </c>
       <c r="B178">
-        <v>60.90294993498494</v>
+        <v>60.89579834386998</v>
       </c>
       <c r="C178">
-        <v>76.77414253745343</v>
+        <v>76.77485381080935</v>
       </c>
     </row>
     <row r="179">
@@ -2330,10 +2330,10 @@
         <v>34060</v>
       </c>
       <c r="B179">
-        <v>61.0668526240027</v>
+        <v>61.05968178644704</v>
       </c>
       <c r="C179">
-        <v>76.96218106800863</v>
+        <v>76.96300583999268</v>
       </c>
     </row>
     <row r="180">
@@ -2341,10 +2341,10 @@
         <v>34151</v>
       </c>
       <c r="B180">
-        <v>61.06327312312387</v>
+        <v>61.05610270589477</v>
       </c>
       <c r="C180">
-        <v>77.14450652950421</v>
+        <v>77.14589252510665</v>
       </c>
     </row>
     <row r="181">
@@ -2352,10 +2352,10 @@
         <v>34243</v>
       </c>
       <c r="B181">
-        <v>61.27679854765792</v>
+        <v>61.26960305698768</v>
       </c>
       <c r="C181">
-        <v>77.38730722820418</v>
+        <v>77.38852223903199</v>
       </c>
     </row>
     <row r="182">
@@ -2363,10 +2363,10 @@
         <v>34335</v>
       </c>
       <c r="B182">
-        <v>61.4095497971248</v>
+        <v>61.40233871800348</v>
       </c>
       <c r="C182">
-        <v>77.5345169067553</v>
+        <v>77.5355966202135</v>
       </c>
     </row>
     <row r="183">
@@ -2374,10 +2374,10 @@
         <v>34425</v>
       </c>
       <c r="B183">
-        <v>61.49777325223769</v>
+        <v>61.49055181338701</v>
       </c>
       <c r="C183">
-        <v>77.70242987618828</v>
+        <v>77.70329053783693</v>
       </c>
     </row>
     <row r="184">
@@ -2385,10 +2385,10 @@
         <v>34516</v>
       </c>
       <c r="B184">
-        <v>61.79096881316023</v>
+        <v>61.78371294552129</v>
       </c>
       <c r="C184">
-        <v>77.86802974698442</v>
+        <v>77.86942140524589</v>
       </c>
     </row>
     <row r="185">
@@ -2396,10 +2396,10 @@
         <v>34608</v>
       </c>
       <c r="B185">
-        <v>62.41411796158537</v>
+        <v>62.40678892002107</v>
       </c>
       <c r="C185">
-        <v>77.96723736859803</v>
+        <v>77.96790305755066</v>
       </c>
     </row>
     <row r="186">
@@ -2407,10 +2407,10 @@
         <v>34700</v>
       </c>
       <c r="B186">
-        <v>62.56571792993649</v>
+        <v>62.55837108659102</v>
       </c>
       <c r="C186">
-        <v>78.15078815793876</v>
+        <v>78.1516692091989</v>
       </c>
     </row>
     <row r="187">
@@ -2418,10 +2418,10 @@
         <v>34790</v>
       </c>
       <c r="B187">
-        <v>62.97775866202089</v>
+        <v>62.97036343437152</v>
       </c>
       <c r="C187">
-        <v>78.20265021597848</v>
+        <v>78.20404045527118</v>
       </c>
     </row>
     <row r="188">
@@ -2429,10 +2429,10 @@
         <v>34881</v>
       </c>
       <c r="B188">
-        <v>63.13633817148697</v>
+        <v>63.1289243224767</v>
       </c>
       <c r="C188">
-        <v>78.60492843488124</v>
+        <v>78.60614134699615</v>
       </c>
     </row>
     <row r="189">
@@ -2440,10 +2440,10 @@
         <v>34973</v>
       </c>
       <c r="B189">
-        <v>63.23636763627214</v>
+        <v>63.22894204119977</v>
       </c>
       <c r="C189">
-        <v>78.9408660222677</v>
+        <v>78.94207565200946</v>
       </c>
     </row>
     <row r="190">
@@ -2451,10 +2451,10 @@
         <v>35065</v>
       </c>
       <c r="B190">
-        <v>63.64803852072887</v>
+        <v>63.63999178304176</v>
       </c>
       <c r="C190">
-        <v>79.42466300287012</v>
+        <v>79.42570216449951</v>
       </c>
     </row>
     <row r="191">
@@ -2462,10 +2462,10 @@
         <v>35156</v>
       </c>
       <c r="B191">
-        <v>64.03114419660771</v>
+        <v>64.0236252740858</v>
       </c>
       <c r="C191">
-        <v>79.74900540662389</v>
+        <v>79.75031241919885</v>
       </c>
     </row>
     <row r="192">
@@ -2473,10 +2473,10 @@
         <v>35247</v>
       </c>
       <c r="B192">
-        <v>64.33254798808214</v>
+        <v>64.32499367291209</v>
       </c>
       <c r="C192">
-        <v>79.6484458078439</v>
+        <v>79.64935542591515</v>
       </c>
     </row>
     <row r="193">
@@ -2484,10 +2484,10 @@
         <v>35339</v>
       </c>
       <c r="B193">
-        <v>64.35015273383419</v>
+        <v>64.3425963514089</v>
       </c>
       <c r="C193">
-        <v>79.95369031659516</v>
+        <v>79.95499644204051</v>
       </c>
     </row>
     <row r="194">
@@ -2495,10 +2495,10 @@
         <v>35431</v>
       </c>
       <c r="B194">
-        <v>64.70554593969375</v>
+        <v>64.69779055271138</v>
       </c>
       <c r="C194">
-        <v>80.20650274157899</v>
+        <v>80.20788763601971</v>
       </c>
     </row>
     <row r="195">
@@ -2506,10 +2506,10 @@
         <v>35521</v>
       </c>
       <c r="B195">
-        <v>64.97972707363895</v>
+        <v>64.97225191016398</v>
       </c>
       <c r="C195">
-        <v>80.10769805814691</v>
+        <v>80.1086831817247</v>
       </c>
     </row>
     <row r="196">
@@ -2517,10 +2517,10 @@
         <v>35612</v>
       </c>
       <c r="B196">
-        <v>65.22639383585464</v>
+        <v>65.2185812793862</v>
       </c>
       <c r="C196">
-        <v>80.3783714308879</v>
+        <v>80.37955516006238</v>
       </c>
     </row>
     <row r="197">
@@ -2528,10 +2528,10 @@
         <v>35704</v>
       </c>
       <c r="B197">
-        <v>65.33764083289995</v>
+        <v>65.32970739704646</v>
       </c>
       <c r="C197">
-        <v>80.58810232655898</v>
+        <v>80.58931465331905</v>
       </c>
     </row>
     <row r="198">
@@ -2539,10 +2539,10 @@
         <v>35796</v>
       </c>
       <c r="B198">
-        <v>65.77270670046303</v>
+        <v>65.76498327318492</v>
       </c>
       <c r="C198">
-        <v>80.63734733732029</v>
+        <v>80.6383872170051</v>
       </c>
     </row>
     <row r="199">
@@ -2550,10 +2550,10 @@
         <v>35886</v>
       </c>
       <c r="B199">
-        <v>65.93882368799798</v>
+        <v>65.93108075426289</v>
       </c>
       <c r="C199">
-        <v>80.67167952142897</v>
+        <v>80.67257542192164</v>
       </c>
     </row>
     <row r="200">
@@ -2561,10 +2561,10 @@
         <v>35977</v>
       </c>
       <c r="B200">
-        <v>66.4404408375903</v>
+        <v>66.43263900094897</v>
       </c>
       <c r="C200">
-        <v>80.46402507692191</v>
+        <v>80.46509356673589</v>
       </c>
     </row>
     <row r="201">
@@ -2572,10 +2572,10 @@
         <v>36069</v>
       </c>
       <c r="B201">
-        <v>66.67364187017955</v>
+        <v>66.66581264966872</v>
       </c>
       <c r="C201">
-        <v>80.10847761074446</v>
+        <v>80.1093396636729</v>
       </c>
     </row>
     <row r="202">
@@ -2583,10 +2583,10 @@
         <v>36161</v>
       </c>
       <c r="B202">
-        <v>66.98054825205001</v>
+        <v>66.97268299274374</v>
       </c>
       <c r="C202">
-        <v>79.93660770203228</v>
+        <v>79.93742862852848</v>
       </c>
     </row>
     <row r="203">
@@ -2594,10 +2594,10 @@
         <v>36251</v>
       </c>
       <c r="B203">
-        <v>67.09474850116956</v>
+        <v>67.08686983178239</v>
       </c>
       <c r="C203">
-        <v>79.94982693402292</v>
+        <v>79.95095368383386</v>
       </c>
     </row>
     <row r="204">
@@ -2605,10 +2605,10 @@
         <v>36342</v>
       </c>
       <c r="B204">
-        <v>67.47601296797737</v>
+        <v>67.46808952822067</v>
       </c>
       <c r="C204">
-        <v>79.87733910155779</v>
+        <v>79.87870384019332</v>
       </c>
     </row>
     <row r="205">
@@ -2616,10 +2616,10 @@
         <v>36434</v>
       </c>
       <c r="B205">
-        <v>68.03850254150942</v>
+        <v>68.03051305083991</v>
       </c>
       <c r="C205">
-        <v>80.34312109964752</v>
+        <v>80.34404899065332</v>
       </c>
     </row>
     <row r="206">
@@ -2627,10 +2627,10 @@
         <v>36526</v>
       </c>
       <c r="B206">
-        <v>68.61887291261435</v>
+        <v>68.61122021738825</v>
       </c>
       <c r="C206">
-        <v>81.06143540089002</v>
+        <v>81.06205119293476</v>
       </c>
     </row>
     <row r="207">
@@ -2638,10 +2638,10 @@
         <v>36617</v>
       </c>
       <c r="B207">
-        <v>68.83147341424075</v>
+        <v>68.82379317118206</v>
       </c>
       <c r="C207">
-        <v>81.48875683707465</v>
+        <v>81.48983155036993</v>
       </c>
     </row>
     <row r="208">
@@ -2649,10 +2649,10 @@
         <v>36708</v>
       </c>
       <c r="B208">
-        <v>69.2632149052464</v>
+        <v>69.25508160147641</v>
       </c>
       <c r="C208">
-        <v>82.1545287411025</v>
+        <v>82.15564002773183</v>
       </c>
     </row>
     <row r="209">
@@ -2660,10 +2660,10 @@
         <v>36800</v>
       </c>
       <c r="B209">
-        <v>70.04624480910219</v>
+        <v>70.03761672966849</v>
       </c>
       <c r="C209">
-        <v>82.77328746043565</v>
+        <v>82.77399119850469</v>
       </c>
     </row>
     <row r="210">
@@ -2671,10 +2671,10 @@
         <v>36892</v>
       </c>
       <c r="B210">
-        <v>70.07410571429902</v>
+        <v>70.06547599137421</v>
       </c>
       <c r="C210">
-        <v>82.86638674680862</v>
+        <v>82.86676477447828</v>
       </c>
     </row>
     <row r="211">
@@ -2682,10 +2682,10 @@
         <v>36982</v>
       </c>
       <c r="B211">
-        <v>70.74714914172947</v>
+        <v>70.73884158546576</v>
       </c>
       <c r="C211">
-        <v>83.56136583058704</v>
+        <v>83.5626013298026</v>
       </c>
     </row>
     <row r="212">
@@ -2693,10 +2693,10 @@
         <v>37073</v>
       </c>
       <c r="B212">
-        <v>71.15550272262247</v>
+        <v>71.14755195230073</v>
       </c>
       <c r="C212">
-        <v>83.71992055919722</v>
+        <v>83.72096950846128</v>
       </c>
     </row>
     <row r="213">
@@ -2704,10 +2704,10 @@
         <v>37165</v>
       </c>
       <c r="B213">
-        <v>71.69303150255001</v>
+        <v>71.68501998434465</v>
       </c>
       <c r="C213">
-        <v>83.65983322591704</v>
+        <v>83.66062709853807</v>
       </c>
     </row>
     <row r="214">
@@ -2715,10 +2715,10 @@
         <v>37257</v>
       </c>
       <c r="B214">
-        <v>72.23591432431039</v>
+        <v>72.22743194827417</v>
       </c>
       <c r="C214">
-        <v>84.05712155252827</v>
+        <v>84.05795860227605</v>
       </c>
     </row>
     <row r="215">
@@ -2726,10 +2726,10 @@
         <v>37347</v>
       </c>
       <c r="B215">
-        <v>73.06488473762485</v>
+        <v>73.05630501889098</v>
       </c>
       <c r="C215">
-        <v>84.1667868164018</v>
+        <v>84.16822021477002</v>
       </c>
     </row>
     <row r="216">
@@ -2737,10 +2737,10 @@
         <v>37438</v>
       </c>
       <c r="B216">
-        <v>73.48618126683344</v>
+        <v>73.47755207692424</v>
       </c>
       <c r="C216">
-        <v>84.36836246213247</v>
+        <v>84.36927136787673</v>
       </c>
     </row>
     <row r="217">
@@ -2748,10 +2748,10 @@
         <v>37530</v>
       </c>
       <c r="B217">
-        <v>73.86028286848401</v>
+        <v>73.85160974931205</v>
       </c>
       <c r="C217">
-        <v>84.63591801258677</v>
+        <v>84.63712985037972</v>
       </c>
     </row>
     <row r="218">
@@ -2759,10 +2759,10 @@
         <v>37622</v>
       </c>
       <c r="B218">
-        <v>74.37422589288694</v>
+        <v>74.36549242343028</v>
       </c>
       <c r="C218">
-        <v>85.30315627839921</v>
+        <v>85.30420098644636</v>
       </c>
     </row>
     <row r="219">
@@ -2770,10 +2770,10 @@
         <v>37712</v>
       </c>
       <c r="B219">
-        <v>74.97863827558231</v>
+        <v>74.96983383238415</v>
       </c>
       <c r="C219">
-        <v>85.3250916085852</v>
+        <v>85.32657814387315</v>
       </c>
     </row>
     <row r="220">
@@ -2781,10 +2781,10 @@
         <v>37803</v>
       </c>
       <c r="B220">
-        <v>75.692289764655</v>
+        <v>75.68340152020167</v>
       </c>
       <c r="C220">
-        <v>85.80635762444636</v>
+        <v>85.80767599824617</v>
       </c>
     </row>
     <row r="221">
@@ -2792,10 +2792,10 @@
         <v>37895</v>
       </c>
       <c r="B221">
-        <v>76.07602488074457</v>
+        <v>76.06709157580319</v>
       </c>
       <c r="C221">
-        <v>86.34477864967319</v>
+        <v>86.34579701816288</v>
       </c>
     </row>
     <row r="222">
@@ -2803,10 +2803,10 @@
         <v>37987</v>
       </c>
       <c r="B222">
-        <v>76.93040359905177</v>
+        <v>76.92093328427045</v>
       </c>
       <c r="C222">
-        <v>86.75612399536632</v>
+        <v>86.75683947969279</v>
       </c>
     </row>
     <row r="223">
@@ -2814,10 +2814,10 @@
         <v>38078</v>
       </c>
       <c r="B223">
-        <v>77.57540170753632</v>
+        <v>77.56585209692943</v>
       </c>
       <c r="C223">
-        <v>87.34040818448908</v>
+        <v>87.34146267208666</v>
       </c>
     </row>
     <row r="224">
@@ -2825,10 +2825,10 @@
         <v>38169</v>
       </c>
       <c r="B224">
-        <v>78.1185997825344</v>
+        <v>78.10942662614848</v>
       </c>
       <c r="C224">
-        <v>87.7037209455157</v>
+        <v>87.70510534117672</v>
       </c>
     </row>
     <row r="225">
@@ -2836,10 +2836,10 @@
         <v>38261</v>
       </c>
       <c r="B225">
-        <v>78.73096598514583</v>
+        <v>78.72172092103297</v>
       </c>
       <c r="C225">
-        <v>88.08161750255672</v>
+        <v>88.08283837178837</v>
       </c>
     </row>
     <row r="226">
@@ -2847,10 +2847,10 @@
         <v>38353</v>
       </c>
       <c r="B226">
-        <v>78.98503053705285</v>
+        <v>78.97575563915042</v>
       </c>
       <c r="C226">
-        <v>88.38063918926755</v>
+        <v>88.38188557575073</v>
       </c>
     </row>
     <row r="227">
@@ -2858,10 +2858,10 @@
         <v>38443</v>
       </c>
       <c r="B227">
-        <v>79.55871270811195</v>
+        <v>79.54937044499452</v>
       </c>
       <c r="C227">
-        <v>88.76051118059604</v>
+        <v>88.76137951445557</v>
       </c>
     </row>
     <row r="228">
@@ -2869,10 +2869,10 @@
         <v>38534</v>
       </c>
       <c r="B228">
-        <v>80.32678804956491</v>
+        <v>80.31735559441583</v>
       </c>
       <c r="C228">
-        <v>89.44077868615619</v>
+        <v>89.44171222076017</v>
       </c>
     </row>
     <row r="229">
@@ -2880,10 +2880,10 @@
         <v>38626</v>
       </c>
       <c r="B229">
-        <v>81.18379967864777</v>
+        <v>81.17472210118936</v>
       </c>
       <c r="C229">
-        <v>89.64848483214173</v>
+        <v>89.64942745877164</v>
       </c>
     </row>
     <row r="230">
@@ -2891,10 +2891,10 @@
         <v>38718</v>
       </c>
       <c r="B230">
-        <v>81.67824221405576</v>
+        <v>81.66910806307148</v>
       </c>
       <c r="C230">
-        <v>90.2290664751151</v>
+        <v>90.23019695508678</v>
       </c>
     </row>
     <row r="231">
@@ -2902,10 +2902,10 @@
         <v>38808</v>
       </c>
       <c r="B231">
-        <v>82.21567410708556</v>
+        <v>82.20647809297714</v>
       </c>
       <c r="C231">
-        <v>90.79740024464428</v>
+        <v>90.79801198550354</v>
       </c>
     </row>
     <row r="232">
@@ -2913,10 +2913,10 @@
         <v>38899</v>
       </c>
       <c r="B232">
-        <v>82.74025118785117</v>
+        <v>82.73053532932748</v>
       </c>
       <c r="C232">
-        <v>91.34914151925935</v>
+        <v>91.35020521265034</v>
       </c>
     </row>
     <row r="233">
@@ -2924,10 +2924,10 @@
         <v>38991</v>
       </c>
       <c r="B233">
-        <v>83.86327838233142</v>
+        <v>83.85296709341063</v>
       </c>
       <c r="C233">
-        <v>91.385028262104</v>
+        <v>91.38634877062276</v>
       </c>
     </row>
     <row r="234">
@@ -2935,10 +2935,10 @@
         <v>39083</v>
       </c>
       <c r="B234">
-        <v>84.04880178202167</v>
+        <v>84.03893226560763</v>
       </c>
       <c r="C234">
-        <v>91.77842599004181</v>
+        <v>91.77968956181489</v>
       </c>
     </row>
     <row r="235">
@@ -2946,10 +2946,10 @@
         <v>39173</v>
       </c>
       <c r="B235">
-        <v>84.31948264191209</v>
+        <v>84.30958134052155</v>
       </c>
       <c r="C235">
-        <v>92.45257156694012</v>
+        <v>92.45350135630642</v>
       </c>
     </row>
     <row r="236">
@@ -2957,10 +2957,10 @@
         <v>39264</v>
       </c>
       <c r="B236">
-        <v>84.74149296267663</v>
+        <v>84.73154210629303</v>
       </c>
       <c r="C236">
-        <v>93.1249777535256</v>
+        <v>93.1264998764342</v>
       </c>
     </row>
     <row r="237">
@@ -2968,10 +2968,10 @@
         <v>39356</v>
       </c>
       <c r="B237">
-        <v>85.53873376664329</v>
+        <v>85.52822405905908</v>
       </c>
       <c r="C237">
-        <v>94.12074068989851</v>
+        <v>94.12183188128425</v>
       </c>
     </row>
     <row r="238">
@@ -2979,10 +2979,10 @@
         <v>39448</v>
       </c>
       <c r="B238">
-        <v>86.3228147041162</v>
+        <v>86.31221032733943</v>
       </c>
       <c r="C238">
-        <v>95.00745975394457</v>
+        <v>95.00833521331273</v>
       </c>
     </row>
     <row r="239">
@@ -2990,10 +2990,10 @@
         <v>39539</v>
       </c>
       <c r="B239">
-        <v>86.51406515220906</v>
+        <v>86.50390614972522</v>
       </c>
       <c r="C239">
-        <v>95.92878603397261</v>
+        <v>95.93039803060834</v>
       </c>
     </row>
     <row r="240">
@@ -3001,10 +3001,10 @@
         <v>39630</v>
       </c>
       <c r="B240">
-        <v>87.10374899432645</v>
+        <v>87.09352074761505</v>
       </c>
       <c r="C240">
-        <v>95.91649730012483</v>
+        <v>95.91783280710214</v>
       </c>
     </row>
     <row r="241">
@@ -3012,10 +3012,10 @@
         <v>39722</v>
       </c>
       <c r="B241">
-        <v>87.0056224320783</v>
+        <v>86.99540570797872</v>
       </c>
       <c r="C241">
-        <v>95.00485234637809</v>
+        <v>95.00604879211561</v>
       </c>
     </row>
     <row r="242">
@@ -3023,10 +3023,10 @@
         <v>39814</v>
       </c>
       <c r="B242">
-        <v>87.11308807390495</v>
+        <v>87.10285873054258</v>
       </c>
       <c r="C242">
-        <v>94.31673382488874</v>
+        <v>94.31780446146014</v>
       </c>
     </row>
     <row r="243">
@@ -3034,10 +3034,10 @@
         <v>39904</v>
       </c>
       <c r="B243">
-        <v>87.36520714446702</v>
+        <v>87.35494819576523</v>
       </c>
       <c r="C243">
-        <v>93.86837043456096</v>
+        <v>93.86978420766606</v>
       </c>
     </row>
     <row r="244">
@@ -3045,10 +3045,10 @@
         <v>39995</v>
       </c>
       <c r="B244">
-        <v>87.96651452566719</v>
+        <v>87.95618496783186</v>
       </c>
       <c r="C244">
-        <v>93.78491749829244</v>
+        <v>93.78654671485192</v>
       </c>
     </row>
     <row r="245">
@@ -3056,10 +3056,10 @@
         <v>40087</v>
       </c>
       <c r="B245">
-        <v>88.68963139747207</v>
+        <v>88.67921692689933</v>
       </c>
       <c r="C245">
-        <v>93.88808468224255</v>
+        <v>93.88907669113846</v>
       </c>
     </row>
     <row r="246">
@@ -3067,10 +3067,10 @@
         <v>40179</v>
       </c>
       <c r="B246">
-        <v>89.54312057922292</v>
+        <v>89.53260588681108</v>
       </c>
       <c r="C246">
-        <v>94.48668055384665</v>
+        <v>94.48745251462746</v>
       </c>
     </row>
     <row r="247">
@@ -3078,10 +3078,10 @@
         <v>40269</v>
       </c>
       <c r="B247">
-        <v>90.21604903937934</v>
+        <v>90.20595683684751</v>
       </c>
       <c r="C247">
-        <v>95.00421393825866</v>
+        <v>95.00550973573661</v>
       </c>
     </row>
     <row r="248">
@@ -3089,10 +3089,10 @@
         <v>40360</v>
       </c>
       <c r="B248">
-        <v>90.52429482756892</v>
+        <v>90.5136649197686</v>
       </c>
       <c r="C248">
-        <v>95.1900380725255</v>
+        <v>95.19129235713835</v>
       </c>
     </row>
     <row r="249">
@@ -3100,10 +3100,10 @@
         <v>40452</v>
       </c>
       <c r="B249">
-        <v>90.78173283783397</v>
+        <v>90.7710727001123</v>
       </c>
       <c r="C249">
-        <v>95.53936974189719</v>
+        <v>95.54083511619179</v>
       </c>
     </row>
     <row r="250">
@@ -3111,10 +3111,10 @@
         <v>40544</v>
       </c>
       <c r="B250">
-        <v>91.41178066976599</v>
+        <v>91.40103521633421</v>
       </c>
       <c r="C250">
-        <v>96.23780123547989</v>
+        <v>96.23847275185736</v>
       </c>
     </row>
     <row r="251">
@@ -3122,10 +3122,10 @@
         <v>40634</v>
       </c>
       <c r="B251">
-        <v>91.52733353912843</v>
+        <v>91.51608420082302</v>
       </c>
       <c r="C251">
-        <v>96.7058224689938</v>
+        <v>96.70735519470482</v>
       </c>
     </row>
     <row r="252">
@@ -3133,10 +3133,10 @@
         <v>40725</v>
       </c>
       <c r="B252">
-        <v>91.61034732208077</v>
+        <v>91.59910126631412</v>
       </c>
       <c r="C252">
-        <v>96.93979518632867</v>
+        <v>96.94105938627024</v>
       </c>
     </row>
     <row r="253">
@@ -3144,10 +3144,10 @@
         <v>40817</v>
       </c>
       <c r="B253">
-        <v>92.21816163367998</v>
+        <v>92.20783623589914</v>
       </c>
       <c r="C253">
-        <v>97.31307344534129</v>
+        <v>97.31424833903345</v>
       </c>
     </row>
     <row r="254">
@@ -3155,10 +3155,10 @@
         <v>40909</v>
       </c>
       <c r="B254">
-        <v>92.63653887661279</v>
+        <v>92.62566093639711</v>
       </c>
       <c r="C254">
-        <v>97.9560884953269</v>
+        <v>97.95733816474421</v>
       </c>
     </row>
     <row r="255">
@@ -3166,10 +3166,10 @@
         <v>41000</v>
       </c>
       <c r="B255">
-        <v>92.8993392506903</v>
+        <v>92.88843045087224</v>
       </c>
       <c r="C255">
-        <v>98.16981887134408</v>
+        <v>98.17139991007487</v>
       </c>
     </row>
     <row r="256">
@@ -3177,10 +3177,10 @@
         <v>41091</v>
       </c>
       <c r="B256">
-        <v>93.29401316316023</v>
+        <v>93.28305801835478</v>
       </c>
       <c r="C256">
-        <v>98.1856848396062</v>
+        <v>98.18697658556576</v>
       </c>
     </row>
     <row r="257">
@@ -3188,10 +3188,10 @@
         <v>41183</v>
       </c>
       <c r="B257">
-        <v>93.79190729666198</v>
+        <v>93.78089368612925</v>
       </c>
       <c r="C257">
-        <v>98.32668854574796</v>
+        <v>98.32723203613185</v>
       </c>
     </row>
     <row r="258">
@@ -3199,10 +3199,10 @@
         <v>41275</v>
       </c>
       <c r="B258">
-        <v>93.79764058600605</v>
+        <v>93.78662630223597</v>
       </c>
       <c r="C258">
-        <v>98.72300577194974</v>
+        <v>98.72427640679275</v>
       </c>
     </row>
     <row r="259">
@@ -3210,10 +3210,10 @@
         <v>41365</v>
       </c>
       <c r="B259">
-        <v>94.37582561321287</v>
+        <v>94.36474343547529</v>
       </c>
       <c r="C259">
-        <v>98.70124463702223</v>
+        <v>98.70251468746588</v>
       </c>
     </row>
     <row r="260">
@@ -3221,10 +3221,10 @@
         <v>41456</v>
       </c>
       <c r="B260">
-        <v>94.8446865515841</v>
+        <v>94.83403752599854</v>
       </c>
       <c r="C260">
-        <v>98.88367808462714</v>
+        <v>98.88495350130154</v>
       </c>
     </row>
     <row r="261">
@@ -3232,10 +3232,10 @@
         <v>41548</v>
       </c>
       <c r="B261">
-        <v>94.85608690041937</v>
+        <v>94.8449483275095</v>
       </c>
       <c r="C261">
-        <v>98.86183169673265</v>
+        <v>98.86310718141152</v>
       </c>
     </row>
     <row r="262">
@@ -3243,10 +3243,10 @@
         <v>41640</v>
       </c>
       <c r="B262">
-        <v>95.1532690435531</v>
+        <v>95.14258226642508</v>
       </c>
       <c r="C262">
-        <v>99.07205310369234</v>
+        <v>99.07333007658444</v>
       </c>
     </row>
     <row r="263">
@@ -3254,10 +3254,10 @@
         <v>41730</v>
       </c>
       <c r="B263">
-        <v>95.45531491456708</v>
+        <v>95.44410597669548</v>
       </c>
       <c r="C263">
-        <v>98.90313420448361</v>
+        <v>98.90440936407308</v>
       </c>
     </row>
     <row r="264">
@@ -3265,10 +3265,10 @@
         <v>41821</v>
       </c>
       <c r="B264">
-        <v>95.80065636552932</v>
+        <v>95.78992877209251</v>
       </c>
       <c r="C264">
-        <v>98.81033832974224</v>
+        <v>98.81196666241291</v>
       </c>
     </row>
     <row r="265">
@@ -3276,10 +3276,10 @@
         <v>41913</v>
       </c>
       <c r="B265">
-        <v>96.0692389769312</v>
+        <v>96.05743411209791</v>
       </c>
       <c r="C265">
-        <v>98.80458600376818</v>
+        <v>98.80655854697179</v>
       </c>
     </row>
     <row r="266">
@@ -3287,10 +3287,10 @@
         <v>42005</v>
       </c>
       <c r="B266">
-        <v>96.301927789441</v>
+        <v>96.29009409145446</v>
       </c>
       <c r="C266">
-        <v>98.83140081665245</v>
+        <v>98.83337418601624</v>
       </c>
     </row>
     <row r="267">
@@ -3298,10 +3298,10 @@
         <v>42095</v>
       </c>
       <c r="B267">
-        <v>96.72343548543277</v>
+        <v>96.71102272678598</v>
       </c>
       <c r="C267">
-        <v>99.28978932498825</v>
+        <v>99.29070697429148</v>
       </c>
     </row>
     <row r="268">
@@ -3309,10 +3309,10 @@
         <v>42186</v>
       </c>
       <c r="B268">
-        <v>97.1217702795559</v>
+        <v>97.1103656564606</v>
       </c>
       <c r="C268">
-        <v>99.2575200982575</v>
+        <v>99.25845767703476</v>
       </c>
     </row>
     <row r="269">
@@ -3320,10 +3320,10 @@
         <v>42278</v>
       </c>
       <c r="B269">
-        <v>97.5959604628888</v>
+        <v>97.5866227363511</v>
       </c>
       <c r="C269">
-        <v>99.24479010148755</v>
+        <v>99.24607730184431</v>
       </c>
     </row>
     <row r="270">
@@ -3331,10 +3331,10 @@
         <v>42370</v>
       </c>
       <c r="B270">
-        <v>98.18235057027779</v>
+        <v>98.17508462987982</v>
       </c>
       <c r="C270">
-        <v>99.04306027014178</v>
+        <v>99.04467452919067</v>
       </c>
     </row>
     <row r="271">
@@ -3342,10 +3342,10 @@
         <v>42461</v>
       </c>
       <c r="B271">
-        <v>98.06302824027547</v>
+        <v>98.05310643804036</v>
       </c>
       <c r="C271">
-        <v>99.3418894555809</v>
+        <v>99.34215946661679</v>
       </c>
     </row>
     <row r="272">
@@ -3353,10 +3353,10 @@
         <v>42552</v>
       </c>
       <c r="B272">
-        <v>98.37100232729922</v>
+        <v>98.35945101185449</v>
       </c>
       <c r="C272">
-        <v>99.45136703046906</v>
+        <v>99.4526514560897</v>
       </c>
     </row>
     <row r="273">
@@ -3364,10 +3364,10 @@
         <v>42644</v>
       </c>
       <c r="B273">
-        <v>98.91604450200771</v>
+        <v>98.89904916706833</v>
       </c>
       <c r="C273">
-        <v>99.68514673420442</v>
+        <v>99.68647294535373</v>
       </c>
     </row>
     <row r="274">
@@ -3375,10 +3375,10 @@
         <v>42736</v>
       </c>
       <c r="B274">
-        <v>99.79370523770771</v>
+        <v>99.78091559981517</v>
       </c>
       <c r="C274">
-        <v>100.0057421393981</v>
+        <v>100.0083855268754</v>
       </c>
     </row>
     <row r="275">
@@ -3397,10 +3397,10 @@
         <v>42917</v>
       </c>
       <c r="B276">
-        <v>100.3990607554662</v>
+        <v>100.3952746154105</v>
       </c>
       <c r="C276">
-        <v>100.1014514845771</v>
+        <v>100.1030034346224</v>
       </c>
     </row>
     <row r="277">
@@ -3408,10 +3408,10 @@
         <v>43009</v>
       </c>
       <c r="B277">
-        <v>101.2037275624249</v>
+        <v>101.1725607103467</v>
       </c>
       <c r="C277">
-        <v>100.6283086615361</v>
+        <v>100.6296943324667</v>
       </c>
     </row>
     <row r="278">
@@ -3419,10 +3419,10 @@
         <v>43101</v>
       </c>
       <c r="B278">
-        <v>101.2035349607754</v>
+        <v>101.1788584929852</v>
       </c>
       <c r="C278">
-        <v>101.2532143201268</v>
+        <v>101.2562893230306</v>
       </c>
     </row>
     <row r="279">
@@ -3430,10 +3430,10 @@
         <v>43191</v>
       </c>
       <c r="B279">
-        <v>101.7158481224675</v>
+        <v>101.7141134263894</v>
       </c>
       <c r="C279">
-        <v>101.8675122001909</v>
+        <v>101.866128121419</v>
       </c>
     </row>
     <row r="280">
@@ -3441,10 +3441,10 @@
         <v>43282</v>
       </c>
       <c r="B280">
-        <v>102.3636723414485</v>
+        <v>102.3666106645227</v>
       </c>
       <c r="C280">
-        <v>102.1542940363568</v>
+        <v>102.1537021554068</v>
       </c>
     </row>
     <row r="281">
@@ -3452,10 +3452,10 @@
         <v>43374</v>
       </c>
       <c r="B281">
-        <v>102.8542059689907</v>
+        <v>102.8292109128206</v>
       </c>
       <c r="C281">
-        <v>102.2366340734824</v>
+        <v>102.2399593569714</v>
       </c>
     </row>
     <row r="282">
@@ -3463,10 +3463,10 @@
         <v>43466</v>
       </c>
       <c r="B282">
-        <v>101.4456990750787</v>
+        <v>101.433195703008</v>
       </c>
       <c r="C282">
-        <v>102.2026705054403</v>
+        <v>102.2070650915036</v>
       </c>
     </row>
     <row r="283">
@@ -3474,10 +3474,10 @@
         <v>43556</v>
       </c>
       <c r="B283">
-        <v>101.0753516031973</v>
+        <v>101.1174350040681</v>
       </c>
       <c r="C283">
-        <v>102.5952643059863</v>
+        <v>102.5937769635533</v>
       </c>
     </row>
     <row r="284">
@@ -3485,10 +3485,10 @@
         <v>43647</v>
       </c>
       <c r="B284">
-        <v>101.3566636066574</v>
+        <v>101.3644236798147</v>
       </c>
       <c r="C284">
-        <v>102.8823595735206</v>
+        <v>102.879464179598</v>
       </c>
     </row>
     <row r="285">
@@ -3496,10 +3496,10 @@
         <v>43739</v>
       </c>
       <c r="B285">
-        <v>101.0803236382015</v>
+        <v>100.9970988456244</v>
       </c>
       <c r="C285">
-        <v>103.1972961908302</v>
+        <v>103.2028549865788</v>
       </c>
     </row>
     <row r="286">
@@ -3507,10 +3507,10 @@
         <v>43831</v>
       </c>
       <c r="B286">
-        <v>97.33148014554892</v>
+        <v>97.25282958364842</v>
       </c>
       <c r="C286">
-        <v>103.4641614507136</v>
+        <v>103.4708640985969</v>
       </c>
     </row>
     <row r="287">
@@ -3518,10 +3518,10 @@
         <v>43922</v>
       </c>
       <c r="B287">
-        <v>85.83385313810351</v>
+        <v>85.85547036583885</v>
       </c>
       <c r="C287">
-        <v>103.6094364633104</v>
+        <v>103.6124208066663</v>
       </c>
     </row>
     <row r="288">
@@ -3529,10 +3529,10 @@
         <v>44013</v>
       </c>
       <c r="B288">
-        <v>99.26097740462409</v>
+        <v>99.32494438460213</v>
       </c>
       <c r="C288">
-        <v>103.6436630871348</v>
+        <v>103.639369326089</v>
       </c>
     </row>
     <row r="289">
@@ -3540,10 +3540,10 @@
         <v>44105</v>
       </c>
       <c r="B289">
-        <v>97.66820056979779</v>
+        <v>97.61511969754508</v>
       </c>
       <c r="C289">
-        <v>103.7955385741272</v>
+        <v>103.7960781761796</v>
       </c>
     </row>
     <row r="290">
@@ -3551,10 +3551,10 @@
         <v>44197</v>
       </c>
       <c r="B290">
-        <v>97.65370536609946</v>
+        <v>97.61825551685386</v>
       </c>
       <c r="C290">
-        <v>104.33456195056</v>
+        <v>104.3450736557276</v>
       </c>
     </row>
     <row r="291">
@@ -3562,10 +3562,10 @@
         <v>44287</v>
       </c>
       <c r="B291">
-        <v>98.66235214052463</v>
+        <v>98.60802041617384</v>
       </c>
       <c r="C291">
-        <v>104.7061265604165</v>
+        <v>104.7072137016547</v>
       </c>
     </row>
     <row r="292">
@@ -3573,10 +3573,10 @@
         <v>44378</v>
       </c>
       <c r="B292">
-        <v>101.9483964079498</v>
+        <v>101.9005616083351</v>
       </c>
       <c r="C292">
-        <v>105.4389547994154</v>
+        <v>105.4218694186277</v>
       </c>
     </row>
     <row r="293">
@@ -3584,10 +3584,10 @@
         <v>44470</v>
       </c>
       <c r="B293">
-        <v>102.5053694683767</v>
+        <v>102.5971366935937</v>
       </c>
       <c r="C293">
-        <v>106.1723697945148</v>
+        <v>106.1835168252719</v>
       </c>
     </row>
     <row r="294">
@@ -3595,10 +3595,10 @@
         <v>44562</v>
       </c>
       <c r="B294">
-        <v>103.7385580011679</v>
+        <v>103.7739117426643</v>
       </c>
       <c r="C294">
-        <v>107.3701517505474</v>
+        <v>107.375723137273</v>
       </c>
     </row>
     <row r="295">
@@ -3606,10 +3606,10 @@
         <v>44652</v>
       </c>
       <c r="B295">
-        <v>104.4024471701864</v>
+        <v>104.3840566116525</v>
       </c>
       <c r="C295">
-        <v>109.336752549737</v>
+        <v>109.3199272290359</v>
       </c>
     </row>
     <row r="296">
@@ -3617,10 +3617,10 @@
         <v>44743</v>
       </c>
       <c r="B296">
-        <v>104.7688762870786</v>
+        <v>104.7354930918001</v>
       </c>
       <c r="C296">
-        <v>111.1880528573855</v>
+        <v>111.149587073966</v>
       </c>
     </row>
     <row r="297">
@@ -3628,10 +3628,10 @@
         <v>44835</v>
       </c>
       <c r="B297">
-        <v>106.8745886329225</v>
+        <v>106.841576021411</v>
       </c>
       <c r="C297">
-        <v>113.18902728244</v>
+        <v>113.2430252337711</v>
       </c>
     </row>
     <row r="298">
@@ -3639,10 +3639,10 @@
         <v>44927</v>
       </c>
       <c r="B298">
-        <v>108.1156625788259</v>
+        <v>108.1861058978573</v>
       </c>
       <c r="C298">
-        <v>115.4161586674342</v>
+        <v>115.481518094307</v>
       </c>
     </row>
     <row r="299">
@@ -3650,10 +3650,10 @@
         <v>45017</v>
       </c>
       <c r="B299">
-        <v>108.7867814371502</v>
+        <v>108.9604409616723</v>
       </c>
       <c r="C299">
-        <v>117.0286599117481</v>
+        <v>117.0791735824385</v>
       </c>
     </row>
     <row r="300">
@@ -3661,10 +3661,18 @@
         <v>45108</v>
       </c>
       <c r="B300">
-        <v>108.8654155644608</v>
+        <v>109.0503679936086</v>
       </c>
       <c r="C300">
-        <v>118.2025797171333</v>
+        <v>118.2277209048462</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2">
+        <v>45200</v>
+      </c>
+      <c r="C301">
+        <v>118.5887614311346</v>
       </c>
     </row>
   </sheetData>

--- a/Conjoncture - comptes trimestriels/data/smpt.xlsx
+++ b/Conjoncture - comptes trimestriels/data/smpt.xlsx
@@ -383,10 +383,10 @@
         <v>17899</v>
       </c>
       <c r="B2">
-        <v>0.848603381923972</v>
+        <v>0.8487107408261036</v>
       </c>
       <c r="C2">
-        <v>5.189544045164789</v>
+        <v>5.189544824949706</v>
       </c>
     </row>
     <row r="3">
@@ -394,10 +394,10 @@
         <v>17989</v>
       </c>
       <c r="B3">
-        <v>0.8724116841950383</v>
+        <v>0.8725220551440791</v>
       </c>
       <c r="C3">
-        <v>5.225925576296143</v>
+        <v>5.225926361547778</v>
       </c>
     </row>
     <row r="4">
@@ -405,10 +405,10 @@
         <v>18080</v>
       </c>
       <c r="B4">
-        <v>0.8781647010560669</v>
+        <v>0.8782757998334281</v>
       </c>
       <c r="C4">
-        <v>5.379847570917224</v>
+        <v>5.379848379297298</v>
       </c>
     </row>
     <row r="5">
@@ -416,10 +416,10 @@
         <v>18172</v>
       </c>
       <c r="B5">
-        <v>0.8790015650894911</v>
+        <v>0.8791127697405804</v>
       </c>
       <c r="C5">
-        <v>5.405084588677946</v>
+        <v>5.405085400850153</v>
       </c>
     </row>
     <row r="6">
@@ -427,10 +427,10 @@
         <v>18264</v>
       </c>
       <c r="B6">
-        <v>0.9036400600016304</v>
+        <v>0.9037543817293426</v>
       </c>
       <c r="C6">
-        <v>5.481853585055668</v>
+        <v>5.481854408763244</v>
       </c>
     </row>
     <row r="7">
@@ -438,10 +438,10 @@
         <v>18354</v>
       </c>
       <c r="B7">
-        <v>0.9399091871826051</v>
+        <v>0.94002809740685</v>
       </c>
       <c r="C7">
-        <v>5.582264316865145</v>
+        <v>5.582265155660515</v>
       </c>
     </row>
     <row r="8">
@@ -449,10 +449,10 @@
         <v>18445</v>
       </c>
       <c r="B8">
-        <v>0.9753459449865384</v>
+        <v>0.9754693384022175</v>
       </c>
       <c r="C8">
-        <v>5.816408085294944</v>
+        <v>5.816408959272938</v>
       </c>
     </row>
     <row r="9">
@@ -460,10 +460,10 @@
         <v>18537</v>
       </c>
       <c r="B9">
-        <v>1.018707342719991</v>
+        <v>1.018836221892803</v>
       </c>
       <c r="C9">
-        <v>5.974578988458366</v>
+        <v>5.974579886203244</v>
       </c>
     </row>
     <row r="10">
@@ -471,10 +471,10 @@
         <v>18629</v>
       </c>
       <c r="B10">
-        <v>1.076966632781541</v>
+        <v>1.077102882480506</v>
       </c>
       <c r="C10">
-        <v>6.27918280884965</v>
+        <v>6.279183752364534</v>
       </c>
     </row>
     <row r="11">
@@ -482,10 +482,10 @@
         <v>18719</v>
       </c>
       <c r="B11">
-        <v>1.166462502744651</v>
+        <v>1.166610074786361</v>
       </c>
       <c r="C11">
-        <v>6.602431913684114</v>
+        <v>6.602432905770661</v>
       </c>
     </row>
     <row r="12">
@@ -493,10 +493,10 @@
         <v>18810</v>
       </c>
       <c r="B12">
-        <v>1.272865815015952</v>
+        <v>1.27302684840254</v>
       </c>
       <c r="C12">
-        <v>6.846145147083122</v>
+        <v>6.846146175790207</v>
       </c>
     </row>
     <row r="13">
@@ -504,10 +504,10 @@
         <v>18902</v>
       </c>
       <c r="B13">
-        <v>1.371804517906859</v>
+        <v>1.371978068272223</v>
       </c>
       <c r="C13">
-        <v>7.194844569708891</v>
+        <v>7.194845650811822</v>
       </c>
     </row>
     <row r="14">
@@ -515,10 +515,10 @@
         <v>18994</v>
       </c>
       <c r="B14">
-        <v>1.430117608436656</v>
+        <v>1.430298536134602</v>
       </c>
       <c r="C14">
-        <v>7.43583664500471</v>
+        <v>7.435837762319297</v>
       </c>
     </row>
     <row r="15">
@@ -526,10 +526,10 @@
         <v>19085</v>
       </c>
       <c r="B15">
-        <v>1.467291211264614</v>
+        <v>1.467476841886533</v>
       </c>
       <c r="C15">
-        <v>7.47779383035326</v>
+        <v>7.477794953972366</v>
       </c>
     </row>
     <row r="16">
@@ -537,10 +537,10 @@
         <v>19176</v>
       </c>
       <c r="B16">
-        <v>1.487248494614707</v>
+        <v>1.487436650081654</v>
       </c>
       <c r="C16">
-        <v>7.508922797539146</v>
+        <v>7.508923925835716</v>
       </c>
     </row>
     <row r="17">
@@ -548,10 +548,10 @@
         <v>19268</v>
       </c>
       <c r="B17">
-        <v>1.497187847110617</v>
+        <v>1.497377260029508</v>
       </c>
       <c r="C17">
-        <v>7.478659546932896</v>
+        <v>7.478660670682086</v>
       </c>
     </row>
     <row r="18">
@@ -559,10 +559,10 @@
         <v>19360</v>
       </c>
       <c r="B18">
-        <v>1.505152329436995</v>
+        <v>1.505342749962144</v>
       </c>
       <c r="C18">
-        <v>7.459447144707698</v>
+        <v>7.459448265570018</v>
       </c>
     </row>
     <row r="19">
@@ -570,10 +570,10 @@
         <v>19450</v>
       </c>
       <c r="B19">
-        <v>1.524657636712872</v>
+        <v>1.524850524902444</v>
       </c>
       <c r="C19">
-        <v>7.45227150132558</v>
+        <v>7.452272621109682</v>
       </c>
     </row>
     <row r="20">
@@ -581,10 +581,10 @@
         <v>19541</v>
       </c>
       <c r="B20">
-        <v>1.540200602075209</v>
+        <v>1.540395456643578</v>
       </c>
       <c r="C20">
-        <v>7.45332216607776</v>
+        <v>7.453323286019735</v>
       </c>
     </row>
     <row r="21">
@@ -592,10 +592,10 @@
         <v>19633</v>
       </c>
       <c r="B21">
-        <v>1.563089462263584</v>
+        <v>1.563287212557982</v>
       </c>
       <c r="C21">
-        <v>7.41620350158299</v>
+        <v>7.416204615947485</v>
       </c>
     </row>
     <row r="22">
@@ -603,10 +603,10 @@
         <v>19725</v>
       </c>
       <c r="B22">
-        <v>1.600408849270152</v>
+        <v>1.600611320932038</v>
       </c>
       <c r="C22">
-        <v>7.479595202771729</v>
+        <v>7.47959632666151</v>
       </c>
     </row>
     <row r="23">
@@ -614,10 +614,10 @@
         <v>19815</v>
       </c>
       <c r="B23">
-        <v>1.638797250246533</v>
+        <v>1.639004578519494</v>
       </c>
       <c r="C23">
-        <v>7.539823419229783</v>
+        <v>7.539824552169502</v>
       </c>
     </row>
     <row r="24">
@@ -625,10 +625,10 @@
         <v>19906</v>
       </c>
       <c r="B24">
-        <v>1.65817674468167</v>
+        <v>1.658386524702161</v>
       </c>
       <c r="C24">
-        <v>7.578661425537217</v>
+        <v>7.578662564312768</v>
       </c>
     </row>
     <row r="25">
@@ -636,10 +636,10 @@
         <v>19998</v>
       </c>
       <c r="B25">
-        <v>1.686664476059446</v>
+        <v>1.686877860132939</v>
       </c>
       <c r="C25">
-        <v>7.602551600344524</v>
+        <v>7.602552742709831</v>
       </c>
     </row>
     <row r="26">
@@ -647,10 +647,10 @@
         <v>20090</v>
       </c>
       <c r="B26">
-        <v>1.717019185709542</v>
+        <v>1.717236410032051</v>
       </c>
       <c r="C26">
-        <v>7.566616119458999</v>
+        <v>7.566617256424611</v>
       </c>
     </row>
     <row r="27">
@@ -658,10 +658,10 @@
         <v>20180</v>
       </c>
       <c r="B27">
-        <v>1.752458689296085</v>
+        <v>1.752680397157404</v>
       </c>
       <c r="C27">
-        <v>7.610226284447112</v>
+        <v>7.610227427965621</v>
       </c>
     </row>
     <row r="28">
@@ -669,10 +669,10 @@
         <v>20271</v>
       </c>
       <c r="B28">
-        <v>1.800796399308374</v>
+        <v>1.801024222492338</v>
       </c>
       <c r="C28">
-        <v>7.653658275785914</v>
+        <v>7.653659425830549</v>
       </c>
     </row>
     <row r="29">
@@ -680,10 +680,10 @@
         <v>20363</v>
       </c>
       <c r="B29">
-        <v>1.853211108564943</v>
+        <v>1.853445562862759</v>
       </c>
       <c r="C29">
-        <v>7.741740106931035</v>
+        <v>7.741741270210914</v>
       </c>
     </row>
     <row r="30">
@@ -691,10 +691,10 @@
         <v>20455</v>
       </c>
       <c r="B30">
-        <v>1.902624269601014</v>
+        <v>1.902864975279432</v>
       </c>
       <c r="C30">
-        <v>7.858457576898002</v>
+        <v>7.858458757715939</v>
       </c>
     </row>
     <row r="31">
@@ -702,10 +702,10 @@
         <v>20546</v>
       </c>
       <c r="B31">
-        <v>1.949292367308396</v>
+        <v>1.949538977082697</v>
       </c>
       <c r="C31">
-        <v>7.944615882052853</v>
+        <v>7.944617075817002</v>
       </c>
     </row>
     <row r="32">
@@ -713,10 +713,10 @@
         <v>20637</v>
       </c>
       <c r="B32">
-        <v>1.993166819613711</v>
+        <v>1.993418980052942</v>
       </c>
       <c r="C32">
-        <v>8.069771926305171</v>
+        <v>8.069773138875366</v>
       </c>
     </row>
     <row r="33">
@@ -724,10 +724,10 @@
         <v>20729</v>
       </c>
       <c r="B33">
-        <v>2.033430562177002</v>
+        <v>2.033687816481388</v>
       </c>
       <c r="C33">
-        <v>8.152865052320072</v>
+        <v>8.152866277375903</v>
       </c>
     </row>
     <row r="34">
@@ -735,10 +735,10 @@
         <v>20821</v>
       </c>
       <c r="B34">
-        <v>2.07231130244205</v>
+        <v>2.072573475644567</v>
       </c>
       <c r="C34">
-        <v>8.157110053267868</v>
+        <v>8.157111278961557</v>
       </c>
     </row>
     <row r="35">
@@ -746,10 +746,10 @@
         <v>20911</v>
       </c>
       <c r="B35">
-        <v>2.120999297539099</v>
+        <v>2.121267630379688</v>
       </c>
       <c r="C35">
-        <v>8.305020767547283</v>
+        <v>8.305022015466152</v>
       </c>
     </row>
     <row r="36">
@@ -757,10 +757,10 @@
         <v>21002</v>
       </c>
       <c r="B36">
-        <v>2.184075623853812</v>
+        <v>2.184351936635665</v>
       </c>
       <c r="C36">
-        <v>8.574367165690399</v>
+        <v>8.574368454081466</v>
       </c>
     </row>
     <row r="37">
@@ -768,10 +768,10 @@
         <v>21094</v>
       </c>
       <c r="B37">
-        <v>2.265442791740517</v>
+        <v>2.265729398483013</v>
       </c>
       <c r="C37">
-        <v>8.885970971605129</v>
+        <v>8.885972306818026</v>
       </c>
     </row>
     <row r="38">
@@ -779,10 +779,10 @@
         <v>21186</v>
       </c>
       <c r="B38">
-        <v>2.354865732095681</v>
+        <v>2.355163651954417</v>
       </c>
       <c r="C38">
-        <v>9.250703844428994</v>
+        <v>9.250705234446936</v>
       </c>
     </row>
     <row r="39">
@@ -790,10 +790,10 @@
         <v>21276</v>
       </c>
       <c r="B39">
-        <v>2.434181002194126</v>
+        <v>2.434488956422865</v>
       </c>
       <c r="C39">
-        <v>9.524631048237588</v>
+        <v>9.524632479416043</v>
       </c>
     </row>
     <row r="40">
@@ -801,10 +801,10 @@
         <v>21367</v>
       </c>
       <c r="B40">
-        <v>2.492267122171221</v>
+        <v>2.492582425017939</v>
       </c>
       <c r="C40">
-        <v>9.63776793222212</v>
+        <v>9.637769380400613</v>
       </c>
     </row>
     <row r="41">
@@ -812,10 +812,10 @@
         <v>21459</v>
       </c>
       <c r="B41">
-        <v>2.538215538062781</v>
+        <v>2.538536653956665</v>
       </c>
       <c r="C41">
-        <v>9.72380773449191</v>
+        <v>9.723809195598809</v>
       </c>
     </row>
     <row r="42">
@@ -823,10 +823,10 @@
         <v>21551</v>
       </c>
       <c r="B42">
-        <v>2.598404326825598</v>
+        <v>2.598733057351265</v>
       </c>
       <c r="C42">
-        <v>9.960427117768329</v>
+        <v>9.960428614429841</v>
       </c>
     </row>
     <row r="43">
@@ -834,10 +834,10 @@
         <v>21641</v>
       </c>
       <c r="B43">
-        <v>2.670955431277874</v>
+        <v>2.671293340422302</v>
       </c>
       <c r="C43">
-        <v>10.05942744798944</v>
+        <v>10.05942895952681</v>
       </c>
     </row>
     <row r="44">
@@ -845,10 +845,10 @@
         <v>21732</v>
       </c>
       <c r="B44">
-        <v>2.727787235788515</v>
+        <v>2.728132334864386</v>
       </c>
       <c r="C44">
-        <v>10.15534405376881</v>
+        <v>10.15534557971869</v>
       </c>
     </row>
     <row r="45">
@@ -856,10 +856,10 @@
         <v>21824</v>
       </c>
       <c r="B45">
-        <v>2.780711627551868</v>
+        <v>2.781063422222779</v>
       </c>
       <c r="C45">
-        <v>10.26913573756732</v>
+        <v>10.26913728061562</v>
       </c>
     </row>
     <row r="46">
@@ -867,10 +867,10 @@
         <v>21916</v>
       </c>
       <c r="B46">
-        <v>2.830292538837072</v>
+        <v>2.830650606111083</v>
       </c>
       <c r="C46">
-        <v>10.3364946182015</v>
+        <v>10.33649617137121</v>
       </c>
     </row>
     <row r="47">
@@ -878,10 +878,10 @@
         <v>22007</v>
       </c>
       <c r="B47">
-        <v>2.884624589797057</v>
+        <v>2.884989530752536</v>
       </c>
       <c r="C47">
-        <v>10.40670028575017</v>
+        <v>10.40670184946903</v>
       </c>
     </row>
     <row r="48">
@@ -889,10 +889,10 @@
         <v>22098</v>
       </c>
       <c r="B48">
-        <v>2.954135559912338</v>
+        <v>2.954509294871703</v>
       </c>
       <c r="C48">
-        <v>10.46094849343656</v>
+        <v>10.4609500653068</v>
       </c>
     </row>
     <row r="49">
@@ -900,10 +900,10 @@
         <v>22190</v>
       </c>
       <c r="B49">
-        <v>3.03956019188987</v>
+        <v>3.039944734129643</v>
       </c>
       <c r="C49">
-        <v>10.51629187082879</v>
+        <v>10.51629345101497</v>
       </c>
     </row>
     <row r="50">
@@ -911,10 +911,10 @@
         <v>22282</v>
       </c>
       <c r="B50">
-        <v>3.117249636550038</v>
+        <v>3.117644007472637</v>
       </c>
       <c r="C50">
-        <v>10.56686368717453</v>
+        <v>10.56686527495967</v>
       </c>
     </row>
     <row r="51">
@@ -922,10 +922,10 @@
         <v>22372</v>
       </c>
       <c r="B51">
-        <v>3.210499402469889</v>
+        <v>3.210905570649849</v>
       </c>
       <c r="C51">
-        <v>10.68750412135854</v>
+        <v>10.6875057272712</v>
       </c>
     </row>
     <row r="52">
@@ -933,10 +933,10 @@
         <v>22463</v>
       </c>
       <c r="B52">
-        <v>3.300739669077177</v>
+        <v>3.301157253775333</v>
       </c>
       <c r="C52">
-        <v>10.77377525881255</v>
+        <v>10.77377687768839</v>
       </c>
     </row>
     <row r="53">
@@ -944,10 +944,10 @@
         <v>22555</v>
       </c>
       <c r="B53">
-        <v>3.393771759090804</v>
+        <v>3.394201113507606</v>
       </c>
       <c r="C53">
-        <v>10.88423535206054</v>
+        <v>10.8842369875342</v>
       </c>
     </row>
     <row r="54">
@@ -955,10 +955,10 @@
         <v>22647</v>
       </c>
       <c r="B54">
-        <v>3.490940022746315</v>
+        <v>3.491381670159269</v>
       </c>
       <c r="C54">
-        <v>11.04657300789192</v>
+        <v>11.04657466775856</v>
       </c>
     </row>
     <row r="55">
@@ -966,10 +966,10 @@
         <v>22737</v>
       </c>
       <c r="B55">
-        <v>3.570949783218352</v>
+        <v>3.571401552862993</v>
       </c>
       <c r="C55">
-        <v>11.17085784085259</v>
+        <v>11.17085951939437</v>
       </c>
     </row>
     <row r="56">
@@ -977,10 +977,10 @@
         <v>22828</v>
       </c>
       <c r="B56">
-        <v>3.652633258475214</v>
+        <v>3.653095362097321</v>
       </c>
       <c r="C56">
-        <v>11.24345619024565</v>
+        <v>11.2434578796961</v>
       </c>
     </row>
     <row r="57">
@@ -988,10 +988,10 @@
         <v>22920</v>
       </c>
       <c r="B57">
-        <v>3.745725862084472</v>
+        <v>3.746199743080949</v>
       </c>
       <c r="C57">
-        <v>11.32319131785306</v>
+        <v>11.32319301928458</v>
       </c>
     </row>
     <row r="58">
@@ -999,10 +999,10 @@
         <v>23012</v>
       </c>
       <c r="B58">
-        <v>3.861107720617766</v>
+        <v>3.861596198857104</v>
       </c>
       <c r="C58">
-        <v>11.36481151401447</v>
+        <v>11.36481322169987</v>
       </c>
     </row>
     <row r="59">
@@ -1010,10 +1010,10 @@
         <v>23102</v>
       </c>
       <c r="B59">
-        <v>3.964845582196655</v>
+        <v>3.965347184568144</v>
       </c>
       <c r="C59">
-        <v>11.66045857692131</v>
+        <v>11.66046032903087</v>
       </c>
     </row>
     <row r="60">
@@ -1021,10 +1021,10 @@
         <v>23193</v>
       </c>
       <c r="B60">
-        <v>4.062126390540752</v>
+        <v>4.062640300146698</v>
       </c>
       <c r="C60">
-        <v>11.89563540109953</v>
+        <v>11.89563718854694</v>
       </c>
     </row>
     <row r="61">
@@ -1032,10 +1032,10 @@
         <v>23285</v>
       </c>
       <c r="B61">
-        <v>4.157981172859786</v>
+        <v>4.158507209290127</v>
       </c>
       <c r="C61">
-        <v>11.98124492104031</v>
+        <v>11.98124672135148</v>
       </c>
     </row>
     <row r="62">
@@ -1043,10 +1043,10 @@
         <v>23377</v>
       </c>
       <c r="B62">
-        <v>4.247629605328271</v>
+        <v>4.248166983402415</v>
       </c>
       <c r="C62">
-        <v>11.99531997192914</v>
+        <v>11.99532177435523</v>
       </c>
     </row>
     <row r="63">
@@ -1054,10 +1054,10 @@
         <v>23468</v>
       </c>
       <c r="B63">
-        <v>4.33780757697651</v>
+        <v>4.338356363687762</v>
       </c>
       <c r="C63">
-        <v>12.06011413919493</v>
+        <v>12.06011595135704</v>
       </c>
     </row>
     <row r="64">
@@ -1065,10 +1065,10 @@
         <v>23559</v>
       </c>
       <c r="B64">
-        <v>4.414522468371597</v>
+        <v>4.415080960472544</v>
       </c>
       <c r="C64">
-        <v>12.15857169260956</v>
+        <v>12.15857351956599</v>
       </c>
     </row>
     <row r="65">
@@ -1076,10 +1076,10 @@
         <v>23651</v>
       </c>
       <c r="B65">
-        <v>4.500813814604933</v>
+        <v>4.501383223636441</v>
       </c>
       <c r="C65">
-        <v>12.24645553711417</v>
+        <v>12.24645737727609</v>
       </c>
     </row>
     <row r="66">
@@ -1087,10 +1087,10 @@
         <v>23743</v>
       </c>
       <c r="B66">
-        <v>4.574448260387467</v>
+        <v>4.575026985093913</v>
       </c>
       <c r="C66">
-        <v>12.33697154654746</v>
+        <v>12.33697340031038</v>
       </c>
     </row>
     <row r="67">
@@ -1098,10 +1098,10 @@
         <v>23833</v>
       </c>
       <c r="B67">
-        <v>4.653146378204699</v>
+        <v>4.653735059203695</v>
       </c>
       <c r="C67">
-        <v>12.38807633227711</v>
+        <v>12.38807819371907</v>
       </c>
     </row>
     <row r="68">
@@ -1109,10 +1109,10 @@
         <v>23924</v>
       </c>
       <c r="B68">
-        <v>4.725165770530678</v>
+        <v>4.725763562880227</v>
       </c>
       <c r="C68">
-        <v>12.44246391051053</v>
+        <v>12.44246578012482</v>
       </c>
     </row>
     <row r="69">
@@ -1120,10 +1120,10 @@
         <v>24016</v>
       </c>
       <c r="B69">
-        <v>4.799216905916722</v>
+        <v>4.799824066657637</v>
       </c>
       <c r="C69">
-        <v>12.55682699243818</v>
+        <v>12.55682887923675</v>
       </c>
     </row>
     <row r="70">
@@ -1131,10 +1131,10 @@
         <v>24108</v>
       </c>
       <c r="B70">
-        <v>4.865088219424075</v>
+        <v>4.865703713706961</v>
       </c>
       <c r="C70">
-        <v>12.70321040561078</v>
+        <v>12.70321231440504</v>
       </c>
     </row>
     <row r="71">
@@ -1142,10 +1142,10 @@
         <v>24198</v>
       </c>
       <c r="B71">
-        <v>4.941563348473231</v>
+        <v>4.942188517812887</v>
       </c>
       <c r="C71">
-        <v>12.7449339815786</v>
+        <v>12.74493589664227</v>
       </c>
     </row>
     <row r="72">
@@ -1153,10 +1153,10 @@
         <v>24289</v>
       </c>
       <c r="B72">
-        <v>5.020626681633682</v>
+        <v>5.021261853470178</v>
       </c>
       <c r="C72">
-        <v>12.84441741072119</v>
+        <v>12.84441934073332</v>
       </c>
     </row>
     <row r="73">
@@ -1164,10 +1164,10 @@
         <v>24381</v>
       </c>
       <c r="B73">
-        <v>5.114911130723162</v>
+        <v>5.115558230717332</v>
       </c>
       <c r="C73">
-        <v>12.91716911067222</v>
+        <v>12.91717105161608</v>
       </c>
     </row>
     <row r="74">
@@ -1175,10 +1175,10 @@
         <v>24473</v>
       </c>
       <c r="B74">
-        <v>5.227068841409451</v>
+        <v>5.227730130751604</v>
       </c>
       <c r="C74">
-        <v>13.05147060741405</v>
+        <v>13.05147256853816</v>
       </c>
     </row>
     <row r="75">
@@ -1186,10 +1186,10 @@
         <v>24563</v>
       </c>
       <c r="B75">
-        <v>5.301161949744806</v>
+        <v>5.301832612788425</v>
       </c>
       <c r="C75">
-        <v>13.13491904678184</v>
+        <v>13.13492102044497</v>
       </c>
     </row>
     <row r="76">
@@ -1197,10 +1197,10 @@
         <v>24654</v>
       </c>
       <c r="B76">
-        <v>5.386705511033866</v>
+        <v>5.387386996403935</v>
       </c>
       <c r="C76">
-        <v>13.22905461725163</v>
+        <v>13.22905660505965</v>
       </c>
     </row>
     <row r="77">
@@ -1208,10 +1208,10 @@
         <v>24746</v>
       </c>
       <c r="B77">
-        <v>5.492531873451168</v>
+        <v>5.493226747174769</v>
       </c>
       <c r="C77">
-        <v>13.37789686054558</v>
+        <v>13.37789887071875</v>
       </c>
     </row>
     <row r="78">
@@ -1219,10 +1219,10 @@
         <v>24838</v>
       </c>
       <c r="B78">
-        <v>5.664956513180907</v>
+        <v>5.665673200769991</v>
       </c>
       <c r="C78">
-        <v>13.59525892252894</v>
+        <v>13.5952609653631</v>
       </c>
     </row>
     <row r="79">
@@ -1230,10 +1230,10 @@
         <v>24929</v>
       </c>
       <c r="B79">
-        <v>5.681445760673939</v>
+        <v>5.682164534358301</v>
       </c>
       <c r="C79">
-        <v>13.64593192766693</v>
+        <v>13.64593397811525</v>
       </c>
     </row>
     <row r="80">
@@ -1241,10 +1241,10 @@
         <v>25020</v>
       </c>
       <c r="B80">
-        <v>6.212375698973011</v>
+        <v>6.213161641910404</v>
       </c>
       <c r="C80">
-        <v>13.98700308185354</v>
+        <v>13.98700518355148</v>
       </c>
     </row>
     <row r="81">
@@ -1252,10 +1252,10 @@
         <v>25112</v>
       </c>
       <c r="B81">
-        <v>6.355763024186976</v>
+        <v>6.356567107407737</v>
       </c>
       <c r="C81">
-        <v>14.19281486585949</v>
+        <v>14.19281699848286</v>
       </c>
     </row>
     <row r="82">
@@ -1263,10 +1263,10 @@
         <v>25204</v>
       </c>
       <c r="B82">
-        <v>6.447407289245456</v>
+        <v>6.448222966607712</v>
       </c>
       <c r="C82">
-        <v>14.56251677788396</v>
+        <v>14.56251896605903</v>
       </c>
     </row>
     <row r="83">
@@ -1274,10 +1274,10 @@
         <v>25294</v>
       </c>
       <c r="B83">
-        <v>6.583203091072532</v>
+        <v>6.584035948295849</v>
       </c>
       <c r="C83">
-        <v>14.73452258861975</v>
+        <v>14.73452480264055</v>
       </c>
     </row>
     <row r="84">
@@ -1285,10 +1285,10 @@
         <v>25385</v>
       </c>
       <c r="B84">
-        <v>6.736236243363986</v>
+        <v>6.737088461187992</v>
       </c>
       <c r="C84">
-        <v>14.92346196856445</v>
+        <v>14.92346421097544</v>
       </c>
     </row>
     <row r="85">
@@ -1296,10 +1296,10 @@
         <v>25477</v>
       </c>
       <c r="B85">
-        <v>6.945997088987324</v>
+        <v>6.9468758441721</v>
       </c>
       <c r="C85">
-        <v>15.15110043377857</v>
+        <v>15.15110271039469</v>
       </c>
     </row>
     <row r="86">
@@ -1307,10 +1307,10 @@
         <v>25569</v>
       </c>
       <c r="B86">
-        <v>7.168921619276116</v>
+        <v>7.169828577191802</v>
       </c>
       <c r="C86">
-        <v>15.27464616161047</v>
+        <v>15.27464845679066</v>
       </c>
     </row>
     <row r="87">
@@ -1318,10 +1318,10 @@
         <v>25659</v>
       </c>
       <c r="B87">
-        <v>7.348714823821548</v>
+        <v>7.349644527817984</v>
       </c>
       <c r="C87">
-        <v>15.49024101767963</v>
+        <v>15.49024334525527</v>
       </c>
     </row>
     <row r="88">
@@ -1329,10 +1329,10 @@
         <v>25750</v>
       </c>
       <c r="B88">
-        <v>7.530498294087229</v>
+        <v>7.53145099595783</v>
       </c>
       <c r="C88">
-        <v>15.70439015868754</v>
+        <v>15.7043925184414</v>
       </c>
     </row>
     <row r="89">
@@ -1340,10 +1340,10 @@
         <v>25842</v>
       </c>
       <c r="B89">
-        <v>7.749731530661333</v>
+        <v>7.750711968268194</v>
       </c>
       <c r="C89">
-        <v>15.85563836475764</v>
+        <v>15.85564074723817</v>
       </c>
     </row>
     <row r="90">
@@ -1351,10 +1351,10 @@
         <v>25934</v>
       </c>
       <c r="B90">
-        <v>7.99479085957115</v>
+        <v>7.995802300236765</v>
       </c>
       <c r="C90">
-        <v>16.09055048336892</v>
+        <v>16.09055290114752</v>
       </c>
     </row>
     <row r="91">
@@ -1362,10 +1362,10 @@
         <v>26024</v>
       </c>
       <c r="B91">
-        <v>8.182420903947953</v>
+        <v>8.183456082152212</v>
       </c>
       <c r="C91">
-        <v>16.36651090340419</v>
+        <v>16.36651336264882</v>
       </c>
     </row>
     <row r="92">
@@ -1373,10 +1373,10 @@
         <v>26115</v>
       </c>
       <c r="B92">
-        <v>8.414357455521735</v>
+        <v>8.415421976589894</v>
       </c>
       <c r="C92">
-        <v>16.563104935584</v>
+        <v>16.563107424369</v>
       </c>
     </row>
     <row r="93">
@@ -1384,10 +1384,10 @@
         <v>26207</v>
       </c>
       <c r="B93">
-        <v>8.652965454696636</v>
+        <v>8.654060162649948</v>
       </c>
       <c r="C93">
-        <v>16.81588738798725</v>
+        <v>16.81588991475554</v>
       </c>
     </row>
     <row r="94">
@@ -1395,10 +1395,10 @@
         <v>26299</v>
       </c>
       <c r="B94">
-        <v>8.818218005025532</v>
+        <v>8.819333619485649</v>
       </c>
       <c r="C94">
-        <v>17.01299752753062</v>
+        <v>17.01300008391684</v>
       </c>
     </row>
     <row r="95">
@@ -1406,10 +1406,10 @@
         <v>26390</v>
       </c>
       <c r="B95">
-        <v>9.045537119134844</v>
+        <v>9.046681492295486</v>
       </c>
       <c r="C95">
-        <v>17.25927594036311</v>
+        <v>17.25927853375531</v>
       </c>
     </row>
     <row r="96">
@@ -1417,10 +1417,10 @@
         <v>26481</v>
       </c>
       <c r="B96">
-        <v>9.282814568982582</v>
+        <v>9.283988960697306</v>
       </c>
       <c r="C96">
-        <v>17.56683968816649</v>
+        <v>17.56684232777346</v>
       </c>
     </row>
     <row r="97">
@@ -1428,10 +1428,10 @@
         <v>26573</v>
       </c>
       <c r="B97">
-        <v>9.589082005389141</v>
+        <v>9.590295143750922</v>
       </c>
       <c r="C97">
-        <v>17.8659614037603</v>
+        <v>17.86596408831353</v>
       </c>
     </row>
     <row r="98">
@@ -1439,10 +1439,10 @@
         <v>26665</v>
       </c>
       <c r="B98">
-        <v>9.884157836609415</v>
+        <v>9.885408305740743</v>
       </c>
       <c r="C98">
-        <v>18.02875474095671</v>
+        <v>18.0287574499714</v>
       </c>
     </row>
     <row r="99">
@@ -1450,10 +1450,10 @@
         <v>26755</v>
       </c>
       <c r="B99">
-        <v>10.1943503257031</v>
+        <v>10.19564003804956</v>
       </c>
       <c r="C99">
-        <v>18.38689010370538</v>
+        <v>18.38689286653376</v>
       </c>
     </row>
     <row r="100">
@@ -1461,10 +1461,10 @@
         <v>26846</v>
       </c>
       <c r="B100">
-        <v>10.56648380650879</v>
+        <v>10.56782059837767</v>
       </c>
       <c r="C100">
-        <v>18.90368344338594</v>
+        <v>18.90368628386809</v>
       </c>
     </row>
     <row r="101">
@@ -1472,10 +1472,10 @@
         <v>26938</v>
       </c>
       <c r="B101">
-        <v>10.9291099912106</v>
+        <v>10.93049265981048</v>
       </c>
       <c r="C101">
-        <v>19.44132604087011</v>
+        <v>19.44132896213885</v>
       </c>
     </row>
     <row r="102">
@@ -1483,10 +1483,10 @@
         <v>27030</v>
       </c>
       <c r="B102">
-        <v>11.40857823768309</v>
+        <v>11.41002156499072</v>
       </c>
       <c r="C102">
-        <v>20.28417958903068</v>
+        <v>20.28418263694725</v>
       </c>
     </row>
     <row r="103">
@@ -1494,10 +1494,10 @@
         <v>27120</v>
       </c>
       <c r="B103">
-        <v>11.94397694245862</v>
+        <v>11.94548800437394</v>
       </c>
       <c r="C103">
-        <v>21.09823895381131</v>
+        <v>21.09824212404908</v>
       </c>
     </row>
     <row r="104">
@@ -1505,10 +1505,10 @@
         <v>27211</v>
       </c>
       <c r="B104">
-        <v>12.53625031462697</v>
+        <v>12.53783630650408</v>
       </c>
       <c r="C104">
-        <v>21.78131772600464</v>
+        <v>21.78132099888235</v>
       </c>
     </row>
     <row r="105">
@@ -1516,10 +1516,10 @@
         <v>27303</v>
       </c>
       <c r="B105">
-        <v>12.98741282652474</v>
+        <v>12.98905589608148</v>
       </c>
       <c r="C105">
-        <v>22.40106483754222</v>
+        <v>22.40106820354361</v>
       </c>
     </row>
     <row r="106">
@@ -1527,10 +1527,10 @@
         <v>27395</v>
       </c>
       <c r="B106">
-        <v>13.66183860956082</v>
+        <v>13.66356700238304</v>
       </c>
       <c r="C106">
-        <v>23.0565258018533</v>
+        <v>23.05652926634477</v>
       </c>
     </row>
     <row r="107">
@@ -1538,10 +1538,10 @@
         <v>27485</v>
       </c>
       <c r="B107">
-        <v>14.25503748444256</v>
+        <v>14.25684092431421</v>
       </c>
       <c r="C107">
-        <v>23.65042623801745</v>
+        <v>23.65042979174886</v>
       </c>
     </row>
     <row r="108">
@@ -1549,10 +1549,10 @@
         <v>27576</v>
       </c>
       <c r="B108">
-        <v>14.74023278382546</v>
+        <v>14.74209760694843</v>
       </c>
       <c r="C108">
-        <v>24.14789719271204</v>
+        <v>24.14790082119382</v>
       </c>
     </row>
     <row r="109">
@@ -1560,10 +1560,10 @@
         <v>27668</v>
       </c>
       <c r="B109">
-        <v>15.2161986358436</v>
+        <v>15.21812367457778</v>
       </c>
       <c r="C109">
-        <v>24.6486417291953</v>
+        <v>24.64864543291934</v>
       </c>
     </row>
     <row r="110">
@@ -1571,10 +1571,10 @@
         <v>27760</v>
       </c>
       <c r="B110">
-        <v>15.74562022337087</v>
+        <v>15.74761224053292</v>
       </c>
       <c r="C110">
-        <v>25.28056511551999</v>
+        <v>25.28056891419734</v>
       </c>
     </row>
     <row r="111">
@@ -1582,10 +1582,10 @@
         <v>27851</v>
       </c>
       <c r="B111">
-        <v>16.31058730476786</v>
+        <v>16.31265079730568</v>
       </c>
       <c r="C111">
-        <v>25.83252338839316</v>
+        <v>25.83252727000818</v>
       </c>
     </row>
     <row r="112">
@@ -1593,10 +1593,10 @@
         <v>27942</v>
       </c>
       <c r="B112">
-        <v>16.8615626220554</v>
+        <v>16.86369581983648</v>
       </c>
       <c r="C112">
-        <v>26.44873329542128</v>
+        <v>26.44873726962847</v>
       </c>
     </row>
     <row r="113">
@@ -1604,10 +1604,10 @@
         <v>28034</v>
       </c>
       <c r="B113">
-        <v>17.39315156393737</v>
+        <v>17.39535201434364</v>
       </c>
       <c r="C113">
-        <v>27.12180226754026</v>
+        <v>27.12180634288332</v>
       </c>
     </row>
     <row r="114">
@@ -1615,10 +1615,10 @@
         <v>28126</v>
       </c>
       <c r="B114">
-        <v>17.87197766473236</v>
+        <v>17.87423869260696</v>
       </c>
       <c r="C114">
-        <v>27.60064248059034</v>
+        <v>27.60064662788431</v>
       </c>
     </row>
     <row r="115">
@@ -1626,10 +1626,10 @@
         <v>28216</v>
       </c>
       <c r="B115">
-        <v>18.26729474052399</v>
+        <v>18.26960578093466</v>
       </c>
       <c r="C115">
-        <v>28.38106297086459</v>
+        <v>28.38106723542515</v>
       </c>
     </row>
     <row r="116">
@@ -1637,10 +1637,10 @@
         <v>28307</v>
       </c>
       <c r="B116">
-        <v>18.75541446508486</v>
+        <v>18.75778725872308</v>
       </c>
       <c r="C116">
-        <v>28.99850426295578</v>
+        <v>28.99850862029355</v>
       </c>
     </row>
     <row r="117">
@@ -1648,10 +1648,10 @@
         <v>28399</v>
       </c>
       <c r="B117">
-        <v>19.31686294535413</v>
+        <v>19.31930676922123</v>
       </c>
       <c r="C117">
-        <v>29.48721926639174</v>
+        <v>29.4872236971642</v>
       </c>
     </row>
     <row r="118">
@@ -1659,10 +1659,10 @@
         <v>28491</v>
       </c>
       <c r="B118">
-        <v>19.83663682283638</v>
+        <v>19.8391464045758</v>
       </c>
       <c r="C118">
-        <v>29.92605802089934</v>
+        <v>29.92606251761205</v>
       </c>
     </row>
     <row r="119">
@@ -1670,10 +1670,10 @@
         <v>28581</v>
       </c>
       <c r="B119">
-        <v>20.42904634154732</v>
+        <v>20.43163087047279</v>
       </c>
       <c r="C119">
-        <v>30.66345602248174</v>
+        <v>30.66346062999645</v>
       </c>
     </row>
     <row r="120">
@@ -1681,10 +1681,10 @@
         <v>28672</v>
       </c>
       <c r="B120">
-        <v>21.06736059337814</v>
+        <v>21.0700258770104</v>
       </c>
       <c r="C120">
-        <v>31.54048258224788</v>
+        <v>31.54048732154528</v>
       </c>
     </row>
     <row r="121">
@@ -1692,10 +1692,10 @@
         <v>28764</v>
       </c>
       <c r="B121">
-        <v>21.6634416995899</v>
+        <v>21.66618239490977</v>
       </c>
       <c r="C121">
-        <v>32.27728605668241</v>
+        <v>32.27729090669247</v>
       </c>
     </row>
     <row r="122">
@@ -1703,10 +1703,10 @@
         <v>28856</v>
       </c>
       <c r="B122">
-        <v>22.274364199372</v>
+        <v>22.2771821840007</v>
       </c>
       <c r="C122">
-        <v>33.01759163402674</v>
+        <v>33.0175965952757</v>
       </c>
     </row>
     <row r="123">
@@ -1714,10 +1714,10 @@
         <v>28946</v>
       </c>
       <c r="B123">
-        <v>23.03128066735574</v>
+        <v>23.03419441134946</v>
       </c>
       <c r="C123">
-        <v>33.91777320375075</v>
+        <v>33.91777830026168</v>
       </c>
     </row>
     <row r="124">
@@ -1725,10 +1725,10 @@
         <v>29037</v>
       </c>
       <c r="B124">
-        <v>23.78322828260604</v>
+        <v>23.786237157343</v>
       </c>
       <c r="C124">
-        <v>35.0901027739116</v>
+        <v>35.09010804657768</v>
       </c>
     </row>
     <row r="125">
@@ -1736,10 +1736,10 @@
         <v>29129</v>
       </c>
       <c r="B125">
-        <v>24.64948040198795</v>
+        <v>24.65259886841226</v>
       </c>
       <c r="C125">
-        <v>35.98245527650666</v>
+        <v>35.98246068325832</v>
       </c>
     </row>
     <row r="126">
@@ -1747,10 +1747,10 @@
         <v>29221</v>
       </c>
       <c r="B126">
-        <v>25.47426686779589</v>
+        <v>25.47806922753189</v>
       </c>
       <c r="C126">
-        <v>37.33448243791493</v>
+        <v>37.33432946204758</v>
       </c>
     </row>
     <row r="127">
@@ -1758,10 +1758,10 @@
         <v>29312</v>
       </c>
       <c r="B127">
-        <v>26.42321834418744</v>
+        <v>26.4265612105637</v>
       </c>
       <c r="C127">
-        <v>38.43013252677847</v>
+        <v>38.42973779906364</v>
       </c>
     </row>
     <row r="128">
@@ -1769,10 +1769,10 @@
         <v>29403</v>
       </c>
       <c r="B128">
-        <v>27.30621186797699</v>
+        <v>27.30966644403686</v>
       </c>
       <c r="C128">
-        <v>39.57243695630245</v>
+        <v>39.57270282787861</v>
       </c>
     </row>
     <row r="129">
@@ -1780,10 +1780,10 @@
         <v>29495</v>
       </c>
       <c r="B129">
-        <v>28.10820571550571</v>
+        <v>28.11176175378082</v>
       </c>
       <c r="C129">
-        <v>40.76567398761865</v>
+        <v>40.7653007468775</v>
       </c>
     </row>
     <row r="130">
@@ -1791,10 +1791,10 @@
         <v>29587</v>
       </c>
       <c r="B130">
-        <v>28.91434827995236</v>
+        <v>28.91800630530709</v>
       </c>
       <c r="C130">
-        <v>42.13131286582759</v>
+        <v>42.13122357821757</v>
       </c>
     </row>
     <row r="131">
@@ -1802,10 +1802,10 @@
         <v>29677</v>
       </c>
       <c r="B131">
-        <v>29.90841307843939</v>
+        <v>29.91219686537803</v>
       </c>
       <c r="C131">
-        <v>43.44837721588848</v>
+        <v>43.44794946410371</v>
       </c>
     </row>
     <row r="132">
@@ -1813,10 +1813,10 @@
         <v>29768</v>
       </c>
       <c r="B132">
-        <v>31.01507256073491</v>
+        <v>31.01899635388797</v>
       </c>
       <c r="C132">
-        <v>45.15469708025029</v>
+        <v>45.15452414932695</v>
       </c>
     </row>
     <row r="133">
@@ -1824,10 +1824,10 @@
         <v>29860</v>
       </c>
       <c r="B133">
-        <v>32.24570410507405</v>
+        <v>32.24978358845219</v>
       </c>
       <c r="C133">
-        <v>46.57244788274332</v>
+        <v>46.57275032376902</v>
       </c>
     </row>
     <row r="134">
@@ -1835,10 +1835,10 @@
         <v>29952</v>
       </c>
       <c r="B134">
-        <v>33.58837083556551</v>
+        <v>33.59262018301582</v>
       </c>
       <c r="C134">
-        <v>47.89072586581693</v>
+        <v>47.89071346054804</v>
       </c>
     </row>
     <row r="135">
@@ -1846,10 +1846,10 @@
         <v>30042</v>
       </c>
       <c r="B135">
-        <v>34.46887630189617</v>
+        <v>34.47323704425982</v>
       </c>
       <c r="C135">
-        <v>49.23680962796627</v>
+        <v>49.23681176800853</v>
       </c>
     </row>
     <row r="136">
@@ -1857,10 +1857,10 @@
         <v>30133</v>
       </c>
       <c r="B136">
-        <v>35.0613177894479</v>
+        <v>35.06575348304204</v>
       </c>
       <c r="C136">
-        <v>50.03590523101563</v>
+        <v>50.0355791535634</v>
       </c>
     </row>
     <row r="137">
@@ -1868,10 +1868,10 @@
         <v>30225</v>
       </c>
       <c r="B137">
-        <v>35.78082009209771</v>
+        <v>35.78534681169875</v>
       </c>
       <c r="C137">
-        <v>51.04936721776918</v>
+        <v>51.04937488848675</v>
       </c>
     </row>
     <row r="138">
@@ -1879,10 +1879,10 @@
         <v>30317</v>
       </c>
       <c r="B138">
-        <v>36.8480879544453</v>
+        <v>36.85274969672999</v>
       </c>
       <c r="C138">
-        <v>52.40278382360339</v>
+        <v>52.40221820702379</v>
       </c>
     </row>
     <row r="139">
@@ -1890,10 +1890,10 @@
         <v>30407</v>
       </c>
       <c r="B139">
-        <v>37.59124247355123</v>
+        <v>37.59658346784466</v>
       </c>
       <c r="C139">
-        <v>53.78737279019442</v>
+        <v>53.78715569823589</v>
       </c>
     </row>
     <row r="140">
@@ -1901,10 +1901,10 @@
         <v>30498</v>
       </c>
       <c r="B140">
-        <v>38.57383461008646</v>
+        <v>38.57871468082735</v>
       </c>
       <c r="C140">
-        <v>54.9618339835524</v>
+        <v>54.96156852170762</v>
       </c>
     </row>
     <row r="141">
@@ -1912,10 +1912,10 @@
         <v>30590</v>
       </c>
       <c r="B141">
-        <v>39.42536124969661</v>
+        <v>39.43034904916816</v>
       </c>
       <c r="C141">
-        <v>56.08892837454702</v>
+        <v>56.08901883922124</v>
       </c>
     </row>
     <row r="142">
@@ -1923,10 +1923,10 @@
         <v>30682</v>
       </c>
       <c r="B142">
-        <v>40.20686967970116</v>
+        <v>40.21195634972736</v>
       </c>
       <c r="C142">
-        <v>57.15410250057502</v>
+        <v>57.15420588016214</v>
       </c>
     </row>
     <row r="143">
@@ -1934,10 +1934,10 @@
         <v>30773</v>
       </c>
       <c r="B143">
-        <v>41.13944431870645</v>
+        <v>41.14464897104516</v>
       </c>
       <c r="C143">
-        <v>58.08896695991006</v>
+        <v>58.08872585376328</v>
       </c>
     </row>
     <row r="144">
@@ -1945,10 +1945,10 @@
         <v>30864</v>
       </c>
       <c r="B144">
-        <v>41.394018299387</v>
+        <v>41.39925515850647</v>
       </c>
       <c r="C144">
-        <v>59.09235789646949</v>
+        <v>59.09261758823761</v>
       </c>
     </row>
     <row r="145">
@@ -1956,10 +1956,10 @@
         <v>30956</v>
       </c>
       <c r="B145">
-        <v>42.3412410424754</v>
+        <v>42.34659773707507</v>
       </c>
       <c r="C145">
-        <v>60.07744638519139</v>
+        <v>60.0773473409672</v>
       </c>
     </row>
     <row r="146">
@@ -1967,10 +1967,10 @@
         <v>31048</v>
       </c>
       <c r="B146">
-        <v>43.10348318145451</v>
+        <v>43.10893630918295</v>
       </c>
       <c r="C146">
-        <v>61.03598015700206</v>
+        <v>61.03538892904643</v>
       </c>
     </row>
     <row r="147">
@@ -1978,10 +1978,10 @@
         <v>31138</v>
       </c>
       <c r="B147">
-        <v>43.76506169263588</v>
+        <v>43.77059851828981</v>
       </c>
       <c r="C147">
-        <v>62.04298367199633</v>
+        <v>62.04299299462323</v>
       </c>
     </row>
     <row r="148">
@@ -1989,10 +1989,10 @@
         <v>31229</v>
       </c>
       <c r="B148">
-        <v>44.28093965713242</v>
+        <v>44.28654174777715</v>
       </c>
       <c r="C148">
-        <v>62.66836719218667</v>
+        <v>62.66821756645782</v>
       </c>
     </row>
     <row r="149">
@@ -2000,10 +2000,10 @@
         <v>31321</v>
       </c>
       <c r="B149">
-        <v>44.81223827303454</v>
+        <v>44.8179075795746</v>
       </c>
       <c r="C149">
-        <v>63.15277821667776</v>
+        <v>63.15257525255188</v>
       </c>
     </row>
     <row r="150">
@@ -2011,10 +2011,10 @@
         <v>31413</v>
       </c>
       <c r="B150">
-        <v>45.11947644908422</v>
+        <v>45.12518462508201</v>
       </c>
       <c r="C150">
-        <v>63.30733885032435</v>
+        <v>63.30755792593864</v>
       </c>
     </row>
     <row r="151">
@@ -2022,10 +2022,10 @@
         <v>31503</v>
       </c>
       <c r="B151">
-        <v>45.89102966539746</v>
+        <v>45.89683545249131</v>
       </c>
       <c r="C151">
-        <v>63.63764422105665</v>
+        <v>63.63708044011069</v>
       </c>
     </row>
     <row r="152">
@@ -2033,10 +2033,10 @@
         <v>31594</v>
       </c>
       <c r="B152">
-        <v>45.93529232178673</v>
+        <v>45.94110370865817</v>
       </c>
       <c r="C152">
-        <v>63.99364643527918</v>
+        <v>63.99348818888877</v>
       </c>
     </row>
     <row r="153">
@@ -2044,10 +2044,10 @@
         <v>31686</v>
       </c>
       <c r="B153">
-        <v>46.22673372136138</v>
+        <v>46.23258197920146</v>
       </c>
       <c r="C153">
-        <v>64.59113577042423</v>
+        <v>64.59094817438566</v>
       </c>
     </row>
     <row r="154">
@@ -2055,10 +2055,10 @@
         <v>31778</v>
       </c>
       <c r="B154">
-        <v>47.05884762358888</v>
+        <v>47.06480115420644</v>
       </c>
       <c r="C154">
-        <v>65.1241813999405</v>
+        <v>65.12419118555056</v>
       </c>
     </row>
     <row r="155">
@@ -2066,10 +2066,10 @@
         <v>31868</v>
       </c>
       <c r="B155">
-        <v>47.27697942929629</v>
+        <v>47.28296055630538</v>
       </c>
       <c r="C155">
-        <v>65.59342984918932</v>
+        <v>65.59362718575595</v>
       </c>
     </row>
     <row r="156">
@@ -2077,10 +2077,10 @@
         <v>31959</v>
       </c>
       <c r="B156">
-        <v>47.77036877648669</v>
+        <v>47.77641232339626</v>
       </c>
       <c r="C156">
-        <v>65.99288344665095</v>
+        <v>65.99326424481924</v>
       </c>
     </row>
     <row r="157">
@@ -2088,10 +2088,10 @@
         <v>32051</v>
       </c>
       <c r="B157">
-        <v>48.32495468791453</v>
+        <v>48.33106839685251</v>
       </c>
       <c r="C157">
-        <v>66.35272552811035</v>
+        <v>66.3531017015858</v>
       </c>
     </row>
     <row r="158">
@@ -2099,10 +2099,10 @@
         <v>32143</v>
       </c>
       <c r="B158">
-        <v>48.93649575665894</v>
+        <v>48.94268683316243</v>
       </c>
       <c r="C158">
-        <v>66.7180973315988</v>
+        <v>66.7181073567119</v>
       </c>
     </row>
     <row r="159">
@@ -2110,10 +2110,10 @@
         <v>32234</v>
       </c>
       <c r="B159">
-        <v>49.30380697093624</v>
+        <v>49.31004451688535</v>
       </c>
       <c r="C159">
-        <v>67.16906499639295</v>
+        <v>67.16924931807495</v>
       </c>
     </row>
     <row r="160">
@@ -2121,10 +2121,10 @@
         <v>32325</v>
       </c>
       <c r="B160">
-        <v>49.90111946728204</v>
+        <v>49.90743258070495</v>
       </c>
       <c r="C160">
-        <v>67.78772466434857</v>
+        <v>67.78756627751655</v>
       </c>
     </row>
     <row r="161">
@@ -2132,10 +2132,10 @@
         <v>32417</v>
       </c>
       <c r="B161">
-        <v>50.4375532204691</v>
+        <v>50.4439341994462</v>
       </c>
       <c r="C161">
-        <v>68.40882608804661</v>
+        <v>68.40883636720993</v>
       </c>
     </row>
     <row r="162">
@@ -2143,10 +2143,10 @@
         <v>32509</v>
       </c>
       <c r="B162">
-        <v>51.03332670535853</v>
+        <v>51.03978305710532</v>
       </c>
       <c r="C162">
-        <v>69.1264640575091</v>
+        <v>69.12626495510864</v>
       </c>
     </row>
     <row r="163">
@@ -2154,10 +2154,10 @@
         <v>32599</v>
       </c>
       <c r="B163">
-        <v>51.71276148740077</v>
+        <v>51.71930379611383</v>
       </c>
       <c r="C163">
-        <v>69.88202491937243</v>
+        <v>69.88218928853271</v>
       </c>
     </row>
     <row r="164">
@@ -2165,10 +2165,10 @@
         <v>32690</v>
       </c>
       <c r="B164">
-        <v>52.16554278664069</v>
+        <v>52.17214237783014</v>
       </c>
       <c r="C164">
-        <v>70.4036216063427</v>
+        <v>70.40348267334028</v>
       </c>
     </row>
     <row r="165">
@@ -2176,10 +2176,10 @@
         <v>32782</v>
       </c>
       <c r="B165">
-        <v>53.04398621451466</v>
+        <v>53.05069693974388</v>
       </c>
       <c r="C165">
-        <v>70.9944520844931</v>
+        <v>70.99460838881097</v>
       </c>
     </row>
     <row r="166">
@@ -2187,10 +2187,10 @@
         <v>32874</v>
       </c>
       <c r="B166">
-        <v>53.68758487795711</v>
+        <v>53.69437702643705</v>
       </c>
       <c r="C166">
-        <v>71.35098598518076</v>
+        <v>71.35113903195655</v>
       </c>
     </row>
     <row r="167">
@@ -2198,10 +2198,10 @@
         <v>32964</v>
       </c>
       <c r="B167">
-        <v>54.56146602068872</v>
+        <v>54.56836872602251</v>
       </c>
       <c r="C167">
-        <v>71.78302644949139</v>
+        <v>71.78303723566468</v>
       </c>
     </row>
     <row r="168">
@@ -2209,10 +2209,10 @@
         <v>33055</v>
       </c>
       <c r="B168">
-        <v>55.28009024456514</v>
+        <v>55.28708386481792</v>
       </c>
       <c r="C168">
-        <v>72.33496400594568</v>
+        <v>72.33460265519042</v>
       </c>
     </row>
     <row r="169">
@@ -2220,10 +2220,10 @@
         <v>33147</v>
       </c>
       <c r="B169">
-        <v>55.88674984047402</v>
+        <v>55.89382021072517</v>
       </c>
       <c r="C169">
-        <v>72.95268640986112</v>
+        <v>72.95307069559004</v>
       </c>
     </row>
     <row r="170">
@@ -2231,10 +2231,10 @@
         <v>33239</v>
       </c>
       <c r="B170">
-        <v>56.06630878783351</v>
+        <v>56.07340187452896</v>
       </c>
       <c r="C170">
-        <v>73.28485917469514</v>
+        <v>73.28500131232677</v>
       </c>
     </row>
     <row r="171">
@@ -2242,10 +2242,10 @@
         <v>33329</v>
       </c>
       <c r="B171">
-        <v>57.00234395248992</v>
+        <v>57.0095554592975</v>
       </c>
       <c r="C171">
-        <v>73.67706899826847</v>
+        <v>73.67708006904206</v>
       </c>
     </row>
     <row r="172">
@@ -2253,10 +2253,10 @@
         <v>33420</v>
       </c>
       <c r="B172">
-        <v>57.41961202091955</v>
+        <v>57.4263129497372</v>
       </c>
       <c r="C172">
-        <v>74.31024500197087</v>
+        <v>74.30974964288927</v>
       </c>
     </row>
     <row r="173">
@@ -2264,10 +2264,10 @@
         <v>33512</v>
       </c>
       <c r="B173">
-        <v>58.32903747663091</v>
+        <v>58.33641682670101</v>
       </c>
       <c r="C173">
-        <v>74.9899788591196</v>
+        <v>74.98960753689353</v>
       </c>
     </row>
     <row r="174">
@@ -2275,10 +2275,10 @@
         <v>33604</v>
       </c>
       <c r="B174">
-        <v>59.13672876037266</v>
+        <v>59.14421029345468</v>
       </c>
       <c r="C174">
-        <v>75.36774137560519</v>
+        <v>75.36775270042052</v>
       </c>
     </row>
     <row r="175">
@@ -2286,10 +2286,10 @@
         <v>33695</v>
       </c>
       <c r="B175">
-        <v>59.32118751135599</v>
+        <v>59.32869238076852</v>
       </c>
       <c r="C175">
-        <v>75.82308166504598</v>
+        <v>75.82258974530609</v>
       </c>
     </row>
     <row r="176">
@@ -2297,10 +2297,10 @@
         <v>33786</v>
       </c>
       <c r="B176">
-        <v>59.93092102904295</v>
+        <v>59.93793250417519</v>
       </c>
       <c r="C176">
-        <v>76.17133105809204</v>
+        <v>76.1714574660875</v>
       </c>
     </row>
     <row r="177">
@@ -2308,10 +2308,10 @@
         <v>33878</v>
       </c>
       <c r="B177">
-        <v>60.49190873834236</v>
+        <v>60.49956171857828</v>
       </c>
       <c r="C177">
-        <v>76.40015438150255</v>
+        <v>76.39966844186701</v>
       </c>
     </row>
     <row r="178">
@@ -2319,10 +2319,10 @@
         <v>33970</v>
       </c>
       <c r="B178">
-        <v>60.89579834386998</v>
+        <v>60.90389670536853</v>
       </c>
       <c r="C178">
-        <v>76.77485381080935</v>
+        <v>76.77525697163561</v>
       </c>
     </row>
     <row r="179">
@@ -2330,10 +2330,10 @@
         <v>34060</v>
       </c>
       <c r="B179">
-        <v>61.05968178644704</v>
+        <v>61.06740659704848</v>
       </c>
       <c r="C179">
-        <v>76.96300583999268</v>
+        <v>76.96301740451368</v>
       </c>
     </row>
     <row r="180">
@@ -2341,10 +2341,10 @@
         <v>34151</v>
       </c>
       <c r="B180">
-        <v>61.05610270589477</v>
+        <v>61.06342806846084</v>
       </c>
       <c r="C180">
-        <v>77.14589252510665</v>
+        <v>77.14562324073987</v>
       </c>
     </row>
     <row r="181">
@@ -2352,10 +2352,10 @@
         <v>34243</v>
       </c>
       <c r="B181">
-        <v>61.26960305698768</v>
+        <v>61.27735442524565</v>
       </c>
       <c r="C181">
-        <v>77.38852223903199</v>
+        <v>77.38803486671208</v>
       </c>
     </row>
     <row r="182">
@@ -2363,10 +2363,10 @@
         <v>34335</v>
       </c>
       <c r="B182">
-        <v>61.40233871800348</v>
+        <v>61.41010687897656</v>
       </c>
       <c r="C182">
-        <v>77.5355966202135</v>
+        <v>77.53550040815263</v>
       </c>
     </row>
     <row r="183">
@@ -2374,10 +2374,10 @@
         <v>34425</v>
       </c>
       <c r="B183">
-        <v>61.49055181338701</v>
+        <v>61.49873219043569</v>
       </c>
       <c r="C183">
-        <v>77.70329053783693</v>
+        <v>77.70340823204451</v>
       </c>
     </row>
     <row r="184">
@@ -2385,10 +2385,10 @@
         <v>34516</v>
       </c>
       <c r="B184">
-        <v>61.78371294552129</v>
+        <v>61.79210935029332</v>
       </c>
       <c r="C184">
-        <v>77.86942140524589</v>
+        <v>77.86953773744757</v>
       </c>
     </row>
     <row r="185">
@@ -2396,10 +2396,10 @@
         <v>34608</v>
       </c>
       <c r="B185">
-        <v>62.40678892002107</v>
+        <v>62.41468415646101</v>
       </c>
       <c r="C185">
-        <v>77.96790305755066</v>
+        <v>77.96819758544726</v>
       </c>
     </row>
     <row r="186">
@@ -2407,10 +2407,10 @@
         <v>34700</v>
       </c>
       <c r="B186">
-        <v>62.55837108659102</v>
+        <v>62.56628550006389</v>
       </c>
       <c r="C186">
-        <v>78.1516692091989</v>
+        <v>78.15131743656013</v>
       </c>
     </row>
     <row r="187">
@@ -2418,10 +2418,10 @@
         <v>34790</v>
       </c>
       <c r="B187">
-        <v>62.97036343437152</v>
+        <v>62.97832997001014</v>
       </c>
       <c r="C187">
-        <v>78.20404045527118</v>
+        <v>78.20433295871403</v>
       </c>
     </row>
     <row r="188">
@@ -2429,10 +2429,10 @@
         <v>34881</v>
       </c>
       <c r="B188">
-        <v>63.1289243224767</v>
+        <v>63.13691091804348</v>
       </c>
       <c r="C188">
-        <v>78.60614134699615</v>
+        <v>78.60614062275708</v>
       </c>
     </row>
     <row r="189">
@@ -2440,10 +2440,10 @@
         <v>34973</v>
       </c>
       <c r="B189">
-        <v>63.22894204119977</v>
+        <v>63.23694129025426</v>
       </c>
       <c r="C189">
-        <v>78.94207565200946</v>
+        <v>78.94228343020416</v>
       </c>
     </row>
     <row r="190">
@@ -2451,10 +2451,10 @@
         <v>35065</v>
       </c>
       <c r="B190">
-        <v>63.63999178304176</v>
+        <v>63.64861590921777</v>
       </c>
       <c r="C190">
-        <v>79.42570216449951</v>
+        <v>79.42589470624618</v>
       </c>
     </row>
     <row r="191">
@@ -2462,10 +2462,10 @@
         <v>35156</v>
       </c>
       <c r="B191">
-        <v>64.0236252740858</v>
+        <v>64.03229798977736</v>
       </c>
       <c r="C191">
-        <v>79.75031241919885</v>
+        <v>79.75013867759408</v>
       </c>
     </row>
     <row r="192">
@@ -2473,10 +2473,10 @@
         <v>35247</v>
       </c>
       <c r="B192">
-        <v>64.32499367291209</v>
+        <v>64.33370456689627</v>
       </c>
       <c r="C192">
-        <v>79.64935542591515</v>
+        <v>79.64957694175189</v>
       </c>
     </row>
     <row r="193">
@@ -2484,10 +2484,10 @@
         <v>35339</v>
       </c>
       <c r="B193">
-        <v>64.3425963514089</v>
+        <v>64.34959193930622</v>
       </c>
       <c r="C193">
-        <v>79.95499644204051</v>
+        <v>79.95480479913968</v>
       </c>
     </row>
     <row r="194">
@@ -2495,10 +2495,10 @@
         <v>35431</v>
       </c>
       <c r="B194">
-        <v>64.69779055271138</v>
+        <v>64.70896470829575</v>
       </c>
       <c r="C194">
-        <v>80.20788763601971</v>
+        <v>80.20766596967697</v>
       </c>
     </row>
     <row r="195">
@@ -2506,10 +2506,10 @@
         <v>35521</v>
       </c>
       <c r="B195">
-        <v>64.97225191016398</v>
+        <v>64.97979951754969</v>
       </c>
       <c r="C195">
-        <v>80.1086831817247</v>
+        <v>80.10833213776348</v>
       </c>
     </row>
     <row r="196">
@@ -2517,10 +2517,10 @@
         <v>35612</v>
       </c>
       <c r="B196">
-        <v>65.2185812793862</v>
+        <v>65.22630995415901</v>
       </c>
       <c r="C196">
-        <v>80.37955516006238</v>
+        <v>80.37959749104294</v>
       </c>
     </row>
     <row r="197">
@@ -2528,10 +2528,10 @@
         <v>35704</v>
       </c>
       <c r="B197">
-        <v>65.32970739704646</v>
+        <v>65.3365820189895</v>
       </c>
       <c r="C197">
-        <v>80.58931465331905</v>
+        <v>80.58903233901718</v>
       </c>
     </row>
     <row r="198">
@@ -2539,10 +2539,10 @@
         <v>35796</v>
       </c>
       <c r="B198">
-        <v>65.76498327318492</v>
+        <v>65.77430885241866</v>
       </c>
       <c r="C198">
-        <v>80.6383872170051</v>
+        <v>80.63807129384408</v>
       </c>
     </row>
     <row r="199">
@@ -2550,10 +2550,10 @@
         <v>35886</v>
       </c>
       <c r="B199">
-        <v>65.93108075426289</v>
+        <v>65.93983273857501</v>
       </c>
       <c r="C199">
-        <v>80.67257542192164</v>
+        <v>80.67279279573415</v>
       </c>
     </row>
     <row r="200">
@@ -2561,10 +2561,10 @@
         <v>35977</v>
       </c>
       <c r="B200">
-        <v>66.43263900094897</v>
+        <v>66.4392447415634</v>
       </c>
       <c r="C200">
-        <v>80.46509356673589</v>
+        <v>80.4650521729814</v>
       </c>
     </row>
     <row r="201">
@@ -2572,10 +2572,10 @@
         <v>36069</v>
       </c>
       <c r="B201">
-        <v>66.66581264966872</v>
+        <v>66.674796265507</v>
       </c>
       <c r="C201">
-        <v>80.1093396636729</v>
+        <v>80.10960820970642</v>
       </c>
     </row>
     <row r="202">
@@ -2583,10 +2583,10 @@
         <v>36161</v>
       </c>
       <c r="B202">
-        <v>66.97268299274374</v>
+        <v>66.98020151767876</v>
       </c>
       <c r="C202">
-        <v>79.93742862852848</v>
+        <v>79.93723073862165</v>
       </c>
     </row>
     <row r="203">
@@ -2594,10 +2594,10 @@
         <v>36251</v>
       </c>
       <c r="B203">
-        <v>67.08686983178239</v>
+        <v>67.09684368753284</v>
       </c>
       <c r="C203">
-        <v>79.95095368383386</v>
+        <v>79.9511555673823</v>
       </c>
     </row>
     <row r="204">
@@ -2605,10 +2605,10 @@
         <v>36342</v>
       </c>
       <c r="B204">
-        <v>67.46808952822067</v>
+        <v>67.47448286516334</v>
       </c>
       <c r="C204">
-        <v>79.87870384019332</v>
+        <v>79.87856531620127</v>
       </c>
     </row>
     <row r="205">
@@ -2616,10 +2616,10 @@
         <v>36434</v>
       </c>
       <c r="B205">
-        <v>68.03051305083991</v>
+        <v>68.04071375286172</v>
       </c>
       <c r="C205">
-        <v>80.34404899065332</v>
+        <v>80.34387157256307</v>
       </c>
     </row>
     <row r="206">
@@ -2627,10 +2627,10 @@
         <v>36526</v>
       </c>
       <c r="B206">
-        <v>68.61122021738825</v>
+        <v>68.61779090868399</v>
       </c>
       <c r="C206">
-        <v>81.06205119293476</v>
+        <v>81.06233096356598</v>
       </c>
     </row>
     <row r="207">
@@ -2638,10 +2638,10 @@
         <v>36617</v>
       </c>
       <c r="B207">
-        <v>68.82379317118206</v>
+        <v>68.83458979199986</v>
       </c>
       <c r="C207">
-        <v>81.48983155036993</v>
+        <v>81.49004474824454</v>
       </c>
     </row>
     <row r="208">
@@ -2649,10 +2649,10 @@
         <v>36708</v>
       </c>
       <c r="B208">
-        <v>69.25508160147641</v>
+        <v>69.2643604199589</v>
       </c>
       <c r="C208">
-        <v>82.15564002773183</v>
+        <v>82.1555023189683</v>
       </c>
     </row>
     <row r="209">
@@ -2660,10 +2660,10 @@
         <v>36800</v>
       </c>
       <c r="B209">
-        <v>70.03761672966849</v>
+        <v>70.04596343937807</v>
       </c>
       <c r="C209">
-        <v>82.77399119850469</v>
+        <v>82.7737872870251</v>
       </c>
     </row>
     <row r="210">
@@ -2671,10 +2671,10 @@
         <v>36892</v>
       </c>
       <c r="B210">
-        <v>70.06547599137421</v>
+        <v>70.07474139739232</v>
       </c>
       <c r="C210">
-        <v>82.86676477447828</v>
+        <v>82.86683360574494</v>
       </c>
     </row>
     <row r="211">
@@ -2682,10 +2682,10 @@
         <v>36982</v>
       </c>
       <c r="B211">
-        <v>70.73884158546576</v>
+        <v>70.74728136693128</v>
       </c>
       <c r="C211">
-        <v>83.5626013298026</v>
+        <v>83.56242049711004</v>
       </c>
     </row>
     <row r="212">
@@ -2693,10 +2693,10 @@
         <v>37073</v>
       </c>
       <c r="B212">
-        <v>71.14755195230073</v>
+        <v>71.15960285393923</v>
       </c>
       <c r="C212">
-        <v>83.72096950846128</v>
+        <v>83.72114200348688</v>
       </c>
     </row>
     <row r="213">
@@ -2704,10 +2704,10 @@
         <v>37165</v>
       </c>
       <c r="B213">
-        <v>71.68501998434465</v>
+        <v>71.69114461722847</v>
       </c>
       <c r="C213">
-        <v>83.66062709853807</v>
+        <v>83.66098810591015</v>
       </c>
     </row>
     <row r="214">
@@ -2715,10 +2715,10 @@
         <v>37257</v>
       </c>
       <c r="B214">
-        <v>72.22743194827417</v>
+        <v>72.23616014192335</v>
       </c>
       <c r="C214">
-        <v>84.05795860227605</v>
+        <v>84.05793017799728</v>
       </c>
     </row>
     <row r="215">
@@ -2726,10 +2726,10 @@
         <v>37347</v>
       </c>
       <c r="B215">
-        <v>73.05630501889098</v>
+        <v>73.06403004243765</v>
       </c>
       <c r="C215">
-        <v>84.16822021477002</v>
+        <v>84.16811107317947</v>
       </c>
     </row>
     <row r="216">
@@ -2737,10 +2737,10 @@
         <v>37438</v>
       </c>
       <c r="B216">
-        <v>73.47755207692424</v>
+        <v>73.49282645982498</v>
       </c>
       <c r="C216">
-        <v>84.36927136787673</v>
+        <v>84.36945166974368</v>
       </c>
     </row>
     <row r="217">
@@ -2748,10 +2748,10 @@
         <v>37530</v>
       </c>
       <c r="B217">
-        <v>73.85160974931205</v>
+        <v>73.85640147798802</v>
       </c>
       <c r="C217">
-        <v>84.63712985037972</v>
+        <v>84.6372008894196</v>
       </c>
     </row>
     <row r="218">
@@ -2759,10 +2759,10 @@
         <v>37622</v>
       </c>
       <c r="B218">
-        <v>74.36549242343028</v>
+        <v>74.37743237572421</v>
       </c>
       <c r="C218">
-        <v>85.30420098644636</v>
+        <v>85.30397715937654</v>
       </c>
     </row>
     <row r="219">
@@ -2770,10 +2770,10 @@
         <v>37712</v>
       </c>
       <c r="B219">
-        <v>74.96983383238415</v>
+        <v>74.97627587033594</v>
       </c>
       <c r="C219">
-        <v>85.32657814387315</v>
+        <v>85.32642545195399</v>
       </c>
     </row>
     <row r="220">
@@ -2781,10 +2781,10 @@
         <v>37803</v>
       </c>
       <c r="B220">
-        <v>75.68340152020167</v>
+        <v>75.69399172482018</v>
       </c>
       <c r="C220">
-        <v>85.80767599824617</v>
+        <v>85.80763593345625</v>
       </c>
     </row>
     <row r="221">
@@ -2792,10 +2792,10 @@
         <v>37895</v>
       </c>
       <c r="B221">
-        <v>76.06709157580319</v>
+        <v>76.07620745028576</v>
       </c>
       <c r="C221">
-        <v>86.34579701816288</v>
+        <v>86.34615805026482</v>
       </c>
     </row>
     <row r="222">
@@ -2803,10 +2803,10 @@
         <v>37987</v>
       </c>
       <c r="B222">
-        <v>76.92093328427045</v>
+        <v>76.93167926241881</v>
       </c>
       <c r="C222">
-        <v>86.75683947969279</v>
+        <v>86.75724866223656</v>
       </c>
     </row>
     <row r="223">
@@ -2814,10 +2814,10 @@
         <v>38078</v>
       </c>
       <c r="B223">
-        <v>77.56585209692943</v>
+        <v>77.57414372413332</v>
       </c>
       <c r="C223">
-        <v>87.34146267208666</v>
+        <v>87.34152186827291</v>
       </c>
     </row>
     <row r="224">
@@ -2825,10 +2825,10 @@
         <v>38169</v>
       </c>
       <c r="B224">
-        <v>78.10942662614848</v>
+        <v>78.1203218991336</v>
       </c>
       <c r="C224">
-        <v>87.70510534117672</v>
+        <v>87.70481319429156</v>
       </c>
     </row>
     <row r="225">
@@ -2836,10 +2836,10 @@
         <v>38261</v>
       </c>
       <c r="B225">
-        <v>78.72172092103297</v>
+        <v>78.73117418273866</v>
       </c>
       <c r="C225">
-        <v>88.08283837178837</v>
+        <v>88.08246295378564</v>
       </c>
     </row>
     <row r="226">
@@ -2847,10 +2847,10 @@
         <v>38353</v>
       </c>
       <c r="B226">
-        <v>78.97575563915042</v>
+        <v>78.98978649900749</v>
       </c>
       <c r="C226">
-        <v>88.38188557575073</v>
+        <v>88.38181662820361</v>
       </c>
     </row>
     <row r="227">
@@ -2858,10 +2858,10 @@
         <v>38443</v>
       </c>
       <c r="B227">
-        <v>79.54937044499452</v>
+        <v>79.55590649819308</v>
       </c>
       <c r="C227">
-        <v>88.76137951445557</v>
+        <v>88.76139285180936</v>
       </c>
     </row>
     <row r="228">
@@ -2869,10 +2869,10 @@
         <v>38534</v>
       </c>
       <c r="B228">
-        <v>80.31735559441583</v>
+        <v>80.32701387343907</v>
       </c>
       <c r="C228">
-        <v>89.44171222076017</v>
+        <v>89.44194553237189</v>
       </c>
     </row>
     <row r="229">
@@ -2880,10 +2880,10 @@
         <v>38626</v>
       </c>
       <c r="B229">
-        <v>81.17472210118936</v>
+        <v>81.18499171504111</v>
       </c>
       <c r="C229">
-        <v>89.64942745877164</v>
+        <v>89.64964356269995</v>
       </c>
     </row>
     <row r="230">
@@ -2891,10 +2891,10 @@
         <v>38718</v>
       </c>
       <c r="B230">
-        <v>81.66910806307148</v>
+        <v>81.669483166999</v>
       </c>
       <c r="C230">
-        <v>90.23019695508678</v>
+        <v>90.23014432798183</v>
       </c>
     </row>
     <row r="231">
@@ -2902,10 +2902,10 @@
         <v>38808</v>
       </c>
       <c r="B231">
-        <v>82.20647809297714</v>
+        <v>82.23281704942906</v>
       </c>
       <c r="C231">
-        <v>90.79801198550354</v>
+        <v>90.79811773606757</v>
       </c>
     </row>
     <row r="232">
@@ -2913,10 +2913,10 @@
         <v>38899</v>
       </c>
       <c r="B232">
-        <v>82.73053532932748</v>
+        <v>82.75735825549236</v>
       </c>
       <c r="C232">
-        <v>91.35020521265034</v>
+        <v>91.35027610094224</v>
       </c>
     </row>
     <row r="233">
@@ -2924,10 +2924,10 @@
         <v>38991</v>
       </c>
       <c r="B233">
-        <v>83.85296709341063</v>
+        <v>83.84131672621461</v>
       </c>
       <c r="C233">
-        <v>91.38634877062276</v>
+        <v>91.38630569130422</v>
       </c>
     </row>
     <row r="234">
@@ -2935,10 +2935,10 @@
         <v>39083</v>
       </c>
       <c r="B234">
-        <v>84.03893226560763</v>
+        <v>84.04268177941357</v>
       </c>
       <c r="C234">
-        <v>91.77968956181489</v>
+        <v>91.77935658875239</v>
       </c>
     </row>
     <row r="235">
@@ -2946,10 +2946,10 @@
         <v>39173</v>
       </c>
       <c r="B235">
-        <v>84.30958134052155</v>
+        <v>84.34030807565699</v>
       </c>
       <c r="C235">
-        <v>92.45350135630642</v>
+        <v>92.45353910901821</v>
       </c>
     </row>
     <row r="236">
@@ -2957,10 +2957,10 @@
         <v>39264</v>
       </c>
       <c r="B236">
-        <v>84.73154210629303</v>
+        <v>84.75543104181861</v>
       </c>
       <c r="C236">
-        <v>93.1264998764342</v>
+        <v>93.12666236408576</v>
       </c>
     </row>
     <row r="237">
@@ -2968,10 +2968,10 @@
         <v>39356</v>
       </c>
       <c r="B237">
-        <v>85.52822405905908</v>
+        <v>85.51279831805991</v>
       </c>
       <c r="C237">
-        <v>94.12183188128425</v>
+        <v>94.12191606309715</v>
       </c>
     </row>
     <row r="238">
@@ -2979,10 +2979,10 @@
         <v>39448</v>
       </c>
       <c r="B238">
-        <v>86.31221032733943</v>
+        <v>86.3342691157484</v>
       </c>
       <c r="C238">
-        <v>95.00833521331273</v>
+        <v>95.00852750325353</v>
       </c>
     </row>
     <row r="239">
@@ -2990,10 +2990,10 @@
         <v>39539</v>
       </c>
       <c r="B239">
-        <v>86.50390614972522</v>
+        <v>86.52987167742384</v>
       </c>
       <c r="C239">
-        <v>95.93039803060834</v>
+        <v>95.93045610571197</v>
       </c>
     </row>
     <row r="240">
@@ -3001,10 +3001,10 @@
         <v>39630</v>
       </c>
       <c r="B240">
-        <v>87.09352074761505</v>
+        <v>87.10453916324882</v>
       </c>
       <c r="C240">
-        <v>95.91783280710214</v>
+        <v>95.91783626554661</v>
       </c>
     </row>
     <row r="241">
@@ -3012,10 +3012,10 @@
         <v>39722</v>
       </c>
       <c r="B241">
-        <v>86.99540570797872</v>
+        <v>86.98007849390203</v>
       </c>
       <c r="C241">
-        <v>95.00604879211561</v>
+        <v>95.00616356429107</v>
       </c>
     </row>
     <row r="242">
@@ -3023,10 +3023,10 @@
         <v>39814</v>
       </c>
       <c r="B242">
-        <v>87.10285873054258</v>
+        <v>87.13059912480131</v>
       </c>
       <c r="C242">
-        <v>94.31780446146014</v>
+        <v>94.317632377352</v>
       </c>
     </row>
     <row r="243">
@@ -3034,10 +3034,10 @@
         <v>39904</v>
       </c>
       <c r="B243">
-        <v>87.35494819576523</v>
+        <v>87.36748546785876</v>
       </c>
       <c r="C243">
-        <v>93.86978420766606</v>
+        <v>93.86992765729735</v>
       </c>
     </row>
     <row r="244">
@@ -3045,10 +3045,10 @@
         <v>39995</v>
       </c>
       <c r="B244">
-        <v>87.95618496783186</v>
+        <v>87.96383343072843</v>
       </c>
       <c r="C244">
-        <v>93.78654671485192</v>
+        <v>93.78644813957872</v>
       </c>
     </row>
     <row r="245">
@@ -3056,10 +3056,10 @@
         <v>40087</v>
       </c>
       <c r="B245">
-        <v>88.67921692689933</v>
+        <v>88.67551369561099</v>
       </c>
       <c r="C245">
-        <v>93.88907669113846</v>
+        <v>93.88894948647658</v>
       </c>
     </row>
     <row r="246">
@@ -3067,10 +3067,10 @@
         <v>40179</v>
       </c>
       <c r="B246">
-        <v>89.53260588681108</v>
+        <v>89.55636442370513</v>
       </c>
       <c r="C246">
-        <v>94.48745251462746</v>
+        <v>94.48764990749049</v>
       </c>
     </row>
     <row r="247">
@@ -3078,10 +3078,10 @@
         <v>40269</v>
       </c>
       <c r="B247">
-        <v>90.20595683684751</v>
+        <v>90.21736901443016</v>
       </c>
       <c r="C247">
-        <v>95.00550973573661</v>
+        <v>95.00534853437263</v>
       </c>
     </row>
     <row r="248">
@@ -3089,10 +3089,10 @@
         <v>40360</v>
       </c>
       <c r="B248">
-        <v>90.5136649197686</v>
+        <v>90.52362918051817</v>
       </c>
       <c r="C248">
-        <v>95.19129235713835</v>
+        <v>95.19113286351768</v>
       </c>
     </row>
     <row r="249">
@@ -3100,10 +3100,10 @@
         <v>40452</v>
       </c>
       <c r="B249">
-        <v>90.7710727001123</v>
+        <v>90.77168888300638</v>
       </c>
       <c r="C249">
-        <v>95.54083511619179</v>
+        <v>95.54031095717971</v>
       </c>
     </row>
     <row r="250">
@@ -3111,10 +3111,10 @@
         <v>40544</v>
       </c>
       <c r="B250">
-        <v>91.40103521633421</v>
+        <v>91.42736364519487</v>
       </c>
       <c r="C250">
-        <v>96.23847275185736</v>
+        <v>96.23876255330923</v>
       </c>
     </row>
     <row r="251">
@@ -3122,10 +3122,10 @@
         <v>40634</v>
       </c>
       <c r="B251">
-        <v>91.51608420082302</v>
+        <v>91.52521317276458</v>
       </c>
       <c r="C251">
-        <v>96.70735519470482</v>
+        <v>96.70709198932647</v>
       </c>
     </row>
     <row r="252">
@@ -3133,10 +3133,10 @@
         <v>40725</v>
       </c>
       <c r="B252">
-        <v>91.59910126631412</v>
+        <v>91.61020101506804</v>
       </c>
       <c r="C252">
-        <v>96.94105938627024</v>
+        <v>96.94100351146301</v>
       </c>
     </row>
     <row r="253">
@@ -3144,10 +3144,10 @@
         <v>40817</v>
       </c>
       <c r="B253">
-        <v>92.20783623589914</v>
+        <v>92.20828151240281</v>
       </c>
       <c r="C253">
-        <v>97.31424833903345</v>
+        <v>97.31430297862356</v>
       </c>
     </row>
     <row r="254">
@@ -3155,10 +3155,10 @@
         <v>40909</v>
       </c>
       <c r="B254">
-        <v>92.62566093639711</v>
+        <v>92.64858209134684</v>
       </c>
       <c r="C254">
-        <v>97.95733816474421</v>
+        <v>97.9576826831958</v>
       </c>
     </row>
     <row r="255">
@@ -3166,10 +3166,10 @@
         <v>41000</v>
       </c>
       <c r="B255">
-        <v>92.88843045087224</v>
+        <v>92.90358994302646</v>
       </c>
       <c r="C255">
-        <v>98.17139991007487</v>
+        <v>98.17107343643858</v>
       </c>
     </row>
     <row r="256">
@@ -3177,10 +3177,10 @@
         <v>41091</v>
       </c>
       <c r="B256">
-        <v>93.28305801835478</v>
+        <v>93.28609437734072</v>
       </c>
       <c r="C256">
-        <v>98.18697658556576</v>
+        <v>98.18697855586166</v>
       </c>
     </row>
     <row r="257">
@@ -3188,10 +3188,10 @@
         <v>41183</v>
       </c>
       <c r="B257">
-        <v>93.78089368612925</v>
+        <v>93.78739551509273</v>
       </c>
       <c r="C257">
-        <v>98.32723203613185</v>
+        <v>98.32761316136165</v>
       </c>
     </row>
     <row r="258">
@@ -3199,10 +3199,10 @@
         <v>41275</v>
       </c>
       <c r="B258">
-        <v>93.78662630223597</v>
+        <v>93.80776208154151</v>
       </c>
       <c r="C258">
-        <v>98.72427640679275</v>
+        <v>98.72428753138148</v>
       </c>
     </row>
     <row r="259">
@@ -3210,10 +3210,10 @@
         <v>41365</v>
       </c>
       <c r="B259">
-        <v>94.36474343547529</v>
+        <v>94.37814681073763</v>
       </c>
       <c r="C259">
-        <v>98.70251468746588</v>
+        <v>98.70253298967302</v>
       </c>
     </row>
     <row r="260">
@@ -3221,10 +3221,10 @@
         <v>41456</v>
       </c>
       <c r="B260">
-        <v>94.83403752599854</v>
+        <v>94.83822288719954</v>
       </c>
       <c r="C260">
-        <v>98.88495350130154</v>
+        <v>98.88496816255611</v>
       </c>
     </row>
     <row r="261">
@@ -3232,10 +3232,10 @@
         <v>41548</v>
       </c>
       <c r="B261">
-        <v>94.8449483275095</v>
+        <v>94.85304941156794</v>
       </c>
       <c r="C261">
-        <v>98.86310718141152</v>
+        <v>98.86312274038488</v>
       </c>
     </row>
     <row r="262">
@@ -3243,10 +3243,10 @@
         <v>41640</v>
       </c>
       <c r="B262">
-        <v>95.14258226642508</v>
+        <v>95.15899977708085</v>
       </c>
       <c r="C262">
-        <v>99.07333007658444</v>
+        <v>99.07370290828763</v>
       </c>
     </row>
     <row r="263">
@@ -3254,10 +3254,10 @@
         <v>41730</v>
       </c>
       <c r="B263">
-        <v>95.44410597669548</v>
+        <v>95.45812701435884</v>
       </c>
       <c r="C263">
-        <v>98.90440936407308</v>
+        <v>98.90407176079684</v>
       </c>
     </row>
     <row r="264">
@@ -3265,10 +3265,10 @@
         <v>41821</v>
       </c>
       <c r="B264">
-        <v>95.78992877209251</v>
+        <v>95.79519665831542</v>
       </c>
       <c r="C264">
-        <v>98.81196666241291</v>
+        <v>98.81162890983059</v>
       </c>
     </row>
     <row r="265">
@@ -3276,10 +3276,10 @@
         <v>41913</v>
       </c>
       <c r="B265">
-        <v>96.05743411209791</v>
+        <v>96.06909929992979</v>
       </c>
       <c r="C265">
-        <v>98.80655854697179</v>
+        <v>98.80657465625565</v>
       </c>
     </row>
     <row r="266">
@@ -3287,10 +3287,10 @@
         <v>42005</v>
       </c>
       <c r="B266">
-        <v>96.29009409145446</v>
+        <v>96.30422597962769</v>
       </c>
       <c r="C266">
-        <v>98.83337418601624</v>
+        <v>98.83338793687379</v>
       </c>
     </row>
     <row r="267">
@@ -3298,10 +3298,10 @@
         <v>42095</v>
       </c>
       <c r="B267">
-        <v>96.71102272678598</v>
+        <v>96.72427272035962</v>
       </c>
       <c r="C267">
-        <v>99.29070697429148</v>
+        <v>99.29071773261498</v>
       </c>
     </row>
     <row r="268">
@@ -3309,10 +3309,10 @@
         <v>42186</v>
       </c>
       <c r="B268">
-        <v>97.1103656564606</v>
+        <v>97.12216469016488</v>
       </c>
       <c r="C268">
-        <v>99.25845767703476</v>
+        <v>99.25848147580204</v>
       </c>
     </row>
     <row r="269">
@@ -3320,10 +3320,10 @@
         <v>42278</v>
       </c>
       <c r="B269">
-        <v>97.5866227363511</v>
+        <v>97.59649440582049</v>
       </c>
       <c r="C269">
-        <v>99.24607730184431</v>
+        <v>99.2460823965703</v>
       </c>
     </row>
     <row r="270">
@@ -3331,10 +3331,10 @@
         <v>42370</v>
       </c>
       <c r="B270">
-        <v>98.17508462987982</v>
+        <v>98.19327748951842</v>
       </c>
       <c r="C270">
-        <v>99.04467452919067</v>
+        <v>99.04503570706471</v>
       </c>
     </row>
     <row r="271">
@@ -3342,10 +3342,10 @@
         <v>42461</v>
       </c>
       <c r="B271">
-        <v>98.05310643804036</v>
+        <v>98.06076569089579</v>
       </c>
       <c r="C271">
-        <v>99.34215946661679</v>
+        <v>99.34216667449382</v>
       </c>
     </row>
     <row r="272">
@@ -3353,10 +3353,10 @@
         <v>42552</v>
       </c>
       <c r="B272">
-        <v>98.35945101185449</v>
+        <v>98.36798477305385</v>
       </c>
       <c r="C272">
-        <v>99.4526514560897</v>
+        <v>99.45268757468618</v>
       </c>
     </row>
     <row r="273">
@@ -3364,10 +3364,10 @@
         <v>42644</v>
       </c>
       <c r="B273">
-        <v>98.89904916706833</v>
+        <v>98.9144494936605</v>
       </c>
       <c r="C273">
-        <v>99.68647294535373</v>
+        <v>99.68646079341048</v>
       </c>
     </row>
     <row r="274">
@@ -3375,10 +3375,10 @@
         <v>42736</v>
       </c>
       <c r="B274">
-        <v>99.78091559981517</v>
+        <v>99.80445887262749</v>
       </c>
       <c r="C274">
-        <v>100.0083855268754</v>
+        <v>100.0084233960206</v>
       </c>
     </row>
     <row r="275">
@@ -3397,10 +3397,10 @@
         <v>42917</v>
       </c>
       <c r="B276">
-        <v>100.3952746154105</v>
+        <v>100.404534022475</v>
       </c>
       <c r="C276">
-        <v>100.1030034346224</v>
+        <v>100.1027574101467</v>
       </c>
     </row>
     <row r="277">
@@ -3408,10 +3408,10 @@
         <v>43009</v>
       </c>
       <c r="B277">
-        <v>101.1725607103467</v>
+        <v>101.1905629968819</v>
       </c>
       <c r="C277">
-        <v>100.6296943324667</v>
+        <v>100.6295921315907</v>
       </c>
     </row>
     <row r="278">
@@ -3419,10 +3419,10 @@
         <v>43101</v>
       </c>
       <c r="B278">
-        <v>101.1788584929852</v>
+        <v>101.2092943664618</v>
       </c>
       <c r="C278">
-        <v>101.2562893230306</v>
+        <v>101.2563761105087</v>
       </c>
     </row>
     <row r="279">
@@ -3430,10 +3430,10 @@
         <v>43191</v>
       </c>
       <c r="B279">
-        <v>101.7141134263894</v>
+        <v>101.7040612466511</v>
       </c>
       <c r="C279">
-        <v>101.866128121419</v>
+        <v>101.8660833992649</v>
       </c>
     </row>
     <row r="280">
@@ -3441,10 +3441,10 @@
         <v>43282</v>
       </c>
       <c r="B280">
-        <v>102.3666106645227</v>
+        <v>102.3690492838695</v>
       </c>
       <c r="C280">
-        <v>102.1537021554068</v>
+        <v>102.153626040197</v>
       </c>
     </row>
     <row r="281">
@@ -3452,10 +3452,10 @@
         <v>43374</v>
       </c>
       <c r="B281">
-        <v>102.8292109128206</v>
+        <v>102.8586142022269</v>
       </c>
       <c r="C281">
-        <v>102.2399593569714</v>
+        <v>102.240712120553</v>
       </c>
     </row>
     <row r="282">
@@ -3463,10 +3463,10 @@
         <v>43466</v>
       </c>
       <c r="B282">
-        <v>101.433195703008</v>
+        <v>101.4582487071279</v>
       </c>
       <c r="C282">
-        <v>102.2070650915036</v>
+        <v>102.2071354286433</v>
       </c>
     </row>
     <row r="283">
@@ -3474,10 +3474,10 @@
         <v>43556</v>
       </c>
       <c r="B283">
-        <v>101.1174350040681</v>
+        <v>101.1081447658146</v>
       </c>
       <c r="C283">
-        <v>102.5937769635533</v>
+        <v>102.5927162254243</v>
       </c>
     </row>
     <row r="284">
@@ -3485,10 +3485,10 @@
         <v>43647</v>
       </c>
       <c r="B284">
-        <v>101.3644236798147</v>
+        <v>101.3580575261873</v>
       </c>
       <c r="C284">
-        <v>102.879464179598</v>
+        <v>102.8790134151972</v>
       </c>
     </row>
     <row r="285">
@@ -3496,10 +3496,10 @@
         <v>43739</v>
       </c>
       <c r="B285">
-        <v>100.9970988456244</v>
+        <v>101.0382662618292</v>
       </c>
       <c r="C285">
-        <v>103.2028549865788</v>
+        <v>103.2043165744489</v>
       </c>
     </row>
     <row r="286">
@@ -3507,10 +3507,10 @@
         <v>43831</v>
       </c>
       <c r="B286">
-        <v>97.25282958364842</v>
+        <v>97.25289844657188</v>
       </c>
       <c r="C286">
-        <v>103.4708640985969</v>
+        <v>103.4702715150726</v>
       </c>
     </row>
     <row r="287">
@@ -3518,10 +3518,10 @@
         <v>43922</v>
       </c>
       <c r="B287">
-        <v>85.85547036583885</v>
+        <v>85.87572925089304</v>
       </c>
       <c r="C287">
-        <v>103.6124208066663</v>
+        <v>103.6131389748794</v>
       </c>
     </row>
     <row r="288">
@@ -3529,10 +3529,10 @@
         <v>44013</v>
       </c>
       <c r="B288">
-        <v>99.32494438460213</v>
+        <v>99.29281802801366</v>
       </c>
       <c r="C288">
-        <v>103.639369326089</v>
+        <v>103.6402021282453</v>
       </c>
     </row>
     <row r="289">
@@ -3540,10 +3540,10 @@
         <v>44105</v>
       </c>
       <c r="B289">
-        <v>97.61511969754508</v>
+        <v>97.67162957008067</v>
       </c>
       <c r="C289">
-        <v>103.7960781761796</v>
+        <v>103.7944743493072</v>
       </c>
     </row>
     <row r="290">
@@ -3551,10 +3551,10 @@
         <v>44197</v>
       </c>
       <c r="B290">
-        <v>97.61825551685386</v>
+        <v>97.54570891963854</v>
       </c>
       <c r="C290">
-        <v>104.3450736557276</v>
+        <v>104.3461984605918</v>
       </c>
     </row>
     <row r="291">
@@ -3562,10 +3562,10 @@
         <v>44287</v>
       </c>
       <c r="B291">
-        <v>98.60802041617384</v>
+        <v>98.58774141812641</v>
       </c>
       <c r="C291">
-        <v>104.7072137016547</v>
+        <v>104.7087109814059</v>
       </c>
     </row>
     <row r="292">
@@ -3573,10 +3573,10 @@
         <v>44378</v>
       </c>
       <c r="B292">
-        <v>101.9005616083351</v>
+        <v>101.8646345598859</v>
       </c>
       <c r="C292">
-        <v>105.4218694186277</v>
+        <v>105.4251164087217</v>
       </c>
     </row>
     <row r="293">
@@ -3584,10 +3584,10 @@
         <v>44470</v>
       </c>
       <c r="B293">
-        <v>102.5971366935937</v>
+        <v>102.7750986633677</v>
       </c>
       <c r="C293">
-        <v>106.1835168252719</v>
+        <v>106.1777533208433</v>
       </c>
     </row>
     <row r="294">
@@ -3595,10 +3595,10 @@
         <v>44562</v>
       </c>
       <c r="B294">
-        <v>103.7739117426643</v>
+        <v>103.5523661112294</v>
       </c>
       <c r="C294">
-        <v>107.375723137273</v>
+        <v>107.3655253663045</v>
       </c>
     </row>
     <row r="295">
@@ -3606,10 +3606,10 @@
         <v>44652</v>
       </c>
       <c r="B295">
-        <v>104.3840566116525</v>
+        <v>104.407511506467</v>
       </c>
       <c r="C295">
-        <v>109.3199272290359</v>
+        <v>109.3142286242796</v>
       </c>
     </row>
     <row r="296">
@@ -3617,10 +3617,10 @@
         <v>44743</v>
       </c>
       <c r="B296">
-        <v>104.7354930918001</v>
+        <v>105.1534702791055</v>
       </c>
       <c r="C296">
-        <v>111.149587073966</v>
+        <v>111.1560653101051</v>
       </c>
     </row>
     <row r="297">
@@ -3628,10 +3628,10 @@
         <v>44835</v>
       </c>
       <c r="B297">
-        <v>106.841576021411</v>
+        <v>106.6715120795439</v>
       </c>
       <c r="C297">
-        <v>113.2430252337711</v>
+        <v>113.2490572518315</v>
       </c>
     </row>
     <row r="298">
@@ -3639,10 +3639,10 @@
         <v>44927</v>
       </c>
       <c r="B298">
-        <v>108.1861058978573</v>
+        <v>107.9015662028295</v>
       </c>
       <c r="C298">
-        <v>115.481518094307</v>
+        <v>115.501279367192</v>
       </c>
     </row>
     <row r="299">
@@ -3650,10 +3650,10 @@
         <v>45017</v>
       </c>
       <c r="B299">
-        <v>108.9604409616723</v>
+        <v>108.7564986716371</v>
       </c>
       <c r="C299">
-        <v>117.0791735824385</v>
+        <v>117.1139097457902</v>
       </c>
     </row>
     <row r="300">
@@ -3661,18 +3661,21 @@
         <v>45108</v>
       </c>
       <c r="B300">
-        <v>109.0503679936086</v>
+        <v>109.221935083555</v>
       </c>
       <c r="C300">
-        <v>118.2277209048462</v>
+        <v>118.2807084351646</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2">
         <v>45200</v>
       </c>
+      <c r="B301">
+        <v>109.8075557143677</v>
+      </c>
       <c r="C301">
-        <v>118.5887614311346</v>
+        <v>118.6351036060223</v>
       </c>
     </row>
   </sheetData>
